--- a/outputs/3_effective_rates_mchenry.xlsx
+++ b/outputs/3_effective_rates_mchenry.xlsx
@@ -3662,10 +3662,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0281653588396913</v>
+        <v>0.0293478126628664</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0355236493146754</v>
+        <v>0.0305825801154047</v>
       </c>
     </row>
     <row r="3">
@@ -3673,10 +3673,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0229643794199899</v>
+        <v>0.0237915017254022</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0290083630541878</v>
+        <v>0.0250687091050353</v>
       </c>
     </row>
     <row r="4">
@@ -3684,10 +3684,10 @@
         <v>5</v>
       </c>
       <c r="B4" t="n">
-        <v>0.0281653588396913</v>
+        <v>0.0293478126628664</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0355236493146754</v>
+        <v>0.0305825801154047</v>
       </c>
     </row>
     <row r="5">
@@ -3695,10 +3695,10 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>0.0281653588396913</v>
+        <v>0.0293478126628664</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0355236493146754</v>
+        <v>0.0305825801154047</v>
       </c>
     </row>
     <row r="6">
@@ -3706,10 +3706,10 @@
         <v>7</v>
       </c>
       <c r="B6" t="n">
-        <v>0.0281653588396913</v>
+        <v>0.0293478126628664</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0355236493146754</v>
+        <v>0.0305825801154047</v>
       </c>
     </row>
     <row r="7">
@@ -3717,10 +3717,10 @@
         <v>8</v>
       </c>
       <c r="B7" t="n">
-        <v>0.0217604848813329</v>
+        <v>0.0219024269551771</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0242145822932722</v>
+        <v>0.02326081341886</v>
       </c>
     </row>
     <row r="8">
@@ -3728,10 +3728,10 @@
         <v>9</v>
       </c>
       <c r="B8" t="n">
-        <v>0.0232002715341996</v>
+        <v>0.0239417957855927</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0283407461831451</v>
+        <v>0.024823148910606</v>
       </c>
     </row>
     <row r="9">
@@ -3739,10 +3739,10 @@
         <v>10</v>
       </c>
       <c r="B9" t="n">
-        <v>0.0213225123361752</v>
+        <v>0.0214928410958598</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0238139438583222</v>
+        <v>0.0227455671389272</v>
       </c>
     </row>
     <row r="10">
@@ -3750,10 +3750,10 @@
         <v>11</v>
       </c>
       <c r="B10" t="n">
-        <v>0.0236382440793572</v>
+        <v>0.02435138164491</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0287413846180951</v>
+        <v>0.0253383951905389</v>
       </c>
     </row>
     <row r="11">
@@ -3761,10 +3761,10 @@
         <v>12</v>
       </c>
       <c r="B11" t="n">
-        <v>0.028401250953901</v>
+        <v>0.0294981067230569</v>
       </c>
       <c r="C11" t="n">
-        <v>0.0348560324436327</v>
+        <v>0.0303370199209755</v>
       </c>
     </row>
     <row r="12">
@@ -3772,10 +3772,10 @@
         <v>13</v>
       </c>
       <c r="B12" t="n">
-        <v>0.0217593959854151</v>
+        <v>0.0219135815856061</v>
       </c>
       <c r="C12" t="n">
-        <v>0.024927832446865</v>
+        <v>0.023902266609618</v>
       </c>
     </row>
     <row r="13">
@@ -3783,10 +3783,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="n">
-        <v>0.0237872164814332</v>
+        <v>0.0239687852829676</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0274225014579534</v>
+        <v>0.0263000682595833</v>
       </c>
     </row>
     <row r="14">
@@ -3794,10 +3794,10 @@
         <v>15</v>
       </c>
       <c r="B14" t="n">
-        <v>0.0217593959854151</v>
+        <v>0.0219135815856061</v>
       </c>
       <c r="C14" t="n">
-        <v>0.024927832446865</v>
+        <v>0.023902266609618</v>
       </c>
     </row>
     <row r="15">
@@ -3805,10 +3805,10 @@
         <v>16</v>
       </c>
       <c r="B15" t="n">
-        <v>0.0217593959854151</v>
+        <v>0.0219135815856061</v>
       </c>
       <c r="C15" t="n">
-        <v>0.024927832446865</v>
+        <v>0.023902266609618</v>
       </c>
     </row>
     <row r="16">
@@ -3816,10 +3816,10 @@
         <v>17</v>
       </c>
       <c r="B16" t="n">
-        <v>0.0237872164814332</v>
+        <v>0.0239687852829676</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0274225014579534</v>
+        <v>0.0263000682595833</v>
       </c>
     </row>
     <row r="17">
@@ -3827,10 +3827,10 @@
         <v>18</v>
       </c>
       <c r="B17" t="n">
-        <v>0.0237872164814332</v>
+        <v>0.0239687852829676</v>
       </c>
       <c r="C17" t="n">
-        <v>0.0274225014579534</v>
+        <v>0.0263000682595833</v>
       </c>
     </row>
     <row r="18">
@@ -3838,10 +3838,10 @@
         <v>19</v>
       </c>
       <c r="B18" t="n">
-        <v>0.0237872164814332</v>
+        <v>0.0239687852829676</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0274225014579534</v>
+        <v>0.0263000682595833</v>
       </c>
     </row>
     <row r="19">
@@ -3849,10 +3849,10 @@
         <v>20</v>
       </c>
       <c r="B19" t="n">
-        <v>0.0237872164814332</v>
+        <v>0.0239687852829676</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0274225014579534</v>
+        <v>0.0263000682595833</v>
       </c>
     </row>
     <row r="20">
@@ -3860,10 +3860,10 @@
         <v>21</v>
       </c>
       <c r="B20" t="n">
-        <v>0.0272571797358399</v>
+        <v>0.0279294074850668</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0340387326837173</v>
+        <v>0.0307301232580826</v>
       </c>
     </row>
     <row r="21">
@@ -3871,10 +3871,10 @@
         <v>22</v>
       </c>
       <c r="B21" t="n">
-        <v>0.0250542365156026</v>
+        <v>0.0254769839798485</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0306647517731826</v>
+        <v>0.0279675056629587</v>
       </c>
     </row>
     <row r="22">
@@ -3882,10 +3882,10 @@
         <v>23</v>
       </c>
       <c r="B22" t="n">
-        <v>0.0272571797358399</v>
+        <v>0.0279294074850668</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0340387326837173</v>
+        <v>0.0307301232580826</v>
       </c>
     </row>
     <row r="23">
@@ -3893,10 +3893,10 @@
         <v>24</v>
       </c>
       <c r="B23" t="n">
-        <v>0.0261536052789598</v>
+        <v>0.0265764332917001</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0317326505981391</v>
+        <v>0.0290347957377507</v>
       </c>
     </row>
     <row r="24">
@@ -3904,10 +3904,10 @@
         <v>25</v>
       </c>
       <c r="B24" t="n">
-        <v>0.0249881572470932</v>
+        <v>0.0253046591895994</v>
       </c>
       <c r="C24" t="n">
-        <v>0.030036786690941</v>
+        <v>0.0277460187741451</v>
       </c>
     </row>
     <row r="25">
@@ -3915,10 +3915,10 @@
         <v>26</v>
       </c>
       <c r="B25" t="n">
-        <v>0.0260875260104505</v>
+        <v>0.026404108501451</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0311046855158975</v>
+        <v>0.0288133088489371</v>
       </c>
     </row>
     <row r="26">
@@ -3926,10 +3926,10 @@
         <v>27</v>
       </c>
       <c r="B26" t="n">
-        <v>0.0260875260104505</v>
+        <v>0.026404108501451</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0311046855158975</v>
+        <v>0.0288133088489371</v>
       </c>
     </row>
     <row r="27">
@@ -3937,10 +3937,10 @@
         <v>28</v>
       </c>
       <c r="B27" t="n">
-        <v>0.0260875260104505</v>
+        <v>0.026404108501451</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0311046855158975</v>
+        <v>0.0288133088489371</v>
       </c>
     </row>
     <row r="28">
@@ -3948,10 +3948,10 @@
         <v>29</v>
       </c>
       <c r="B28" t="n">
-        <v>0.0272571797358399</v>
+        <v>0.0279294074850668</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0340387326837173</v>
+        <v>0.0307301232580826</v>
       </c>
     </row>
     <row r="29">
@@ -3959,10 +3959,10 @@
         <v>30</v>
       </c>
       <c r="B29" t="n">
-        <v>0.0260875260104505</v>
+        <v>0.026404108501451</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0311046855158975</v>
+        <v>0.0288133088489371</v>
       </c>
     </row>
     <row r="30">
@@ -3970,10 +3970,10 @@
         <v>31</v>
       </c>
       <c r="B30" t="n">
-        <v>0.0260875260104505</v>
+        <v>0.026404108501451</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0311046855158975</v>
+        <v>0.0288133088489371</v>
       </c>
     </row>
     <row r="31">
@@ -3981,10 +3981,10 @@
         <v>32</v>
       </c>
       <c r="B31" t="n">
-        <v>0.0260875260104505</v>
+        <v>0.026404108501451</v>
       </c>
       <c r="C31" t="n">
-        <v>0.0311046855158975</v>
+        <v>0.0288133088489371</v>
       </c>
     </row>
     <row r="32">
@@ -3992,10 +3992,10 @@
         <v>33</v>
       </c>
       <c r="B32" t="n">
-        <v>0.0260875260104505</v>
+        <v>0.026404108501451</v>
       </c>
       <c r="C32" t="n">
-        <v>0.0311046855158975</v>
+        <v>0.0288133088489371</v>
       </c>
     </row>
     <row r="33">
@@ -4003,10 +4003,10 @@
         <v>34</v>
       </c>
       <c r="B33" t="n">
-        <v>0.0260875260104505</v>
+        <v>0.026404108501451</v>
       </c>
       <c r="C33" t="n">
-        <v>0.0311046855158975</v>
+        <v>0.0288133088489371</v>
       </c>
     </row>
     <row r="34">
@@ -4014,10 +4014,10 @@
         <v>35</v>
       </c>
       <c r="B34" t="n">
-        <v>0.0260875260104505</v>
+        <v>0.026404108501451</v>
       </c>
       <c r="C34" t="n">
-        <v>0.0311046855158975</v>
+        <v>0.0288133088489371</v>
       </c>
     </row>
     <row r="35">
@@ -4025,10 +4025,10 @@
         <v>36</v>
       </c>
       <c r="B35" t="n">
-        <v>0.0260875260104505</v>
+        <v>0.026404108501451</v>
       </c>
       <c r="C35" t="n">
-        <v>0.0311046855158975</v>
+        <v>0.0288133088489371</v>
       </c>
     </row>
     <row r="36">
@@ -4036,10 +4036,10 @@
         <v>37</v>
       </c>
       <c r="B36" t="n">
-        <v>0.0260875260104505</v>
+        <v>0.026404108501451</v>
       </c>
       <c r="C36" t="n">
-        <v>0.0311046855158975</v>
+        <v>0.0288133088489371</v>
       </c>
     </row>
     <row r="37">
@@ -4047,10 +4047,10 @@
         <v>38</v>
       </c>
       <c r="B37" t="n">
-        <v>0.0245778065644076</v>
+        <v>0.0248693190846688</v>
       </c>
       <c r="C37" t="n">
-        <v>0.0294374756479241</v>
+        <v>0.0272658782035706</v>
       </c>
     </row>
     <row r="38">
@@ -4058,10 +4058,10 @@
         <v>39</v>
       </c>
       <c r="B38" t="n">
-        <v>0.0277423578083797</v>
+        <v>0.0280260706806598</v>
       </c>
       <c r="C38" t="n">
-        <v>0.0328715725167354</v>
+        <v>0.0307552146368546</v>
       </c>
     </row>
     <row r="39">
@@ -4069,10 +4069,10 @@
         <v>40</v>
       </c>
       <c r="B39" t="n">
-        <v>0.0256771753277648</v>
+        <v>0.0259687683965204</v>
       </c>
       <c r="C39" t="n">
-        <v>0.0305053744728806</v>
+        <v>0.0283331682783626</v>
       </c>
     </row>
     <row r="40">
@@ -4080,10 +4080,10 @@
         <v>41</v>
       </c>
       <c r="B40" t="n">
-        <v>0.0271815128871403</v>
+        <v>0.0274729212220511</v>
       </c>
       <c r="C40" t="n">
-        <v>0.0323130249826721</v>
+        <v>0.0301424872350345</v>
       </c>
     </row>
     <row r="41">
@@ -4091,10 +4091,10 @@
         <v>42</v>
       </c>
       <c r="B41" t="n">
-        <v>0.0271373718632615</v>
+        <v>0.0274288843835227</v>
       </c>
       <c r="C41" t="n">
-        <v>0.0322591145979563</v>
+        <v>0.0300875171536028</v>
       </c>
     </row>
     <row r="42">
@@ -4102,10 +4102,10 @@
         <v>43</v>
       </c>
       <c r="B42" t="n">
-        <v>0.0253088642678132</v>
+        <v>0.025600272602724</v>
       </c>
       <c r="C42" t="n">
-        <v>0.0302496783688031</v>
+        <v>0.0280791406211655</v>
       </c>
     </row>
     <row r="43">
@@ -4113,10 +4113,10 @@
         <v>44</v>
       </c>
       <c r="B43" t="n">
-        <v>0.0256771753277648</v>
+        <v>0.0259687683965204</v>
       </c>
       <c r="C43" t="n">
-        <v>0.0305053744728806</v>
+        <v>0.0283331682783626</v>
       </c>
     </row>
     <row r="44">
@@ -4124,10 +4124,10 @@
         <v>45</v>
       </c>
       <c r="B44" t="n">
-        <v>0.0256771753277648</v>
+        <v>0.0259687683965204</v>
       </c>
       <c r="C44" t="n">
-        <v>0.0305053744728806</v>
+        <v>0.0283331682783626</v>
       </c>
     </row>
     <row r="45">
@@ -4135,10 +4135,10 @@
         <v>46</v>
       </c>
       <c r="B45" t="n">
-        <v>0.0256771753277648</v>
+        <v>0.0259687683965204</v>
       </c>
       <c r="C45" t="n">
-        <v>0.0305053744728806</v>
+        <v>0.0283331682783626</v>
       </c>
     </row>
     <row r="46">
@@ -4146,10 +4146,10 @@
         <v>47</v>
       </c>
       <c r="B46" t="n">
-        <v>0.0256771753277648</v>
+        <v>0.0259687683965204</v>
       </c>
       <c r="C46" t="n">
-        <v>0.0305053744728806</v>
+        <v>0.0283331682783626</v>
       </c>
     </row>
     <row r="47">
@@ -4157,10 +4157,10 @@
         <v>48</v>
       </c>
       <c r="B47" t="n">
-        <v>0.0256771753277648</v>
+        <v>0.0259687683965204</v>
       </c>
       <c r="C47" t="n">
-        <v>0.0305053744728806</v>
+        <v>0.0283331682783626</v>
       </c>
     </row>
     <row r="48">
@@ -4168,10 +4168,10 @@
         <v>49</v>
       </c>
       <c r="B48" t="n">
-        <v>0.0256771753277648</v>
+        <v>0.0259687683965204</v>
       </c>
       <c r="C48" t="n">
-        <v>0.0305053744728806</v>
+        <v>0.0283331682783626</v>
       </c>
     </row>
     <row r="49">
@@ -4179,10 +4179,10 @@
         <v>50</v>
       </c>
       <c r="B49" t="n">
-        <v>0.0256771753277648</v>
+        <v>0.0259687683965204</v>
       </c>
       <c r="C49" t="n">
-        <v>0.0305053744728806</v>
+        <v>0.0283331682783626</v>
       </c>
     </row>
     <row r="50">
@@ -4190,10 +4190,10 @@
         <v>51</v>
       </c>
       <c r="B50" t="n">
-        <v>0.0256771753277648</v>
+        <v>0.0259687683965204</v>
       </c>
       <c r="C50" t="n">
-        <v>0.0305053744728806</v>
+        <v>0.0283331682783626</v>
       </c>
     </row>
     <row r="51">
@@ -4201,10 +4201,10 @@
         <v>52</v>
       </c>
       <c r="B51" t="n">
-        <v>0.0256771753277648</v>
+        <v>0.0259687683965204</v>
       </c>
       <c r="C51" t="n">
-        <v>0.0305053744728806</v>
+        <v>0.0283331682783626</v>
       </c>
     </row>
     <row r="52">
@@ -4212,10 +4212,10 @@
         <v>53</v>
       </c>
       <c r="B52" t="n">
-        <v>0.0256771753277648</v>
+        <v>0.0259687683965204</v>
       </c>
       <c r="C52" t="n">
-        <v>0.0305053744728806</v>
+        <v>0.0283331682783626</v>
       </c>
     </row>
     <row r="53">
@@ -4223,10 +4223,10 @@
         <v>54</v>
       </c>
       <c r="B53" t="n">
-        <v>0.0232160733070779</v>
+        <v>0.0239961959604084</v>
       </c>
       <c r="C53" t="n">
-        <v>0.0291283632103605</v>
+        <v>0.0255128634068223</v>
       </c>
     </row>
     <row r="54">
@@ -4234,10 +4234,10 @@
         <v>55</v>
       </c>
       <c r="B54" t="n">
-        <v>0.0284170527267793</v>
+        <v>0.0295525068978726</v>
       </c>
       <c r="C54" t="n">
-        <v>0.0356436494708481</v>
+        <v>0.0310267344171918</v>
       </c>
     </row>
     <row r="55">
@@ -4245,10 +4245,10 @@
         <v>56</v>
       </c>
       <c r="B55" t="n">
-        <v>0.0284170527267793</v>
+        <v>0.0295525068978726</v>
       </c>
       <c r="C55" t="n">
-        <v>0.0356436494708481</v>
+        <v>0.0310267344171918</v>
       </c>
     </row>
     <row r="56">
@@ -4256,10 +4256,10 @@
         <v>57</v>
       </c>
       <c r="B56" t="n">
-        <v>0.022981917368248</v>
+        <v>0.0237234416196411</v>
       </c>
       <c r="C56" t="n">
-        <v>0.0287013246095595</v>
+        <v>0.0251837273370204</v>
       </c>
     </row>
     <row r="57">
@@ -4267,10 +4267,10 @@
         <v>58</v>
       </c>
       <c r="B57" t="n">
-        <v>0.0265037981580394</v>
+        <v>0.0272274434224567</v>
       </c>
       <c r="C57" t="n">
-        <v>0.0348307421561868</v>
+        <v>0.0298154629283147</v>
       </c>
     </row>
     <row r="58">
@@ -4278,10 +4278,10 @@
         <v>59</v>
       </c>
       <c r="B58" t="n">
-        <v>0.0247228788264791</v>
+        <v>0.0253794799990264</v>
       </c>
       <c r="C58" t="n">
-        <v>0.0323033523466454</v>
+        <v>0.0277340945064925</v>
       </c>
     </row>
     <row r="59">
@@ -4289,10 +4289,10 @@
         <v>60</v>
       </c>
       <c r="B59" t="n">
-        <v>0.0234198899134057</v>
+        <v>0.0241330274789584</v>
       </c>
       <c r="C59" t="n">
-        <v>0.0291019630445095</v>
+        <v>0.0256989736169533</v>
       </c>
     </row>
     <row r="60">
@@ -4300,10 +4300,10 @@
         <v>61</v>
       </c>
       <c r="B60" t="n">
-        <v>0.0251608513716367</v>
+        <v>0.0257890658583437</v>
       </c>
       <c r="C60" t="n">
-        <v>0.0327039907815954</v>
+        <v>0.0282493407864254</v>
       </c>
     </row>
     <row r="61">
@@ -4311,10 +4311,10 @@
         <v>62</v>
       </c>
       <c r="B61" t="n">
-        <v>0.0247628366998084</v>
+        <v>0.0255714050430714</v>
       </c>
       <c r="C61" t="n">
-        <v>0.0312287144191009</v>
+        <v>0.0272650957588426</v>
       </c>
     </row>
     <row r="62">
@@ -4322,10 +4322,10 @@
         <v>63</v>
       </c>
       <c r="B62" t="n">
-        <v>0.0306952939852276</v>
+        <v>0.0316660272841467</v>
       </c>
       <c r="C62" t="n">
-        <v>0.0408962896798976</v>
+        <v>0.0347081506865819</v>
       </c>
     </row>
     <row r="63">
@@ -4333,10 +4333,10 @@
         <v>64</v>
       </c>
       <c r="B63" t="n">
-        <v>0.0211041581702237</v>
+        <v>0.0212744869299082</v>
       </c>
       <c r="C63" t="n">
-        <v>0.0241745222847366</v>
+        <v>0.0231061455653415</v>
       </c>
     </row>
     <row r="64">
@@ -4344,10 +4344,10 @@
         <v>65</v>
       </c>
       <c r="B64" t="n">
-        <v>0.0263392767647738</v>
+        <v>0.0270660367516795</v>
       </c>
       <c r="C64" t="n">
-        <v>0.034748573471042</v>
+        <v>0.0296413586606685</v>
       </c>
     </row>
     <row r="65">
@@ -4355,10 +4355,10 @@
         <v>66</v>
       </c>
       <c r="B65" t="n">
-        <v>0.030530772591962</v>
+        <v>0.0315046206133696</v>
       </c>
       <c r="C65" t="n">
-        <v>0.0408141209947528</v>
+        <v>0.0345340464189358</v>
       </c>
     </row>
     <row r="66">
@@ -4366,10 +4366,10 @@
         <v>67</v>
       </c>
       <c r="B66" t="n">
-        <v>0.0249963299783711</v>
+        <v>0.0256276591875665</v>
       </c>
       <c r="C66" t="n">
-        <v>0.0326218220964506</v>
+        <v>0.0280752365187792</v>
       </c>
     </row>
     <row r="67">
@@ -4377,10 +4377,10 @@
         <v>68</v>
       </c>
       <c r="B67" t="n">
-        <v>0.0252421719766749</v>
+        <v>0.0258665240933887</v>
       </c>
       <c r="C67" t="n">
-        <v>0.0328750532954879</v>
+        <v>0.0283756638217035</v>
       </c>
     </row>
     <row r="68">
@@ -4388,10 +4388,10 @@
         <v>69</v>
       </c>
       <c r="B68" t="n">
-        <v>0.0265753678855792</v>
+        <v>0.0271997200022931</v>
       </c>
       <c r="C68" t="n">
-        <v>0.0343184511436066</v>
+        <v>0.0298190616698223</v>
       </c>
     </row>
     <row r="69">
@@ -4399,10 +4399,10 @@
         <v>70</v>
       </c>
       <c r="B69" t="n">
-        <v>0.0261566833928902</v>
+        <v>0.0263257256467813</v>
       </c>
       <c r="C69" t="n">
-        <v>0.0306500055888217</v>
+        <v>0.029469394669871</v>
       </c>
     </row>
     <row r="70">
@@ -4410,10 +4410,10 @@
         <v>71</v>
       </c>
       <c r="B70" t="n">
-        <v>0.030530772591962</v>
+        <v>0.0315046206133696</v>
       </c>
       <c r="C70" t="n">
-        <v>0.0408141209947528</v>
+        <v>0.0345340464189358</v>
       </c>
     </row>
     <row r="71">
@@ -4421,10 +4421,10 @@
         <v>72</v>
       </c>
       <c r="B71" t="n">
-        <v>0.0282783606013491</v>
+        <v>0.0290051205882549</v>
       </c>
       <c r="C71" t="n">
-        <v>0.0362067994362037</v>
+        <v>0.0310995846258302</v>
       </c>
     </row>
     <row r="72">
@@ -4432,10 +4432,10 @@
         <v>73</v>
       </c>
       <c r="B72" t="n">
-        <v>0.0249963299783711</v>
+        <v>0.0256276591875665</v>
       </c>
       <c r="C72" t="n">
-        <v>0.0326218220964506</v>
+        <v>0.0280752365187792</v>
       </c>
     </row>
     <row r="73">
@@ -4443,10 +4443,10 @@
         <v>74</v>
       </c>
       <c r="B73" t="n">
-        <v>0.0263392767647738</v>
+        <v>0.0270660367516795</v>
       </c>
       <c r="C73" t="n">
-        <v>0.034748573471042</v>
+        <v>0.0296413586606685</v>
       </c>
     </row>
     <row r="74">
@@ -4454,10 +4454,10 @@
         <v>75</v>
       </c>
       <c r="B74" t="n">
-        <v>0.0249963299783711</v>
+        <v>0.0256276591875665</v>
       </c>
       <c r="C74" t="n">
-        <v>0.0326218220964506</v>
+        <v>0.0280752365187792</v>
       </c>
     </row>
     <row r="75">
@@ -4465,10 +4465,10 @@
         <v>76</v>
       </c>
       <c r="B75" t="n">
-        <v>0.0252421719766749</v>
+        <v>0.0258665240933887</v>
       </c>
       <c r="C75" t="n">
-        <v>0.0328750532954879</v>
+        <v>0.0283756638217035</v>
       </c>
     </row>
     <row r="76">
@@ -4476,10 +4476,10 @@
         <v>77</v>
       </c>
       <c r="B76" t="n">
-        <v>0.0271812558132502</v>
+        <v>0.0278056079299641</v>
       </c>
       <c r="C76" t="n">
-        <v>0.0343332792606496</v>
+        <v>0.0298338897868652</v>
       </c>
     </row>
     <row r="77">
@@ -4487,10 +4487,10 @@
         <v>78</v>
       </c>
       <c r="B77" t="n">
-        <v>0.0276724726736781</v>
+        <v>0.0283992326605839</v>
       </c>
       <c r="C77" t="n">
-        <v>0.0361919713191607</v>
+        <v>0.0310847565087873</v>
       </c>
     </row>
     <row r="78">
@@ -4498,10 +4498,10 @@
         <v>79</v>
       </c>
       <c r="B78" t="n">
-        <v>0.0265753678855792</v>
+        <v>0.0271997200022931</v>
       </c>
       <c r="C78" t="n">
-        <v>0.0343184511436066</v>
+        <v>0.0298190616698223</v>
       </c>
     </row>
     <row r="79">
@@ -4509,10 +4509,10 @@
         <v>80</v>
       </c>
       <c r="B79" t="n">
-        <v>0.030530772591962</v>
+        <v>0.0315046206133696</v>
       </c>
       <c r="C79" t="n">
-        <v>0.0408141209947528</v>
+        <v>0.0345340464189358</v>
       </c>
     </row>
     <row r="80">
@@ -4520,10 +4520,10 @@
         <v>81</v>
       </c>
       <c r="B80" t="n">
-        <v>0.030530772591962</v>
+        <v>0.0315046206133696</v>
       </c>
       <c r="C80" t="n">
-        <v>0.0408141209947528</v>
+        <v>0.0345340464189358</v>
       </c>
     </row>
     <row r="81">
@@ -4531,10 +4531,10 @@
         <v>82</v>
       </c>
       <c r="B81" t="n">
-        <v>0.0265753678855792</v>
+        <v>0.0271997200022931</v>
       </c>
       <c r="C81" t="n">
-        <v>0.0343184511436066</v>
+        <v>0.0298190616698223</v>
       </c>
     </row>
     <row r="82">
@@ -4542,10 +4542,10 @@
         <v>83</v>
       </c>
       <c r="B82" t="n">
-        <v>0.0284521909952257</v>
+        <v>0.0291789711614413</v>
       </c>
       <c r="C82" t="n">
-        <v>0.0370838501236035</v>
+        <v>0.0319755661136138</v>
       </c>
     </row>
     <row r="83">
@@ -4553,10 +4553,10 @@
         <v>84</v>
       </c>
       <c r="B83" t="n">
-        <v>0.030530772591962</v>
+        <v>0.0315046206133696</v>
       </c>
       <c r="C83" t="n">
-        <v>0.0408141209947528</v>
+        <v>0.0345340464189358</v>
       </c>
     </row>
     <row r="84">
@@ -4564,10 +4564,10 @@
         <v>85</v>
       </c>
       <c r="B84" t="n">
-        <v>0.0263392767647738</v>
+        <v>0.0270660367516795</v>
       </c>
       <c r="C84" t="n">
-        <v>0.034748573471042</v>
+        <v>0.0296413586606685</v>
       </c>
     </row>
     <row r="85">
@@ -4575,10 +4575,10 @@
         <v>86</v>
       </c>
       <c r="B85" t="n">
-        <v>0.030530772591962</v>
+        <v>0.0315046206133696</v>
       </c>
       <c r="C85" t="n">
-        <v>0.0408141209947528</v>
+        <v>0.0345340464189358</v>
       </c>
     </row>
     <row r="86">
@@ -4586,10 +4586,10 @@
         <v>87</v>
       </c>
       <c r="B86" t="n">
-        <v>0.030530772591962</v>
+        <v>0.0315046206133696</v>
       </c>
       <c r="C86" t="n">
-        <v>0.0408141209947528</v>
+        <v>0.0345340464189358</v>
       </c>
     </row>
     <row r="87">
@@ -4597,10 +4597,10 @@
         <v>88</v>
       </c>
       <c r="B87" t="n">
-        <v>0.0260218902982226</v>
+        <v>0.0266462625942462</v>
       </c>
       <c r="C87" t="n">
-        <v>0.0337669320999307</v>
+        <v>0.02926647342653</v>
       </c>
     </row>
     <row r="88">
@@ -4608,10 +4608,10 @@
         <v>89</v>
       </c>
       <c r="B88" t="n">
-        <v>0.0273550862071269</v>
+        <v>0.0279794585031505</v>
       </c>
       <c r="C88" t="n">
-        <v>0.0352103299480494</v>
+        <v>0.0307098712746488</v>
       </c>
     </row>
     <row r="89">
@@ -4619,10 +4619,10 @@
         <v>90</v>
       </c>
       <c r="B89" t="n">
-        <v>0.0273550862071269</v>
+        <v>0.0279794585031505</v>
       </c>
       <c r="C89" t="n">
-        <v>0.0352103299480494</v>
+        <v>0.0307098712746488</v>
       </c>
     </row>
     <row r="90">
@@ -4630,10 +4630,10 @@
         <v>91</v>
       </c>
       <c r="B90" t="n">
-        <v>0.0266771339186175</v>
+        <v>0.0270881832566696</v>
       </c>
       <c r="C90" t="n">
-        <v>0.0322934313082674</v>
+        <v>0.0297528820902606</v>
       </c>
     </row>
     <row r="91">
@@ -4641,10 +4641,10 @@
         <v>92</v>
       </c>
       <c r="B91" t="n">
-        <v>0.0283971838137878</v>
+        <v>0.0288552896337066</v>
       </c>
       <c r="C91" t="n">
-        <v>0.0344292203431155</v>
+        <v>0.0317154609508699</v>
       </c>
     </row>
     <row r="92">
@@ -4652,10 +4652,10 @@
         <v>93</v>
       </c>
       <c r="B92" t="n">
-        <v>0.0249924821993402</v>
+        <v>0.0251720368475844</v>
       </c>
       <c r="C92" t="n">
-        <v>0.0293050910506735</v>
+        <v>0.0281051343880508</v>
       </c>
     </row>
     <row r="93">
@@ -4663,10 +4663,10 @@
         <v>94</v>
       </c>
       <c r="B93" t="n">
-        <v>0.0233939099582064</v>
+        <v>0.0234950719015959</v>
       </c>
       <c r="C93" t="n">
-        <v>0.0263024886628502</v>
+        <v>0.0255478404523603</v>
       </c>
     </row>
     <row r="94">
@@ -4674,10 +4674,10 @@
         <v>95</v>
       </c>
       <c r="B94" t="n">
-        <v>0.0248576891046726</v>
+        <v>0.0254925737950493</v>
       </c>
       <c r="C94" t="n">
-        <v>0.0324220175617825</v>
+        <v>0.0279022131447099</v>
       </c>
     </row>
     <row r="95">
@@ -4685,10 +4685,10 @@
         <v>96</v>
       </c>
       <c r="B95" t="n">
-        <v>0.0276140890874906</v>
+        <v>0.0280251384255428</v>
       </c>
       <c r="C95" t="n">
-        <v>0.0333978091356403</v>
+        <v>0.0308572599176335</v>
       </c>
     </row>
     <row r="96">
@@ -4696,10 +4696,10 @@
         <v>97</v>
       </c>
       <c r="B96" t="n">
-        <v>0.0245640261977023</v>
+        <v>0.0246669590333328</v>
       </c>
       <c r="C96" t="n">
-        <v>0.0274464611140916</v>
+        <v>0.0266766261781102</v>
       </c>
     </row>
     <row r="97">
@@ -4707,10 +4707,10 @@
         <v>98</v>
       </c>
       <c r="B97" t="n">
-        <v>0.0235208807561278</v>
+        <v>0.0236032607569225</v>
       </c>
       <c r="C97" t="n">
-        <v>0.0263730553265696</v>
+        <v>0.0257313800649315</v>
       </c>
     </row>
     <row r="98">
@@ -4718,10 +4718,10 @@
         <v>99</v>
       </c>
       <c r="B98" t="n">
-        <v>0.0268041047165389</v>
+        <v>0.0271963721119962</v>
       </c>
       <c r="C98" t="n">
-        <v>0.0323639979719868</v>
+        <v>0.0299364217028318</v>
       </c>
     </row>
     <row r="99">
@@ -4729,10 +4729,10 @@
         <v>100</v>
       </c>
       <c r="B99" t="n">
-        <v>0.0266056097823638</v>
+        <v>0.0270036115768163</v>
       </c>
       <c r="C99" t="n">
-        <v>0.0321440238537149</v>
+        <v>0.0296809825187766</v>
       </c>
     </row>
     <row r="100">
@@ -4740,10 +4740,10 @@
         <v>101</v>
       </c>
       <c r="B100" t="n">
-        <v>0.0286162177551928</v>
+        <v>0.0290272670932449</v>
       </c>
       <c r="C100" t="n">
-        <v>0.0337516572734291</v>
+        <v>0.0312111080554223</v>
       </c>
     </row>
     <row r="101">
@@ -4751,10 +4751,10 @@
         <v>102</v>
       </c>
       <c r="B101" t="n">
-        <v>0.0246410831352982</v>
+        <v>0.0248076492417258</v>
       </c>
       <c r="C101" t="n">
-        <v>0.0288211382619773</v>
+        <v>0.027697917548384</v>
       </c>
     </row>
     <row r="102">
@@ -4762,10 +4762,10 @@
         <v>103</v>
       </c>
       <c r="B102" t="n">
-        <v>0.0245640261977023</v>
+        <v>0.0246669590333328</v>
       </c>
       <c r="C102" t="n">
-        <v>0.0274464611140916</v>
+        <v>0.0266766261781102</v>
       </c>
     </row>
     <row r="103">
@@ -4773,10 +4773,10 @@
         <v>104</v>
       </c>
       <c r="B103" t="n">
-        <v>0.0237453090222484</v>
+        <v>0.0238594595074545</v>
       </c>
       <c r="C103" t="n">
-        <v>0.0267864414515464</v>
+        <v>0.0259550572920272</v>
       </c>
     </row>
     <row r="104">
@@ -4784,10 +4784,10 @@
         <v>105</v>
       </c>
       <c r="B104" t="n">
-        <v>0.0278472501581134</v>
+        <v>0.0282600703884064</v>
       </c>
       <c r="C104" t="n">
-        <v>0.0334374037595088</v>
+        <v>0.0308816678160105</v>
       </c>
     </row>
     <row r="105">
@@ -4795,10 +4795,10 @@
         <v>106</v>
       </c>
       <c r="B105" t="n">
-        <v>0.0242373547333495</v>
+        <v>0.0243197347341442</v>
       </c>
       <c r="C105" t="n">
-        <v>0.0271505415623895</v>
+        <v>0.0265088663007514</v>
       </c>
     </row>
     <row r="106">
@@ -4806,10 +4806,10 @@
         <v>107</v>
       </c>
       <c r="B106" t="n">
-        <v>0.0241103839354281</v>
+        <v>0.0242115458788176</v>
       </c>
       <c r="C106" t="n">
-        <v>0.0270799748986701</v>
+        <v>0.0263253266881803</v>
       </c>
     </row>
     <row r="107">
@@ -4817,10 +4817,10 @@
         <v>108</v>
       </c>
       <c r="B107" t="n">
-        <v>0.0253575571125199</v>
+        <v>0.0255241232189475</v>
       </c>
       <c r="C107" t="n">
-        <v>0.0295986244977973</v>
+        <v>0.028475403784204</v>
       </c>
     </row>
     <row r="108">
@@ -4828,10 +4828,10 @@
         <v>109</v>
       </c>
       <c r="B108" t="n">
-        <v>0.0251139598533767</v>
+        <v>0.0252621782786329</v>
       </c>
       <c r="C108" t="n">
-        <v>0.0284382776976983</v>
+        <v>0.0275104193129696</v>
       </c>
     </row>
     <row r="109">
@@ -4839,10 +4839,10 @@
         <v>110</v>
       </c>
       <c r="B109" t="n">
-        <v>0.0283256596775342</v>
+        <v>0.0287707179538532</v>
       </c>
       <c r="C109" t="n">
-        <v>0.0342798128885631</v>
+        <v>0.0316435613793859</v>
       </c>
     </row>
     <row r="110">
@@ -4850,10 +4850,10 @@
         <v>111</v>
       </c>
       <c r="B110" t="n">
-        <v>0.0243308651270796</v>
+        <v>0.0244320270704691</v>
       </c>
       <c r="C110" t="n">
-        <v>0.0274068664902231</v>
+        <v>0.0266522182797332</v>
       </c>
     </row>
     <row r="111">
@@ -4861,10 +4861,10 @@
         <v>112</v>
       </c>
       <c r="B111" t="n">
-        <v>0.0257089561765619</v>
+        <v>0.0258885108248061</v>
       </c>
       <c r="C111" t="n">
-        <v>0.0300825772864935</v>
+        <v>0.0288826206238708</v>
       </c>
     </row>
     <row r="112">
@@ -4872,10 +4872,10 @@
         <v>113</v>
       </c>
       <c r="B112" t="n">
-        <v>0.0245640261977023</v>
+        <v>0.0246669590333328</v>
       </c>
       <c r="C112" t="n">
-        <v>0.0274464611140916</v>
+        <v>0.0266766261781102</v>
       </c>
     </row>
     <row r="113">
@@ -4883,10 +4883,10 @@
         <v>114</v>
       </c>
       <c r="B113" t="n">
-        <v>0.0245640261977023</v>
+        <v>0.0246669590333328</v>
       </c>
       <c r="C113" t="n">
-        <v>0.0274464611140916</v>
+        <v>0.0266766261781102</v>
       </c>
     </row>
     <row r="114">
@@ -4894,10 +4894,10 @@
         <v>115</v>
       </c>
       <c r="B114" t="n">
-        <v>0.0246981076024075</v>
+        <v>0.0248010404380379</v>
       </c>
       <c r="C114" t="n">
-        <v>0.0274464611140916</v>
+        <v>0.0266766261781102</v>
       </c>
     </row>
     <row r="115">
@@ -4905,10 +4905,10 @@
         <v>116</v>
       </c>
       <c r="B115" t="n">
-        <v>0.0246978724036638</v>
+        <v>0.0248008052392943</v>
       </c>
       <c r="C115" t="n">
-        <v>0.0274464611140916</v>
+        <v>0.0266766261781102</v>
       </c>
     </row>
     <row r="116">
@@ -4916,10 +4916,10 @@
         <v>117</v>
       </c>
       <c r="B116" t="n">
-        <v>0.0263256781082445</v>
+        <v>0.0265052327564887</v>
       </c>
       <c r="C116" t="n">
-        <v>0.0307484888987923</v>
+        <v>0.0295485322361696</v>
       </c>
     </row>
     <row r="117">
@@ -4927,10 +4927,10 @@
         <v>118</v>
       </c>
       <c r="B117" t="n">
-        <v>0.0281373006254432</v>
+        <v>0.0285295680209005</v>
       </c>
       <c r="C117" t="n">
-        <v>0.0338073958201056</v>
+        <v>0.0313798195509505</v>
       </c>
     </row>
     <row r="118">
@@ -4938,10 +4938,10 @@
         <v>119</v>
       </c>
       <c r="B118" t="n">
-        <v>0.0245640261977023</v>
+        <v>0.0246669590333328</v>
       </c>
       <c r="C118" t="n">
-        <v>0.0274464611140916</v>
+        <v>0.0266766261781102</v>
       </c>
     </row>
     <row r="119">
@@ -4949,10 +4949,10 @@
         <v>120</v>
       </c>
       <c r="B119" t="n">
-        <v>0.0283971838137878</v>
+        <v>0.0288552896337066</v>
       </c>
       <c r="C119" t="n">
-        <v>0.0344292203431155</v>
+        <v>0.0317154609508699</v>
       </c>
     </row>
     <row r="120">
@@ -4960,10 +4960,10 @@
         <v>121</v>
       </c>
       <c r="B120" t="n">
-        <v>0.0283971838137878</v>
+        <v>0.0288552896337066</v>
       </c>
       <c r="C120" t="n">
-        <v>0.0344292203431155</v>
+        <v>0.0317154609508699</v>
       </c>
     </row>
     <row r="121">
@@ -4971,10 +4971,10 @@
         <v>122</v>
       </c>
       <c r="B121" t="n">
-        <v>0.0252311657319251</v>
+        <v>0.0253340985675555</v>
       </c>
       <c r="C121" t="n">
-        <v>0.0274464611140916</v>
+        <v>0.0266766261781102</v>
       </c>
     </row>
     <row r="122">
@@ -4982,10 +4982,10 @@
         <v>123</v>
       </c>
       <c r="B122" t="n">
-        <v>0.0283971838137878</v>
+        <v>0.0288552896337066</v>
       </c>
       <c r="C122" t="n">
-        <v>0.0344292203431155</v>
+        <v>0.0317154609508699</v>
       </c>
     </row>
     <row r="123">
@@ -4993,10 +4993,10 @@
         <v>124</v>
       </c>
       <c r="B123" t="n">
-        <v>0.0248576891046726</v>
+        <v>0.0254925737950493</v>
       </c>
       <c r="C123" t="n">
-        <v>0.0324220175617825</v>
+        <v>0.0279022131447099</v>
       </c>
     </row>
     <row r="124">
@@ -5004,10 +5004,10 @@
         <v>125</v>
       </c>
       <c r="B124" t="n">
-        <v>0.0283971838137878</v>
+        <v>0.0288552896337066</v>
       </c>
       <c r="C124" t="n">
-        <v>0.0344292203431155</v>
+        <v>0.0317154609508699</v>
       </c>
     </row>
     <row r="125">
@@ -5015,10 +5015,10 @@
         <v>126</v>
       </c>
       <c r="B125" t="n">
-        <v>0.0245640261977023</v>
+        <v>0.0246669590333328</v>
       </c>
       <c r="C125" t="n">
-        <v>0.0274464611140916</v>
+        <v>0.0266766261781102</v>
       </c>
     </row>
     <row r="126">
@@ -5026,10 +5026,10 @@
         <v>127</v>
       </c>
       <c r="B126" t="n">
-        <v>0.0245640261977023</v>
+        <v>0.0246669590333328</v>
       </c>
       <c r="C126" t="n">
-        <v>0.0274464611140916</v>
+        <v>0.0266766261781102</v>
       </c>
     </row>
     <row r="127">
@@ -5037,10 +5037,10 @@
         <v>128</v>
       </c>
       <c r="B127" t="n">
-        <v>0.0245640261977023</v>
+        <v>0.0246669590333328</v>
       </c>
       <c r="C127" t="n">
-        <v>0.0274464611140916</v>
+        <v>0.0266766261781102</v>
       </c>
     </row>
     <row r="128">
@@ -5048,10 +5048,10 @@
         <v>129</v>
       </c>
       <c r="B128" t="n">
-        <v>0.0245640261977023</v>
+        <v>0.0246669590333328</v>
       </c>
       <c r="C128" t="n">
-        <v>0.0274464611140916</v>
+        <v>0.0266766261781102</v>
       </c>
     </row>
     <row r="129">
@@ -5059,10 +5059,10 @@
         <v>130</v>
       </c>
       <c r="B129" t="n">
-        <v>0.0245640261977023</v>
+        <v>0.0246669590333328</v>
       </c>
       <c r="C129" t="n">
-        <v>0.0274464611140916</v>
+        <v>0.0266766261781102</v>
       </c>
     </row>
     <row r="130">
@@ -5070,10 +5070,10 @@
         <v>131</v>
       </c>
       <c r="B130" t="n">
-        <v>0.0269706033351246</v>
+        <v>0.027605508204811</v>
       </c>
       <c r="C130" t="n">
-        <v>0.0347572942143441</v>
+        <v>0.0302364205976552</v>
       </c>
     </row>
     <row r="131">
@@ -5081,10 +5081,10 @@
         <v>132</v>
       </c>
       <c r="B131" t="n">
-        <v>0.0271053964297922</v>
+        <v>0.0272849712573462</v>
       </c>
       <c r="C131" t="n">
-        <v>0.0316403677032351</v>
+        <v>0.0304393418409961</v>
       </c>
     </row>
     <row r="132">
@@ -5092,10 +5092,10 @@
         <v>133</v>
       </c>
       <c r="B132" t="n">
-        <v>0.0271053964297922</v>
+        <v>0.0272849712573462</v>
       </c>
       <c r="C132" t="n">
-        <v>0.0316403677032351</v>
+        <v>0.0304393418409961</v>
       </c>
     </row>
     <row r="133">
@@ -5103,10 +5103,10 @@
         <v>134</v>
       </c>
       <c r="B133" t="n">
-        <v>0.0271053964297922</v>
+        <v>0.0272849712573462</v>
       </c>
       <c r="C133" t="n">
-        <v>0.0316403677032351</v>
+        <v>0.0304393418409961</v>
       </c>
     </row>
     <row r="134">
@@ -5114,10 +5114,10 @@
         <v>135</v>
       </c>
       <c r="B134" t="n">
-        <v>0.0245640261977023</v>
+        <v>0.0246669590333328</v>
       </c>
       <c r="C134" t="n">
-        <v>0.0274464611140916</v>
+        <v>0.0266766261781102</v>
       </c>
     </row>
     <row r="135">
@@ -5125,10 +5125,10 @@
         <v>136</v>
       </c>
       <c r="B135" t="n">
-        <v>0.0247271058671107</v>
+        <v>0.0248282678105002</v>
       </c>
       <c r="C135" t="n">
-        <v>0.0277458865109689</v>
+        <v>0.0269912383004791</v>
       </c>
     </row>
     <row r="136">
@@ -5136,10 +5136,10 @@
         <v>137</v>
       </c>
       <c r="B136" t="n">
-        <v>0.0259742790442025</v>
+        <v>0.0261408451506301</v>
       </c>
       <c r="C136" t="n">
-        <v>0.0302645361100961</v>
+        <v>0.0291413153965028</v>
       </c>
     </row>
     <row r="137">
@@ -5147,10 +5147,10 @@
         <v>138</v>
       </c>
       <c r="B137" t="n">
-        <v>0.0265855612965891</v>
+        <v>0.0268309543692948</v>
       </c>
       <c r="C137" t="n">
-        <v>0.0313703134218022</v>
+        <v>0.029884173636089</v>
       </c>
     </row>
     <row r="138">
@@ -5158,10 +5158,10 @@
         <v>139</v>
       </c>
       <c r="B138" t="n">
-        <v>0.0261987073103231</v>
+        <v>0.0263970439011621</v>
       </c>
       <c r="C138" t="n">
-        <v>0.0306779222350729</v>
+        <v>0.0293649926235985</v>
       </c>
     </row>
     <row r="139">
@@ -5169,10 +5169,10 @@
         <v>140</v>
       </c>
       <c r="B139" t="n">
-        <v>0.0257722005208879</v>
+        <v>0.0259517753484419</v>
       </c>
       <c r="C139" t="n">
-        <v>0.0301969698551163</v>
+        <v>0.0289959439928774</v>
       </c>
     </row>
     <row r="140">
@@ -5180,10 +5180,10 @@
         <v>141</v>
       </c>
       <c r="B140" t="n">
-        <v>0.0256374074262203</v>
+        <v>0.0262723122959067</v>
       </c>
       <c r="C140" t="n">
-        <v>0.0333138963662253</v>
+        <v>0.0287930227495364</v>
       </c>
     </row>
     <row r="141">
@@ -5191,10 +5191,10 @@
         <v>142</v>
       </c>
       <c r="B141" t="n">
-        <v>0.0275838230380866</v>
+        <v>0.0279761106128536</v>
       </c>
       <c r="C141" t="n">
-        <v>0.0332558767764296</v>
+        <v>0.0308272313076583</v>
       </c>
     </row>
     <row r="142">
@@ -5202,10 +5202,10 @@
         <v>143</v>
       </c>
       <c r="B142" t="n">
-        <v>0.0271053964297922</v>
+        <v>0.0272849712573462</v>
       </c>
       <c r="C142" t="n">
-        <v>0.0316403677032351</v>
+        <v>0.0304393418409961</v>
       </c>
     </row>
     <row r="143">
@@ -5213,10 +5213,10 @@
         <v>144</v>
       </c>
       <c r="B143" t="n">
-        <v>0.0289170189469909</v>
+        <v>0.0293093065217579</v>
       </c>
       <c r="C143" t="n">
-        <v>0.0346992746245484</v>
+        <v>0.032270629155777</v>
       </c>
     </row>
     <row r="144">
@@ -5224,10 +5224,10 @@
         <v>145</v>
       </c>
       <c r="B144" t="n">
-        <v>0.0269706033351246</v>
+        <v>0.027605508204811</v>
       </c>
       <c r="C144" t="n">
-        <v>0.0347572942143441</v>
+        <v>0.0302364205976552</v>
       </c>
     </row>
     <row r="145">
@@ -5235,10 +5235,10 @@
         <v>146</v>
       </c>
       <c r="B145" t="n">
-        <v>0.0245640261977023</v>
+        <v>0.0246669590333328</v>
       </c>
       <c r="C145" t="n">
-        <v>0.0274464611140916</v>
+        <v>0.0266766261781102</v>
       </c>
     </row>
     <row r="146">
@@ -5246,10 +5246,10 @@
         <v>147</v>
       </c>
       <c r="B146" t="n">
-        <v>0.0245640261977023</v>
+        <v>0.0246669590333328</v>
       </c>
       <c r="C146" t="n">
-        <v>0.0274464611140916</v>
+        <v>0.0266766261781102</v>
       </c>
     </row>
     <row r="147">
@@ -5257,10 +5257,10 @@
         <v>148</v>
       </c>
       <c r="B147" t="n">
-        <v>0.0248540766650322</v>
+        <v>0.0249364566658268</v>
       </c>
       <c r="C147" t="n">
-        <v>0.0278164531746884</v>
+        <v>0.0271747779130502</v>
       </c>
     </row>
     <row r="148">
@@ -5268,10 +5268,10 @@
         <v>149</v>
       </c>
       <c r="B148" t="n">
-        <v>0.0245640261977023</v>
+        <v>0.0246669590333328</v>
       </c>
       <c r="C148" t="n">
-        <v>0.0274464611140916</v>
+        <v>0.0266766261781102</v>
       </c>
     </row>
     <row r="149">
@@ -5279,10 +5279,10 @@
         <v>150</v>
       </c>
       <c r="B149" t="n">
-        <v>0.0245640261977023</v>
+        <v>0.0246669590333328</v>
       </c>
       <c r="C149" t="n">
-        <v>0.0274464611140916</v>
+        <v>0.0266766261781102</v>
       </c>
     </row>
     <row r="150">
@@ -5290,10 +5290,10 @@
         <v>151</v>
       </c>
       <c r="B150" t="n">
-        <v>0.0245640261977023</v>
+        <v>0.0246669590333328</v>
       </c>
       <c r="C150" t="n">
-        <v>0.0274464611140916</v>
+        <v>0.0266766261781102</v>
       </c>
     </row>
     <row r="151">
@@ -5301,10 +5301,10 @@
         <v>152</v>
       </c>
       <c r="B151" t="n">
-        <v>0.0283971838137878</v>
+        <v>0.0288552896337066</v>
       </c>
       <c r="C151" t="n">
-        <v>0.0344292203431155</v>
+        <v>0.0317154609508699</v>
       </c>
     </row>
     <row r="152">
@@ -5312,10 +5312,10 @@
         <v>153</v>
       </c>
       <c r="B152" t="n">
-        <v>0.0283971838137878</v>
+        <v>0.0288552896337066</v>
       </c>
       <c r="C152" t="n">
-        <v>0.0344292203431155</v>
+        <v>0.0317154609508699</v>
       </c>
     </row>
     <row r="153">
@@ -5323,10 +5323,10 @@
         <v>154</v>
       </c>
       <c r="B153" t="n">
-        <v>0.0245640261977023</v>
+        <v>0.0246669590333328</v>
       </c>
       <c r="C153" t="n">
-        <v>0.0274464611140916</v>
+        <v>0.0266766261781102</v>
       </c>
     </row>
     <row r="154">
@@ -5334,10 +5334,10 @@
         <v>155</v>
       </c>
       <c r="B154" t="n">
-        <v>0.0266771339186175</v>
+        <v>0.0270881832566696</v>
       </c>
       <c r="C154" t="n">
-        <v>0.0322934313082674</v>
+        <v>0.0297528820902606</v>
       </c>
     </row>
     <row r="155">
@@ -5345,10 +5345,10 @@
         <v>156</v>
       </c>
       <c r="B155" t="n">
-        <v>0.0245640261977023</v>
+        <v>0.0246669590333328</v>
       </c>
       <c r="C155" t="n">
-        <v>0.0274464611140916</v>
+        <v>0.0266766261781102</v>
       </c>
     </row>
     <row r="156">
@@ -5356,10 +5356,10 @@
         <v>157</v>
       </c>
       <c r="B156" t="n">
-        <v>0.0233939099582064</v>
+        <v>0.0234950719015959</v>
       </c>
       <c r="C156" t="n">
-        <v>0.0263024886628502</v>
+        <v>0.0255478404523603</v>
       </c>
     </row>
     <row r="157">
@@ -5367,10 +5367,10 @@
         <v>158</v>
       </c>
       <c r="B157" t="n">
-        <v>0.0245640261977023</v>
+        <v>0.0246669590333328</v>
       </c>
       <c r="C157" t="n">
-        <v>0.0274464611140916</v>
+        <v>0.0266766261781102</v>
       </c>
     </row>
     <row r="158">
@@ -5378,10 +5378,10 @@
         <v>159</v>
       </c>
       <c r="B158" t="n">
-        <v>0.0279196215230277</v>
+        <v>0.0283182835475201</v>
       </c>
       <c r="C158" t="n">
-        <v>0.0328944405792199</v>
+        <v>0.0304283119762737</v>
       </c>
     </row>
     <row r="159">
@@ -5389,10 +5389,10 @@
         <v>160</v>
       </c>
       <c r="B159" t="n">
-        <v>0.0266056097823638</v>
+        <v>0.0270036115768163</v>
       </c>
       <c r="C159" t="n">
-        <v>0.0321440238537149</v>
+        <v>0.0296809825187766</v>
       </c>
     </row>
     <row r="160">
@@ -5400,10 +5400,10 @@
         <v>161</v>
       </c>
       <c r="B160" t="n">
-        <v>0.0237717612128129</v>
+        <v>0.0238541077200623</v>
       </c>
       <c r="C160" t="n">
-        <v>0.0265916265161969</v>
+        <v>0.025951547071325</v>
       </c>
     </row>
     <row r="161">
@@ -5411,10 +5411,10 @@
         <v>162</v>
       </c>
       <c r="B161" t="n">
-        <v>0.0263257348545754</v>
+        <v>0.026723795650811</v>
       </c>
       <c r="C161" t="n">
-        <v>0.0318094785195712</v>
+        <v>0.0293456652505938</v>
       </c>
     </row>
     <row r="162">
@@ -5422,10 +5422,10 @@
         <v>163</v>
       </c>
       <c r="B162" t="n">
-        <v>0.0279911456592814</v>
+        <v>0.0284028552273734</v>
       </c>
       <c r="C162" t="n">
-        <v>0.0330438480337724</v>
+        <v>0.0305002115477577</v>
       </c>
     </row>
     <row r="163">
@@ -5433,10 +5433,10 @@
         <v>164</v>
       </c>
       <c r="B163" t="n">
-        <v>0.0276397465952393</v>
+        <v>0.0280384676215148</v>
       </c>
       <c r="C163" t="n">
-        <v>0.0325598952450762</v>
+        <v>0.0300929947080908</v>
       </c>
     </row>
     <row r="164">
@@ -5444,10 +5444,10 @@
         <v>165</v>
       </c>
       <c r="B164" t="n">
-        <v>0.0247079216988703</v>
+        <v>0.0248097438722997</v>
       </c>
       <c r="C164" t="n">
-        <v>0.0270529053883551</v>
+        <v>0.0262951699098574</v>
       </c>
     </row>
     <row r="165">
@@ -5455,10 +5455,10 @@
         <v>166</v>
       </c>
       <c r="B165" t="n">
-        <v>0.0249154252617443</v>
+        <v>0.0250313466391914</v>
       </c>
       <c r="C165" t="n">
-        <v>0.0279304139027878</v>
+        <v>0.027083843017777</v>
       </c>
     </row>
     <row r="166">
@@ -5466,10 +5466,10 @@
         <v>167</v>
       </c>
       <c r="B166" t="n">
-        <v>0.0246981076024075</v>
+        <v>0.0248010404380379</v>
       </c>
       <c r="C166" t="n">
-        <v>0.0274464611140916</v>
+        <v>0.0266766261781102</v>
       </c>
     </row>
     <row r="167">
@@ -5477,10 +5477,10 @@
         <v>168</v>
       </c>
       <c r="B167" t="n">
-        <v>0.0245640261977023</v>
+        <v>0.0246669590333328</v>
       </c>
       <c r="C167" t="n">
-        <v>0.0274464611140916</v>
+        <v>0.0266766261781102</v>
       </c>
     </row>
     <row r="168">
@@ -5488,10 +5488,10 @@
         <v>169</v>
       </c>
       <c r="B168" t="n">
-        <v>0.0245640261977023</v>
+        <v>0.0246669590333328</v>
       </c>
       <c r="C168" t="n">
-        <v>0.0274464611140916</v>
+        <v>0.0266766261781102</v>
       </c>
     </row>
     <row r="169">
@@ -5499,10 +5499,10 @@
         <v>170</v>
       </c>
       <c r="B169" t="n">
-        <v>0.024704272001753</v>
+        <v>0.0248072048373835</v>
       </c>
       <c r="C169" t="n">
-        <v>0.0274464611140916</v>
+        <v>0.0266766261781102</v>
       </c>
     </row>
     <row r="170">
@@ -5510,10 +5510,10 @@
         <v>171</v>
       </c>
       <c r="B170" t="n">
-        <v>0.0245640261977023</v>
+        <v>0.0246669590333328</v>
       </c>
       <c r="C170" t="n">
-        <v>0.0274464611140916</v>
+        <v>0.0266766261781102</v>
       </c>
     </row>
     <row r="171">
@@ -5521,10 +5521,10 @@
         <v>172</v>
       </c>
       <c r="B171" t="n">
-        <v>0.0280011959940886</v>
+        <v>0.0283998703666347</v>
       </c>
       <c r="C171" t="n">
-        <v>0.0329857169648571</v>
+        <v>0.0305193851006589</v>
       </c>
     </row>
     <row r="172">
@@ -5532,10 +5532,10 @@
         <v>173</v>
       </c>
       <c r="B172" t="n">
-        <v>0.0280011959940886</v>
+        <v>0.0283998703666347</v>
       </c>
       <c r="C172" t="n">
-        <v>0.0329857169648571</v>
+        <v>0.0305193851006589</v>
       </c>
     </row>
     <row r="173">
@@ -5543,10 +5543,10 @@
         <v>174</v>
       </c>
       <c r="B173" t="n">
-        <v>0.0266871842534247</v>
+        <v>0.0270851983959309</v>
       </c>
       <c r="C173" t="n">
-        <v>0.0322353002393522</v>
+        <v>0.0297720556431618</v>
       </c>
     </row>
     <row r="174">
@@ -5554,10 +5554,10 @@
         <v>175</v>
       </c>
       <c r="B174" t="n">
-        <v>0.0245640261977023</v>
+        <v>0.0246669590333328</v>
       </c>
       <c r="C174" t="n">
-        <v>0.0274464611140916</v>
+        <v>0.0266766261781102</v>
       </c>
     </row>
     <row r="175">
@@ -5565,10 +5565,10 @@
         <v>176</v>
       </c>
       <c r="B175" t="n">
-        <v>0.0245640261977023</v>
+        <v>0.0246669590333328</v>
       </c>
       <c r="C175" t="n">
-        <v>0.0274464611140916</v>
+        <v>0.0266766261781102</v>
       </c>
     </row>
     <row r="176">
@@ -5576,10 +5576,10 @@
         <v>177</v>
       </c>
       <c r="B176" t="n">
-        <v>0.0248269889522913</v>
+        <v>0.0249095201933855</v>
       </c>
       <c r="C176" t="n">
-        <v>0.0276056149564376</v>
+        <v>0.0269638670646853</v>
       </c>
     </row>
     <row r="177">
@@ -5587,10 +5587,10 @@
         <v>178</v>
       </c>
       <c r="B177" t="n">
-        <v>0.0245640261977023</v>
+        <v>0.0246669590333328</v>
       </c>
       <c r="C177" t="n">
-        <v>0.0274464611140916</v>
+        <v>0.0266766261781102</v>
       </c>
     </row>
     <row r="178">
@@ -5598,10 +5598,10 @@
         <v>179</v>
       </c>
       <c r="B178" t="n">
-        <v>0.0267752041716453</v>
+        <v>0.0273334202700448</v>
       </c>
       <c r="C178" t="n">
-        <v>0.033159244835971</v>
+        <v>0.0297004990967824</v>
       </c>
     </row>
     <row r="179">
@@ -5609,10 +5609,10 @@
         <v>180</v>
       </c>
       <c r="B179" t="n">
-        <v>0.0225326928932524</v>
+        <v>0.0229568097272872</v>
       </c>
       <c r="C179" t="n">
-        <v>0.0275862413897166</v>
+        <v>0.0249160168522748</v>
       </c>
     </row>
     <row r="180">
@@ -5620,10 +5620,10 @@
         <v>181</v>
       </c>
       <c r="B180" t="n">
-        <v>0.0257217377956331</v>
+        <v>0.0258409868195463</v>
       </c>
       <c r="C180" t="n">
-        <v>0.00789334244005186</v>
+        <v>0.00705662945162071</v>
       </c>
     </row>
     <row r="181">
@@ -5631,10 +5631,10 @@
         <v>182</v>
       </c>
       <c r="B181" t="n">
-        <v>0.0235631918156219</v>
+        <v>0.0240198656101154</v>
       </c>
       <c r="C181" t="n">
-        <v>0.0289373171185855</v>
+        <v>0.0260787120075522</v>
       </c>
     </row>
     <row r="182">
@@ -5642,10 +5642,10 @@
         <v>183</v>
       </c>
       <c r="B182" t="n">
-        <v>0.0257447052492758</v>
+        <v>0.0262703643872166</v>
       </c>
       <c r="C182" t="n">
-        <v>0.0318081691071022</v>
+        <v>0.028537803941505</v>
       </c>
     </row>
     <row r="183">
@@ -5653,10 +5653,10 @@
         <v>184</v>
       </c>
       <c r="B183" t="n">
-        <v>0.0267752041716453</v>
+        <v>0.0273334202700448</v>
       </c>
       <c r="C183" t="n">
-        <v>0.033159244835971</v>
+        <v>0.0297004990967824</v>
       </c>
     </row>
     <row r="184">
@@ -5664,10 +5664,10 @@
         <v>185</v>
       </c>
       <c r="B184" t="n">
-        <v>0.0267752041716453</v>
+        <v>0.0273334202700448</v>
       </c>
       <c r="C184" t="n">
-        <v>0.033159244835971</v>
+        <v>0.0297004990967824</v>
       </c>
     </row>
     <row r="185">
@@ -5675,10 +5675,10 @@
         <v>186</v>
       </c>
       <c r="B185" t="n">
-        <v>0.0267752041716453</v>
+        <v>0.0273334202700448</v>
       </c>
       <c r="C185" t="n">
-        <v>0.033159244835971</v>
+        <v>0.0297004990967824</v>
       </c>
     </row>
     <row r="186">
@@ -5686,10 +5686,10 @@
         <v>187</v>
       </c>
       <c r="B186" t="n">
-        <v>0.0267752041716453</v>
+        <v>0.0273334202700448</v>
       </c>
       <c r="C186" t="n">
-        <v>0.033159244835971</v>
+        <v>0.0297004990967824</v>
       </c>
     </row>
     <row r="187">
@@ -5697,10 +5697,10 @@
         <v>188</v>
       </c>
       <c r="B187" t="n">
-        <v>0.0267752041716453</v>
+        <v>0.0273334202700448</v>
       </c>
       <c r="C187" t="n">
-        <v>0.033159244835971</v>
+        <v>0.0297004990967824</v>
       </c>
     </row>
     <row r="188">
@@ -5708,10 +5708,10 @@
         <v>189</v>
       </c>
       <c r="B188" t="n">
-        <v>0.0267752041716453</v>
+        <v>0.0273334202700448</v>
       </c>
       <c r="C188" t="n">
-        <v>0.033159244835971</v>
+        <v>0.0297004990967824</v>
       </c>
     </row>
     <row r="189">
@@ -5719,10 +5719,10 @@
         <v>190</v>
       </c>
       <c r="B189" t="n">
-        <v>0.0262728600754885</v>
+        <v>0.0269997955286579</v>
       </c>
       <c r="C189" t="n">
-        <v>0.034626273539172</v>
+        <v>0.0295118633759119</v>
       </c>
     </row>
     <row r="190">
@@ -5730,10 +5730,10 @@
         <v>191</v>
       </c>
       <c r="B190" t="n">
-        <v>0.0223902534249731</v>
+        <v>0.022770267532121</v>
       </c>
       <c r="C190" t="n">
-        <v>0.0272046613923463</v>
+        <v>0.0247124344813626</v>
       </c>
     </row>
     <row r="191">
@@ -5741,10 +5741,10 @@
         <v>192</v>
       </c>
       <c r="B191" t="n">
-        <v>0.0256946455873987</v>
+        <v>0.0263517034677799</v>
       </c>
       <c r="C191" t="n">
-        <v>0.033511150398044</v>
+        <v>0.0287359583570484</v>
       </c>
     </row>
     <row r="192">
@@ -5752,10 +5752,10 @@
         <v>193</v>
       </c>
       <c r="B192" t="n">
-        <v>0.0266327647033659</v>
+        <v>0.0271468780748785</v>
       </c>
       <c r="C192" t="n">
-        <v>0.0327776648386007</v>
+        <v>0.0294969167258702</v>
       </c>
     </row>
     <row r="193">
@@ -5763,10 +5763,10 @@
         <v>194</v>
       </c>
       <c r="B193" t="n">
-        <v>0.0229684679130629</v>
+        <v>0.023418359592999</v>
       </c>
       <c r="C193" t="n">
-        <v>0.0283197845334743</v>
+        <v>0.0254883395002261</v>
       </c>
     </row>
     <row r="194">
@@ -5774,10 +5774,10 @@
         <v>195</v>
       </c>
       <c r="B194" t="n">
-        <v>0.0223786621777862</v>
+        <v>0.0227410605636791</v>
       </c>
       <c r="C194" t="n">
-        <v>0.0270733313642792</v>
+        <v>0.024737133528</v>
       </c>
     </row>
     <row r="195">
@@ -5785,10 +5785,10 @@
         <v>196</v>
       </c>
       <c r="B195" t="n">
-        <v>0.0256830543402119</v>
+        <v>0.0263224964993379</v>
       </c>
       <c r="C195" t="n">
-        <v>0.0333798203699769</v>
+        <v>0.0287606574036858</v>
       </c>
     </row>
     <row r="196">
@@ -5796,10 +5796,10 @@
         <v>197</v>
       </c>
       <c r="B196" t="n">
-        <v>0.0304643559026767</v>
+        <v>0.0314383793903479</v>
       </c>
       <c r="C196" t="n">
-        <v>0.0406918210628828</v>
+        <v>0.0344045511341791</v>
       </c>
     </row>
     <row r="197">
@@ -5807,10 +5807,10 @@
         <v>198</v>
       </c>
       <c r="B197" t="n">
-        <v>0.0256022657809965</v>
+        <v>0.0260838221920504</v>
       </c>
       <c r="C197" t="n">
-        <v>0.0314265891097319</v>
+        <v>0.0283342215705928</v>
       </c>
     </row>
     <row r="198">
@@ -5818,10 +5818,10 @@
         <v>199</v>
       </c>
       <c r="B198" t="n">
-        <v>0.0234207523473425</v>
+        <v>0.0238333234149491</v>
       </c>
       <c r="C198" t="n">
-        <v>0.0285557371212152</v>
+        <v>0.02587512963664</v>
       </c>
     </row>
     <row r="199">
@@ -5829,10 +5829,10 @@
         <v>200</v>
       </c>
       <c r="B199" t="n">
-        <v>0.0304643559026767</v>
+        <v>0.0314383793903479</v>
       </c>
       <c r="C199" t="n">
-        <v>0.0406918210628828</v>
+        <v>0.0344045511341791</v>
       </c>
     </row>
     <row r="200">
@@ -5840,10 +5840,10 @@
         <v>201</v>
       </c>
       <c r="B200" t="n">
-        <v>0.0266327647033659</v>
+        <v>0.0271468780748785</v>
       </c>
       <c r="C200" t="n">
-        <v>0.0327776648386007</v>
+        <v>0.0294969167258702</v>
       </c>
     </row>
     <row r="201">
@@ -5851,10 +5851,10 @@
         <v>202</v>
       </c>
       <c r="B201" t="n">
-        <v>0.0300791439880832</v>
+        <v>0.0311003820504761</v>
       </c>
       <c r="C201" t="n">
-        <v>0.0404489121095385</v>
+        <v>0.0340355623378695</v>
       </c>
     </row>
     <row r="202">
@@ -5862,10 +5862,10 @@
         <v>203</v>
       </c>
       <c r="B202" t="n">
-        <v>0.025887648160895</v>
+        <v>0.026661798188786</v>
       </c>
       <c r="C202" t="n">
-        <v>0.0343833645858277</v>
+        <v>0.0291428745796023</v>
       </c>
     </row>
     <row r="203">
@@ -5873,10 +5873,10 @@
         <v>204</v>
       </c>
       <c r="B203" t="n">
-        <v>0.0245358364595531</v>
+        <v>0.0252092773615914</v>
       </c>
       <c r="C203" t="n">
-        <v>0.0321818736111684</v>
+        <v>0.0275216712478809</v>
       </c>
     </row>
     <row r="204">
@@ -5884,10 +5884,10 @@
         <v>205</v>
       </c>
       <c r="B204" t="n">
-        <v>0.0261232235411462</v>
+        <v>0.0266877035982115</v>
       </c>
       <c r="C204" t="n">
-        <v>0.0323640442148547</v>
+        <v>0.0289306312695365</v>
       </c>
     </row>
     <row r="205">
@@ -5895,10 +5895,10 @@
         <v>206</v>
       </c>
       <c r="B205" t="n">
-        <v>0.0247714118398043</v>
+        <v>0.0252351827710168</v>
       </c>
       <c r="C205" t="n">
-        <v>0.0301625532401954</v>
+        <v>0.0273094279378151</v>
       </c>
     </row>
     <row r="206">
@@ -5906,10 +5906,10 @@
         <v>207</v>
       </c>
       <c r="B206" t="n">
-        <v>0.0289399941224666</v>
+        <v>0.029592798480721</v>
       </c>
       <c r="C206" t="n">
-        <v>0.0355586182267205</v>
+        <v>0.0319815490708363</v>
       </c>
     </row>
     <row r="207">
@@ -5917,10 +5917,10 @@
         <v>208</v>
       </c>
       <c r="B207" t="n">
-        <v>0.0261568529975456</v>
+        <v>0.0266575138109532</v>
       </c>
       <c r="C207" t="n">
-        <v>0.0319036208434375</v>
+        <v>0.0288632802616652</v>
       </c>
     </row>
     <row r="208">
@@ -5928,10 +5928,10 @@
         <v>209</v>
       </c>
       <c r="B208" t="n">
-        <v>0.025887648160895</v>
+        <v>0.026661798188786</v>
       </c>
       <c r="C208" t="n">
-        <v>0.0343833645858277</v>
+        <v>0.0291428745796023</v>
       </c>
     </row>
     <row r="209">
@@ -5939,10 +5939,10 @@
         <v>210</v>
       </c>
       <c r="B209" t="n">
-        <v>0.0278267319974703</v>
+        <v>0.0286008820253614</v>
       </c>
       <c r="C209" t="n">
-        <v>0.0358415905509894</v>
+        <v>0.030601100544764</v>
       </c>
     </row>
     <row r="210">
@@ -5950,10 +5950,10 @@
         <v>211</v>
       </c>
       <c r="B210" t="n">
-        <v>0.0275545529647254</v>
+        <v>0.0281704674407847</v>
       </c>
       <c r="C210" t="n">
-        <v>0.0338175506234784</v>
+        <v>0.0304276967469863</v>
       </c>
     </row>
     <row r="211">
@@ -5961,10 +5961,10 @@
         <v>212</v>
       </c>
       <c r="B211" t="n">
-        <v>0.0275441989458829</v>
+        <v>0.028043127521406</v>
       </c>
       <c r="C211" t="n">
-        <v>0.0328011198256885</v>
+        <v>0.0297899127543336</v>
       </c>
     </row>
     <row r="212">
@@ -5972,10 +5972,10 @@
         <v>213</v>
       </c>
       <c r="B212" t="n">
-        <v>0.0278267319974703</v>
+        <v>0.0286008820253614</v>
       </c>
       <c r="C212" t="n">
-        <v>0.0358415905509894</v>
+        <v>0.030601100544764</v>
       </c>
     </row>
     <row r="213">
@@ -5983,10 +5983,10 @@
         <v>214</v>
       </c>
       <c r="B213" t="n">
-        <v>0.0280623073777215</v>
+        <v>0.0286267874347868</v>
       </c>
       <c r="C213" t="n">
-        <v>0.0338222701800164</v>
+        <v>0.0303888572346982</v>
       </c>
     </row>
     <row r="214">
@@ -5994,10 +5994,10 @@
         <v>215</v>
       </c>
       <c r="B214" t="n">
-        <v>0.0283833578625078</v>
+        <v>0.029245809378844</v>
       </c>
       <c r="C214" t="n">
-        <v>0.0372307213643253</v>
+        <v>0.0318470834472659</v>
       </c>
     </row>
     <row r="215">
@@ -6005,10 +6005,10 @@
         <v>216</v>
       </c>
       <c r="B215" t="n">
-        <v>0.0300791439880832</v>
+        <v>0.0311003820504761</v>
       </c>
       <c r="C215" t="n">
-        <v>0.0404489121095385</v>
+        <v>0.0340355623378695</v>
       </c>
     </row>
     <row r="216">
@@ -6016,10 +6016,10 @@
         <v>217</v>
       </c>
       <c r="B216" t="n">
-        <v>0.0283833578625078</v>
+        <v>0.029245809378844</v>
       </c>
       <c r="C216" t="n">
-        <v>0.0372307213643253</v>
+        <v>0.0318470834472659</v>
       </c>
     </row>
     <row r="217">
@@ -6027,10 +6027,10 @@
         <v>218</v>
       </c>
       <c r="B217" t="n">
-        <v>0.0283833578625078</v>
+        <v>0.029245809378844</v>
       </c>
       <c r="C217" t="n">
-        <v>0.0372307213643253</v>
+        <v>0.0318470834472659</v>
       </c>
     </row>
     <row r="218">
@@ -6038,10 +6038,10 @@
         <v>219</v>
       </c>
       <c r="B218" t="n">
-        <v>0.0300791439880832</v>
+        <v>0.0311003820504761</v>
       </c>
       <c r="C218" t="n">
-        <v>0.0404489121095385</v>
+        <v>0.0340355623378695</v>
       </c>
     </row>
     <row r="219">
@@ -6049,10 +6049,10 @@
         <v>220</v>
       </c>
       <c r="B219" t="n">
-        <v>0.0259032759875334</v>
+        <v>0.0265749846516872</v>
       </c>
       <c r="C219" t="n">
-        <v>0.0330793725934194</v>
+        <v>0.0284483037405493</v>
       </c>
     </row>
     <row r="220">
@@ -6060,10 +6060,10 @@
         <v>221</v>
       </c>
       <c r="B220" t="n">
-        <v>0.0300791439880832</v>
+        <v>0.0311003820504761</v>
       </c>
       <c r="C220" t="n">
-        <v>0.0404489121095385</v>
+        <v>0.0340355623378695</v>
       </c>
     </row>
     <row r="221">
@@ -6071,10 +6071,10 @@
         <v>222</v>
       </c>
       <c r="B221" t="n">
-        <v>0.028995723014736</v>
+        <v>0.0296037213428476</v>
       </c>
       <c r="C221" t="n">
-        <v>0.0353853138158546</v>
+        <v>0.0319976429799652</v>
       </c>
     </row>
     <row r="222">
@@ -6082,10 +6082,10 @@
         <v>223</v>
       </c>
       <c r="B222" t="n">
-        <v>0.0266657170790104</v>
+        <v>0.0270688178542421</v>
       </c>
       <c r="C222" t="n">
-        <v>0.0322079537458926</v>
+        <v>0.0297439425953168</v>
       </c>
     </row>
     <row r="223">
@@ -6093,10 +6093,10 @@
         <v>224</v>
       </c>
       <c r="B223" t="n">
-        <v>0.0276928428029287</v>
+        <v>0.0278667447344233</v>
       </c>
       <c r="C223" t="n">
-        <v>0.0308991400964436</v>
+        <v>0.0296909004616226</v>
       </c>
     </row>
     <row r="224">
@@ -6104,10 +6104,10 @@
         <v>225</v>
       </c>
       <c r="B224" t="n">
-        <v>0.0248271407320737</v>
+        <v>0.0252461056331434</v>
       </c>
       <c r="C224" t="n">
-        <v>0.0299892488293295</v>
+        <v>0.027325521846944</v>
       </c>
     </row>
     <row r="225">
@@ -6115,10 +6115,10 @@
         <v>226</v>
       </c>
       <c r="B225" t="n">
-        <v>0.0283857669741807</v>
+        <v>0.0288359242312791</v>
       </c>
       <c r="C225" t="n">
-        <v>0.0343437427807407</v>
+        <v>0.0317065214559261</v>
       </c>
     </row>
     <row r="226">
@@ -6126,10 +6126,10 @@
         <v>227</v>
       </c>
       <c r="B226" t="n">
-        <v>0.026212581889815</v>
+        <v>0.0266684366730797</v>
       </c>
       <c r="C226" t="n">
-        <v>0.0317303164325716</v>
+        <v>0.0288793741707941</v>
       </c>
     </row>
     <row r="227">
@@ -6137,10 +6137,10 @@
         <v>228</v>
       </c>
       <c r="B227" t="n">
-        <v>0.0292680328070302</v>
+        <v>0.0294520242483144</v>
       </c>
       <c r="C227" t="n">
-        <v>0.032197734747439</v>
+        <v>0.0308877202885357</v>
       </c>
     </row>
     <row r="228">
@@ -6148,10 +6148,10 @@
         <v>229</v>
       </c>
       <c r="B228" t="n">
-        <v>0.0267529303053471</v>
+        <v>0.0269285644747262</v>
       </c>
       <c r="C228" t="n">
-        <v>0.0301037765774908</v>
+        <v>0.0288664034322523</v>
       </c>
     </row>
     <row r="229">
@@ -6159,10 +6159,10 @@
         <v>230</v>
       </c>
       <c r="B229" t="n">
-        <v>0.0257670532296552</v>
+        <v>0.0261842858928405</v>
       </c>
       <c r="C229" t="n">
-        <v>0.0307846123482823</v>
+        <v>0.0281500188763143</v>
       </c>
     </row>
     <row r="230">
@@ -6170,10 +6170,10 @@
         <v>231</v>
       </c>
       <c r="B230" t="n">
-        <v>0.0274778934612703</v>
+        <v>0.0278621788003619</v>
       </c>
       <c r="C230" t="n">
-        <v>0.0327459131294597</v>
+        <v>0.0303964707445019</v>
       </c>
     </row>
     <row r="231">
@@ -6181,10 +6181,10 @@
         <v>232</v>
       </c>
       <c r="B231" t="n">
-        <v>0.0290491078599042</v>
+        <v>0.0292230097913989</v>
       </c>
       <c r="C231" t="n">
-        <v>0.0323253778127316</v>
+        <v>0.0311171381779105</v>
       </c>
     </row>
     <row r="232">
@@ -6192,10 +6192,10 @@
         <v>233</v>
       </c>
       <c r="B232" t="n">
-        <v>0.0288341585182459</v>
+        <v>0.0292184438573375</v>
       </c>
       <c r="C232" t="n">
-        <v>0.0341721508457477</v>
+        <v>0.0318227084607899</v>
       </c>
     </row>
     <row r="233">
@@ -6203,10 +6203,10 @@
         <v>234</v>
       </c>
       <c r="B233" t="n">
-        <v>0.0281383714630884</v>
+        <v>0.0283508955146625</v>
       </c>
       <c r="C233" t="n">
-        <v>0.0318448441807329</v>
+        <v>0.0304202557561023</v>
       </c>
     </row>
     <row r="234">
@@ -6214,10 +6214,10 @@
         <v>235</v>
       </c>
       <c r="B234" t="n">
-        <v>0.0273635519959171</v>
+        <v>0.0277666527711488</v>
       </c>
       <c r="C234" t="n">
-        <v>0.0330144871255975</v>
+        <v>0.0305504759750218</v>
       </c>
     </row>
     <row r="235">
@@ -6225,10 +6225,10 @@
         <v>236</v>
       </c>
       <c r="B235" t="n">
-        <v>0.0271233182866308</v>
+        <v>0.0275405509498161</v>
       </c>
       <c r="C235" t="n">
-        <v>0.0322108500645703</v>
+        <v>0.0295762565926023</v>
       </c>
     </row>
     <row r="236">
@@ -6236,10 +6236,10 @@
         <v>237</v>
       </c>
       <c r="B236" t="n">
-        <v>0.0261834057890492</v>
+        <v>0.026602370690119</v>
       </c>
       <c r="C236" t="n">
-        <v>0.0314154865456174</v>
+        <v>0.028751759563232</v>
       </c>
     </row>
     <row r="237">
@@ -6247,10 +6247,10 @@
         <v>238</v>
       </c>
       <c r="B237" t="n">
-        <v>0.0286048009155857</v>
+        <v>0.0290079016908174</v>
       </c>
       <c r="C237" t="n">
-        <v>0.0336661797110543</v>
+        <v>0.0312021685604786</v>
       </c>
     </row>
     <row r="238">
@@ -6258,10 +6258,10 @@
         <v>239</v>
       </c>
       <c r="B238" t="n">
-        <v>0.0277637007471517</v>
+        <v>0.0279476921884359</v>
       </c>
       <c r="C238" t="n">
-        <v>0.0312614011447521</v>
+        <v>0.0299513866858488</v>
       </c>
     </row>
     <row r="239">
@@ -6269,10 +6269,10 @@
         <v>240</v>
       </c>
       <c r="B239" t="n">
-        <v>0.0247193014671441</v>
+        <v>0.0253650195372952</v>
       </c>
       <c r="C239" t="n">
-        <v>0.0322659733356883</v>
+        <v>0.027709734037195</v>
       </c>
     </row>
     <row r="240">
@@ -6280,10 +6280,10 @@
         <v>241</v>
       </c>
       <c r="B240" t="n">
-        <v>0.0295360714302682</v>
+        <v>0.029863849144494</v>
       </c>
       <c r="C240" t="n">
-        <v>0.0337587739607738</v>
+        <v>0.0319846722414234</v>
       </c>
     </row>
     <row r="241">
@@ -6291,10 +6291,10 @@
         <v>242</v>
       </c>
       <c r="B241" t="n">
-        <v>0.0276102818569948</v>
+        <v>0.0281813903029112</v>
       </c>
       <c r="C241" t="n">
-        <v>0.0336442462126125</v>
+        <v>0.0304437906561152</v>
       </c>
     </row>
     <row r="242">
@@ -6302,10 +6302,10 @@
         <v>243</v>
       </c>
       <c r="B242" t="n">
-        <v>0.0309215125880095</v>
+        <v>0.0312861801844303</v>
       </c>
       <c r="C242" t="n">
-        <v>0.0354998415640159</v>
+        <v>0.0335385245652735</v>
       </c>
     </row>
     <row r="243">
@@ -6313,10 +6313,10 @@
         <v>244</v>
       </c>
       <c r="B243" t="n">
-        <v>0.026766224568649</v>
+        <v>0.0271851894697187</v>
       </c>
       <c r="C243" t="n">
-        <v>0.0314474747944912</v>
+        <v>0.0287837478121057</v>
       </c>
     </row>
     <row r="244">
@@ -6324,10 +6324,10 @@
         <v>245</v>
       </c>
       <c r="B244" t="n">
-        <v>0.0276306476254083</v>
+        <v>0.027807644893908</v>
       </c>
       <c r="C244" t="n">
-        <v>0.0303525585670327</v>
+        <v>0.0291128422068852</v>
       </c>
     </row>
     <row r="245">
@@ -6335,10 +6335,10 @@
         <v>246</v>
       </c>
       <c r="B245" t="n">
-        <v>0.0257755429943985</v>
+        <v>0.0262249873146928</v>
       </c>
       <c r="C245" t="n">
-        <v>0.0312454871438385</v>
+        <v>0.0284159963482687</v>
       </c>
     </row>
     <row r="246">
@@ -6346,10 +6346,10 @@
         <v>247</v>
       </c>
       <c r="B246" t="n">
-        <v>0.0274933768149289</v>
+        <v>0.027672106321313</v>
       </c>
       <c r="C246" t="n">
-        <v>0.0309330295894823</v>
+        <v>0.0296641797189173</v>
       </c>
     </row>
     <row r="247">
@@ -6357,10 +6357,10 @@
         <v>248</v>
       </c>
       <c r="B247" t="n">
-        <v>0.0286048009155857</v>
+        <v>0.0290079016908174</v>
       </c>
       <c r="C247" t="n">
-        <v>0.0336661797110543</v>
+        <v>0.0312021685604786</v>
       </c>
     </row>
     <row r="248">
@@ -6368,10 +6368,10 @@
         <v>249</v>
       </c>
       <c r="B248" t="n">
-        <v>0.0283857669741807</v>
+        <v>0.0288359242312791</v>
       </c>
       <c r="C248" t="n">
-        <v>0.0343437427807407</v>
+        <v>0.0317065214559261</v>
       </c>
     </row>
     <row r="249">
@@ -6379,10 +6379,10 @@
         <v>250</v>
       </c>
       <c r="B249" t="n">
-        <v>0.0281091953623227</v>
+        <v>0.0282848295317018</v>
       </c>
       <c r="C249" t="n">
-        <v>0.0315300142937787</v>
+        <v>0.0302926411485402</v>
       </c>
     </row>
     <row r="250">
@@ -6390,10 +6390,10 @@
         <v>251</v>
       </c>
       <c r="B250" t="n">
-        <v>0.0283857669741807</v>
+        <v>0.0288359242312791</v>
       </c>
       <c r="C250" t="n">
-        <v>0.0343437427807407</v>
+        <v>0.0317065214559261</v>
       </c>
     </row>
     <row r="251">
@@ -6401,10 +6401,10 @@
         <v>252</v>
       </c>
       <c r="B251" t="n">
-        <v>0.0284332893125104</v>
+        <v>0.0286102865810101</v>
       </c>
       <c r="C251" t="n">
-        <v>0.0317283931084352</v>
+        <v>0.0304886767482876</v>
       </c>
     </row>
     <row r="252">
@@ -6412,10 +6412,10 @@
         <v>253</v>
       </c>
       <c r="B252" t="n">
-        <v>0.0297895543694859</v>
+        <v>0.0299665516379857</v>
       </c>
       <c r="C252" t="n">
-        <v>0.0331546308247231</v>
+        <v>0.0319149144645756</v>
       </c>
     </row>
     <row r="253">
@@ -6423,10 +6423,10 @@
         <v>254</v>
       </c>
       <c r="B253" t="n">
-        <v>0.0288496418719044</v>
+        <v>0.0290283713782886</v>
       </c>
       <c r="C253" t="n">
-        <v>0.0323592673057703</v>
+        <v>0.0310904174352053</v>
       </c>
     </row>
     <row r="254">
@@ -6434,10 +6434,10 @@
         <v>255</v>
       </c>
       <c r="B254" t="n">
-        <v>0.0283857669741807</v>
+        <v>0.0288359242312791</v>
       </c>
       <c r="C254" t="n">
-        <v>0.0343437427807407</v>
+        <v>0.0317065214559261</v>
       </c>
     </row>
     <row r="255">
@@ -6445,10 +6445,10 @@
         <v>256</v>
       </c>
       <c r="B255" t="n">
-        <v>0.0283857669741807</v>
+        <v>0.0288359242312791</v>
       </c>
       <c r="C255" t="n">
-        <v>0.0343437427807407</v>
+        <v>0.0317065214559261</v>
       </c>
     </row>
     <row r="256">
@@ -6456,10 +6456,10 @@
         <v>257</v>
       </c>
       <c r="B256" t="n">
-        <v>0.028995723014736</v>
+        <v>0.0296037213428476</v>
       </c>
       <c r="C256" t="n">
-        <v>0.0353853138158546</v>
+        <v>0.0319976429799652</v>
       </c>
     </row>
     <row r="257">
@@ -6467,10 +6467,10 @@
         <v>258</v>
       </c>
       <c r="B257" t="n">
-        <v>0.0266657170790104</v>
+        <v>0.0270688178542421</v>
       </c>
       <c r="C257" t="n">
-        <v>0.0322079537458926</v>
+        <v>0.0297439425953168</v>
       </c>
     </row>
     <row r="258">
@@ -6478,10 +6478,10 @@
         <v>259</v>
       </c>
       <c r="B258" t="n">
-        <v>0.0276928428029287</v>
+        <v>0.0278667447344233</v>
       </c>
       <c r="C258" t="n">
-        <v>0.0308991400964436</v>
+        <v>0.0296909004616226</v>
       </c>
     </row>
     <row r="259">
@@ -6489,10 +6489,10 @@
         <v>260</v>
       </c>
       <c r="B259" t="n">
-        <v>0.029595533311637</v>
+        <v>0.0296548864015467</v>
       </c>
       <c r="C259" t="n">
-        <v>0.0333850565249528</v>
+        <v>0.0329504928243496</v>
       </c>
     </row>
     <row r="260">
@@ -6500,10 +6500,10 @@
         <v>261</v>
       </c>
       <c r="B260" t="n">
-        <v>0.0286820129421975</v>
+        <v>0.028741378380161</v>
       </c>
       <c r="C260" t="n">
-        <v>0.0323713167425377</v>
+        <v>0.0319365497806826</v>
       </c>
     </row>
     <row r="261">
@@ -6511,10 +6511,10 @@
         <v>262</v>
       </c>
       <c r="B261" t="n">
-        <v>0.0293099937615065</v>
+        <v>0.0296942914486518</v>
       </c>
       <c r="C261" t="n">
-        <v>0.0350480395166241</v>
+        <v>0.0326983938704143</v>
       </c>
     </row>
     <row r="262">
@@ -6522,10 +6522,10 @@
         <v>263</v>
       </c>
       <c r="B262" t="n">
-        <v>0.0279082046834206</v>
+        <v>0.0282989181450926</v>
       </c>
       <c r="C262" t="n">
-        <v>0.0328089630168451</v>
+        <v>0.03041937248133</v>
       </c>
     </row>
     <row r="263">
@@ -6533,10 +6533,10 @@
         <v>264</v>
       </c>
       <c r="B263" t="n">
-        <v>0.0307270098139796</v>
+        <v>0.0307863752519431</v>
       </c>
       <c r="C263" t="n">
-        <v>0.0346679444373788</v>
+        <v>0.0342331774755237</v>
       </c>
     </row>
     <row r="264">
@@ -6544,10 +6544,10 @@
         <v>265</v>
       </c>
       <c r="B264" t="n">
-        <v>0.0286004384711366</v>
+        <v>0.0286597915610464</v>
       </c>
       <c r="C264" t="n">
-        <v>0.0322800403569005</v>
+        <v>0.0318454766562974</v>
       </c>
     </row>
     <row r="265">
@@ -6555,10 +6555,10 @@
         <v>266</v>
       </c>
       <c r="B265" t="n">
-        <v>0.0271834224186635</v>
+        <v>0.0275677077577551</v>
       </c>
       <c r="C265" t="n">
-        <v>0.0326601354361457</v>
+        <v>0.030310693051188</v>
       </c>
     </row>
     <row r="266">
@@ -6566,10 +6566,10 @@
         <v>267</v>
       </c>
       <c r="B266" t="n">
-        <v>0.0262958903994817</v>
+        <v>0.0265426543414446</v>
       </c>
       <c r="C266" t="n">
-        <v>0.030476932201658</v>
+        <v>0.0285511650281317</v>
       </c>
     </row>
     <row r="267">
@@ -6577,10 +6577,10 @@
         <v>268</v>
       </c>
       <c r="B267" t="n">
-        <v>0.0280827331314835</v>
+        <v>0.0281609016575334</v>
       </c>
       <c r="C267" t="n">
-        <v>0.0318278586666474</v>
+        <v>0.0312787262004262</v>
       </c>
     </row>
     <row r="268">
@@ -6588,10 +6588,10 @@
         <v>269</v>
       </c>
       <c r="B268" t="n">
-        <v>0.0272649968897244</v>
+        <v>0.0276492945768697</v>
       </c>
       <c r="C268" t="n">
-        <v>0.0327514118217829</v>
+        <v>0.0304017661755732</v>
       </c>
     </row>
     <row r="269">
@@ -6599,10 +6599,10 @@
         <v>270</v>
       </c>
       <c r="B269" t="n">
-        <v>0.0265941929427568</v>
+        <v>0.0269842461743888</v>
       </c>
       <c r="C269" t="n">
-        <v>0.0320585462913401</v>
+        <v>0.0296720430238329</v>
       </c>
     </row>
     <row r="270">
@@ -6610,10 +6610,10 @@
         <v>271</v>
       </c>
       <c r="B270" t="n">
-        <v>0.0283856590333241</v>
+        <v>0.0285744933669875</v>
       </c>
       <c r="C270" t="n">
-        <v>0.0319547072221239</v>
+        <v>0.030617638010728</v>
       </c>
     </row>
     <row r="271">
@@ -6621,10 +6621,10 @@
         <v>272</v>
       </c>
       <c r="B271" t="n">
-        <v>0.0279332755811036</v>
+        <v>0.028187033695851</v>
       </c>
       <c r="C271" t="n">
-        <v>0.0323221083820643</v>
+        <v>0.0303260431097822</v>
       </c>
     </row>
     <row r="272">
@@ -6632,10 +6632,10 @@
         <v>273</v>
       </c>
       <c r="B272" t="n">
-        <v>0.030023044214946</v>
+        <v>0.0302188727213939</v>
       </c>
       <c r="C272" t="n">
-        <v>0.0337998834025302</v>
+        <v>0.0323925160923785</v>
       </c>
     </row>
     <row r="273">
@@ -6643,10 +6643,10 @@
         <v>274</v>
       </c>
       <c r="B273" t="n">
-        <v>0.0273635519959171</v>
+        <v>0.0277666527711488</v>
       </c>
       <c r="C273" t="n">
-        <v>0.0330144871255975</v>
+        <v>0.0305504759750218</v>
       </c>
     </row>
     <row r="274">
@@ -6654,10 +6654,10 @@
         <v>275</v>
       </c>
       <c r="B274" t="n">
-        <v>0.0306454353429187</v>
+        <v>0.0307047884328285</v>
       </c>
       <c r="C274" t="n">
-        <v>0.0345766680517416</v>
+        <v>0.0341421043511385</v>
       </c>
     </row>
     <row r="275">
@@ -6665,10 +6665,10 @@
         <v>276</v>
       </c>
       <c r="B275" t="n">
-        <v>0.0267472915500713</v>
+        <v>0.0271504046733567</v>
       </c>
       <c r="C275" t="n">
-        <v>0.0322992301315298</v>
+        <v>0.0298350157197021</v>
       </c>
     </row>
     <row r="276">
@@ -6676,10 +6676,10 @@
         <v>277</v>
       </c>
       <c r="B276" t="n">
-        <v>0.0287922884218534</v>
+        <v>0.0291954015451388</v>
       </c>
       <c r="C276" t="n">
-        <v>0.0345958578263709</v>
+        <v>0.0321316434145432</v>
       </c>
     </row>
     <row r="277">
@@ -6687,10 +6687,10 @@
         <v>278</v>
       </c>
       <c r="B277" t="n">
-        <v>0.0278002224593602</v>
+        <v>0.0280469864013231</v>
       </c>
       <c r="C277" t="n">
-        <v>0.031413265804345</v>
+        <v>0.0294874986308186</v>
       </c>
     </row>
     <row r="278">
@@ -6698,10 +6698,10 @@
         <v>279</v>
       </c>
       <c r="B278" t="n">
-        <v>0.0294376076409821</v>
+        <v>0.0296913657557295</v>
       </c>
       <c r="C278" t="n">
-        <v>0.0332584419847513</v>
+        <v>0.0312623767124692</v>
       </c>
     </row>
     <row r="279">
@@ -6709,10 +6709,10 @@
         <v>280</v>
       </c>
       <c r="B279" t="n">
-        <v>0.0302251032305207</v>
+        <v>0.0302978648894531</v>
       </c>
       <c r="C279" t="n">
-        <v>0.0341866110363064</v>
+        <v>0.0336715155164675</v>
       </c>
     </row>
     <row r="280">
@@ -6720,10 +6720,10 @@
         <v>281</v>
       </c>
       <c r="B280" t="n">
-        <v>0.0293099937615065</v>
+        <v>0.0296942914486518</v>
       </c>
       <c r="C280" t="n">
-        <v>0.0350480395166241</v>
+        <v>0.0326983938704143</v>
       </c>
     </row>
     <row r="281">
@@ -6731,10 +6731,10 @@
         <v>282</v>
       </c>
       <c r="B281" t="n">
-        <v>0.0307270098139796</v>
+        <v>0.0307863752519431</v>
       </c>
       <c r="C281" t="n">
-        <v>0.0346679444373788</v>
+        <v>0.0342331774755237</v>
       </c>
     </row>
     <row r="282">
@@ -6742,10 +6742,10 @@
         <v>283</v>
       </c>
       <c r="B282" t="n">
-        <v>0.0296771077826979</v>
+        <v>0.0297364732206614</v>
       </c>
       <c r="C282" t="n">
-        <v>0.03347633291059</v>
+        <v>0.0330415659487348</v>
       </c>
     </row>
     <row r="283">
@@ -6753,10 +6753,10 @@
         <v>284</v>
       </c>
       <c r="B283" t="n">
-        <v>0.0315273762748245</v>
+        <v>0.0317232047812724</v>
       </c>
       <c r="C283" t="n">
-        <v>0.0347362170052171</v>
+        <v>0.0333288496950655</v>
       </c>
     </row>
     <row r="284">
@@ -6764,10 +6764,10 @@
         <v>285</v>
       </c>
       <c r="B284" t="n">
-        <v>0.0279797288196743</v>
+        <v>0.0283834898249459</v>
       </c>
       <c r="C284" t="n">
-        <v>0.0329583704713976</v>
+        <v>0.0304912720528139</v>
       </c>
     </row>
     <row r="285">
@@ -6775,10 +6775,10 @@
         <v>286</v>
       </c>
       <c r="B285" t="n">
-        <v>0.0296771077826979</v>
+        <v>0.0297364732206614</v>
       </c>
       <c r="C285" t="n">
-        <v>0.03347633291059</v>
+        <v>0.0330415659487348</v>
       </c>
     </row>
     <row r="286">
@@ -6786,10 +6786,10 @@
         <v>287</v>
       </c>
       <c r="B286" t="n">
-        <v>0.0266757674138177</v>
+        <v>0.0270658329935034</v>
       </c>
       <c r="C286" t="n">
-        <v>0.0321498226769774</v>
+        <v>0.0297631161482181</v>
       </c>
     </row>
     <row r="287">
@@ -6797,10 +6797,10 @@
         <v>288</v>
       </c>
       <c r="B287" t="n">
-        <v>0.0279897791544815</v>
+        <v>0.0283805049642072</v>
       </c>
       <c r="C287" t="n">
-        <v>0.0329002394024823</v>
+        <v>0.0305104456057152</v>
       </c>
     </row>
     <row r="288">
@@ -6808,10 +6808,10 @@
         <v>289</v>
       </c>
       <c r="B288" t="n">
-        <v>0.0284332893125104</v>
+        <v>0.0286102865810101</v>
       </c>
       <c r="C288" t="n">
-        <v>0.0317283931084352</v>
+        <v>0.0304886767482876</v>
       </c>
     </row>
     <row r="289">
@@ -6819,10 +6819,10 @@
         <v>290</v>
       </c>
       <c r="B289" t="n">
-        <v>0.0297895543694859</v>
+        <v>0.0299665516379857</v>
       </c>
       <c r="C289" t="n">
-        <v>0.0331546308247231</v>
+        <v>0.0319149144645756</v>
       </c>
     </row>
     <row r="290">
@@ -6830,10 +6830,10 @@
         <v>291</v>
       </c>
       <c r="B290" t="n">
-        <v>0.0306926327803047</v>
+        <v>0.0308814671139681</v>
       </c>
       <c r="C290" t="n">
-        <v>0.0342668753662133</v>
+        <v>0.0329298061548174</v>
       </c>
     </row>
     <row r="291">
@@ -6841,10 +6841,10 @@
         <v>292</v>
       </c>
       <c r="B291" t="n">
-        <v>0.0323946270985259</v>
+        <v>0.0324539925364894</v>
       </c>
       <c r="C291" t="n">
-        <v>0.0364951098177051</v>
+        <v>0.03606034285585</v>
       </c>
     </row>
     <row r="292">
@@ -6852,10 +6852,10 @@
         <v>293</v>
       </c>
       <c r="B292" t="n">
-        <v>0.0182412057092252</v>
+        <v>0.0184323625240346</v>
       </c>
       <c r="C292" t="n">
-        <v>0.0210448121019748</v>
+        <v>0.0196069687484853</v>
       </c>
     </row>
     <row r="293">
@@ -6863,10 +6863,10 @@
         <v>294</v>
       </c>
       <c r="B293" t="n">
-        <v>0.022483716987618</v>
+        <v>0.0228089730667921</v>
       </c>
       <c r="C293" t="n">
-        <v>0.0266178155482292</v>
+        <v>0.0243914509929929</v>
       </c>
     </row>
     <row r="294">
@@ -6874,10 +6874,10 @@
         <v>295</v>
       </c>
       <c r="B294" t="n">
-        <v>0.026926258533828</v>
+        <v>0.0274373410859254</v>
       </c>
       <c r="C294" t="n">
-        <v>0.03304256647997</v>
+        <v>0.0298517144526849</v>
       </c>
     </row>
     <row r="295">
@@ -6885,10 +6885,10 @@
         <v>296</v>
       </c>
       <c r="B295" t="n">
-        <v>0.022483716987618</v>
+        <v>0.0228089730667921</v>
       </c>
       <c r="C295" t="n">
-        <v>0.0266178155482292</v>
+        <v>0.0243914509929929</v>
       </c>
     </row>
     <row r="296">
@@ -6896,10 +6896,10 @@
         <v>297</v>
       </c>
       <c r="B296" t="n">
-        <v>0.0226837472554351</v>
+        <v>0.0230607305431679</v>
       </c>
       <c r="C296" t="n">
-        <v>0.0274695630337155</v>
+        <v>0.0250672322081773</v>
       </c>
     </row>
     <row r="297">
@@ -6907,10 +6907,10 @@
         <v>298</v>
       </c>
       <c r="B297" t="n">
-        <v>0.0214532180652486</v>
+        <v>0.021745917183964</v>
       </c>
       <c r="C297" t="n">
-        <v>0.0252667398193603</v>
+        <v>0.0232287558377155</v>
       </c>
     </row>
     <row r="298">
@@ -6918,10 +6918,10 @@
         <v>299</v>
       </c>
       <c r="B298" t="n">
-        <v>0.0214532180652486</v>
+        <v>0.021745917183964</v>
       </c>
       <c r="C298" t="n">
-        <v>0.0252667398193603</v>
+        <v>0.0232287558377155</v>
       </c>
     </row>
     <row r="299">
@@ -6929,10 +6929,10 @@
         <v>300</v>
       </c>
       <c r="B299" t="n">
-        <v>0.0258957596114585</v>
+        <v>0.0263742852030973</v>
       </c>
       <c r="C299" t="n">
-        <v>0.0316914907511011</v>
+        <v>0.0286890192974075</v>
       </c>
     </row>
     <row r="300">
@@ -6940,10 +6940,10 @@
         <v>301</v>
       </c>
       <c r="B300" t="n">
-        <v>0.0192717046315946</v>
+        <v>0.0194954184068627</v>
       </c>
       <c r="C300" t="n">
-        <v>0.0223958878308436</v>
+        <v>0.0207696639037627</v>
       </c>
     </row>
     <row r="301">
@@ -6951,10 +6951,10 @@
         <v>302</v>
       </c>
       <c r="B301" t="n">
-        <v>0.0237142461778046</v>
+        <v>0.024123786425996</v>
       </c>
       <c r="C301" t="n">
-        <v>0.0288206387625844</v>
+        <v>0.0262299273634547</v>
       </c>
     </row>
     <row r="302">
@@ -6962,10 +6962,10 @@
         <v>303</v>
       </c>
       <c r="B302" t="n">
-        <v>0.0182412057092252</v>
+        <v>0.0184323625240346</v>
       </c>
       <c r="C302" t="n">
-        <v>0.0210448121019748</v>
+        <v>0.0196069687484853</v>
       </c>
     </row>
     <row r="303">
@@ -6973,10 +6973,10 @@
         <v>304</v>
       </c>
       <c r="B303" t="n">
-        <v>0.022483716987618</v>
+        <v>0.0228089730667921</v>
       </c>
       <c r="C303" t="n">
-        <v>0.0266178155482292</v>
+        <v>0.0243914509929929</v>
       </c>
     </row>
     <row r="304">
@@ -6984,10 +6984,10 @@
         <v>305</v>
       </c>
       <c r="B304" t="n">
-        <v>0.0219186705386112</v>
+        <v>0.0222781065244775</v>
       </c>
       <c r="C304" t="n">
-        <v>0.0264327923333655</v>
+        <v>0.0241934769594488</v>
       </c>
     </row>
     <row r="305">
@@ -6995,10 +6995,10 @@
         <v>306</v>
       </c>
       <c r="B305" t="n">
-        <v>0.0236463159007244</v>
+        <v>0.0240057518865907</v>
       </c>
       <c r="C305" t="n">
-        <v>0.0272940417405827</v>
+        <v>0.0250547263666661</v>
       </c>
     </row>
     <row r="306">
@@ -7006,10 +7006,10 @@
         <v>307</v>
       </c>
       <c r="B306" t="n">
-        <v>0.0174877202395882</v>
+        <v>0.0176789454737861</v>
       </c>
       <c r="C306" t="n">
-        <v>0.0201393714296918</v>
+        <v>0.0187085144531194</v>
       </c>
     </row>
     <row r="307">
@@ -7017,10 +7017,10 @@
         <v>308</v>
       </c>
       <c r="B307" t="n">
-        <v>0.0233766617865735</v>
+        <v>0.023508127242287</v>
       </c>
       <c r="C307" t="n">
-        <v>0.0276607752409899</v>
+        <v>0.0256842485431101</v>
       </c>
     </row>
     <row r="308">
@@ -7028,10 +7028,10 @@
         <v>309</v>
       </c>
       <c r="B308" t="n">
-        <v>0.0233396375753334</v>
+        <v>0.0234776902133956</v>
       </c>
       <c r="C308" t="n">
-        <v>0.0275775216880105</v>
+        <v>0.0256590694638851</v>
       </c>
     </row>
     <row r="309">
@@ -7039,10 +7039,10 @@
         <v>310</v>
       </c>
       <c r="B309" t="n">
-        <v>0.0175131532036414</v>
+        <v>0.0176801755342356</v>
       </c>
       <c r="C309" t="n">
-        <v>0.020091294954604</v>
+        <v>0.0187583925789818</v>
       </c>
     </row>
     <row r="310">
@@ -7050,10 +7050,10 @@
         <v>311</v>
       </c>
       <c r="B310" t="n">
-        <v>0.0225395045566866</v>
+        <v>0.0228946564194109</v>
       </c>
       <c r="C310" t="n">
-        <v>0.0272051782014927</v>
+        <v>0.0248606748688504</v>
       </c>
     </row>
     <row r="311">
@@ -7061,10 +7061,10 @@
         <v>312</v>
       </c>
       <c r="B311" t="n">
-        <v>0.0219302617857981</v>
+        <v>0.0223073134929194</v>
       </c>
       <c r="C311" t="n">
-        <v>0.0265641223614326</v>
+        <v>0.0241687779128114</v>
       </c>
     </row>
     <row r="312">
@@ -7072,10 +7072,10 @@
         <v>313</v>
       </c>
       <c r="B312" t="n">
-        <v>0.0174761289924013</v>
+        <v>0.0176497385053442</v>
       </c>
       <c r="C312" t="n">
-        <v>0.0200080414016247</v>
+        <v>0.0187332134997568</v>
       </c>
     </row>
     <row r="313">
@@ -7083,10 +7083,10 @@
         <v>314</v>
       </c>
       <c r="B313" t="n">
-        <v>0.0225024803454466</v>
+        <v>0.0228642193905195</v>
       </c>
       <c r="C313" t="n">
-        <v>0.0271219246485133</v>
+        <v>0.0248354957896254</v>
       </c>
     </row>
     <row r="314">
@@ -7094,10 +7094,10 @@
         <v>315</v>
       </c>
       <c r="B314" t="n">
-        <v>0.0239604715934088</v>
+        <v>0.0240942401083289</v>
       </c>
       <c r="C314" t="n">
-        <v>0.0283499075561377</v>
+        <v>0.0263262673732867</v>
       </c>
     </row>
     <row r="315">
@@ -7105,10 +7105,10 @@
         <v>316</v>
       </c>
       <c r="B315" t="n">
-        <v>0.0261727730641909</v>
+        <v>0.026683924035677</v>
       </c>
       <c r="C315" t="n">
-        <v>0.032137125807687</v>
+        <v>0.0289532601573189</v>
       </c>
     </row>
     <row r="316">
@@ -7116,10 +7116,10 @@
         <v>317</v>
       </c>
       <c r="B316" t="n">
-        <v>0.0382217539708401</v>
+        <v>0.0385811899567063</v>
       </c>
       <c r="C316" t="n">
-        <v>0.0272940417405827</v>
+        <v>0.0250547263666661</v>
       </c>
     </row>
     <row r="317">
@@ -7127,10 +7127,10 @@
         <v>318</v>
       </c>
       <c r="B317" t="n">
-        <v>0.0261727730641909</v>
+        <v>0.026683924035677</v>
       </c>
       <c r="C317" t="n">
-        <v>0.032137125807687</v>
+        <v>0.0289532601573189</v>
       </c>
     </row>
     <row r="318">
@@ -7138,10 +7138,10 @@
         <v>319</v>
       </c>
       <c r="B318" t="n">
-        <v>0.0255170486932432</v>
+        <v>0.0259682049270847</v>
       </c>
       <c r="C318" t="n">
-        <v>0.0309514378940882</v>
+        <v>0.0281096944026722</v>
       </c>
     </row>
     <row r="319">
@@ -7149,10 +7149,10 @@
         <v>320</v>
       </c>
       <c r="B319" t="n">
-        <v>0.0249051137566481</v>
+        <v>0.0250511574313888</v>
       </c>
       <c r="C319" t="n">
-        <v>0.0287507690623833</v>
+        <v>0.0266189187038703</v>
       </c>
     </row>
     <row r="320">
@@ -7160,10 +7160,10 @@
         <v>321</v>
       </c>
       <c r="B320" t="n">
-        <v>0.0241970783645939</v>
+        <v>0.0243661060976845</v>
       </c>
       <c r="C320" t="n">
-        <v>0.0288472899724521</v>
+        <v>0.0266591827802088</v>
       </c>
     </row>
     <row r="321">
@@ -7171,10 +7171,10 @@
         <v>322</v>
       </c>
       <c r="B321" t="n">
-        <v>0.0233980481872886</v>
+        <v>0.0235604472709184</v>
       </c>
       <c r="C321" t="n">
-        <v>0.0278089986140086</v>
+        <v>0.0257640063414885</v>
       </c>
     </row>
     <row r="322">
@@ -7182,10 +7182,10 @@
         <v>323</v>
       </c>
       <c r="B322" t="n">
-        <v>0.0255144475196426</v>
+        <v>0.0259376455799565</v>
       </c>
       <c r="C322" t="n">
-        <v>0.0309377939644374</v>
+        <v>0.0280930373477191</v>
       </c>
     </row>
     <row r="323">
@@ -7193,10 +7193,10 @@
         <v>324</v>
       </c>
       <c r="B323" t="n">
-        <v>0.0268844882212235</v>
+        <v>0.0273339122171805</v>
       </c>
       <c r="C323" t="n">
-        <v>0.0318489368763391</v>
+        <v>0.0290363268953406</v>
       </c>
     </row>
     <row r="324">
@@ -7204,10 +7204,10 @@
         <v>325</v>
       </c>
       <c r="B324" t="n">
-        <v>0.0241600541533538</v>
+        <v>0.0243356690687931</v>
       </c>
       <c r="C324" t="n">
-        <v>0.0287640364194728</v>
+        <v>0.0266340037009838</v>
       </c>
     </row>
     <row r="325">
@@ -7215,10 +7215,10 @@
         <v>326</v>
       </c>
       <c r="B325" t="n">
-        <v>0.0233954470136879</v>
+        <v>0.0235298879237902</v>
       </c>
       <c r="C325" t="n">
-        <v>0.0277953546843578</v>
+        <v>0.0257473492865353</v>
       </c>
     </row>
     <row r="326">
@@ -7226,10 +7226,10 @@
         <v>327</v>
       </c>
       <c r="B326" t="n">
-        <v>0.0247154173423373</v>
+        <v>0.0251319867531903</v>
       </c>
       <c r="C326" t="n">
-        <v>0.0298995026059939</v>
+        <v>0.0271978609089987</v>
       </c>
     </row>
     <row r="327">
@@ -7237,10 +7237,10 @@
         <v>328</v>
       </c>
       <c r="B327" t="n">
-        <v>0.0283001898181643</v>
+        <v>0.0289034895968525</v>
       </c>
       <c r="C327" t="n">
-        <v>0.0346064352773712</v>
+        <v>0.0312279632118434</v>
       </c>
     </row>
     <row r="328">
@@ -7248,10 +7248,10 @@
         <v>329</v>
       </c>
       <c r="B328" t="n">
-        <v>0.0228116372068526</v>
+        <v>0.0229437750577482</v>
       </c>
       <c r="C328" t="n">
-        <v>0.02710622236921</v>
+        <v>0.0251053304563588</v>
       </c>
     </row>
     <row r="329">
@@ -7259,10 +7259,10 @@
         <v>330</v>
       </c>
       <c r="B329" t="n">
-        <v>0.0247654877152689</v>
+        <v>0.0249261545610142</v>
       </c>
       <c r="C329" t="n">
-        <v>0.0287064975962595</v>
+        <v>0.0266906388341569</v>
       </c>
     </row>
     <row r="330">
@@ -7270,10 +7270,10 @@
         <v>331</v>
       </c>
       <c r="B330" t="n">
-        <v>0.0274985584672583</v>
+        <v>0.0280672714229581</v>
       </c>
       <c r="C330" t="n">
-        <v>0.0335544999892769</v>
+        <v>0.0303161297181699</v>
       </c>
     </row>
     <row r="331">
@@ -7281,10 +7281,10 @@
         <v>332</v>
       </c>
       <c r="B331" t="n">
-        <v>0.0256017737520391</v>
+        <v>0.025748392366806</v>
       </c>
       <c r="C331" t="n">
-        <v>0.0300756551550251</v>
+        <v>0.0280105659621046</v>
       </c>
     </row>
     <row r="332">
@@ -7292,10 +7292,10 @@
         <v>333</v>
       </c>
       <c r="B332" t="n">
-        <v>0.0292419174497816</v>
+        <v>0.0296911270385818</v>
       </c>
       <c r="C332" t="n">
-        <v>0.0351827122002457</v>
+        <v>0.032063831684672</v>
       </c>
     </row>
     <row r="333">
@@ -7303,10 +7303,10 @@
         <v>334</v>
       </c>
       <c r="B333" t="n">
-        <v>0.0262427425299143</v>
+        <v>0.0263991190277841</v>
       </c>
       <c r="C333" t="n">
-        <v>0.030990880389735</v>
+        <v>0.028745447762811</v>
       </c>
     </row>
     <row r="334">
@@ -7314,10 +7314,10 @@
         <v>335</v>
       </c>
       <c r="B334" t="n">
-        <v>0.0268921079545559</v>
+        <v>0.0273245910186358</v>
       </c>
       <c r="C334" t="n">
-        <v>0.03245390034005</v>
+        <v>0.0295528473615784</v>
       </c>
     </row>
     <row r="335">
@@ -7325,10 +7325,10 @@
         <v>336</v>
       </c>
       <c r="B335" t="n">
-        <v>0.0238929330346886</v>
+        <v>0.0240325830078381</v>
       </c>
       <c r="C335" t="n">
-        <v>0.0282620685295393</v>
+        <v>0.0262344634397174</v>
       </c>
     </row>
     <row r="336">
@@ -7336,10 +7336,10 @@
         <v>337</v>
       </c>
       <c r="B336" t="n">
-        <v>0.0277646626351362</v>
+        <v>0.0282181625718119</v>
       </c>
       <c r="C336" t="n">
-        <v>0.0328983294067702</v>
+        <v>0.030009022756018</v>
       </c>
     </row>
     <row r="337">
@@ -7347,10 +7347,10 @@
         <v>338</v>
       </c>
       <c r="B337" t="n">
-        <v>0.0263946219335552</v>
+        <v>0.0268218959345879</v>
       </c>
       <c r="C337" t="n">
-        <v>0.0319871864948685</v>
+        <v>0.0290657332083964</v>
       </c>
     </row>
     <row r="338">
@@ -7358,10 +7358,10 @@
         <v>339</v>
       </c>
       <c r="B338" t="n">
-        <v>0.0255176196837614</v>
+        <v>0.0256660066885775</v>
       </c>
       <c r="C338" t="n">
-        <v>0.0302157774269819</v>
+        <v>0.0280080180971176</v>
       </c>
     </row>
     <row r="339">
@@ -7369,10 +7369,10 @@
         <v>340</v>
       </c>
       <c r="B339" t="n">
-        <v>0.0249306377128072</v>
+        <v>0.0253515327139145</v>
       </c>
       <c r="C339" t="n">
-        <v>0.0302486616492896</v>
+        <v>0.0274510185175425</v>
       </c>
     </row>
     <row r="340">
@@ -7380,10 +7380,10 @@
         <v>341</v>
       </c>
       <c r="B340" t="n">
-        <v>0.0268844882212235</v>
+        <v>0.0273339122171805</v>
       </c>
       <c r="C340" t="n">
-        <v>0.0318489368763391</v>
+        <v>0.0290363268953406</v>
       </c>
     </row>
     <row r="341">
@@ -7391,10 +7391,10 @@
         <v>342</v>
       </c>
       <c r="B341" t="n">
-        <v>0.0260828568703175</v>
+        <v>0.0264976940432861</v>
       </c>
       <c r="C341" t="n">
-        <v>0.0307970015882449</v>
+        <v>0.0281244934016672</v>
       </c>
     </row>
     <row r="342">
@@ -7402,10 +7402,10 @@
         <v>343</v>
       </c>
       <c r="B342" t="n">
-        <v>0.0239638563643629</v>
+        <v>0.0240899363871199</v>
       </c>
       <c r="C342" t="n">
-        <v>0.0276545623081652</v>
+        <v>0.0257788053404834</v>
       </c>
     </row>
     <row r="343">
@@ -7413,10 +7413,10 @@
         <v>344</v>
       </c>
       <c r="B343" t="n">
-        <v>0.0257452565089136</v>
+        <v>0.0258964239437362</v>
       </c>
       <c r="C343" t="n">
-        <v>0.0305241665445535</v>
+        <v>0.0282583336096289</v>
       </c>
     </row>
     <row r="344">
@@ -7424,10 +7424,10 @@
         <v>345</v>
       </c>
       <c r="B344" t="n">
-        <v>0.0292637999267469</v>
+        <v>0.0297130095155471</v>
       </c>
       <c r="C344" t="n">
-        <v>0.0352068555164735</v>
+        <v>0.0320879750008998</v>
       </c>
     </row>
     <row r="345">
@@ -7435,10 +7435,10 @@
         <v>346</v>
       </c>
       <c r="B345" t="n">
-        <v>0.0290361631015947</v>
+        <v>0.0294825922603885</v>
       </c>
       <c r="C345" t="n">
-        <v>0.0348984663989019</v>
+        <v>0.0318376594883885</v>
       </c>
     </row>
     <row r="346">
@@ -7446,10 +7446,10 @@
         <v>347</v>
       </c>
       <c r="B346" t="n">
-        <v>0.0236230838388401</v>
+        <v>0.0237603051789488</v>
       </c>
       <c r="C346" t="n">
-        <v>0.0281037438019294</v>
+        <v>0.0259976647990467</v>
       </c>
     </row>
     <row r="347">
@@ -7457,10 +7457,10 @@
         <v>348</v>
       </c>
       <c r="B347" t="n">
-        <v>0.026080616889403</v>
+        <v>0.0262317843242255</v>
       </c>
       <c r="C347" t="n">
-        <v>0.0308912765482783</v>
+        <v>0.0286254436133537</v>
       </c>
     </row>
     <row r="348">
@@ -7468,10 +7468,10 @@
         <v>349</v>
       </c>
       <c r="B348" t="n">
-        <v>0.0259782399753447</v>
+        <v>0.0261294074101672</v>
       </c>
       <c r="C348" t="n">
-        <v>0.0307779098809141</v>
+        <v>0.0285120769459895</v>
       </c>
     </row>
     <row r="349">
@@ -7479,10 +7479,10 @@
         <v>350</v>
       </c>
       <c r="B349" t="n">
-        <v>0.0294749009162126</v>
+        <v>0.0299241105050128</v>
       </c>
       <c r="C349" t="n">
-        <v>0.0354364555366062</v>
+        <v>0.0323175750210325</v>
       </c>
     </row>
     <row r="350">
@@ -7490,10 +7490,10 @@
         <v>351</v>
       </c>
       <c r="B350" t="n">
-        <v>0.0299054870782299</v>
+        <v>0.0305208522906905</v>
       </c>
       <c r="C350" t="n">
-        <v>0.0364309307705553</v>
+        <v>0.0329380887382141</v>
       </c>
     </row>
     <row r="351">
@@ -7501,10 +7501,10 @@
         <v>352</v>
       </c>
       <c r="B351" t="n">
-        <v>0.0285278266433165</v>
+        <v>0.0291339068520111</v>
       </c>
       <c r="C351" t="n">
-        <v>0.0349148243949428</v>
+        <v>0.0314782787243547</v>
       </c>
     </row>
     <row r="352">
@@ -7512,10 +7512,10 @@
         <v>353</v>
       </c>
       <c r="B352" t="n">
-        <v>0.0279213761306141</v>
+        <v>0.0283912264476888</v>
       </c>
       <c r="C352" t="n">
-        <v>0.0338142247457158</v>
+        <v>0.0307149963677633</v>
       </c>
     </row>
     <row r="353">
@@ -7523,10 +7523,10 @@
         <v>354</v>
       </c>
       <c r="B353" t="n">
-        <v>0.0260245642098779</v>
+        <v>0.0261757316447004</v>
       </c>
       <c r="C353" t="n">
-        <v>0.0305241665445535</v>
+        <v>0.0282583336096289</v>
       </c>
     </row>
     <row r="354">
@@ -7534,10 +7534,10 @@
         <v>355</v>
       </c>
       <c r="B354" t="n">
-        <v>0.0225964168363826</v>
+        <v>0.022724229097024</v>
       </c>
       <c r="C354" t="n">
-        <v>0.0267570633259143</v>
+        <v>0.024852172847815</v>
       </c>
     </row>
     <row r="355">
@@ -7545,10 +7545,10 @@
         <v>356</v>
       </c>
       <c r="B355" t="n">
-        <v>0.0269043946415805</v>
+        <v>0.0273538186375375</v>
       </c>
       <c r="C355" t="n">
-        <v>0.0318489368763391</v>
+        <v>0.0290363268953406</v>
       </c>
     </row>
     <row r="356">
@@ -7556,10 +7556,10 @@
         <v>357</v>
       </c>
       <c r="B356" t="n">
-        <v>0.0257895836454397</v>
+        <v>0.0259407510802622</v>
       </c>
       <c r="C356" t="n">
-        <v>0.0305241665445535</v>
+        <v>0.0282583336096289</v>
       </c>
     </row>
     <row r="357">
@@ -7567,10 +7567,10 @@
         <v>358</v>
       </c>
       <c r="B357" t="n">
-        <v>0.0253379822555061</v>
+        <v>0.0254868063602531</v>
       </c>
       <c r="C357" t="n">
-        <v>0.0290591581799549</v>
+        <v>0.0268692342163817</v>
       </c>
     </row>
     <row r="358">
@@ -7578,10 +7578,10 @@
         <v>359</v>
       </c>
       <c r="B358" t="n">
-        <v>0.0251042877310385</v>
+        <v>0.0252456972827581</v>
       </c>
       <c r="C358" t="n">
-        <v>0.0296089413098436</v>
+        <v>0.0275234518089225</v>
       </c>
     </row>
     <row r="359">
@@ -7589,10 +7589,10 @@
         <v>360</v>
       </c>
       <c r="B359" t="n">
-        <v>0.0241205698598408</v>
+        <v>0.0242630002629968</v>
       </c>
       <c r="C359" t="n">
-        <v>0.0285704576471109</v>
+        <v>0.0264847789522287</v>
       </c>
     </row>
     <row r="360">
@@ -7600,10 +7600,10 @@
         <v>361</v>
       </c>
       <c r="B360" t="n">
-        <v>0.0249051137566481</v>
+        <v>0.0250511574313888</v>
       </c>
       <c r="C360" t="n">
-        <v>0.0287507690623833</v>
+        <v>0.0266189187038703</v>
       </c>
     </row>
     <row r="361">
@@ -7611,10 +7611,10 @@
         <v>362</v>
       </c>
       <c r="B361" t="n">
-        <v>0.0249051137566481</v>
+        <v>0.0250511574313888</v>
       </c>
       <c r="C361" t="n">
-        <v>0.0287507690623833</v>
+        <v>0.0266189187038703</v>
       </c>
     </row>
     <row r="362">
@@ -7622,10 +7622,10 @@
         <v>363</v>
       </c>
       <c r="B362" t="n">
-        <v>0.0302765322671186</v>
+        <v>0.0307603286789072</v>
       </c>
       <c r="C362" t="n">
-        <v>0.0364883908247005</v>
+        <v>0.033229408514706</v>
       </c>
     </row>
     <row r="363">
@@ -7633,10 +7633,10 @@
         <v>364</v>
       </c>
       <c r="B363" t="n">
-        <v>0.0251327505818004</v>
+        <v>0.0252815746865474</v>
       </c>
       <c r="C363" t="n">
-        <v>0.0290591581799549</v>
+        <v>0.0268692342163817</v>
       </c>
     </row>
     <row r="364">
@@ -7644,10 +7644,10 @@
         <v>365</v>
       </c>
       <c r="B364" t="n">
-        <v>0.0253379822555061</v>
+        <v>0.0254868063602531</v>
       </c>
       <c r="C364" t="n">
-        <v>0.0290591581799549</v>
+        <v>0.0268692342163817</v>
       </c>
     </row>
     <row r="365">
@@ -7655,10 +7655,10 @@
         <v>366</v>
       </c>
       <c r="B365" t="n">
-        <v>0.0276124619209897</v>
+        <v>0.0280618859169467</v>
       </c>
       <c r="C365" t="n">
-        <v>0.0318489368763391</v>
+        <v>0.0290363268953406</v>
       </c>
     </row>
     <row r="366">
@@ -7666,10 +7666,10 @@
         <v>367</v>
       </c>
       <c r="B366" t="n">
-        <v>0.0253379822555061</v>
+        <v>0.0254868063602531</v>
       </c>
       <c r="C366" t="n">
-        <v>0.0290591581799549</v>
+        <v>0.0268692342163817</v>
       </c>
     </row>
     <row r="367">
@@ -7677,10 +7677,10 @@
         <v>368</v>
       </c>
       <c r="B367" t="n">
-        <v>0.0253379822555061</v>
+        <v>0.0254868063602531</v>
       </c>
       <c r="C367" t="n">
-        <v>0.0290591581799549</v>
+        <v>0.0268692342163817</v>
       </c>
     </row>
     <row r="368">
@@ -7688,10 +7688,10 @@
         <v>369</v>
       </c>
       <c r="B368" t="n">
-        <v>0.0252372909381589</v>
+        <v>0.0253979577839042</v>
       </c>
       <c r="C368" t="n">
-        <v>0.0287064975962595</v>
+        <v>0.0266906388341569</v>
       </c>
     </row>
     <row r="369">
@@ -7699,10 +7699,10 @@
         <v>370</v>
       </c>
       <c r="B369" t="n">
-        <v>0.0282364658580262</v>
+        <v>0.0286899657947019</v>
       </c>
       <c r="C369" t="n">
-        <v>0.0328983294067702</v>
+        <v>0.030009022756018</v>
       </c>
     </row>
     <row r="370">
@@ -7710,10 +7710,10 @@
         <v>371</v>
       </c>
       <c r="B370" t="n">
-        <v>0.0249051137566481</v>
+        <v>0.0250511574313888</v>
       </c>
       <c r="C370" t="n">
-        <v>0.0287507690623833</v>
+        <v>0.0266189187038703</v>
       </c>
     </row>
     <row r="371">
@@ -7721,10 +7721,10 @@
         <v>372</v>
       </c>
       <c r="B371" t="n">
-        <v>0.0249051137566481</v>
+        <v>0.0250511574313888</v>
       </c>
       <c r="C371" t="n">
-        <v>0.0287507690623833</v>
+        <v>0.0266189187038703</v>
       </c>
     </row>
     <row r="372">
@@ -7732,10 +7732,10 @@
         <v>373</v>
       </c>
       <c r="B372" t="n">
-        <v>0.0249051137566481</v>
+        <v>0.0250511574313888</v>
       </c>
       <c r="C372" t="n">
-        <v>0.0287507690623833</v>
+        <v>0.0266189187038703</v>
       </c>
     </row>
     <row r="373">
@@ -7743,10 +7743,10 @@
         <v>374</v>
       </c>
       <c r="B373" t="n">
-        <v>0.0257452565089136</v>
+        <v>0.0258964239437362</v>
       </c>
       <c r="C373" t="n">
-        <v>0.0305241665445535</v>
+        <v>0.0282583336096289</v>
       </c>
     </row>
     <row r="374">
@@ -7754,10 +7754,10 @@
         <v>375</v>
       </c>
       <c r="B374" t="n">
-        <v>0.0290142806246294</v>
+        <v>0.0294607097834232</v>
       </c>
       <c r="C374" t="n">
-        <v>0.0348743230826741</v>
+        <v>0.0318135161721607</v>
       </c>
     </row>
     <row r="375">
@@ -7765,10 +7765,10 @@
         <v>376</v>
       </c>
       <c r="B375" t="n">
-        <v>0.0257452565089136</v>
+        <v>0.0258964239437362</v>
       </c>
       <c r="C375" t="n">
-        <v>0.0305241665445535</v>
+        <v>0.0282583336096289</v>
       </c>
     </row>
     <row r="376">
@@ -7776,10 +7776,10 @@
         <v>377</v>
       </c>
       <c r="B376" t="n">
-        <v>0.0292419174497816</v>
+        <v>0.0296911270385818</v>
       </c>
       <c r="C376" t="n">
-        <v>0.0351827122002457</v>
+        <v>0.032063831684672</v>
       </c>
     </row>
     <row r="377">
@@ -7787,10 +7787,10 @@
         <v>378</v>
       </c>
       <c r="B377" t="n">
-        <v>0.0271793222282034</v>
+        <v>0.0276287462241604</v>
       </c>
       <c r="C377" t="n">
-        <v>0.0318489368763391</v>
+        <v>0.0290363268953406</v>
       </c>
     </row>
     <row r="378">
@@ -7798,10 +7798,10 @@
         <v>379</v>
       </c>
       <c r="B378" t="n">
-        <v>0.0257452565089136</v>
+        <v>0.0258964239437362</v>
       </c>
       <c r="C378" t="n">
-        <v>0.0305241665445535</v>
+        <v>0.0282583336096289</v>
       </c>
     </row>
     <row r="379">
@@ -7809,10 +7809,10 @@
         <v>380</v>
       </c>
       <c r="B379" t="n">
-        <v>0.0262427425299143</v>
+        <v>0.0263991190277841</v>
       </c>
       <c r="C379" t="n">
-        <v>0.030990880389735</v>
+        <v>0.028745447762811</v>
       </c>
     </row>
     <row r="380">
@@ -7820,10 +7820,10 @@
         <v>381</v>
       </c>
       <c r="B380" t="n">
-        <v>0.0297189986794793</v>
+        <v>0.0301682082682795</v>
       </c>
       <c r="C380" t="n">
-        <v>0.0351827122002457</v>
+        <v>0.032063831684672</v>
       </c>
     </row>
     <row r="381">
@@ -7831,10 +7831,10 @@
         <v>382</v>
       </c>
       <c r="B381" t="n">
-        <v>0.0249051137566481</v>
+        <v>0.0250511574313888</v>
       </c>
       <c r="C381" t="n">
-        <v>0.0287507690623833</v>
+        <v>0.0266189187038703</v>
       </c>
     </row>
     <row r="382">
@@ -7842,10 +7842,10 @@
         <v>383</v>
       </c>
       <c r="B382" t="n">
-        <v>0.0249051137566481</v>
+        <v>0.0250511574313888</v>
       </c>
       <c r="C382" t="n">
-        <v>0.0287507690623833</v>
+        <v>0.0266189187038703</v>
       </c>
     </row>
     <row r="383">
@@ -7853,10 +7853,10 @@
         <v>384</v>
       </c>
       <c r="B383" t="n">
-        <v>0.0249051137566481</v>
+        <v>0.0250511574313888</v>
       </c>
       <c r="C383" t="n">
-        <v>0.0287507690623833</v>
+        <v>0.0266189187038703</v>
       </c>
     </row>
     <row r="384">
@@ -7864,10 +7864,10 @@
         <v>385</v>
       </c>
       <c r="B384" t="n">
-        <v>0.0257452565089136</v>
+        <v>0.0258964239437362</v>
       </c>
       <c r="C384" t="n">
-        <v>0.0305241665445535</v>
+        <v>0.0282583336096289</v>
       </c>
     </row>
     <row r="385">
@@ -7875,10 +7875,10 @@
         <v>386</v>
       </c>
       <c r="B385" t="n">
-        <v>0.0292419174497816</v>
+        <v>0.0296911270385818</v>
       </c>
       <c r="C385" t="n">
-        <v>0.0351827122002457</v>
+        <v>0.032063831684672</v>
       </c>
     </row>
     <row r="386">
@@ -7886,10 +7886,10 @@
         <v>387</v>
       </c>
       <c r="B386" t="n">
-        <v>0.0292419174497816</v>
+        <v>0.0296911270385818</v>
       </c>
       <c r="C386" t="n">
-        <v>0.0351827122002457</v>
+        <v>0.032063831684672</v>
       </c>
     </row>
     <row r="387">
@@ -7897,10 +7897,10 @@
         <v>388</v>
       </c>
       <c r="B387" t="n">
-        <v>0.0292419174497816</v>
+        <v>0.0296911270385818</v>
       </c>
       <c r="C387" t="n">
-        <v>0.0351827122002457</v>
+        <v>0.032063831684672</v>
       </c>
     </row>
     <row r="388">
@@ -7908,10 +7908,10 @@
         <v>389</v>
       </c>
       <c r="B388" t="n">
-        <v>0.0269244162885754</v>
+        <v>0.0273738402845324</v>
       </c>
       <c r="C388" t="n">
-        <v>0.0318489368763391</v>
+        <v>0.0290363268953406</v>
       </c>
     </row>
     <row r="389">
@@ -7919,10 +7919,10 @@
         <v>390</v>
       </c>
       <c r="B389" t="n">
-        <v>0.0270258699048305</v>
+        <v>0.0274752939007875</v>
       </c>
       <c r="C389" t="n">
-        <v>0.0318489368763391</v>
+        <v>0.0290363268953406</v>
       </c>
     </row>
     <row r="390">
@@ -7930,10 +7930,10 @@
         <v>391</v>
       </c>
       <c r="B390" t="n">
-        <v>0.0262242385539245</v>
+        <v>0.0266390757268931</v>
       </c>
       <c r="C390" t="n">
-        <v>0.0307970015882449</v>
+        <v>0.0281244934016672</v>
       </c>
     </row>
     <row r="391">
@@ -7941,10 +7941,10 @@
         <v>392</v>
       </c>
       <c r="B391" t="n">
-        <v>0.0257452565089136</v>
+        <v>0.0258964239437362</v>
       </c>
       <c r="C391" t="n">
-        <v>0.0305241665445535</v>
+        <v>0.0282583336096289</v>
       </c>
     </row>
     <row r="392">
@@ -7952,10 +7952,10 @@
         <v>393</v>
       </c>
       <c r="B392" t="n">
-        <v>0.0257452565089136</v>
+        <v>0.0258964239437362</v>
       </c>
       <c r="C392" t="n">
-        <v>0.0305241665445535</v>
+        <v>0.0282583336096289</v>
       </c>
     </row>
     <row r="393">
@@ -7963,10 +7963,10 @@
         <v>394</v>
       </c>
       <c r="B393" t="n">
-        <v>0.0256017737520391</v>
+        <v>0.025748392366806</v>
       </c>
       <c r="C393" t="n">
-        <v>0.0300756551550251</v>
+        <v>0.0280105659621046</v>
       </c>
     </row>
     <row r="394">
@@ -7974,10 +7974,10 @@
         <v>395</v>
       </c>
       <c r="B394" t="n">
-        <v>0.0271321665453516</v>
+        <v>0.0275815905413085</v>
       </c>
       <c r="C394" t="n">
-        <v>0.032105649811106</v>
+        <v>0.0292930398301075</v>
       </c>
     </row>
     <row r="395">
@@ -7985,10 +7985,10 @@
         <v>396</v>
       </c>
       <c r="B395" t="n">
-        <v>0.0236230838388401</v>
+        <v>0.0237603051789488</v>
       </c>
       <c r="C395" t="n">
-        <v>0.0281037438019294</v>
+        <v>0.0259976647990467</v>
       </c>
     </row>
     <row r="396">
@@ -7996,10 +7996,10 @@
         <v>397</v>
       </c>
       <c r="B396" t="n">
-        <v>0.0249051137566481</v>
+        <v>0.0250511574313888</v>
       </c>
       <c r="C396" t="n">
-        <v>0.0287507690623833</v>
+        <v>0.0266189187038703</v>
       </c>
     </row>
     <row r="397">
@@ -8007,10 +8007,10 @@
         <v>398</v>
       </c>
       <c r="B397" t="n">
-        <v>0.0257786815719539</v>
+        <v>0.0262378994564971</v>
       </c>
       <c r="C397" t="n">
-        <v>0.0312500845026209</v>
+        <v>0.0283880406962195</v>
       </c>
     </row>
     <row r="398">
@@ -8018,10 +8018,10 @@
         <v>399</v>
       </c>
       <c r="B398" t="n">
-        <v>0.028561822696875</v>
+        <v>0.029173184126265</v>
       </c>
       <c r="C398" t="n">
-        <v>0.0349050818859039</v>
+        <v>0.0315063095053907</v>
       </c>
     </row>
     <row r="399">
@@ -8029,10 +8029,10 @@
         <v>400</v>
       </c>
       <c r="B399" t="n">
-        <v>0.0271558595506528</v>
+        <v>0.0274080552360013</v>
       </c>
       <c r="C399" t="n">
-        <v>0.0305190990021528</v>
+        <v>0.0289941545023312</v>
       </c>
     </row>
     <row r="400">
@@ -8040,10 +8040,10 @@
         <v>401</v>
       </c>
       <c r="B400" t="n">
-        <v>0.0234283896205137</v>
+        <v>0.0236545737773759</v>
       </c>
       <c r="C400" t="n">
-        <v>0.0262741807663446</v>
+        <v>0.0250233601653782</v>
       </c>
     </row>
     <row r="401">
@@ -8051,10 +8051,10 @@
         <v>402</v>
       </c>
       <c r="B401" t="n">
-        <v>0.0265148907727777</v>
+        <v>0.0267573285750232</v>
       </c>
       <c r="C401" t="n">
-        <v>0.0296038737674429</v>
+        <v>0.0282592727016248</v>
       </c>
     </row>
     <row r="402">
@@ -8062,10 +8062,10 @@
         <v>403</v>
       </c>
       <c r="B402" t="n">
-        <v>0.0252400317954482</v>
+        <v>0.0254853159463103</v>
       </c>
       <c r="C402" t="n">
-        <v>0.0293033941943355</v>
+        <v>0.0273935802286779</v>
       </c>
     </row>
     <row r="403">
@@ -8073,10 +8073,10 @@
         <v>404</v>
       </c>
       <c r="B403" t="n">
-        <v>0.0289933051145475</v>
+        <v>0.0292602761608826</v>
       </c>
       <c r="C403" t="n">
-        <v>0.0329024907387744</v>
+        <v>0.0308526807631352</v>
       </c>
     </row>
     <row r="404">
@@ -8084,10 +8084,10 @@
         <v>405</v>
       </c>
       <c r="B404" t="n">
-        <v>0.0302658414547135</v>
+        <v>0.0308772028841034</v>
       </c>
       <c r="C404" t="n">
-        <v>0.0349050818859039</v>
+        <v>0.0315063095053907</v>
       </c>
     </row>
     <row r="405">
@@ -8095,10 +8095,10 @@
         <v>406</v>
       </c>
       <c r="B405" t="n">
-        <v>0.0267443638553268</v>
+        <v>0.0269896480061889</v>
       </c>
       <c r="C405" t="n">
-        <v>0.0302397277970224</v>
+        <v>0.0283299138313649</v>
       </c>
     </row>
     <row r="406">
@@ -8106,10 +8106,10 @@
         <v>407</v>
       </c>
       <c r="B406" t="n">
-        <v>0.0243932404142126</v>
+        <v>0.0248155684165608</v>
       </c>
       <c r="C406" t="n">
-        <v>0.0295090168993788</v>
+        <v>0.0268341883723695</v>
       </c>
     </row>
     <row r="407">
@@ -8117,10 +8117,10 @@
         <v>408</v>
       </c>
       <c r="B407" t="n">
-        <v>0.0246635643464355</v>
+        <v>0.0250911542836837</v>
       </c>
       <c r="C407" t="n">
-        <v>0.0298373884546485</v>
+        <v>0.0271213953393009</v>
       </c>
     </row>
     <row r="408">
@@ -8128,10 +8128,10 @@
         <v>409</v>
       </c>
       <c r="B408" t="n">
-        <v>0.0264937281723146</v>
+        <v>0.0265420823242493</v>
       </c>
       <c r="C408" t="n">
-        <v>0.0277508989113118</v>
+        <v>0.0274146035128353</v>
       </c>
     </row>
     <row r="409">
@@ -8139,10 +8139,10 @@
         <v>410</v>
       </c>
       <c r="B409" t="n">
-        <v>0.0269360471905832</v>
+        <v>0.0271379782920107</v>
       </c>
       <c r="C409" t="n">
-        <v>0.0297104638481567</v>
+        <v>0.0285884760760409</v>
       </c>
     </row>
     <row r="410">
@@ -8150,10 +8150,10 @@
         <v>411</v>
       </c>
       <c r="B410" t="n">
-        <v>0.0295661895957415</v>
+        <v>0.0300370499441263</v>
       </c>
       <c r="C410" t="n">
-        <v>0.0353665991066698</v>
+        <v>0.0323179473623722</v>
       </c>
     </row>
     <row r="411">
@@ -8161,10 +8161,10 @@
         <v>412</v>
       </c>
       <c r="B411" t="n">
-        <v>0.0271461210999342</v>
+        <v>0.027603606746593</v>
       </c>
       <c r="C411" t="n">
-        <v>0.0321475834848719</v>
+        <v>0.0293146731888879</v>
       </c>
     </row>
     <row r="412">
@@ -8172,10 +8172,10 @@
         <v>413</v>
       </c>
       <c r="B412" t="n">
-        <v>0.0260871412274083</v>
+        <v>0.0263202940258878</v>
       </c>
       <c r="C412" t="n">
-        <v>0.0290879300027765</v>
+        <v>0.0277996252987116</v>
       </c>
     </row>
     <row r="413">
@@ -8183,10 +8183,10 @@
         <v>414</v>
       </c>
       <c r="B413" t="n">
-        <v>0.0274168706716357</v>
+        <v>0.0276379987110777</v>
       </c>
       <c r="C413" t="n">
-        <v>0.0296345191032792</v>
+        <v>0.0283763059881802</v>
       </c>
     </row>
     <row r="414">
@@ -8194,10 +8194,10 @@
         <v>415</v>
       </c>
       <c r="B414" t="n">
-        <v>0.0281283746454935</v>
+        <v>0.0283545588023557</v>
       </c>
       <c r="C414" t="n">
-        <v>0.0311639346120146</v>
+        <v>0.0299131140110483</v>
       </c>
     </row>
     <row r="415">
@@ -8205,10 +8205,10 @@
         <v>416</v>
       </c>
       <c r="B415" t="n">
-        <v>0.0272163801005158</v>
+        <v>0.0276705139241803</v>
       </c>
       <c r="C415" t="n">
-        <v>0.0326377872464741</v>
+        <v>0.0298069630392786</v>
       </c>
     </row>
     <row r="416">
@@ -8216,10 +8216,10 @@
         <v>417</v>
       </c>
       <c r="B416" t="n">
-        <v>0.0227168856466559</v>
+        <v>0.0229380136860979</v>
       </c>
       <c r="C416" t="n">
-        <v>0.0247447652576091</v>
+        <v>0.0234865521425101</v>
       </c>
     </row>
     <row r="417">
@@ -8227,10 +8227,10 @@
         <v>418</v>
       </c>
       <c r="B417" t="n">
-        <v>0.0248060500554271</v>
+        <v>0.0250415192160553</v>
       </c>
       <c r="C417" t="n">
-        <v>0.0277902871419571</v>
+        <v>0.0264831701792376</v>
       </c>
     </row>
     <row r="418">
@@ -8238,10 +8238,10 @@
         <v>419</v>
       </c>
       <c r="B418" t="n">
-        <v>0.0236308947362601</v>
+        <v>0.023849105014238</v>
       </c>
       <c r="C418" t="n">
-        <v>0.026505994725744</v>
+        <v>0.0252574124931193</v>
       </c>
     </row>
     <row r="419">
@@ -8249,10 +8249,10 @@
         <v>420</v>
       </c>
       <c r="B419" t="n">
-        <v>0.0240945460815693</v>
+        <v>0.0243249591247773</v>
       </c>
       <c r="C419" t="n">
-        <v>0.0262608716332216</v>
+        <v>0.0249463621563695</v>
       </c>
     </row>
     <row r="420">
@@ -8260,10 +8260,10 @@
         <v>421</v>
       </c>
       <c r="B420" t="n">
-        <v>0.0260490055041768</v>
+        <v>0.02651348532362</v>
       </c>
       <c r="C420" t="n">
-        <v>0.0315784560578906</v>
+        <v>0.028675247663151</v>
       </c>
     </row>
     <row r="421">
@@ -8271,10 +8271,10 @@
         <v>422</v>
       </c>
       <c r="B421" t="n">
-        <v>0.0243783005100577</v>
+        <v>0.0246044846669199</v>
       </c>
       <c r="C421" t="n">
-        <v>0.0272743433772907</v>
+        <v>0.0260235227763244</v>
       </c>
     </row>
     <row r="422">
@@ -8282,10 +8282,10 @@
         <v>423</v>
       </c>
       <c r="B422" t="n">
-        <v>0.0274993752632426</v>
+        <v>0.0277564964792683</v>
       </c>
       <c r="C422" t="n">
-        <v>0.0318418764521136</v>
+        <v>0.0298347096352077</v>
       </c>
     </row>
     <row r="423">
@@ -8293,10 +8293,10 @@
         <v>424</v>
       </c>
       <c r="B423" t="n">
-        <v>0.0269229078142298</v>
+        <v>0.0273623348166417</v>
       </c>
       <c r="C423" t="n">
-        <v>0.0323758707124266</v>
+        <v>0.0295625247458307</v>
       </c>
     </row>
     <row r="424">
@@ -8304,10 +8304,10 @@
         <v>425</v>
       </c>
       <c r="B424" t="n">
-        <v>0.025770900849126</v>
+        <v>0.0262025138552402</v>
       </c>
       <c r="C424" t="n">
-        <v>0.0310251232749913</v>
+        <v>0.0282939983862288</v>
       </c>
     </row>
     <row r="425">
@@ -8315,10 +8315,10 @@
         <v>426</v>
       </c>
       <c r="B425" t="n">
-        <v>0.0292785146769408</v>
+        <v>0.0297609636599639</v>
       </c>
       <c r="C425" t="n">
-        <v>0.0351866136208575</v>
+        <v>0.0321085195206611</v>
       </c>
     </row>
     <row r="426">
@@ -8326,10 +8326,10 @@
         <v>427</v>
       </c>
       <c r="B426" t="n">
-        <v>0.0287894595220272</v>
+        <v>0.0294036013814236</v>
       </c>
       <c r="C426" t="n">
-        <v>0.0352134710034755</v>
+        <v>0.031756625017902</v>
       </c>
     </row>
     <row r="427">
@@ -8337,10 +8337,10 @@
         <v>428</v>
       </c>
       <c r="B427" t="n">
-        <v>0.0307239939283306</v>
+        <v>0.031228963728904</v>
       </c>
       <c r="C427" t="n">
-        <v>0.0367992775923403</v>
+        <v>0.0336214841737109</v>
       </c>
     </row>
     <row r="428">
@@ -8348,10 +8348,10 @@
         <v>429</v>
       </c>
       <c r="B428" t="n">
-        <v>0.0271763815391337</v>
+        <v>0.0277508530863286</v>
       </c>
       <c r="C428" t="n">
-        <v>0.0331640142826618</v>
+        <v>0.0299524571815406</v>
       </c>
     </row>
     <row r="429">
@@ -8359,10 +8359,10 @@
         <v>430</v>
       </c>
       <c r="B429" t="n">
-        <v>0.0285561241908629</v>
+        <v>0.0287915933514911</v>
       </c>
       <c r="C429" t="n">
-        <v>0.031679878376681</v>
+        <v>0.0303727614139616</v>
       </c>
     </row>
     <row r="430">
@@ -8370,10 +8370,10 @@
         <v>431</v>
       </c>
       <c r="B430" t="n">
-        <v>0.0267469541300278</v>
+        <v>0.0269806616367177</v>
       </c>
       <c r="C430" t="n">
-        <v>0.0294182379065619</v>
+        <v>0.0280544793003822</v>
       </c>
     </row>
     <row r="431">
@@ -8381,10 +8381,10 @@
         <v>432</v>
       </c>
       <c r="B431" t="n">
-        <v>0.0269282227255006</v>
+        <v>0.0271776379808427</v>
       </c>
       <c r="C431" t="n">
-        <v>0.0302107098845812</v>
+        <v>0.0287438389898198</v>
       </c>
     </row>
     <row r="432">
@@ -8392,10 +8392,10 @@
         <v>433</v>
       </c>
       <c r="B432" t="n">
-        <v>0.0281207103443517</v>
+        <v>0.0285690498751862</v>
       </c>
       <c r="C432" t="n">
-        <v>0.033753935135187</v>
+        <v>0.0308049827093224</v>
       </c>
     </row>
     <row r="433">
@@ -8403,10 +8403,10 @@
         <v>434</v>
       </c>
       <c r="B433" t="n">
-        <v>0.0283136638832419</v>
+        <v>0.028599969020779</v>
       </c>
       <c r="C433" t="n">
-        <v>0.0319517774878233</v>
+        <v>0.0302976913136699</v>
       </c>
     </row>
     <row r="434">
@@ -8414,10 +8414,10 @@
         <v>435</v>
       </c>
       <c r="B434" t="n">
-        <v>0.0254827434741108</v>
+        <v>0.0257096379119025</v>
       </c>
       <c r="C434" t="n">
-        <v>0.0285980459130984</v>
+        <v>0.0272308743367701</v>
       </c>
     </row>
     <row r="435">
@@ -8425,10 +8425,10 @@
         <v>436</v>
       </c>
       <c r="B435" t="n">
-        <v>0.0278930735191995</v>
+        <v>0.0283386326200276</v>
       </c>
       <c r="C435" t="n">
-        <v>0.0334455460176154</v>
+        <v>0.0305546671968111</v>
       </c>
     </row>
     <row r="436">
@@ -8436,10 +8436,10 @@
         <v>437</v>
       </c>
       <c r="B436" t="n">
-        <v>0.0291572841751165</v>
+        <v>0.0296096563448427</v>
       </c>
       <c r="C436" t="n">
-        <v>0.0342657380110789</v>
+        <v>0.0313782721604232</v>
       </c>
     </row>
     <row r="437">
@@ -8447,10 +8447,10 @@
         <v>438</v>
       </c>
       <c r="B437" t="n">
-        <v>0.0271763815391337</v>
+        <v>0.0277508530863286</v>
       </c>
       <c r="C437" t="n">
-        <v>0.0331640142826618</v>
+        <v>0.0299524571815406</v>
       </c>
     </row>
     <row r="438">
@@ -8458,10 +8458,10 @@
         <v>439</v>
       </c>
       <c r="B438" t="n">
-        <v>0.029435725006928</v>
+        <v>0.0300220336192866</v>
       </c>
       <c r="C438" t="n">
-        <v>0.0357024965404399</v>
+        <v>0.0323935865880704</v>
       </c>
     </row>
     <row r="439">
@@ -8469,10 +8469,10 @@
         <v>440</v>
       </c>
       <c r="B439" t="n">
-        <v>0.0253397354536107</v>
+        <v>0.0255649143732059</v>
       </c>
       <c r="C439" t="n">
-        <v>0.0283195813512299</v>
+        <v>0.0270335150155065</v>
       </c>
     </row>
     <row r="440">
@@ -8480,10 +8480,10 @@
         <v>441</v>
       </c>
       <c r="B440" t="n">
-        <v>0.027337458901788</v>
+        <v>0.0277863692539446</v>
       </c>
       <c r="C440" t="n">
-        <v>0.0329262628251983</v>
+        <v>0.0299593304247799</v>
       </c>
     </row>
     <row r="441">
@@ -8491,10 +8491,10 @@
         <v>442</v>
       </c>
       <c r="B441" t="n">
-        <v>0.0301499994025769</v>
+        <v>0.0306231628101683</v>
       </c>
       <c r="C441" t="n">
-        <v>0.0360557314218176</v>
+        <v>0.0329599661925488</v>
       </c>
     </row>
     <row r="442">
@@ -8502,10 +8502,10 @@
         <v>443</v>
       </c>
       <c r="B442" t="n">
-        <v>0.0277396693574881</v>
+        <v>0.0279941681020433</v>
       </c>
       <c r="C442" t="n">
-        <v>0.0312082313173007</v>
+        <v>0.0296361733325078</v>
       </c>
     </row>
     <row r="443">
@@ -8513,10 +8513,10 @@
         <v>444</v>
       </c>
       <c r="B443" t="n">
-        <v>0.0299356437451992</v>
+        <v>0.030406504093584</v>
       </c>
       <c r="C443" t="n">
-        <v>0.0353665991066698</v>
+        <v>0.0323179473623722</v>
       </c>
     </row>
     <row r="444">
@@ -8524,10 +8524,10 @@
         <v>445</v>
       </c>
       <c r="B444" t="n">
-        <v>0.0275253137001105</v>
+        <v>0.027777509385459</v>
       </c>
       <c r="C444" t="n">
-        <v>0.0305190990021528</v>
+        <v>0.0289941545023312</v>
       </c>
     </row>
     <row r="445">
@@ -8535,10 +8535,10 @@
         <v>446</v>
       </c>
       <c r="B445" t="n">
-        <v>0.0274645953094703</v>
+        <v>0.0277167910085558</v>
       </c>
       <c r="C445" t="n">
-        <v>0.0308587090055035</v>
+        <v>0.0293337622575545</v>
       </c>
     </row>
     <row r="446">
@@ -8546,10 +8546,10 @@
         <v>447</v>
       </c>
       <c r="B446" t="n">
-        <v>0.0272474212989278</v>
+        <v>0.0274996169842763</v>
       </c>
       <c r="C446" t="n">
-        <v>0.0305190990021528</v>
+        <v>0.0289941545023312</v>
       </c>
     </row>
     <row r="447">
@@ -8557,10 +8557,10 @@
         <v>448</v>
       </c>
       <c r="B447" t="n">
-        <v>0.0276633543238115</v>
+        <v>0.0281058766632285</v>
       </c>
       <c r="C447" t="n">
-        <v>0.0332051237244182</v>
+        <v>0.0303603010324957</v>
       </c>
     </row>
     <row r="448">
@@ -8568,10 +8568,10 @@
         <v>449</v>
       </c>
       <c r="B448" t="n">
-        <v>0.0295035503284923</v>
+        <v>0.0299608215679943</v>
       </c>
       <c r="C448" t="n">
-        <v>0.0354813588087784</v>
+        <v>0.0323421779782193</v>
       </c>
     </row>
     <row r="449">
@@ -8579,10 +8579,10 @@
         <v>450</v>
       </c>
       <c r="B449" t="n">
-        <v>0.0305194535520345</v>
+        <v>0.030992616959626</v>
       </c>
       <c r="C449" t="n">
-        <v>0.0360557314218176</v>
+        <v>0.0329599661925488</v>
       </c>
     </row>
     <row r="450">
@@ -8590,10 +8590,10 @@
         <v>451</v>
       </c>
       <c r="B450" t="n">
-        <v>0.0271704691164564</v>
+        <v>0.0274226648018049</v>
       </c>
       <c r="C450" t="n">
-        <v>0.0305351322691118</v>
+        <v>0.0290101877692902</v>
       </c>
     </row>
     <row r="451">
@@ -8601,10 +8601,10 @@
         <v>452</v>
       </c>
       <c r="B451" t="n">
-        <v>0.0273873836389978</v>
+        <v>0.0276395793243463</v>
       </c>
       <c r="C451" t="n">
-        <v>0.0305190990021528</v>
+        <v>0.0289941545023312</v>
       </c>
     </row>
     <row r="452">
@@ -8612,10 +8612,10 @@
         <v>453</v>
       </c>
       <c r="B452" t="n">
-        <v>0.0274993752632426</v>
+        <v>0.0277564964792683</v>
       </c>
       <c r="C452" t="n">
-        <v>0.0318418764521136</v>
+        <v>0.0298347096352077</v>
       </c>
     </row>
     <row r="453">
@@ -8623,10 +8623,10 @@
         <v>454</v>
       </c>
       <c r="B453" t="n">
-        <v>0.0252400317954482</v>
+        <v>0.0254853159463103</v>
       </c>
       <c r="C453" t="n">
-        <v>0.0293033941943355</v>
+        <v>0.0273935802286779</v>
       </c>
     </row>
     <row r="454">
@@ -8634,10 +8634,10 @@
         <v>455</v>
       </c>
       <c r="B454" t="n">
-        <v>0.0293385527705893</v>
+        <v>0.0298066326889677</v>
       </c>
       <c r="C454" t="n">
-        <v>0.0350582099890982</v>
+        <v>0.0320676318498609</v>
       </c>
     </row>
     <row r="455">
@@ -8645,10 +8645,10 @@
         <v>456</v>
       </c>
       <c r="B455" t="n">
-        <v>0.0304227409192166</v>
+        <v>0.0308853990201084</v>
       </c>
       <c r="C455" t="n">
-        <v>0.0363123998306633</v>
+        <v>0.0332830035702723</v>
       </c>
     </row>
     <row r="456">
@@ -8656,10 +8656,10 @@
         <v>457</v>
       </c>
       <c r="B456" t="n">
-        <v>0.0276854210644733</v>
+        <v>0.0279676299376059</v>
       </c>
       <c r="C456" t="n">
-        <v>0.03059196903186</v>
+        <v>0.0290549936310151</v>
       </c>
     </row>
     <row r="457">
@@ -8667,10 +8667,10 @@
         <v>458</v>
       </c>
       <c r="B457" t="n">
-        <v>0.0280124108741279</v>
+        <v>0.0282564043119834</v>
       </c>
       <c r="C457" t="n">
-        <v>0.0314648997261463</v>
+        <v>0.0299592107102312</v>
       </c>
     </row>
     <row r="458">
@@ -8678,10 +8678,10 @@
         <v>459</v>
       </c>
       <c r="B458" t="n">
-        <v>0.0296305190398791</v>
+        <v>0.0299036797529752</v>
       </c>
       <c r="C458" t="n">
-        <v>0.0335893441023953</v>
+        <v>0.0315147144903294</v>
       </c>
     </row>
     <row r="459">
@@ -8689,10 +8689,10 @@
         <v>460</v>
       </c>
       <c r="B459" t="n">
-        <v>0.0297944981004481</v>
+        <v>0.0302530599369353</v>
       </c>
       <c r="C459" t="n">
-        <v>0.0349525913746999</v>
+        <v>0.0320403058876175</v>
       </c>
     </row>
     <row r="460">
@@ -8700,10 +8700,10 @@
         <v>461</v>
       </c>
       <c r="B460" t="n">
-        <v>0.0273841680553594</v>
+        <v>0.0276240652288103</v>
       </c>
       <c r="C460" t="n">
-        <v>0.0301050912701829</v>
+        <v>0.0287165130275765</v>
       </c>
     </row>
     <row r="461">
@@ -8711,10 +8711,10 @@
         <v>462</v>
       </c>
       <c r="B461" t="n">
-        <v>0.0296305190398791</v>
+        <v>0.0299036797529752</v>
       </c>
       <c r="C461" t="n">
-        <v>0.0335893441023953</v>
+        <v>0.0315147144903294</v>
       </c>
     </row>
     <row r="462">
@@ -8722,10 +8722,10 @@
         <v>463</v>
       </c>
       <c r="B462" t="n">
-        <v>0.0297944981004481</v>
+        <v>0.0302530599369353</v>
       </c>
       <c r="C462" t="n">
-        <v>0.0349525913746999</v>
+        <v>0.0320403058876175</v>
       </c>
     </row>
     <row r="463">
@@ -8733,10 +8733,10 @@
         <v>464</v>
       </c>
       <c r="B463" t="n">
-        <v>0.0271563420068673</v>
+        <v>0.0276248448951765</v>
       </c>
       <c r="C463" t="n">
-        <v>0.0327661908782334</v>
+        <v>0.0298478507100789</v>
       </c>
     </row>
     <row r="464">
@@ -8744,10 +8744,10 @@
         <v>465</v>
       </c>
       <c r="B464" t="n">
-        <v>0.0261514926517863</v>
+        <v>0.0265441894181399</v>
       </c>
       <c r="C464" t="n">
-        <v>0.0300575817813869</v>
+        <v>0.0281825166453497</v>
       </c>
     </row>
     <row r="465">
@@ -8755,10 +8755,10 @@
         <v>466</v>
       </c>
       <c r="B465" t="n">
-        <v>0.0271558595506528</v>
+        <v>0.0274080552360013</v>
       </c>
       <c r="C465" t="n">
-        <v>0.0305190990021528</v>
+        <v>0.0289941545023312</v>
       </c>
     </row>
     <row r="466">
@@ -8766,10 +8766,10 @@
         <v>467</v>
       </c>
       <c r="B466" t="n">
-        <v>0.028561822696875</v>
+        <v>0.029173184126265</v>
       </c>
       <c r="C466" t="n">
-        <v>0.0349050818859039</v>
+        <v>0.0315063095053907</v>
       </c>
     </row>
     <row r="467">
@@ -8777,10 +8777,10 @@
         <v>468</v>
       </c>
       <c r="B467" t="n">
-        <v>0.0231859730551474</v>
+        <v>0.0233879041565748</v>
       </c>
       <c r="C467" t="n">
-        <v>0.0258208726134327</v>
+        <v>0.0246988848413169</v>
       </c>
     </row>
     <row r="468">
@@ -8788,10 +8788,10 @@
         <v>469</v>
       </c>
       <c r="B468" t="n">
-        <v>0.0269282227255006</v>
+        <v>0.0271776379808427</v>
       </c>
       <c r="C468" t="n">
-        <v>0.0302107098845812</v>
+        <v>0.0287438389898198</v>
       </c>
     </row>
     <row r="469">
@@ -8799,10 +8799,10 @@
         <v>470</v>
       </c>
       <c r="B469" t="n">
-        <v>0.0271558595506528</v>
+        <v>0.0274080552360013</v>
       </c>
       <c r="C469" t="n">
-        <v>0.0305190990021528</v>
+        <v>0.0289941545023312</v>
       </c>
     </row>
     <row r="470">
@@ -8810,10 +8810,10 @@
         <v>471</v>
       </c>
       <c r="B470" t="n">
-        <v>0.028561822696875</v>
+        <v>0.029173184126265</v>
       </c>
       <c r="C470" t="n">
-        <v>0.0349050818859039</v>
+        <v>0.0315063095053907</v>
       </c>
     </row>
     <row r="471">
@@ -8821,10 +8821,10 @@
         <v>472</v>
       </c>
       <c r="B471" t="n">
-        <v>0.0227436540368788</v>
+        <v>0.0227920081888135</v>
       </c>
       <c r="C471" t="n">
-        <v>0.0238613076765878</v>
+        <v>0.0235250122781113</v>
       </c>
     </row>
     <row r="472">
@@ -8832,10 +8832,10 @@
         <v>473</v>
       </c>
       <c r="B472" t="n">
-        <v>0.0284168376655348</v>
+        <v>0.0288661144982559</v>
       </c>
       <c r="C472" t="n">
-        <v>0.0334364849990874</v>
+        <v>0.0305804958737581</v>
       </c>
     </row>
     <row r="473">
@@ -8843,10 +8843,10 @@
         <v>474</v>
       </c>
       <c r="B473" t="n">
-        <v>0.0278446202170051</v>
+        <v>0.0280750332602131</v>
       </c>
       <c r="C473" t="n">
-        <v>0.0301504628679456</v>
+        <v>0.0288359533910935</v>
       </c>
     </row>
     <row r="474">
@@ -8854,10 +8854,10 @@
         <v>475</v>
       </c>
       <c r="B474" t="n">
-        <v>0.0271558595506528</v>
+        <v>0.0274080552360013</v>
       </c>
       <c r="C474" t="n">
-        <v>0.0305190990021528</v>
+        <v>0.0289941545023312</v>
       </c>
     </row>
     <row r="475">
@@ -8865,10 +8865,10 @@
         <v>476</v>
       </c>
       <c r="B475" t="n">
-        <v>0.025124824587565</v>
+        <v>0.0253528846958523</v>
       </c>
       <c r="C475" t="n">
-        <v>0.0275666090124048</v>
+        <v>0.0262753836210467</v>
       </c>
     </row>
     <row r="476">
@@ -8876,10 +8876,10 @@
         <v>477</v>
       </c>
       <c r="B476" t="n">
-        <v>0.0271558595506528</v>
+        <v>0.0274080552360013</v>
       </c>
       <c r="C476" t="n">
-        <v>0.0305190990021528</v>
+        <v>0.0289941545023312</v>
       </c>
     </row>
     <row r="477">
@@ -8887,10 +8887,10 @@
         <v>478</v>
       </c>
       <c r="B477" t="n">
-        <v>0.0248060500554271</v>
+        <v>0.0250415192160553</v>
       </c>
       <c r="C477" t="n">
-        <v>0.0277902871419571</v>
+        <v>0.0264831701792376</v>
       </c>
     </row>
     <row r="478">
@@ -8898,10 +8898,10 @@
         <v>479</v>
       </c>
       <c r="B478" t="n">
-        <v>0.0269282227255006</v>
+        <v>0.0271776379808427</v>
       </c>
       <c r="C478" t="n">
-        <v>0.0302107098845812</v>
+        <v>0.0287438389898198</v>
       </c>
     </row>
     <row r="479">
@@ -8909,10 +8909,10 @@
         <v>480</v>
       </c>
       <c r="B479" t="n">
-        <v>0.028561822696875</v>
+        <v>0.029173184126265</v>
       </c>
       <c r="C479" t="n">
-        <v>0.0349050818859039</v>
+        <v>0.0315063095053907</v>
       </c>
     </row>
     <row r="480">
@@ -8920,10 +8920,10 @@
         <v>481</v>
       </c>
       <c r="B480" t="n">
-        <v>0.028561822696875</v>
+        <v>0.029173184126265</v>
       </c>
       <c r="C480" t="n">
-        <v>0.0349050818859039</v>
+        <v>0.0315063095053907</v>
       </c>
     </row>
     <row r="481">
@@ -8931,10 +8931,10 @@
         <v>482</v>
       </c>
       <c r="B481" t="n">
-        <v>0.028561822696875</v>
+        <v>0.029173184126265</v>
       </c>
       <c r="C481" t="n">
-        <v>0.0349050818859039</v>
+        <v>0.0315063095053907</v>
       </c>
     </row>
     <row r="482">
@@ -8942,10 +8942,10 @@
         <v>483</v>
       </c>
       <c r="B482" t="n">
-        <v>0.0265148907727777</v>
+        <v>0.0267573285750232</v>
       </c>
       <c r="C482" t="n">
-        <v>0.0296038737674429</v>
+        <v>0.0282592727016248</v>
       </c>
     </row>
     <row r="483">
@@ -8953,10 +8953,10 @@
         <v>484</v>
       </c>
       <c r="B483" t="n">
-        <v>0.0289933051145475</v>
+        <v>0.0292602761608826</v>
       </c>
       <c r="C483" t="n">
-        <v>0.0329024907387744</v>
+        <v>0.0308526807631352</v>
       </c>
     </row>
     <row r="484">
@@ -8964,10 +8964,10 @@
         <v>485</v>
       </c>
       <c r="B484" t="n">
-        <v>0.0265148907727777</v>
+        <v>0.0267573285750232</v>
       </c>
       <c r="C484" t="n">
-        <v>0.0296038737674429</v>
+        <v>0.0282592727016248</v>
       </c>
     </row>
     <row r="485">
@@ -8975,10 +8975,10 @@
         <v>486</v>
       </c>
       <c r="B485" t="n">
-        <v>0.0248060500554271</v>
+        <v>0.0250415192160553</v>
       </c>
       <c r="C485" t="n">
-        <v>0.0277902871419571</v>
+        <v>0.0264831701792376</v>
       </c>
     </row>
     <row r="486">
@@ -8986,10 +8986,10 @@
         <v>487</v>
       </c>
       <c r="B486" t="n">
-        <v>0.0252400317954482</v>
+        <v>0.0254853159463103</v>
       </c>
       <c r="C486" t="n">
-        <v>0.0293033941943355</v>
+        <v>0.0273935802286779</v>
       </c>
     </row>
     <row r="487">
@@ -8997,10 +8997,10 @@
         <v>488</v>
       </c>
       <c r="B487" t="n">
-        <v>0.0289933051145475</v>
+        <v>0.0292602761608826</v>
       </c>
       <c r="C487" t="n">
-        <v>0.0329024907387744</v>
+        <v>0.0308526807631352</v>
       </c>
     </row>
     <row r="488">
@@ -9008,10 +9008,10 @@
         <v>489</v>
       </c>
       <c r="B488" t="n">
-        <v>0.0309449068564749</v>
+        <v>0.0313952002738435</v>
       </c>
       <c r="C488" t="n">
-        <v>0.0286429948219451</v>
+        <v>0.02595855526932</v>
       </c>
     </row>
     <row r="489">
@@ -9019,10 +9019,10 @@
         <v>490</v>
       </c>
       <c r="B489" t="n">
-        <v>0.0264937281723146</v>
+        <v>0.0265420823242493</v>
       </c>
       <c r="C489" t="n">
-        <v>0.0277508989113118</v>
+        <v>0.0274146035128353</v>
       </c>
     </row>
     <row r="490">
@@ -9030,10 +9030,10 @@
         <v>491</v>
       </c>
       <c r="B490" t="n">
-        <v>0.0288772661803063</v>
+        <v>0.0292657399618338</v>
       </c>
       <c r="C490" t="n">
-        <v>0.0269623396511919</v>
+        <v>0.0246314804673998</v>
       </c>
     </row>
     <row r="491">
@@ -9041,10 +9041,10 @@
         <v>492</v>
       </c>
       <c r="B491" t="n">
-        <v>0.0230646277190717</v>
+        <v>0.023132178809021</v>
       </c>
       <c r="C491" t="n">
-        <v>0.0236176595057181</v>
+        <v>0.0231451387642585</v>
       </c>
     </row>
     <row r="492">
@@ -9052,10 +9052,10 @@
         <v>493</v>
       </c>
       <c r="B492" t="n">
-        <v>0.0269745516533671</v>
+        <v>0.0270421027433163</v>
       </c>
       <c r="C492" t="n">
-        <v>0.0276749541664342</v>
+        <v>0.0272024334249746</v>
       </c>
     </row>
     <row r="493">
@@ -9063,10 +9063,10 @@
         <v>494</v>
       </c>
       <c r="B493" t="n">
-        <v>0.0274168706716357</v>
+        <v>0.0276379987110777</v>
       </c>
       <c r="C493" t="n">
-        <v>0.0296345191032792</v>
+        <v>0.0283763059881802</v>
       </c>
     </row>
     <row r="494">
@@ -9074,10 +9074,10 @@
         <v>495</v>
       </c>
       <c r="B494" t="n">
-        <v>0.025129278692326</v>
+        <v>0.0252245095040703</v>
       </c>
       <c r="C494" t="n">
-        <v>0.0252874746026188</v>
+        <v>0.0246752271585536</v>
       </c>
     </row>
     <row r="495">
@@ -9085,10 +9085,10 @@
         <v>496</v>
       </c>
       <c r="B495" t="n">
-        <v>0.0225838042380193</v>
+        <v>0.022632158389954</v>
       </c>
       <c r="C495" t="n">
-        <v>0.0236936042505957</v>
+        <v>0.0233573088521192</v>
       </c>
     </row>
     <row r="496">
@@ -9096,10 +9096,10 @@
         <v>497</v>
       </c>
       <c r="B496" t="n">
-        <v>0.0249694288934665</v>
+        <v>0.0250646597052107</v>
       </c>
       <c r="C496" t="n">
-        <v>0.0251197711766267</v>
+        <v>0.0245075237325614</v>
       </c>
     </row>
     <row r="497">
@@ -9107,10 +9107,10 @@
         <v>498</v>
       </c>
       <c r="B497" t="n">
-        <v>0.0274993752632426</v>
+        <v>0.0277564964792683</v>
       </c>
       <c r="C497" t="n">
-        <v>0.0318418764521136</v>
+        <v>0.0298347096352077</v>
       </c>
     </row>
     <row r="498">
@@ -9118,10 +9118,10 @@
         <v>499</v>
       </c>
       <c r="B498" t="n">
-        <v>0.0312569412016292</v>
+        <v>0.0316928725797442</v>
       </c>
       <c r="C498" t="n">
-        <v>0.0285124638727195</v>
+        <v>0.0259373941668448</v>
       </c>
     </row>
     <row r="499">
@@ -9129,10 +9129,10 @@
         <v>500</v>
       </c>
       <c r="B499" t="n">
-        <v>0.0281665381532756</v>
+        <v>0.0282292543444638</v>
       </c>
       <c r="C499" t="n">
-        <v>0.0317998084269498</v>
+        <v>0.0313541431817228</v>
       </c>
     </row>
     <row r="500">
@@ -9140,10 +9140,10 @@
         <v>501</v>
       </c>
       <c r="B500" t="n">
-        <v>0.0290371159791659</v>
+        <v>0.0294255897606934</v>
       </c>
       <c r="C500" t="n">
-        <v>0.027130043077184</v>
+        <v>0.0247991838933919</v>
       </c>
     </row>
     <row r="501">
@@ -9151,10 +9151,10 @@
         <v>502</v>
       </c>
       <c r="B501" t="n">
-        <v>0.0268147018545076</v>
+        <v>0.0268822529444568</v>
       </c>
       <c r="C501" t="n">
-        <v>0.0275072507404421</v>
+        <v>0.0270347299989825</v>
       </c>
     </row>
     <row r="502">
@@ -9162,10 +9162,10 @@
         <v>503</v>
       </c>
       <c r="B502" t="n">
-        <v>0.0265827976650904</v>
+        <v>0.0266432684294987</v>
       </c>
       <c r="C502" t="n">
-        <v>0.0282251222994569</v>
+        <v>0.0278262615953987</v>
       </c>
     </row>
     <row r="503">
@@ -9173,10 +9173,10 @@
         <v>504</v>
       </c>
       <c r="B503" t="n">
-        <v>0.0270636211461429</v>
+        <v>0.0271432888485657</v>
       </c>
       <c r="C503" t="n">
-        <v>0.0281491775545794</v>
+        <v>0.027614091507538</v>
       </c>
     </row>
     <row r="504">
@@ -9184,10 +9184,10 @@
         <v>505</v>
       </c>
       <c r="B504" t="n">
-        <v>0.0232244775179313</v>
+        <v>0.0232920286078805</v>
       </c>
       <c r="C504" t="n">
-        <v>0.0237853629317103</v>
+        <v>0.0233128421902507</v>
       </c>
     </row>
     <row r="505">
@@ -9195,10 +9195,10 @@
         <v>506</v>
       </c>
       <c r="B505" t="n">
-        <v>0.0263338783734551</v>
+        <v>0.0263822325253898</v>
       </c>
       <c r="C505" t="n">
-        <v>0.0275831954853197</v>
+        <v>0.0272469000868431</v>
       </c>
     </row>
     <row r="506">
@@ -9206,10 +9206,10 @@
         <v>507</v>
       </c>
       <c r="B506" t="n">
-        <v>0.0307820673547011</v>
+        <v>0.0311982208580236</v>
       </c>
       <c r="C506" t="n">
-        <v>0.0284644513221005</v>
+        <v>0.0259938654357027</v>
       </c>
     </row>
     <row r="507">
@@ -9217,10 +9217,10 @@
         <v>508</v>
       </c>
       <c r="B507" t="n">
-        <v>0.0250401509343818</v>
+        <v>0.025135381746126</v>
       </c>
       <c r="C507" t="n">
-        <v>0.0251197711766267</v>
+        <v>0.0245075237325614</v>
       </c>
     </row>
     <row r="508">
@@ -9228,10 +9228,10 @@
         <v>509</v>
       </c>
       <c r="B508" t="n">
-        <v>0.0310359111206707</v>
+        <v>0.0314862045380393</v>
       </c>
       <c r="C508" t="n">
-        <v>0.0286429948219451</v>
+        <v>0.02595855526932</v>
       </c>
     </row>
     <row r="509">
@@ -9239,10 +9239,10 @@
         <v>510</v>
       </c>
       <c r="B509" t="n">
-        <v>0.0289933051145475</v>
+        <v>0.0292602761608826</v>
       </c>
       <c r="C509" t="n">
-        <v>0.0329024907387744</v>
+        <v>0.0308526807631352</v>
       </c>
     </row>
     <row r="510">
@@ -9250,10 +9250,10 @@
         <v>511</v>
       </c>
       <c r="B510" t="n">
-        <v>0.0236667965361999</v>
+        <v>0.0238879245756419</v>
       </c>
       <c r="C510" t="n">
-        <v>0.0257449278685552</v>
+        <v>0.0244867147534562</v>
       </c>
     </row>
     <row r="511">
@@ -9261,10 +9261,10 @@
         <v>512</v>
       </c>
       <c r="B511" t="n">
-        <v>0.0292432074648368</v>
+        <v>0.0293059360040788</v>
       </c>
       <c r="C511" t="n">
-        <v>0.0329961009806393</v>
+        <v>0.0325502324741603</v>
       </c>
     </row>
     <row r="512">
@@ -9272,10 +9272,10 @@
         <v>513</v>
       </c>
       <c r="B512" t="n">
-        <v>0.0319607267806648</v>
+        <v>0.0320234553199068</v>
       </c>
       <c r="C512" t="n">
-        <v>0.0360148778877544</v>
+        <v>0.0355690093812754</v>
       </c>
     </row>
     <row r="513">
@@ -9283,10 +9283,10 @@
         <v>514</v>
       </c>
       <c r="B513" t="n">
-        <v>0.0309449068564749</v>
+        <v>0.0313952002738435</v>
       </c>
       <c r="C513" t="n">
-        <v>0.0286429948219451</v>
+        <v>0.02595855526932</v>
       </c>
     </row>
     <row r="514">
@@ -9294,10 +9294,10 @@
         <v>515</v>
       </c>
       <c r="B514" t="n">
-        <v>0.0309449068564749</v>
+        <v>0.0313952002738435</v>
       </c>
       <c r="C514" t="n">
-        <v>0.0286429948219451</v>
+        <v>0.02595855526932</v>
       </c>
     </row>
     <row r="515">
@@ -9305,10 +9305,10 @@
         <v>516</v>
       </c>
       <c r="B515" t="n">
-        <v>0.0312569412016292</v>
+        <v>0.0316928725797442</v>
       </c>
       <c r="C515" t="n">
-        <v>0.0285124638727195</v>
+        <v>0.0259373941668448</v>
       </c>
     </row>
   </sheetData>
@@ -9377,7 +9377,7 @@
         <v>531</v>
       </c>
       <c r="C2" t="n">
-        <v>2267001189</v>
+        <v>2603110830</v>
       </c>
       <c r="D2" t="n">
         <v>1045004847</v>
@@ -9386,7 +9386,7 @@
         <v>1022739012</v>
       </c>
       <c r="F2" t="n">
-        <v>23127650802</v>
+        <v>22791541161</v>
       </c>
       <c r="G2" t="n">
         <v>25217832</v>
@@ -9410,10 +9410,10 @@
         <v>532</v>
       </c>
       <c r="N2" t="n">
-        <v>0.000973887591646456</v>
+        <v>0.000988249630899982</v>
       </c>
       <c r="O2" t="n">
-        <v>0.00117984905276719</v>
+        <v>0.00107047920601672</v>
       </c>
     </row>
     <row r="3">
@@ -9424,7 +9424,7 @@
         <v>534</v>
       </c>
       <c r="C3" t="n">
-        <v>2778560532</v>
+        <v>3138431670</v>
       </c>
       <c r="D3" t="n">
         <v>1069093614</v>
@@ -9433,7 +9433,7 @@
         <v>1083855210</v>
       </c>
       <c r="F3" t="n">
-        <v>26348466810</v>
+        <v>25988595672</v>
       </c>
       <c r="G3" t="n">
         <v>37831512</v>
@@ -9457,10 +9457,10 @@
         <v>535</v>
       </c>
       <c r="N3" t="n">
-        <v>0.00218023439820488</v>
+        <v>0.00221042469566809</v>
       </c>
       <c r="O3" t="n">
-        <v>0.00261042646771236</v>
+        <v>0.00238793634084514</v>
       </c>
     </row>
     <row r="4">
@@ -9471,7 +9471,7 @@
         <v>537</v>
       </c>
       <c r="C4" t="n">
-        <v>80265144</v>
+        <v>102993411</v>
       </c>
       <c r="D4" t="n">
         <v>227324319</v>
@@ -9480,7 +9480,7 @@
         <v>62656917</v>
       </c>
       <c r="F4" t="n">
-        <v>624979773</v>
+        <v>602251506</v>
       </c>
       <c r="G4" t="n">
         <v>842541</v>
@@ -9504,10 +9504,10 @@
         <v>538</v>
       </c>
       <c r="N4" t="n">
-        <v>0.000937953619180568</v>
+        <v>0.000973350891047834</v>
       </c>
       <c r="O4" t="n">
-        <v>0.00119090579025445</v>
+        <v>0.00102750602461832</v>
       </c>
     </row>
     <row r="5">
@@ -9518,7 +9518,7 @@
         <v>540</v>
       </c>
       <c r="C5" t="n">
-        <v>2778560532</v>
+        <v>3138431670</v>
       </c>
       <c r="D5" t="n">
         <v>1069093614</v>
@@ -9527,7 +9527,7 @@
         <v>1083855210</v>
       </c>
       <c r="F5" t="n">
-        <v>26348466810</v>
+        <v>25988595672</v>
       </c>
       <c r="G5" t="n">
         <v>37831512</v>
@@ -9551,10 +9551,10 @@
         <v>541</v>
       </c>
       <c r="N5" t="n">
-        <v>0.000657315047015443</v>
+        <v>0.000666417066877518</v>
       </c>
       <c r="O5" t="n">
-        <v>0.000784820165016819</v>
+        <v>0.000717928896389911</v>
       </c>
     </row>
     <row r="6">
@@ -9565,7 +9565,7 @@
         <v>543</v>
       </c>
       <c r="C6" t="n">
-        <v>69640446</v>
+        <v>92368713</v>
       </c>
       <c r="D6" t="n">
         <v>14889294</v>
@@ -9574,7 +9574,7 @@
         <v>55503177</v>
       </c>
       <c r="F6" t="n">
-        <v>355401399</v>
+        <v>332673132</v>
       </c>
       <c r="G6" t="n">
         <v>677655</v>
@@ -9598,10 +9598,10 @@
         <v>544</v>
       </c>
       <c r="N6" t="n">
-        <v>0.00520097941970137</v>
+        <v>0.00555631093746421</v>
       </c>
       <c r="O6" t="n">
-        <v>0.00651528626048759</v>
+        <v>0.00551387101036944</v>
       </c>
     </row>
     <row r="7">
@@ -9612,7 +9612,7 @@
         <v>546</v>
       </c>
       <c r="C7" t="n">
-        <v>30435378</v>
+        <v>50069268</v>
       </c>
       <c r="D7" t="n">
         <v>54520995</v>
@@ -9621,7 +9621,7 @@
         <v>44125878</v>
       </c>
       <c r="F7" t="n">
-        <v>364632117</v>
+        <v>344998227</v>
       </c>
       <c r="G7" t="n">
         <v>164886</v>
@@ -9645,10 +9645,10 @@
         <v>547</v>
       </c>
       <c r="N7" t="n">
-        <v>0.00150409199966332</v>
+        <v>0.00158969005368251</v>
       </c>
       <c r="O7" t="n">
-        <v>0.00202485041292759</v>
+        <v>0.00160279373631418</v>
       </c>
     </row>
     <row r="8">
@@ -9659,7 +9659,7 @@
         <v>549</v>
       </c>
       <c r="C8" t="n">
-        <v>77783832</v>
+        <v>100512099</v>
       </c>
       <c r="D8" t="n">
         <v>210913956</v>
@@ -9668,7 +9668,7 @@
         <v>62656917</v>
       </c>
       <c r="F8" t="n">
-        <v>604836558</v>
+        <v>582108291</v>
       </c>
       <c r="G8" t="n">
         <v>842541</v>
@@ -9692,10 +9692,10 @@
         <v>550</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0167108967642793</v>
+        <v>0.0173633693872263</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0212175111655094</v>
+        <v>0.018262064900851</v>
       </c>
     </row>
     <row r="9">
@@ -9706,7 +9706,7 @@
         <v>551</v>
       </c>
       <c r="C9" t="n">
-        <v>17044467</v>
+        <v>18000000</v>
       </c>
       <c r="D9" t="n">
         <v>116175045</v>
@@ -9715,7 +9715,7 @@
         <v>13168542</v>
       </c>
       <c r="F9" t="n">
-        <v>188492331</v>
+        <v>187536798</v>
       </c>
       <c r="G9" t="n">
         <v>59340</v>
@@ -9739,10 +9739,10 @@
         <v>552</v>
       </c>
       <c r="N9" t="n">
-        <v>0.00137592616433822</v>
+        <v>0.00138293675036512</v>
       </c>
       <c r="O9" t="n">
-        <v>0.00159154422520445</v>
+        <v>0.00154275230455117</v>
       </c>
     </row>
     <row r="10">
@@ -9800,7 +9800,7 @@
         <v>555</v>
       </c>
       <c r="C11" t="n">
-        <v>17380692</v>
+        <v>18336225</v>
       </c>
       <c r="D11" t="n">
         <v>102844743</v>
@@ -9809,7 +9809,7 @@
         <v>13168542</v>
       </c>
       <c r="F11" t="n">
-        <v>175341024</v>
+        <v>174385491</v>
       </c>
       <c r="G11" t="n">
         <v>59340</v>
@@ -9833,10 +9833,10 @@
         <v>556</v>
       </c>
       <c r="N11" t="n">
-        <v>0.0148331375662549</v>
+        <v>0.0149144146974934</v>
       </c>
       <c r="O11" t="n">
-        <v>0.0166907088406865</v>
+        <v>0.0161844831291722</v>
       </c>
     </row>
     <row r="12">
@@ -9847,7 +9847,7 @@
         <v>557</v>
       </c>
       <c r="C12" t="n">
-        <v>13431624</v>
+        <v>14387157</v>
       </c>
       <c r="D12" t="n">
         <v>61860492</v>
@@ -9856,7 +9856,7 @@
         <v>13168542</v>
       </c>
       <c r="F12" t="n">
-        <v>136665762</v>
+        <v>135710229</v>
       </c>
       <c r="G12" t="n">
         <v>59340</v>
@@ -9880,10 +9880,10 @@
         <v>558</v>
       </c>
       <c r="N12" t="n">
-        <v>0.00173889521795517</v>
+        <v>0.00175113874430202</v>
       </c>
       <c r="O12" t="n">
-        <v>0.00207048369547769</v>
+        <v>0.00199868673264286</v>
       </c>
     </row>
     <row r="13">
@@ -9894,7 +9894,7 @@
         <v>559</v>
       </c>
       <c r="C13" t="n">
-        <v>13155540</v>
+        <v>14111073</v>
       </c>
       <c r="D13" t="n">
         <v>1138128</v>
@@ -9903,7 +9903,7 @@
         <v>10497201</v>
       </c>
       <c r="F13" t="n">
-        <v>71716047</v>
+        <v>70760514</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -9927,10 +9927,10 @@
         <v>560</v>
       </c>
       <c r="N13" t="n">
-        <v>0.00202782049601814</v>
+        <v>0.0020552036973615</v>
       </c>
       <c r="O13" t="n">
-        <v>0.0024946690110884</v>
+        <v>0.00239780164996537</v>
       </c>
     </row>
     <row r="14">
@@ -10176,7 +10176,7 @@
         <v>573</v>
       </c>
       <c r="C19" t="n">
-        <v>65669319</v>
+        <v>80023140</v>
       </c>
       <c r="D19" t="n">
         <v>52853190</v>
@@ -10185,7 +10185,7 @@
         <v>79630614</v>
       </c>
       <c r="F19" t="n">
-        <v>629548767</v>
+        <v>615194946</v>
       </c>
       <c r="G19" t="n">
         <v>124200</v>
@@ -10209,10 +10209,10 @@
         <v>574</v>
       </c>
       <c r="N19" t="n">
-        <v>0.0000342480378489884</v>
+        <v>0.0000350471182186858</v>
       </c>
       <c r="O19" t="n">
-        <v>0.0000424163306393266</v>
+        <v>0.0000386028505161238</v>
       </c>
     </row>
     <row r="20">
@@ -10223,7 +10223,7 @@
         <v>576</v>
       </c>
       <c r="C20" t="n">
-        <v>80664114</v>
+        <v>95020794</v>
       </c>
       <c r="D20" t="n">
         <v>63740841</v>
@@ -10232,7 +10232,7 @@
         <v>84305205</v>
       </c>
       <c r="F20" t="n">
-        <v>1120319178</v>
+        <v>1105962498</v>
       </c>
       <c r="G20" t="n">
         <v>3161067</v>
@@ -10256,10 +10256,10 @@
         <v>577</v>
       </c>
       <c r="N20" t="n">
-        <v>0.0097787525243989</v>
+        <v>0.00990569210964331</v>
       </c>
       <c r="O20" t="n">
-        <v>0.0118372889082484</v>
+        <v>0.0108896060855069</v>
       </c>
     </row>
     <row r="21">
@@ -10270,7 +10270,7 @@
         <v>578</v>
       </c>
       <c r="C21" t="n">
-        <v>45032010</v>
+        <v>59344266</v>
       </c>
       <c r="D21" t="n">
         <v>37540788</v>
@@ -10279,7 +10279,7 @@
         <v>33278196</v>
       </c>
       <c r="F21" t="n">
-        <v>269280633</v>
+        <v>254968377</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -10303,10 +10303,10 @@
         <v>579</v>
       </c>
       <c r="N21" t="n">
-        <v>0.00189458686395765</v>
+        <v>0.00200093657104779</v>
       </c>
       <c r="O21" t="n">
-        <v>0.00263740131139484</v>
+        <v>0.00222986342125088</v>
       </c>
     </row>
     <row r="22">
@@ -10317,7 +10317,7 @@
         <v>581</v>
       </c>
       <c r="C22" t="n">
-        <v>80664114</v>
+        <v>95020794</v>
       </c>
       <c r="D22" t="n">
         <v>63740841</v>
@@ -10326,7 +10326,7 @@
         <v>84305205</v>
       </c>
       <c r="F22" t="n">
-        <v>1120319178</v>
+        <v>1105962498</v>
       </c>
       <c r="G22" t="n">
         <v>3161067</v>
@@ -10350,10 +10350,10 @@
         <v>582</v>
       </c>
       <c r="N22" t="n">
-        <v>0.00794343902590945</v>
+        <v>0.00804655410657514</v>
       </c>
       <c r="O22" t="n">
-        <v>0.00961562149626138</v>
+        <v>0.00884580339072864</v>
       </c>
     </row>
     <row r="23">
@@ -10364,7 +10364,7 @@
         <v>584</v>
       </c>
       <c r="C23" t="n">
-        <v>79582629</v>
+        <v>93939309</v>
       </c>
       <c r="D23" t="n">
         <v>63592296</v>
@@ -10373,7 +10373,7 @@
         <v>84305205</v>
       </c>
       <c r="F23" t="n">
-        <v>1049442846</v>
+        <v>1035086166</v>
       </c>
       <c r="G23" t="n">
         <v>3161067</v>
@@ -10397,10 +10397,10 @@
         <v>585</v>
       </c>
       <c r="N23" t="n">
-        <v>0.000554826527446736</v>
+        <v>0.000562521990077491</v>
       </c>
       <c r="O23" t="n">
-        <v>0.000672666953423767</v>
+        <v>0.000618487085667052</v>
       </c>
     </row>
     <row r="24">
@@ -10411,7 +10411,7 @@
         <v>586</v>
       </c>
       <c r="C24" t="n">
-        <v>37842567</v>
+        <v>52083720</v>
       </c>
       <c r="D24" t="n">
         <v>2314977</v>
@@ -10420,7 +10420,7 @@
         <v>26510100</v>
       </c>
       <c r="F24" t="n">
-        <v>139992378</v>
+        <v>125751225</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -10444,10 +10444,10 @@
         <v>587</v>
       </c>
       <c r="N24" t="n">
-        <v>0.00220294322023732</v>
+        <v>0.00245242350521834</v>
       </c>
       <c r="O24" t="n">
-        <v>0.00337398091053476</v>
+        <v>0.00276261759512389</v>
       </c>
     </row>
     <row r="25">
@@ -10458,7 +10458,7 @@
         <v>588</v>
       </c>
       <c r="C25" t="n">
-        <v>65669319</v>
+        <v>80023140</v>
       </c>
       <c r="D25" t="n">
         <v>52853190</v>
@@ -10467,7 +10467,7 @@
         <v>79630614</v>
       </c>
       <c r="F25" t="n">
-        <v>629548767</v>
+        <v>615194946</v>
       </c>
       <c r="G25" t="n">
         <v>124200</v>
@@ -10491,10 +10491,10 @@
         <v>589</v>
       </c>
       <c r="N25" t="n">
-        <v>0.00103694649917407</v>
+        <v>0.00106114069084046</v>
       </c>
       <c r="O25" t="n">
-        <v>0.00128426108771846</v>
+        <v>0.00116879838603732</v>
       </c>
     </row>
     <row r="26">
@@ -10552,7 +10552,7 @@
         <v>592</v>
       </c>
       <c r="C27" t="n">
-        <v>28031505</v>
+        <v>28075929</v>
       </c>
       <c r="D27" t="n">
         <v>8739006</v>
@@ -10561,7 +10561,7 @@
         <v>49854789</v>
       </c>
       <c r="F27" t="n">
-        <v>606366843</v>
+        <v>606322419</v>
       </c>
       <c r="G27" t="n">
         <v>781575</v>
@@ -10585,10 +10585,10 @@
         <v>593</v>
       </c>
       <c r="N27" t="n">
-        <v>0.00109936876335724</v>
+        <v>0.0010994493118516</v>
       </c>
       <c r="O27" t="n">
-        <v>0.0010678988249565</v>
+        <v>0.00106729007479203</v>
       </c>
     </row>
     <row r="28">
@@ -10599,7 +10599,7 @@
         <v>594</v>
       </c>
       <c r="C28" t="n">
-        <v>33167004</v>
+        <v>33211428</v>
       </c>
       <c r="D28" t="n">
         <v>26077749</v>
@@ -10608,7 +10608,7 @@
         <v>51027009</v>
       </c>
       <c r="F28" t="n">
-        <v>779708946</v>
+        <v>779664522</v>
       </c>
       <c r="G28" t="n">
         <v>2848344</v>
@@ -10632,10 +10632,10 @@
         <v>595</v>
       </c>
       <c r="N28" t="n">
-        <v>0.00182850759544831</v>
+        <v>0.00182861178079872</v>
       </c>
       <c r="O28" t="n">
-        <v>0.00200943622915325</v>
+        <v>0.00200837653243732</v>
       </c>
     </row>
     <row r="29">
@@ -10646,7 +10646,7 @@
         <v>596</v>
       </c>
       <c r="C29" t="n">
-        <v>24016599</v>
+        <v>24058164</v>
       </c>
       <c r="D29" t="n">
         <v>20973</v>
@@ -10655,7 +10655,7 @@
         <v>45762207</v>
       </c>
       <c r="F29" t="n">
-        <v>2334159</v>
+        <v>2292594</v>
       </c>
       <c r="G29" t="n">
         <v>124200</v>
@@ -10740,7 +10740,7 @@
         <v>600</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>13232280</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
@@ -10749,7 +10749,7 @@
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>28295184</v>
+        <v>15062904</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -11210,7 +11210,7 @@
         <v>620</v>
       </c>
       <c r="C41" t="n">
-        <v>14994795</v>
+        <v>14997654</v>
       </c>
       <c r="D41" t="n">
         <v>10887651</v>
@@ -11219,7 +11219,7 @@
         <v>4674591</v>
       </c>
       <c r="F41" t="n">
-        <v>490770411</v>
+        <v>490767552</v>
       </c>
       <c r="G41" t="n">
         <v>3036867</v>
@@ -11243,10 +11243,10 @@
         <v>621</v>
       </c>
       <c r="N41" t="n">
-        <v>0.000660843854337421</v>
+        <v>0.000660847704128573</v>
       </c>
       <c r="O41" t="n">
-        <v>0.000727366375340847</v>
+        <v>0.000727260665978896</v>
       </c>
     </row>
     <row r="42">
@@ -11915,7 +11915,7 @@
         <v>650</v>
       </c>
       <c r="C56" t="n">
-        <v>46166256</v>
+        <v>49260633</v>
       </c>
       <c r="D56" t="n">
         <v>57855981</v>
@@ -11924,7 +11924,7 @@
         <v>18531039</v>
       </c>
       <c r="F56" t="n">
-        <v>143853144</v>
+        <v>140758767</v>
       </c>
       <c r="G56" t="n">
         <v>677655</v>
@@ -11948,10 +11948,10 @@
         <v>651</v>
       </c>
       <c r="N56" t="n">
-        <v>0.00175578588675128</v>
+        <v>0.00179438428868875</v>
       </c>
       <c r="O56" t="n">
-        <v>0.0021448505691003</v>
+        <v>0.0020469480381012</v>
       </c>
     </row>
     <row r="57">
@@ -12009,7 +12009,7 @@
         <v>654</v>
       </c>
       <c r="C58" t="n">
-        <v>283837173</v>
+        <v>365536605</v>
       </c>
       <c r="D58" t="n">
         <v>162744420</v>
@@ -12018,7 +12018,7 @@
         <v>132940740</v>
       </c>
       <c r="F58" t="n">
-        <v>2250065487</v>
+        <v>2168366055</v>
       </c>
       <c r="G58" t="n">
         <v>1687149</v>
@@ -12042,10 +12042,10 @@
         <v>655</v>
       </c>
       <c r="N58" t="n">
-        <v>0.00271887295074092</v>
+        <v>0.00282131431447814</v>
       </c>
       <c r="O58" t="n">
-        <v>0.00371829559979586</v>
+        <v>0.00310887444644049</v>
       </c>
     </row>
     <row r="59">
@@ -12056,7 +12056,7 @@
         <v>656</v>
       </c>
       <c r="C59" t="n">
-        <v>22764312</v>
+        <v>22841820</v>
       </c>
       <c r="D59" t="n">
         <v>204286224</v>
@@ -12065,7 +12065,7 @@
         <v>30103542</v>
       </c>
       <c r="F59" t="n">
-        <v>1090905813</v>
+        <v>1090828305</v>
       </c>
       <c r="G59" t="n">
         <v>554229</v>
@@ -12089,10 +12089,10 @@
         <v>657</v>
       </c>
       <c r="N59" t="n">
-        <v>0.000321060879707678</v>
+        <v>0.00032108369245149</v>
       </c>
       <c r="O59" t="n">
-        <v>0.000347217233368315</v>
+        <v>0.000346708933636151</v>
       </c>
     </row>
     <row r="60">
@@ -12103,7 +12103,7 @@
         <v>658</v>
       </c>
       <c r="C60" t="n">
-        <v>287968209</v>
+        <v>369683397</v>
       </c>
       <c r="D60" t="n">
         <v>209796042</v>
@@ -12112,7 +12112,7 @@
         <v>129433335</v>
       </c>
       <c r="F60" t="n">
-        <v>2692273302</v>
+        <v>2610558114</v>
       </c>
       <c r="G60" t="n">
         <v>1687149</v>
@@ -12136,10 +12136,10 @@
         <v>659</v>
       </c>
       <c r="N60" t="n">
-        <v>0.0181307973428026</v>
+        <v>0.01869832407416</v>
       </c>
       <c r="O60" t="n">
-        <v>0.024472321669227</v>
+        <v>0.020465723136687</v>
       </c>
     </row>
     <row r="61">
@@ -12150,7 +12150,7 @@
         <v>660</v>
       </c>
       <c r="C61" t="n">
-        <v>265203897</v>
+        <v>346841577</v>
       </c>
       <c r="D61" t="n">
         <v>4010454</v>
@@ -12159,7 +12159,7 @@
         <v>99329793</v>
       </c>
       <c r="F61" t="n">
-        <v>1572445002</v>
+        <v>1490807322</v>
       </c>
       <c r="G61" t="n">
         <v>1132920</v>
@@ -12183,10 +12183,10 @@
         <v>661</v>
       </c>
       <c r="N61" t="n">
-        <v>0.00451255670689588</v>
+        <v>0.00475966755414151</v>
       </c>
       <c r="O61" t="n">
-        <v>0.0064127647570791</v>
+        <v>0.00523939669190338</v>
       </c>
     </row>
     <row r="62">
@@ -12197,7 +12197,7 @@
         <v>662</v>
       </c>
       <c r="C62" t="n">
-        <v>31912668</v>
+        <v>34168938</v>
       </c>
       <c r="D62" t="n">
         <v>60388071</v>
@@ -12206,7 +12206,7 @@
         <v>5972787</v>
       </c>
       <c r="F62" t="n">
-        <v>985330470</v>
+        <v>983074200</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -12230,10 +12230,10 @@
         <v>663</v>
       </c>
       <c r="N62" t="n">
-        <v>0.00135710855465578</v>
+        <v>0.00136022327714429</v>
       </c>
       <c r="O62" t="n">
-        <v>0.00163564328315445</v>
+        <v>0.00154370770065312</v>
       </c>
     </row>
     <row r="63">
@@ -12244,7 +12244,7 @@
         <v>664</v>
       </c>
       <c r="C63" t="n">
-        <v>17778519</v>
+        <v>17794275</v>
       </c>
       <c r="D63" t="n">
         <v>7885884</v>
@@ -12253,7 +12253,7 @@
         <v>419772</v>
       </c>
       <c r="F63" t="n">
-        <v>762926310</v>
+        <v>762910554</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -12277,10 +12277,10 @@
         <v>665</v>
       </c>
       <c r="N63" t="n">
-        <v>0.00162176816264208</v>
+        <v>0.00162180165618734</v>
       </c>
       <c r="O63" t="n">
-        <v>0.00184477542424176</v>
+        <v>0.00184317960747548</v>
       </c>
     </row>
     <row r="64">
@@ -12385,7 +12385,7 @@
         <v>670</v>
       </c>
       <c r="C66" t="n">
-        <v>471173358</v>
+        <v>524470260</v>
       </c>
       <c r="D66" t="n">
         <v>46329957</v>
@@ -12394,7 +12394,7 @@
         <v>176198811</v>
       </c>
       <c r="F66" t="n">
-        <v>3603720720</v>
+        <v>3550423818</v>
       </c>
       <c r="G66" t="n">
         <v>9622755</v>
@@ -12418,10 +12418,10 @@
         <v>671</v>
       </c>
       <c r="N66" t="n">
-        <v>0.00658320685571883</v>
+        <v>0.00668203013671874</v>
       </c>
       <c r="O66" t="n">
-        <v>0.00797902743946968</v>
+        <v>0.00737209691963126</v>
       </c>
     </row>
     <row r="67">
@@ -12432,7 +12432,7 @@
         <v>672</v>
       </c>
       <c r="C67" t="n">
-        <v>446620095</v>
+        <v>499776954</v>
       </c>
       <c r="D67" t="n">
         <v>41087181</v>
@@ -12441,7 +12441,7 @@
         <v>161194548</v>
       </c>
       <c r="F67" t="n">
-        <v>3309600207</v>
+        <v>3256443348</v>
       </c>
       <c r="G67" t="n">
         <v>5314503</v>
@@ -12465,10 +12465,10 @@
         <v>673</v>
       </c>
       <c r="N67" t="n">
-        <v>0.000820666147003296</v>
+        <v>0.000834062367972139</v>
       </c>
       <c r="O67" t="n">
-        <v>0.000998834179123256</v>
+        <v>0.000918505621139472</v>
       </c>
     </row>
     <row r="68">
@@ -12479,7 +12479,7 @@
         <v>674</v>
       </c>
       <c r="C68" t="n">
-        <v>12955794</v>
+        <v>12971550</v>
       </c>
       <c r="D68" t="n">
         <v>496992</v>
@@ -12488,7 +12488,7 @@
         <v>171405</v>
       </c>
       <c r="F68" t="n">
-        <v>608819625</v>
+        <v>608803869</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -12512,10 +12512,10 @@
         <v>675</v>
       </c>
       <c r="N68" t="n">
-        <v>0.000779718321547643</v>
+        <v>0.000779738500857433</v>
       </c>
       <c r="O68" t="n">
-        <v>0.000891878804442802</v>
+        <v>0.000890809604826521</v>
       </c>
     </row>
     <row r="69">
@@ -12855,7 +12855,7 @@
         <v>690</v>
       </c>
       <c r="C76" t="n">
-        <v>455749173</v>
+        <v>509046075</v>
       </c>
       <c r="D76" t="n">
         <v>43305153</v>
@@ -12864,7 +12864,7 @@
         <v>176198811</v>
       </c>
       <c r="F76" t="n">
-        <v>3309149298</v>
+        <v>3255852396</v>
       </c>
       <c r="G76" t="n">
         <v>9622755</v>
@@ -12888,10 +12888,10 @@
         <v>691</v>
       </c>
       <c r="N76" t="n">
-        <v>0.0129944008316545</v>
+        <v>0.0132071135788675</v>
       </c>
       <c r="O76" t="n">
-        <v>0.0157836576942067</v>
+        <v>0.0145560380876743</v>
       </c>
     </row>
     <row r="77">
@@ -12902,7 +12902,7 @@
         <v>692</v>
       </c>
       <c r="C77" t="n">
-        <v>598058193</v>
+        <v>652440708</v>
       </c>
       <c r="D77" t="n">
         <v>63789504</v>
@@ -12911,7 +12911,7 @@
         <v>189725427</v>
       </c>
       <c r="F77" t="n">
-        <v>4374815988</v>
+        <v>4320433473</v>
       </c>
       <c r="G77" t="n">
         <v>9622755</v>
@@ -12935,10 +12935,10 @@
         <v>693</v>
       </c>
       <c r="N77" t="n">
-        <v>0.00149479736472061</v>
+        <v>0.00151361280086073</v>
       </c>
       <c r="O77" t="n">
-        <v>0.00177420876052234</v>
+        <v>0.00165963999490433</v>
       </c>
     </row>
     <row r="78">
@@ -12949,7 +12949,7 @@
         <v>694</v>
       </c>
       <c r="C78" t="n">
-        <v>485233044</v>
+        <v>539615559</v>
       </c>
       <c r="D78" t="n">
         <v>48329877</v>
@@ -12958,7 +12958,7 @@
         <v>32817657</v>
       </c>
       <c r="F78" t="n">
-        <v>3930156162</v>
+        <v>3875773647</v>
       </c>
       <c r="G78" t="n">
         <v>9472281</v>
@@ -12982,10 +12982,10 @@
         <v>695</v>
       </c>
       <c r="N78" t="n">
-        <v>0.000972625682653472</v>
+        <v>0.000986272978804843</v>
       </c>
       <c r="O78" t="n">
-        <v>0.0011826075494491</v>
+        <v>0.00107025702365951</v>
       </c>
     </row>
     <row r="79">
@@ -12996,7 +12996,7 @@
         <v>696</v>
       </c>
       <c r="C79" t="n">
-        <v>447673695</v>
+        <v>500763423</v>
       </c>
       <c r="D79" t="n">
         <v>5680032</v>
@@ -13005,7 +13005,7 @@
         <v>153865899</v>
       </c>
       <c r="F79" t="n">
-        <v>1993672140</v>
+        <v>1940582412</v>
       </c>
       <c r="G79" t="n">
         <v>5161419</v>
@@ -13029,10 +13029,10 @@
         <v>697</v>
       </c>
       <c r="N79" t="n">
-        <v>0.00172004989517033</v>
+        <v>0.00176710637703699</v>
       </c>
       <c r="O79" t="n">
-        <v>0.00213578903484812</v>
+        <v>0.00196257886060929</v>
       </c>
     </row>
     <row r="80">
@@ -13043,7 +13043,7 @@
         <v>698</v>
       </c>
       <c r="C80" t="n">
-        <v>140802999</v>
+        <v>141888612</v>
       </c>
       <c r="D80" t="n">
         <v>25046247</v>
@@ -13052,7 +13052,7 @@
         <v>13698021</v>
       </c>
       <c r="F80" t="n">
-        <v>1250701746</v>
+        <v>1249616133</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -13076,10 +13076,10 @@
         <v>699</v>
       </c>
       <c r="N80" t="n">
-        <v>0.00046926708296128</v>
+        <v>0.000469674762113527</v>
       </c>
       <c r="O80" t="n">
-        <v>0.000514881390427067</v>
+        <v>0.000511288781472635</v>
       </c>
     </row>
     <row r="81">
@@ -13090,7 +13090,7 @@
         <v>700</v>
       </c>
       <c r="C81" t="n">
-        <v>143278410</v>
+        <v>144364023</v>
       </c>
       <c r="D81" t="n">
         <v>23421012</v>
@@ -13099,7 +13099,7 @@
         <v>13698021</v>
       </c>
       <c r="F81" t="n">
-        <v>1235673417</v>
+        <v>1234587804</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -13123,10 +13123,10 @@
         <v>701</v>
       </c>
       <c r="N81" t="n">
-        <v>0.0166457827910042</v>
+        <v>0.0166604199663712</v>
       </c>
       <c r="O81" t="n">
-        <v>0.0182556952769553</v>
+        <v>0.0181303102090721</v>
       </c>
     </row>
     <row r="82">
@@ -13184,7 +13184,7 @@
         <v>704</v>
       </c>
       <c r="C83" t="n">
-        <v>80219343</v>
+        <v>81304956</v>
       </c>
       <c r="D83" t="n">
         <v>5504733</v>
@@ -13193,7 +13193,7 @@
         <v>471156</v>
       </c>
       <c r="F83" t="n">
-        <v>718403907</v>
+        <v>717318294</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -13217,10 +13217,10 @@
         <v>705</v>
       </c>
       <c r="N83" t="n">
-        <v>0.00117011623949593</v>
+        <v>0.00117188713173684</v>
       </c>
       <c r="O83" t="n">
-        <v>0.00114397245124142</v>
+        <v>0.00112878572574988</v>
       </c>
     </row>
     <row r="84">
@@ -13231,7 +13231,7 @@
         <v>706</v>
       </c>
       <c r="C84" t="n">
-        <v>27028674</v>
+        <v>27168717</v>
       </c>
       <c r="D84" t="n">
         <v>3617541</v>
@@ -13240,7 +13240,7 @@
         <v>15004263</v>
       </c>
       <c r="F84" t="n">
-        <v>301025916</v>
+        <v>300885873</v>
       </c>
       <c r="G84" t="n">
         <v>4308252</v>
@@ -13264,10 +13264,10 @@
         <v>707</v>
       </c>
       <c r="N84" t="n">
-        <v>0.000749142010749666</v>
+        <v>0.000749490688118814</v>
       </c>
       <c r="O84" t="n">
-        <v>0.000849426724570781</v>
+        <v>0.00084660604965549</v>
       </c>
     </row>
     <row r="85">
@@ -14265,7 +14265,7 @@
         <v>750</v>
       </c>
       <c r="C106" t="n">
-        <v>8501529</v>
+        <v>8598633</v>
       </c>
       <c r="D106" t="n">
         <v>1764972</v>
@@ -14274,7 +14274,7 @@
         <v>15004263</v>
       </c>
       <c r="F106" t="n">
-        <v>193356708</v>
+        <v>193259604</v>
       </c>
       <c r="G106" t="n">
         <v>4308252</v>
@@ -14298,10 +14298,10 @@
         <v>751</v>
       </c>
       <c r="N106" t="n">
-        <v>0.00131401174066389</v>
+        <v>0.00131467197070382</v>
       </c>
       <c r="O106" t="n">
-        <v>0.000750416725504937</v>
+        <v>0.000747329457497086</v>
       </c>
     </row>
     <row r="107">
@@ -14500,7 +14500,7 @@
         <v>761</v>
       </c>
       <c r="C111" t="n">
-        <v>24883692</v>
+        <v>24973266</v>
       </c>
       <c r="D111" t="n">
         <v>366921</v>
@@ -14509,7 +14509,7 @@
         <v>15250785</v>
       </c>
       <c r="F111" t="n">
-        <v>591838836</v>
+        <v>591749262</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -14533,10 +14533,10 @@
         <v>762</v>
       </c>
       <c r="N111" t="n">
-        <v>0.0000815744710609021</v>
+        <v>0.0000815868191146134</v>
       </c>
       <c r="O111" t="n">
-        <v>0.0000912763856372166</v>
+        <v>0.0000910731243852092</v>
       </c>
     </row>
     <row r="112">
@@ -14641,7 +14641,7 @@
         <v>767</v>
       </c>
       <c r="C114" t="n">
-        <v>73785048</v>
+        <v>87080523</v>
       </c>
       <c r="D114" t="n">
         <v>161161329</v>
@@ -14650,7 +14650,7 @@
         <v>49329501</v>
       </c>
       <c r="F114" t="n">
-        <v>600456153</v>
+        <v>587160678</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -14674,10 +14674,10 @@
         <v>768</v>
       </c>
       <c r="N114" t="n">
-        <v>0.00830163535687842</v>
+        <v>0.00848961488187395</v>
       </c>
       <c r="O114" t="n">
-        <v>0.0102983666049087</v>
+        <v>0.0092946157681198</v>
       </c>
     </row>
     <row r="115">
@@ -14688,7 +14688,7 @@
         <v>769</v>
       </c>
       <c r="C115" t="n">
-        <v>76475793</v>
+        <v>89945466</v>
       </c>
       <c r="D115" t="n">
         <v>230480913</v>
@@ -14697,7 +14697,7 @@
         <v>25806972</v>
       </c>
       <c r="F115" t="n">
-        <v>848235192</v>
+        <v>834765519</v>
       </c>
       <c r="G115" t="n">
         <v>619335</v>
@@ -14721,10 +14721,10 @@
         <v>770</v>
       </c>
       <c r="N115" t="n">
-        <v>0.00109171148371783</v>
+        <v>0.00110932720497287</v>
       </c>
       <c r="O115" t="n">
-        <v>0.00134084515607297</v>
+        <v>0.00118481608136841</v>
       </c>
     </row>
     <row r="116">
@@ -14735,7 +14735,7 @@
         <v>771</v>
       </c>
       <c r="C116" t="n">
-        <v>87710373</v>
+        <v>101180046</v>
       </c>
       <c r="D116" t="n">
         <v>256397943</v>
@@ -14744,7 +14744,7 @@
         <v>52415874</v>
       </c>
       <c r="F116" t="n">
-        <v>912859875</v>
+        <v>899390202</v>
       </c>
       <c r="G116" t="n">
         <v>619335</v>
@@ -14768,10 +14768,10 @@
         <v>772</v>
       </c>
       <c r="N116" t="n">
-        <v>0.00636392806727319</v>
+        <v>0.00645923712208731</v>
       </c>
       <c r="O116" t="n">
-        <v>0.00763642217578267</v>
+        <v>0.00696674221554843</v>
       </c>
     </row>
     <row r="117">
@@ -14782,7 +14782,7 @@
         <v>773</v>
       </c>
       <c r="C117" t="n">
-        <v>87710373</v>
+        <v>101180046</v>
       </c>
       <c r="D117" t="n">
         <v>256397943</v>
@@ -14791,7 +14791,7 @@
         <v>52415874</v>
       </c>
       <c r="F117" t="n">
-        <v>912859875</v>
+        <v>899390202</v>
       </c>
       <c r="G117" t="n">
         <v>619335</v>
@@ -14815,10 +14815,10 @@
         <v>774</v>
       </c>
       <c r="N117" t="n">
-        <v>0.000481902635933034</v>
+        <v>0.0004891198269914</v>
       </c>
       <c r="O117" t="n">
-        <v>0.000578261116206159</v>
+        <v>0.000527550210969145</v>
       </c>
     </row>
     <row r="118">
@@ -14829,7 +14829,7 @@
         <v>775</v>
       </c>
       <c r="C118" t="n">
-        <v>57857898</v>
+        <v>70497624</v>
       </c>
       <c r="D118" t="n">
         <v>11811975</v>
@@ -14838,7 +14838,7 @@
         <v>18421551</v>
       </c>
       <c r="F118" t="n">
-        <v>412462800</v>
+        <v>399823074</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -14862,10 +14862,10 @@
         <v>776</v>
       </c>
       <c r="N118" t="n">
-        <v>0.00321201235602338</v>
+        <v>0.00331355465992941</v>
       </c>
       <c r="O118" t="n">
-        <v>0.00422192771738558</v>
+        <v>0.00362178708923019</v>
       </c>
     </row>
     <row r="119">
@@ -14876,7 +14876,7 @@
         <v>778</v>
       </c>
       <c r="C119" t="n">
-        <v>57212706</v>
+        <v>69847986</v>
       </c>
       <c r="D119" t="n">
         <v>11150244</v>
@@ -14885,7 +14885,7 @@
         <v>20772930</v>
       </c>
       <c r="F119" t="n">
-        <v>412569495</v>
+        <v>399934215</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -14909,10 +14909,10 @@
         <v>779</v>
       </c>
       <c r="N119" t="n">
-        <v>0.00103049892236943</v>
+        <v>0.00106305588282813</v>
       </c>
       <c r="O119" t="n">
-        <v>0.00135107572886884</v>
+        <v>0.0011626951552774</v>
       </c>
     </row>
     <row r="120">
@@ -14923,7 +14923,7 @@
         <v>781</v>
       </c>
       <c r="C120" t="n">
-        <v>83783865</v>
+        <v>97253538</v>
       </c>
       <c r="D120" t="n">
         <v>275019723</v>
@@ -14932,7 +14932,7 @@
         <v>51669531</v>
       </c>
       <c r="F120" t="n">
-        <v>958673508</v>
+        <v>945203835</v>
       </c>
       <c r="G120" t="n">
         <v>619335</v>
@@ -14956,10 +14956,10 @@
         <v>782</v>
       </c>
       <c r="N120" t="n">
-        <v>0.00104894697893331</v>
+        <v>0.00106389504862726</v>
       </c>
       <c r="O120" t="n">
-        <v>0.00126232730259491</v>
+        <v>0.00114815334620857</v>
       </c>
     </row>
     <row r="121">
@@ -14970,7 +14970,7 @@
         <v>783</v>
       </c>
       <c r="C121" t="n">
-        <v>52782912</v>
+        <v>65454669</v>
       </c>
       <c r="D121" t="n">
         <v>66435006</v>
@@ -14979,7 +14979,7 @@
         <v>21191067</v>
       </c>
       <c r="F121" t="n">
-        <v>395857551</v>
+        <v>383185794</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -15003,10 +15003,10 @@
         <v>784</v>
       </c>
       <c r="N121" t="n">
-        <v>0.00143313133364987</v>
+        <v>0.00148052424928884</v>
       </c>
       <c r="O121" t="n">
-        <v>0.0018949233486548</v>
+        <v>0.00161779478680867</v>
       </c>
     </row>
     <row r="122">
@@ -15299,7 +15299,7 @@
         <v>797</v>
       </c>
       <c r="C128" t="n">
-        <v>5583852</v>
+        <v>6207570</v>
       </c>
       <c r="D128" t="n">
         <v>98810349</v>
@@ -15308,7 +15308,7 @@
         <v>3314175</v>
       </c>
       <c r="F128" t="n">
-        <v>245298966</v>
+        <v>244675248</v>
       </c>
       <c r="G128" t="n">
         <v>438456</v>
@@ -15332,10 +15332,10 @@
         <v>798</v>
       </c>
       <c r="N128" t="n">
-        <v>0.00129069186537052</v>
+        <v>0.00129398205412261</v>
       </c>
       <c r="O128" t="n">
-        <v>0.0015133433512845</v>
+        <v>0.00141421241589646</v>
       </c>
     </row>
     <row r="129">
@@ -15440,7 +15440,7 @@
         <v>803</v>
       </c>
       <c r="C131" t="n">
-        <v>264963771</v>
+        <v>344422689</v>
       </c>
       <c r="D131" t="n">
         <v>68755218</v>
@@ -15449,7 +15449,7 @@
         <v>103812264</v>
       </c>
       <c r="F131" t="n">
-        <v>1504046466</v>
+        <v>1424587548</v>
       </c>
       <c r="G131" t="n">
         <v>1248693</v>
@@ -15473,10 +15473,10 @@
         <v>804</v>
       </c>
       <c r="N131" t="n">
-        <v>0.000905479950776999</v>
+        <v>0.00095598471425078</v>
       </c>
       <c r="O131" t="n">
-        <v>0.0012704343979402</v>
+        <v>0.00104522361958685</v>
       </c>
     </row>
     <row r="132">
@@ -15487,7 +15487,7 @@
         <v>805</v>
       </c>
       <c r="C132" t="n">
-        <v>39194013</v>
+        <v>40654785</v>
       </c>
       <c r="D132" t="n">
         <v>33182787</v>
@@ -15496,7 +15496,7 @@
         <v>35398725</v>
       </c>
       <c r="F132" t="n">
-        <v>1154284419</v>
+        <v>1152823647</v>
       </c>
       <c r="G132" t="n">
         <v>4564041</v>
@@ -15520,10 +15520,10 @@
         <v>806</v>
       </c>
       <c r="N132" t="n">
-        <v>0.00136706124939905</v>
+        <v>0.00136879348728349</v>
       </c>
       <c r="O132" t="n">
-        <v>0.00151680462513656</v>
+        <v>0.0014876711147191</v>
       </c>
     </row>
     <row r="133">
@@ -15534,7 +15534,7 @@
         <v>807</v>
       </c>
       <c r="C133" t="n">
-        <v>723507276</v>
+        <v>840372303</v>
       </c>
       <c r="D133" t="n">
         <v>42853293</v>
@@ -15543,7 +15543,7 @@
         <v>305724852</v>
       </c>
       <c r="F133" t="n">
-        <v>5540996604</v>
+        <v>5424131577</v>
       </c>
       <c r="G133" t="n">
         <v>8850519</v>
@@ -15567,10 +15567,10 @@
         <v>808</v>
       </c>
       <c r="N133" t="n">
-        <v>0.011293865575522</v>
+        <v>0.0115371963072127</v>
       </c>
       <c r="O133" t="n">
-        <v>0.0139882744799043</v>
+        <v>0.0125619206427574</v>
       </c>
     </row>
     <row r="134">
@@ -15581,7 +15581,7 @@
         <v>809</v>
       </c>
       <c r="C134" t="n">
-        <v>959403912</v>
+        <v>1092193107</v>
       </c>
       <c r="D134" t="n">
         <v>65038554</v>
@@ -15590,7 +15590,7 @@
         <v>420237234</v>
       </c>
       <c r="F134" t="n">
-        <v>8703682911</v>
+        <v>8570893716</v>
       </c>
       <c r="G134" t="n">
         <v>8897724</v>
@@ -15614,10 +15614,10 @@
         <v>810</v>
       </c>
       <c r="N134" t="n">
-        <v>0.00739356802723945</v>
+        <v>0.00750811686882432</v>
       </c>
       <c r="O134" t="n">
-        <v>0.00881194405171792</v>
+        <v>0.00803826811750003</v>
       </c>
     </row>
     <row r="135">
@@ -15628,7 +15628,7 @@
         <v>811</v>
       </c>
       <c r="C135" t="n">
-        <v>719036517</v>
+        <v>834440772</v>
       </c>
       <c r="D135" t="n">
         <v>5992029</v>
@@ -15637,7 +15637,7 @@
         <v>220317930</v>
       </c>
       <c r="F135" t="n">
-        <v>3227986395</v>
+        <v>3112582140</v>
       </c>
       <c r="G135" t="n">
         <v>4819521</v>
@@ -15661,10 +15661,10 @@
         <v>812</v>
       </c>
       <c r="N135" t="n">
-        <v>0.00415020237432011</v>
+        <v>0.00430407815705131</v>
       </c>
       <c r="O135" t="n">
-        <v>0.00517180200841958</v>
+        <v>0.00460593992389026</v>
       </c>
     </row>
     <row r="136">
@@ -15675,7 +15675,7 @@
         <v>813</v>
       </c>
       <c r="C136" t="n">
-        <v>723329679</v>
+        <v>839533599</v>
       </c>
       <c r="D136" t="n">
         <v>16288350</v>
@@ -15684,7 +15684,7 @@
         <v>241141446</v>
       </c>
       <c r="F136" t="n">
-        <v>4480373277</v>
+        <v>4364169357</v>
       </c>
       <c r="G136" t="n">
         <v>6518256</v>
@@ -15708,10 +15708,10 @@
         <v>814</v>
       </c>
       <c r="N136" t="n">
-        <v>0.00138544115774129</v>
+        <v>0.00142233103993631</v>
       </c>
       <c r="O136" t="n">
-        <v>0.00174106760324214</v>
+        <v>0.00155385232385004</v>
       </c>
     </row>
     <row r="137">
@@ -15910,7 +15910,7 @@
         <v>823</v>
       </c>
       <c r="C141" t="n">
-        <v>382831455</v>
+        <v>403607808</v>
       </c>
       <c r="D141" t="n">
         <v>63752826</v>
@@ -15919,7 +15919,7 @@
         <v>232884657</v>
       </c>
       <c r="F141" t="n">
-        <v>3525136545</v>
+        <v>3504360192</v>
       </c>
       <c r="G141" t="n">
         <v>197679</v>
@@ -15943,10 +15943,10 @@
         <v>824</v>
       </c>
       <c r="N141" t="n">
-        <v>0.00000464996455903242</v>
+        <v>0.00000467753287388102</v>
       </c>
       <c r="O141" t="n">
-        <v>0.00000530749469814102</v>
+        <v>0.0000051342477400734</v>
       </c>
     </row>
     <row r="142">
@@ -15957,7 +15957,7 @@
         <v>825</v>
       </c>
       <c r="C142" t="n">
-        <v>382831455</v>
+        <v>403607808</v>
       </c>
       <c r="D142" t="n">
         <v>63752826</v>
@@ -15966,7 +15966,7 @@
         <v>232884657</v>
       </c>
       <c r="F142" t="n">
-        <v>3525136545</v>
+        <v>3504360192</v>
       </c>
       <c r="G142" t="n">
         <v>197679</v>
@@ -15990,10 +15990,10 @@
         <v>826</v>
       </c>
       <c r="N142" t="n">
-        <v>0.000956558878487358</v>
+        <v>0.000962230043503473</v>
       </c>
       <c r="O142" t="n">
-        <v>0.00109182249237616</v>
+        <v>0.00105618328097568</v>
       </c>
     </row>
     <row r="143">
@@ -16098,7 +16098,7 @@
         <v>831</v>
       </c>
       <c r="C145" t="n">
-        <v>116455479</v>
+        <v>126795411</v>
       </c>
       <c r="D145" t="n">
         <v>7501329</v>
@@ -16107,7 +16107,7 @@
         <v>144605901</v>
       </c>
       <c r="F145" t="n">
-        <v>2430990945</v>
+        <v>2420651013</v>
       </c>
       <c r="G145" t="n">
         <v>1515246</v>
@@ -16131,10 +16131,10 @@
         <v>832</v>
       </c>
       <c r="N145" t="n">
-        <v>0.00163738518162189</v>
+        <v>0.00164437935440634</v>
       </c>
       <c r="O145" t="n">
-        <v>0.00184517618040631</v>
+        <v>0.00177487808165054</v>
       </c>
     </row>
     <row r="146">
@@ -16145,7 +16145,7 @@
         <v>833</v>
       </c>
       <c r="C146" t="n">
-        <v>129976800</v>
+        <v>140316732</v>
       </c>
       <c r="D146" t="n">
         <v>14546883</v>
@@ -16154,7 +16154,7 @@
         <v>132088344</v>
       </c>
       <c r="F146" t="n">
-        <v>2483791626</v>
+        <v>2473451694</v>
       </c>
       <c r="G146" t="n">
         <v>9</v>
@@ -16178,10 +16178,10 @@
         <v>834</v>
       </c>
       <c r="N146" t="n">
-        <v>0.000740446509581718</v>
+        <v>0.000743541846586797</v>
       </c>
       <c r="O146" t="n">
-        <v>0.000829253011991553</v>
+        <v>0.000797776286665084</v>
       </c>
     </row>
     <row r="147">
@@ -16756,7 +16756,7 @@
         <v>859</v>
       </c>
       <c r="C159" t="n">
-        <v>111568272</v>
+        <v>121908204</v>
       </c>
       <c r="D159" t="n">
         <v>6878862</v>
@@ -16765,7 +16765,7 @@
         <v>99838653</v>
       </c>
       <c r="F159" t="n">
-        <v>1996928019</v>
+        <v>1986588087</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -16789,10 +16789,10 @@
         <v>860</v>
       </c>
       <c r="N159" t="n">
-        <v>0.011129886514953</v>
+        <v>0.0111878161232525</v>
       </c>
       <c r="O159" t="n">
-        <v>0.0126250272075998</v>
+        <v>0.0120363292454693</v>
       </c>
     </row>
     <row r="160">
@@ -16803,7 +16803,7 @@
         <v>861</v>
       </c>
       <c r="C160" t="n">
-        <v>113607849</v>
+        <v>123905454</v>
       </c>
       <c r="D160" t="n">
         <v>4589529</v>
@@ -16812,7 +16812,7 @@
         <v>144605301</v>
       </c>
       <c r="F160" t="n">
-        <v>1975803942</v>
+        <v>1965506337</v>
       </c>
       <c r="G160" t="n">
         <v>9</v>
@@ -16836,10 +16836,10 @@
         <v>862</v>
       </c>
       <c r="N160" t="n">
-        <v>0.00225934346779434</v>
+        <v>0.00227118053295801</v>
       </c>
       <c r="O160" t="n">
-        <v>0.00253848225777812</v>
+        <v>0.00244112940652973</v>
       </c>
     </row>
     <row r="161">
@@ -16991,7 +16991,7 @@
         <v>869</v>
       </c>
       <c r="C164" t="n">
-        <v>13925325</v>
+        <v>14099523</v>
       </c>
       <c r="D164" t="n">
         <v>95236614</v>
@@ -17000,7 +17000,7 @@
         <v>3086373</v>
       </c>
       <c r="F164" t="n">
-        <v>312403722</v>
+        <v>312229524</v>
       </c>
       <c r="G164" t="n">
         <v>619335</v>
@@ -17024,10 +17024,10 @@
         <v>870</v>
       </c>
       <c r="N164" t="n">
-        <v>0.00385909381066849</v>
+        <v>0.00386124686274063</v>
       </c>
       <c r="O164" t="n">
-        <v>0.00387361567316796</v>
+        <v>0.00383435230842779</v>
       </c>
     </row>
     <row r="165">
@@ -17038,7 +17038,7 @@
         <v>871</v>
       </c>
       <c r="C165" t="n">
-        <v>4862937</v>
+        <v>4900539</v>
       </c>
       <c r="D165" t="n">
         <v>68145921</v>
@@ -17047,7 +17047,7 @@
         <v>2340030</v>
       </c>
       <c r="F165" t="n">
-        <v>229704498</v>
+        <v>229666896</v>
       </c>
       <c r="G165" t="n">
         <v>619335</v>
@@ -17071,10 +17071,10 @@
         <v>872</v>
       </c>
       <c r="N165" t="n">
-        <v>0.00158418569583256</v>
+        <v>0.00158444506516951</v>
       </c>
       <c r="O165" t="n">
-        <v>0.00177824499265372</v>
+        <v>0.00176901014271116</v>
       </c>
     </row>
     <row r="166">
@@ -17179,7 +17179,7 @@
         <v>877</v>
       </c>
       <c r="C168" t="n">
-        <v>26165859</v>
+        <v>26302455</v>
       </c>
       <c r="D168" t="n">
         <v>100033362</v>
@@ -17188,7 +17188,7 @@
         <v>26720898</v>
       </c>
       <c r="F168" t="n">
-        <v>346305696</v>
+        <v>346169100</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -17212,10 +17212,10 @@
         <v>878</v>
       </c>
       <c r="N168" t="n">
-        <v>0.000830700226195529</v>
+        <v>0.000831028014921031</v>
       </c>
       <c r="O168" t="n">
-        <v>0.000872804320370788</v>
+        <v>0.000870555847345225</v>
       </c>
     </row>
     <row r="169">
@@ -17273,7 +17273,7 @@
         <v>881</v>
       </c>
       <c r="C170" t="n">
-        <v>147223506</v>
+        <v>162936096</v>
       </c>
       <c r="D170" t="n">
         <v>63133305</v>
@@ -17282,7 +17282,7 @@
         <v>70141068</v>
       </c>
       <c r="F170" t="n">
-        <v>4086441579</v>
+        <v>4070728989</v>
       </c>
       <c r="G170" t="n">
         <v>885459</v>
@@ -17306,10 +17306,10 @@
         <v>882</v>
       </c>
       <c r="N170" t="n">
-        <v>0.00216609142670433</v>
+        <v>0.00217445231404964</v>
       </c>
       <c r="O170" t="n">
-        <v>0.0025550959835801</v>
+        <v>0.00238284755343943</v>
       </c>
     </row>
     <row r="171">
@@ -17320,7 +17320,7 @@
         <v>883</v>
       </c>
       <c r="C171" t="n">
-        <v>129360411</v>
+        <v>145073001</v>
       </c>
       <c r="D171" t="n">
         <v>65351754</v>
@@ -17329,7 +17329,7 @@
         <v>69912534</v>
       </c>
       <c r="F171" t="n">
-        <v>3408750087</v>
+        <v>3393037497</v>
       </c>
       <c r="G171" t="n">
         <v>327921</v>
@@ -17353,10 +17353,10 @@
         <v>884</v>
       </c>
       <c r="N171" t="n">
-        <v>0.000880174413912674</v>
+        <v>0.000884250354631433</v>
       </c>
       <c r="O171" t="n">
-        <v>0.00104939253043106</v>
+        <v>0.000972695860677324</v>
       </c>
     </row>
     <row r="172">
@@ -17367,7 +17367,7 @@
         <v>885</v>
       </c>
       <c r="C172" t="n">
-        <v>134713014</v>
+        <v>150425604</v>
       </c>
       <c r="D172" t="n">
         <v>65402943</v>
@@ -17376,7 +17376,7 @@
         <v>69979902</v>
       </c>
       <c r="F172" t="n">
-        <v>3805359126</v>
+        <v>3789646536</v>
       </c>
       <c r="G172" t="n">
         <v>327921</v>
@@ -17400,10 +17400,10 @@
         <v>886</v>
       </c>
       <c r="N172" t="n">
-        <v>0.0156882586828942</v>
+        <v>0.0157533051652393</v>
       </c>
       <c r="O172" t="n">
-        <v>0.0186083867211115</v>
+        <v>0.0172818048383964</v>
       </c>
     </row>
     <row r="173">
@@ -17414,7 +17414,7 @@
         <v>887</v>
       </c>
       <c r="C173" t="n">
-        <v>144721863</v>
+        <v>160434453</v>
       </c>
       <c r="D173" t="n">
         <v>56501802</v>
@@ -17423,7 +17423,7 @@
         <v>69394725</v>
       </c>
       <c r="F173" t="n">
-        <v>3998747028</v>
+        <v>3983034438</v>
       </c>
       <c r="G173" t="n">
         <v>885459</v>
@@ -17447,10 +17447,10 @@
         <v>888</v>
       </c>
       <c r="N173" t="n">
-        <v>0.000583809806835323</v>
+        <v>0.000586112866041958</v>
       </c>
       <c r="O173" t="n">
-        <v>0.000689132315147858</v>
+        <v>0.000642018830176558</v>
       </c>
     </row>
     <row r="174">
@@ -17508,7 +17508,7 @@
         <v>891</v>
       </c>
       <c r="C175" t="n">
-        <v>153097920</v>
+        <v>173455104</v>
       </c>
       <c r="D175" t="n">
         <v>43193754</v>
@@ -17517,7 +17517,7 @@
         <v>69979902</v>
       </c>
       <c r="F175" t="n">
-        <v>5427770739</v>
+        <v>5407413555</v>
       </c>
       <c r="G175" t="n">
         <v>885459</v>
@@ -17541,10 +17541,10 @@
         <v>892</v>
       </c>
       <c r="N175" t="n">
-        <v>0.000265675646474647</v>
+        <v>0.000266675830382276</v>
       </c>
       <c r="O175" t="n">
-        <v>0.000318251448590887</v>
+        <v>0.000291637760593889</v>
       </c>
     </row>
     <row r="176">
@@ -17555,7 +17555,7 @@
         <v>893</v>
       </c>
       <c r="C176" t="n">
-        <v>95151837</v>
+        <v>110864427</v>
       </c>
       <c r="D176" t="n">
         <v>3220992</v>
@@ -17564,7 +17564,7 @@
         <v>68180733</v>
       </c>
       <c r="F176" t="n">
-        <v>2060119704</v>
+        <v>2044407114</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -17588,10 +17588,10 @@
         <v>894</v>
       </c>
       <c r="N176" t="n">
-        <v>0.00150966674296024</v>
+        <v>0.00152126950759862</v>
       </c>
       <c r="O176" t="n">
-        <v>0.000955414378025471</v>
+        <v>0.000871569417334999</v>
       </c>
     </row>
     <row r="177">
@@ -17602,7 +17602,7 @@
         <v>895</v>
       </c>
       <c r="C177" t="n">
-        <v>512214636</v>
+        <v>535976133</v>
       </c>
       <c r="D177" t="n">
         <v>1157334</v>
@@ -17611,7 +17611,7 @@
         <v>103940124</v>
       </c>
       <c r="F177" t="n">
-        <v>3549368499</v>
+        <v>3525607002</v>
       </c>
       <c r="G177" t="n">
         <v>16134336</v>
@@ -17635,10 +17635,10 @@
         <v>896</v>
       </c>
       <c r="N177" t="n">
-        <v>0.00137766043491333</v>
+        <v>0.00138694543867938</v>
       </c>
       <c r="O177" t="n">
-        <v>0.00151610637561252</v>
+        <v>0.00145981001385936</v>
       </c>
     </row>
     <row r="178">
@@ -17649,7 +17649,7 @@
         <v>897</v>
       </c>
       <c r="C178" t="n">
-        <v>379558284</v>
+        <v>387956490</v>
       </c>
       <c r="D178" t="n">
         <v>436419</v>
@@ -17658,7 +17658,7 @@
         <v>18372402</v>
       </c>
       <c r="F178" t="n">
-        <v>2067794736</v>
+        <v>2059396530</v>
       </c>
       <c r="G178" t="n">
         <v>5171916</v>
@@ -17682,10 +17682,10 @@
         <v>898</v>
       </c>
       <c r="N178" t="n">
-        <v>0.00170884071735058</v>
+        <v>0.00171580935896789</v>
       </c>
       <c r="O178" t="n">
-        <v>0.00181358662548583</v>
+        <v>0.00177610252238721</v>
       </c>
     </row>
     <row r="179">
@@ -17696,7 +17696,7 @@
         <v>899</v>
       </c>
       <c r="C179" t="n">
-        <v>151455813</v>
+        <v>166732518</v>
       </c>
       <c r="D179" t="n">
         <v>1218429</v>
@@ -17705,7 +17705,7 @@
         <v>64723971</v>
       </c>
       <c r="F179" t="n">
-        <v>2339927907</v>
+        <v>2324651202</v>
       </c>
       <c r="G179" t="n">
         <v>10916520</v>
@@ -17729,10 +17729,10 @@
         <v>900</v>
       </c>
       <c r="N179" t="n">
-        <v>0.0021221726700735</v>
+        <v>0.00213611876478735</v>
       </c>
       <c r="O179" t="n">
-        <v>0.00242042274262412</v>
+        <v>0.00226066881058224</v>
       </c>
     </row>
     <row r="180">
@@ -17743,7 +17743,7 @@
         <v>902</v>
       </c>
       <c r="C180" t="n">
-        <v>118062534</v>
+        <v>150854811</v>
       </c>
       <c r="D180" t="n">
         <v>323124</v>
@@ -17752,7 +17752,7 @@
         <v>23282499</v>
       </c>
       <c r="F180" t="n">
-        <v>2717531619</v>
+        <v>2684739342</v>
       </c>
       <c r="G180" t="n">
         <v>1576818</v>
@@ -17776,10 +17776,10 @@
         <v>903</v>
       </c>
       <c r="N180" t="n">
-        <v>0.000227636825152245</v>
+        <v>0.00023041725515862</v>
       </c>
       <c r="O180" t="n">
-        <v>0.000308389117571609</v>
+        <v>0.000250315512511362</v>
       </c>
     </row>
     <row r="181">
@@ -19294,7 +19294,7 @@
         <v>968</v>
       </c>
       <c r="C213" t="n">
-        <v>1191867555</v>
+        <v>1322997300</v>
       </c>
       <c r="D213" t="n">
         <v>32368443</v>
@@ -19303,7 +19303,7 @@
         <v>401299920</v>
       </c>
       <c r="F213" t="n">
-        <v>7761574950</v>
+        <v>7630445205</v>
       </c>
       <c r="G213" t="n">
         <v>20906661</v>
@@ -19327,10 +19327,10 @@
         <v>969</v>
       </c>
       <c r="N213" t="n">
-        <v>0.000527308525185343</v>
+        <v>0.000536370359794753</v>
       </c>
       <c r="O213" t="n">
-        <v>0.000616898057123593</v>
+        <v>0.0005699840541412</v>
       </c>
     </row>
     <row r="214">
@@ -19341,7 +19341,7 @@
         <v>970</v>
       </c>
       <c r="C214" t="n">
-        <v>493787319</v>
+        <v>517548816</v>
       </c>
       <c r="D214" t="n">
         <v>5971671</v>
@@ -19350,7 +19350,7 @@
         <v>61072614</v>
       </c>
       <c r="F214" t="n">
-        <v>2720212737</v>
+        <v>2696451240</v>
       </c>
       <c r="G214" t="n">
         <v>12613680</v>
@@ -19374,10 +19374,10 @@
         <v>971</v>
       </c>
       <c r="N214" t="n">
-        <v>0.00137499142957656</v>
+        <v>0.00138710804205011</v>
       </c>
       <c r="O214" t="n">
-        <v>0.0015235414916867</v>
+        <v>0.00146097618610496</v>
       </c>
     </row>
     <row r="215">
@@ -19388,7 +19388,7 @@
         <v>972</v>
       </c>
       <c r="C215" t="n">
-        <v>490078623</v>
+        <v>513840120</v>
       </c>
       <c r="D215" t="n">
         <v>2978508</v>
@@ -19397,7 +19397,7 @@
         <v>63348624</v>
       </c>
       <c r="F215" t="n">
-        <v>2779297716</v>
+        <v>2755536219</v>
       </c>
       <c r="G215" t="n">
         <v>10055058</v>
@@ -19421,10 +19421,10 @@
         <v>973</v>
       </c>
       <c r="N215" t="n">
-        <v>0.00281254050078887</v>
+        <v>0.00283679355622362</v>
       </c>
       <c r="O215" t="n">
-        <v>0.00312946859661935</v>
+        <v>0.00300063576776889</v>
       </c>
     </row>
     <row r="216">
@@ -19435,7 +19435,7 @@
         <v>974</v>
       </c>
       <c r="C216" t="n">
-        <v>493787319</v>
+        <v>517548816</v>
       </c>
       <c r="D216" t="n">
         <v>4168866</v>
@@ -19444,7 +19444,7 @@
         <v>61072614</v>
       </c>
       <c r="F216" t="n">
-        <v>2690498532</v>
+        <v>2666737035</v>
       </c>
       <c r="G216" t="n">
         <v>12613680</v>
@@ -19468,10 +19468,10 @@
         <v>975</v>
       </c>
       <c r="N216" t="n">
-        <v>0.0158759997197426</v>
+        <v>0.0160174600567618</v>
       </c>
       <c r="O216" t="n">
-        <v>0.0176090259881857</v>
+        <v>0.0168858989201281</v>
       </c>
     </row>
     <row r="217">
@@ -19482,7 +19482,7 @@
         <v>976</v>
       </c>
       <c r="C217" t="n">
-        <v>105778092</v>
+        <v>115999164</v>
       </c>
       <c r="D217" t="n">
         <v>1392408</v>
@@ -19491,7 +19491,7 @@
         <v>138217815</v>
       </c>
       <c r="F217" t="n">
-        <v>1560457380</v>
+        <v>1550236308</v>
       </c>
       <c r="G217" t="n">
         <v>9</v>
@@ -19515,10 +19515,10 @@
         <v>977</v>
       </c>
       <c r="N217" t="n">
-        <v>0.00149392985130494</v>
+        <v>0.00150377968161426</v>
       </c>
       <c r="O217" t="n">
-        <v>0.00106061428666076</v>
+        <v>0.00101797112792749</v>
       </c>
     </row>
     <row r="218">
@@ -19858,7 +19858,7 @@
         <v>992</v>
       </c>
       <c r="C225" t="n">
-        <v>58245417</v>
+        <v>63829653</v>
       </c>
       <c r="D225" t="n">
         <v>3618168</v>
@@ -19867,7 +19867,7 @@
         <v>1760742</v>
       </c>
       <c r="F225" t="n">
-        <v>616758987</v>
+        <v>611174751</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -19891,10 +19891,10 @@
         <v>993</v>
       </c>
       <c r="N225" t="n">
-        <v>0.00210103652693106</v>
+        <v>0.00212023346494561</v>
       </c>
       <c r="O225" t="n">
-        <v>0.00160005308788386</v>
+        <v>0.00146382774490076</v>
       </c>
     </row>
     <row r="226">
@@ -19952,7 +19952,7 @@
         <v>996</v>
       </c>
       <c r="C227" t="n">
-        <v>906375</v>
+        <v>906381</v>
       </c>
       <c r="D227" t="n">
         <v>0</v>
@@ -19961,7 +19961,7 @@
         <v>0</v>
       </c>
       <c r="F227" t="n">
-        <v>134848215</v>
+        <v>134848209</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -19985,10 +19985,10 @@
         <v>997</v>
       </c>
       <c r="N227" t="n">
-        <v>0.000308735758817519</v>
+        <v>0.000308735772554554</v>
       </c>
       <c r="O227" t="n">
-        <v>0.000339610003350732</v>
+        <v>0.000339607755223266</v>
       </c>
     </row>
     <row r="228">
@@ -20140,7 +20140,7 @@
         <v>1004</v>
       </c>
       <c r="C231" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D231" t="n">
         <v>0</v>
@@ -20149,7 +20149,7 @@
         <v>0</v>
       </c>
       <c r="F231" t="n">
-        <v>77715060</v>
+        <v>77715057</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -20422,7 +20422,7 @@
         <v>1016</v>
       </c>
       <c r="C237" t="n">
-        <v>11893041</v>
+        <v>18600951</v>
       </c>
       <c r="D237" t="n">
         <v>0</v>
@@ -20431,7 +20431,7 @@
         <v>0</v>
       </c>
       <c r="F237" t="n">
-        <v>6707961</v>
+        <v>51</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -20469,7 +20469,7 @@
         <v>1018</v>
       </c>
       <c r="C238" t="n">
-        <v>0</v>
+        <v>3034353</v>
       </c>
       <c r="D238" t="n">
         <v>0</v>
@@ -20478,7 +20478,7 @@
         <v>0</v>
       </c>
       <c r="F238" t="n">
-        <v>3034401</v>
+        <v>48</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -20563,7 +20563,7 @@
         <v>1022</v>
       </c>
       <c r="C240" t="n">
-        <v>47561724</v>
+        <v>53145960</v>
       </c>
       <c r="D240" t="n">
         <v>0</v>
@@ -20572,7 +20572,7 @@
         <v>1717158</v>
       </c>
       <c r="F240" t="n">
-        <v>382833663</v>
+        <v>377249427</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -20596,10 +20596,10 @@
         <v>1023</v>
       </c>
       <c r="N240" t="n">
-        <v>0.013941820628245</v>
+        <v>0.0141481944782384</v>
       </c>
       <c r="O240" t="n">
-        <v>0.0106564205332418</v>
+        <v>0.00957175802512719</v>
       </c>
     </row>
     <row r="241">
@@ -20610,7 +20610,7 @@
         <v>1024</v>
       </c>
       <c r="C241" t="n">
-        <v>39756246</v>
+        <v>45340482</v>
       </c>
       <c r="D241" t="n">
         <v>0</v>
@@ -20619,7 +20619,7 @@
         <v>1717158</v>
       </c>
       <c r="F241" t="n">
-        <v>362735613</v>
+        <v>357151377</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -20643,10 +20643,10 @@
         <v>1025</v>
       </c>
       <c r="N241" t="n">
-        <v>0.00126493493761254</v>
+        <v>0.00128471281240503</v>
       </c>
       <c r="O241" t="n">
-        <v>0.000880471735572995</v>
+        <v>0.00077598791609609</v>
       </c>
     </row>
     <row r="242">
@@ -20657,7 +20657,7 @@
         <v>1026</v>
       </c>
       <c r="C242" t="n">
-        <v>52687542</v>
+        <v>58271778</v>
       </c>
       <c r="D242" t="n">
         <v>0</v>
@@ -20666,7 +20666,7 @@
         <v>1760742</v>
       </c>
       <c r="F242" t="n">
-        <v>389867697</v>
+        <v>384283461</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -20690,10 +20690,10 @@
         <v>1027</v>
       </c>
       <c r="N242" t="n">
-        <v>0.00190480117439476</v>
+        <v>0.00193248089618975</v>
       </c>
       <c r="O242" t="n">
-        <v>0.00150211167090857</v>
+        <v>0.00136238496830292</v>
       </c>
     </row>
     <row r="243">
@@ -20832,7 +20832,7 @@
         <v>1033</v>
       </c>
       <c r="C2" t="n">
-        <v>719036517</v>
+        <v>834440772</v>
       </c>
       <c r="D2" t="n">
         <v>5992029</v>
@@ -20841,7 +20841,7 @@
         <v>220317930</v>
       </c>
       <c r="F2" t="n">
-        <v>3227986395</v>
+        <v>3112582140</v>
       </c>
       <c r="G2" t="n">
         <v>4819521</v>
@@ -20855,7 +20855,7 @@
         <v>1035</v>
       </c>
       <c r="C3" t="n">
-        <v>719036517</v>
+        <v>834440772</v>
       </c>
       <c r="D3" t="n">
         <v>5992029</v>
@@ -20864,7 +20864,7 @@
         <v>220317930</v>
       </c>
       <c r="F3" t="n">
-        <v>3227983860</v>
+        <v>3112579605</v>
       </c>
       <c r="G3" t="n">
         <v>4819521</v>
@@ -21141,14 +21141,14 @@
         <v>1053</v>
       </c>
       <c r="C21" t="n">
-        <v>2864325</v>
+        <v>2950911</v>
       </c>
       <c r="D21"/>
       <c r="E21" t="n">
         <v>183945</v>
       </c>
       <c r="F21" t="n">
-        <v>8798058</v>
+        <v>8711472</v>
       </c>
       <c r="G21"/>
     </row>
@@ -21359,14 +21359,14 @@
         <v>1068</v>
       </c>
       <c r="C35" t="n">
-        <v>41858712</v>
+        <v>45015438</v>
       </c>
       <c r="D35"/>
       <c r="E35" t="n">
         <v>14105595</v>
       </c>
       <c r="F35" t="n">
-        <v>33002490</v>
+        <v>29845764</v>
       </c>
       <c r="G35"/>
     </row>
@@ -21414,14 +21414,14 @@
         <v>1071</v>
       </c>
       <c r="C38" t="n">
-        <v>29303985</v>
+        <v>29730783</v>
       </c>
       <c r="D38"/>
       <c r="E38" t="n">
         <v>294861</v>
       </c>
       <c r="F38" t="n">
-        <v>550584</v>
+        <v>123786</v>
       </c>
       <c r="G38"/>
     </row>
@@ -21452,13 +21452,11 @@
         <v>1073</v>
       </c>
       <c r="C40" t="n">
-        <v>21844194</v>
+        <v>22951650</v>
       </c>
       <c r="D40"/>
       <c r="E40"/>
-      <c r="F40" t="n">
-        <v>1107456</v>
-      </c>
+      <c r="F40"/>
       <c r="G40"/>
     </row>
     <row r="41">
@@ -21469,14 +21467,14 @@
         <v>1074</v>
       </c>
       <c r="C41" t="n">
-        <v>12811368</v>
+        <v>15296136</v>
       </c>
       <c r="D41"/>
       <c r="E41" t="n">
         <v>1717158</v>
       </c>
       <c r="F41" t="n">
-        <v>7657662</v>
+        <v>5172894</v>
       </c>
       <c r="G41"/>
     </row>
@@ -21488,7 +21486,7 @@
         <v>1075</v>
       </c>
       <c r="C42" t="n">
-        <v>13001133</v>
+        <v>13149438</v>
       </c>
       <c r="D42" t="n">
         <v>37542</v>
@@ -21497,7 +21495,7 @@
         <v>1065699</v>
       </c>
       <c r="F42" t="n">
-        <v>8051967</v>
+        <v>7903662</v>
       </c>
       <c r="G42"/>
     </row>
@@ -21566,14 +21564,14 @@
         <v>1079</v>
       </c>
       <c r="C46" t="n">
-        <v>17351379</v>
+        <v>17528916</v>
       </c>
       <c r="D46"/>
       <c r="E46" t="n">
         <v>694224</v>
       </c>
       <c r="F46" t="n">
-        <v>3618888</v>
+        <v>3441351</v>
       </c>
       <c r="G46"/>
     </row>
@@ -21585,14 +21583,14 @@
         <v>1080</v>
       </c>
       <c r="C47" t="n">
-        <v>4230204</v>
+        <v>4304322</v>
       </c>
       <c r="D47" t="n">
         <v>7023</v>
       </c>
       <c r="E47"/>
       <c r="F47" t="n">
-        <v>407496</v>
+        <v>333378</v>
       </c>
       <c r="G47"/>
     </row>
@@ -21604,12 +21602,12 @@
         <v>1081</v>
       </c>
       <c r="C48" t="n">
-        <v>38319375</v>
+        <v>42208203</v>
       </c>
       <c r="D48"/>
       <c r="E48"/>
       <c r="F48" t="n">
-        <v>20328474</v>
+        <v>16439646</v>
       </c>
       <c r="G48"/>
     </row>
@@ -21621,7 +21619,7 @@
         <v>1082</v>
       </c>
       <c r="C49" t="n">
-        <v>50260458</v>
+        <v>53794416</v>
       </c>
       <c r="D49" t="n">
         <v>10056</v>
@@ -21630,7 +21628,7 @@
         <v>18452643</v>
       </c>
       <c r="F49" t="n">
-        <v>20454684</v>
+        <v>16920726</v>
       </c>
       <c r="G49"/>
     </row>
@@ -21661,7 +21659,7 @@
         <v>1085</v>
       </c>
       <c r="C51" t="n">
-        <v>1191867555</v>
+        <v>1322997300</v>
       </c>
       <c r="D51" t="n">
         <v>32368443</v>
@@ -21670,7 +21668,7 @@
         <v>401299920</v>
       </c>
       <c r="F51" t="n">
-        <v>7761574950</v>
+        <v>7630445205</v>
       </c>
       <c r="G51" t="n">
         <v>20906661</v>
@@ -21684,7 +21682,7 @@
         <v>1086</v>
       </c>
       <c r="C52" t="n">
-        <v>14994795</v>
+        <v>14997654</v>
       </c>
       <c r="D52" t="n">
         <v>10887651</v>
@@ -21693,7 +21691,7 @@
         <v>4674591</v>
       </c>
       <c r="F52" t="n">
-        <v>490770411</v>
+        <v>490767552</v>
       </c>
       <c r="G52" t="n">
         <v>3036867</v>
@@ -21707,7 +21705,7 @@
         <v>1087</v>
       </c>
       <c r="C53" t="n">
-        <v>30435378</v>
+        <v>50069268</v>
       </c>
       <c r="D53" t="n">
         <v>54520995</v>
@@ -21716,7 +21714,7 @@
         <v>44125878</v>
       </c>
       <c r="F53" t="n">
-        <v>364632117</v>
+        <v>344998227</v>
       </c>
       <c r="G53" t="n">
         <v>164886</v>
@@ -21730,7 +21728,7 @@
         <v>1088</v>
       </c>
       <c r="C54" t="n">
-        <v>26165859</v>
+        <v>26302455</v>
       </c>
       <c r="D54" t="n">
         <v>100033362</v>
@@ -21739,7 +21737,7 @@
         <v>26720898</v>
       </c>
       <c r="F54" t="n">
-        <v>346305696</v>
+        <v>346169100</v>
       </c>
       <c r="G54"/>
     </row>
@@ -21751,7 +21749,7 @@
         <v>1089</v>
       </c>
       <c r="C55" t="n">
-        <v>264963771</v>
+        <v>344422689</v>
       </c>
       <c r="D55" t="n">
         <v>68755218</v>
@@ -21760,7 +21758,7 @@
         <v>103812264</v>
       </c>
       <c r="F55" t="n">
-        <v>1504046466</v>
+        <v>1424587548</v>
       </c>
       <c r="G55" t="n">
         <v>1248693</v>
@@ -21774,7 +21772,7 @@
         <v>1090</v>
       </c>
       <c r="C56" t="n">
-        <v>153097920</v>
+        <v>173455104</v>
       </c>
       <c r="D56" t="n">
         <v>43193754</v>
@@ -21783,7 +21781,7 @@
         <v>69979902</v>
       </c>
       <c r="F56" t="n">
-        <v>5427770739</v>
+        <v>5407413555</v>
       </c>
       <c r="G56" t="n">
         <v>885459</v>
@@ -21797,7 +21795,7 @@
         <v>1091</v>
       </c>
       <c r="C57" t="n">
-        <v>31912668</v>
+        <v>34168938</v>
       </c>
       <c r="D57" t="n">
         <v>60388071</v>
@@ -21806,7 +21804,7 @@
         <v>5972787</v>
       </c>
       <c r="F57" t="n">
-        <v>985330470</v>
+        <v>983074200</v>
       </c>
       <c r="G57"/>
     </row>
@@ -21839,7 +21837,7 @@
         <v>1093</v>
       </c>
       <c r="C59" t="n">
-        <v>13431624</v>
+        <v>14387157</v>
       </c>
       <c r="D59" t="n">
         <v>61860492</v>
@@ -21848,7 +21846,7 @@
         <v>13168542</v>
       </c>
       <c r="F59" t="n">
-        <v>136665762</v>
+        <v>135710229</v>
       </c>
       <c r="G59" t="n">
         <v>59340</v>
@@ -21862,7 +21860,7 @@
         <v>1094</v>
       </c>
       <c r="C60" t="n">
-        <v>52782912</v>
+        <v>65454669</v>
       </c>
       <c r="D60" t="n">
         <v>66435006</v>
@@ -21871,7 +21869,7 @@
         <v>21191067</v>
       </c>
       <c r="F60" t="n">
-        <v>395857551</v>
+        <v>383185794</v>
       </c>
       <c r="G60"/>
     </row>
@@ -21883,7 +21881,7 @@
         <v>1095</v>
       </c>
       <c r="C61" t="n">
-        <v>485233044</v>
+        <v>539615559</v>
       </c>
       <c r="D61" t="n">
         <v>48329877</v>
@@ -21892,7 +21890,7 @@
         <v>32817657</v>
       </c>
       <c r="F61" t="n">
-        <v>3930156162</v>
+        <v>3875773647</v>
       </c>
       <c r="G61" t="n">
         <v>9472281</v>
@@ -21906,7 +21904,7 @@
         <v>1096</v>
       </c>
       <c r="C62" t="n">
-        <v>382831455</v>
+        <v>403607808</v>
       </c>
       <c r="D62" t="n">
         <v>63752826</v>
@@ -21915,7 +21913,7 @@
         <v>232884657</v>
       </c>
       <c r="F62" t="n">
-        <v>3525136545</v>
+        <v>3504360192</v>
       </c>
       <c r="G62" t="n">
         <v>197679</v>
@@ -21929,7 +21927,7 @@
         <v>1097</v>
       </c>
       <c r="C63" t="n">
-        <v>65669319</v>
+        <v>80023140</v>
       </c>
       <c r="D63" t="n">
         <v>52853190</v>
@@ -21938,7 +21936,7 @@
         <v>79630614</v>
       </c>
       <c r="F63" t="n">
-        <v>629548767</v>
+        <v>615194946</v>
       </c>
       <c r="G63" t="n">
         <v>124200</v>
@@ -21952,7 +21950,7 @@
         <v>1098</v>
       </c>
       <c r="C64" t="n">
-        <v>4862937</v>
+        <v>4900539</v>
       </c>
       <c r="D64" t="n">
         <v>68145921</v>
@@ -21961,7 +21959,7 @@
         <v>2340030</v>
       </c>
       <c r="F64" t="n">
-        <v>229704498</v>
+        <v>229666896</v>
       </c>
       <c r="G64" t="n">
         <v>619335</v>
@@ -21975,7 +21973,7 @@
         <v>1099</v>
       </c>
       <c r="C65" t="n">
-        <v>5583852</v>
+        <v>6207570</v>
       </c>
       <c r="D65" t="n">
         <v>98810349</v>
@@ -21984,7 +21982,7 @@
         <v>3314175</v>
       </c>
       <c r="F65" t="n">
-        <v>245298966</v>
+        <v>244675248</v>
       </c>
       <c r="G65" t="n">
         <v>438456</v>
@@ -21998,7 +21996,7 @@
         <v>1100</v>
       </c>
       <c r="C66" t="n">
-        <v>46166256</v>
+        <v>49260633</v>
       </c>
       <c r="D66" t="n">
         <v>57855981</v>
@@ -22007,7 +22005,7 @@
         <v>18531039</v>
       </c>
       <c r="F66" t="n">
-        <v>143853144</v>
+        <v>140758767</v>
       </c>
       <c r="G66" t="n">
         <v>677655</v>

--- a/outputs/3_effective_rates_mchenry.xlsx
+++ b/outputs/3_effective_rates_mchenry.xlsx
@@ -3746,10 +3746,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0327229856944844</v>
+        <v>0.0330639540484632</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0358444518789108</v>
+        <v>0.0345339104176219</v>
       </c>
     </row>
     <row r="3">
@@ -3757,10 +3757,10 @@
         <v>4</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0257173355885039</v>
+        <v>0.0259503582129605</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0288830190153557</v>
+        <v>0.0278066922507509</v>
       </c>
     </row>
     <row r="4">
@@ -3768,10 +3768,10 @@
         <v>5</v>
       </c>
       <c r="B4" t="n">
-        <v>0.0327229856944844</v>
+        <v>0.0330639540484632</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0358444518789108</v>
+        <v>0.0345339104176219</v>
       </c>
     </row>
     <row r="5">
@@ -3779,10 +3779,10 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>0.0327229856944844</v>
+        <v>0.0330639540484632</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0358444518789108</v>
+        <v>0.0345339104176219</v>
       </c>
     </row>
     <row r="6">
@@ -3790,10 +3790,10 @@
         <v>7</v>
       </c>
       <c r="B6" t="n">
-        <v>0.0327229856944844</v>
+        <v>0.0330639540484632</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0358444518789108</v>
+        <v>0.0345339104176219</v>
       </c>
     </row>
     <row r="7">
@@ -3801,10 +3801,10 @@
         <v>8</v>
       </c>
       <c r="B7" t="n">
-        <v>0.0327229856944844</v>
+        <v>0.0330639540484632</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0358444518789108</v>
+        <v>0.0345339104176219</v>
       </c>
     </row>
     <row r="8">
@@ -3812,10 +3812,10 @@
         <v>9</v>
       </c>
       <c r="B8" t="n">
-        <v>0.0327229856944844</v>
+        <v>0.0330639540484632</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0358444518789108</v>
+        <v>0.0345339104176219</v>
       </c>
     </row>
     <row r="9">
@@ -3823,10 +3823,10 @@
         <v>10</v>
       </c>
       <c r="B9" t="n">
-        <v>0.023518202146886</v>
+        <v>0.023676254934719</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0261205781846069</v>
+        <v>0.0250735468954593</v>
       </c>
     </row>
     <row r="10">
@@ -3834,10 +3834,10 @@
         <v>11</v>
       </c>
       <c r="B10" t="n">
-        <v>0.0256640561708136</v>
+        <v>0.0258843952953473</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0283027918733732</v>
+        <v>0.0272741116959002</v>
       </c>
     </row>
     <row r="11">
@@ -3845,10 +3845,10 @@
         <v>12</v>
       </c>
       <c r="B11" t="n">
-        <v>0.0230982758544085</v>
+        <v>0.0232565743684788</v>
       </c>
       <c r="C11" t="n">
-        <v>0.025556257284808</v>
+        <v>0.0245364303310349</v>
       </c>
     </row>
     <row r="12">
@@ -3856,10 +3856,10 @@
         <v>13</v>
       </c>
       <c r="B12" t="n">
-        <v>0.0260839824632911</v>
+        <v>0.0263040758615875</v>
       </c>
       <c r="C12" t="n">
-        <v>0.028867112773172</v>
+        <v>0.0278112282603246</v>
       </c>
     </row>
     <row r="13">
@@ -3867,10 +3867,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="n">
-        <v>0.0326697062767941</v>
+        <v>0.03299799113085</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0352642247369283</v>
+        <v>0.0340013298627712</v>
       </c>
     </row>
     <row r="14">
@@ -3878,10 +3878,10 @@
         <v>15</v>
       </c>
       <c r="B14" t="n">
-        <v>0.023679464286321</v>
+        <v>0.0238531506330512</v>
       </c>
       <c r="C14" t="n">
-        <v>0.027049585671023</v>
+        <v>0.0259087129469234</v>
       </c>
     </row>
     <row r="15">
@@ -3889,10 +3889,10 @@
         <v>16</v>
       </c>
       <c r="B15" t="n">
-        <v>0.0259608440655094</v>
+        <v>0.0261726625331803</v>
       </c>
       <c r="C15" t="n">
-        <v>0.0299040408919038</v>
+        <v>0.0286319180964474</v>
       </c>
     </row>
     <row r="16">
@@ -3900,10 +3900,10 @@
         <v>17</v>
       </c>
       <c r="B16" t="n">
-        <v>0.023679464286321</v>
+        <v>0.0238531506330512</v>
       </c>
       <c r="C16" t="n">
-        <v>0.027049585671023</v>
+        <v>0.0259087129469234</v>
       </c>
     </row>
     <row r="17">
@@ -3911,10 +3911,10 @@
         <v>18</v>
       </c>
       <c r="B17" t="n">
-        <v>0.023679464286321</v>
+        <v>0.0238531506330512</v>
       </c>
       <c r="C17" t="n">
-        <v>0.027049585671023</v>
+        <v>0.0259087129469234</v>
       </c>
     </row>
     <row r="18">
@@ -3922,10 +3922,10 @@
         <v>19</v>
       </c>
       <c r="B18" t="n">
-        <v>0.0259608440655094</v>
+        <v>0.0261726625331803</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0299040408919038</v>
+        <v>0.0286319180964474</v>
       </c>
     </row>
     <row r="19">
@@ -3933,10 +3933,10 @@
         <v>20</v>
       </c>
       <c r="B19" t="n">
-        <v>0.0259608440655094</v>
+        <v>0.0261726625331803</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0299040408919038</v>
+        <v>0.0286319180964474</v>
       </c>
     </row>
     <row r="20">
@@ -3944,10 +3944,10 @@
         <v>21</v>
       </c>
       <c r="B20" t="n">
-        <v>0.0259608440655094</v>
+        <v>0.0261726625331803</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0299040408919038</v>
+        <v>0.0286319180964474</v>
       </c>
     </row>
     <row r="21">
@@ -3955,10 +3955,10 @@
         <v>22</v>
       </c>
       <c r="B21" t="n">
-        <v>0.0259608440655094</v>
+        <v>0.0261726625331803</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0299040408919038</v>
+        <v>0.0286319180964474</v>
       </c>
     </row>
     <row r="22">
@@ -3966,10 +3966,10 @@
         <v>23</v>
       </c>
       <c r="B22" t="n">
-        <v>0.030230846759925</v>
+        <v>0.0309969389567095</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0374572991900156</v>
+        <v>0.034008647431567</v>
       </c>
     </row>
     <row r="23">
@@ -3977,10 +3977,10 @@
         <v>24</v>
       </c>
       <c r="B23" t="n">
-        <v>0.0279009146416543</v>
+        <v>0.0283709273202908</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0338307282798322</v>
+        <v>0.0310201519996141</v>
       </c>
     </row>
     <row r="24">
@@ -3988,10 +3988,10 @@
         <v>25</v>
       </c>
       <c r="B24" t="n">
-        <v>0.030230846759925</v>
+        <v>0.0309969389567095</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0374572991900156</v>
+        <v>0.034008647431567</v>
       </c>
     </row>
     <row r="25">
@@ -3999,10 +3999,10 @@
         <v>26</v>
       </c>
       <c r="B25" t="n">
-        <v>0.0291785451980525</v>
+        <v>0.0296487446773501</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0368326702470084</v>
+        <v>0.0340187819433583</v>
       </c>
     </row>
     <row r="26">
@@ -4010,10 +4010,10 @@
         <v>27</v>
       </c>
       <c r="B26" t="n">
-        <v>0.0277965363647827</v>
+        <v>0.0281465928283363</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0331321357313858</v>
+        <v>0.0307370384285794</v>
       </c>
     </row>
     <row r="27">
@@ -4021,10 +4021,10 @@
         <v>28</v>
       </c>
       <c r="B27" t="n">
-        <v>0.0290741669211809</v>
+        <v>0.0294244101853956</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0361340776985619</v>
+        <v>0.0337356683723237</v>
       </c>
     </row>
     <row r="28">
@@ -4032,10 +4032,10 @@
         <v>29</v>
       </c>
       <c r="B28" t="n">
-        <v>0.030764253720952</v>
+        <v>0.0311801709326904</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0381089168299567</v>
+        <v>0.0357081526401049</v>
       </c>
     </row>
     <row r="29">
@@ -4043,10 +4043,10 @@
         <v>30</v>
       </c>
       <c r="B29" t="n">
-        <v>0.0290741669211809</v>
+        <v>0.0294244101853956</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0361340776985619</v>
+        <v>0.0337356683723237</v>
       </c>
     </row>
     <row r="30">
@@ -4054,10 +4054,10 @@
         <v>31</v>
       </c>
       <c r="B30" t="n">
-        <v>0.030230846759925</v>
+        <v>0.0309969389567095</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0374572991900156</v>
+        <v>0.034008647431567</v>
       </c>
     </row>
     <row r="31">
@@ -4065,10 +4065,10 @@
         <v>32</v>
       </c>
       <c r="B31" t="n">
-        <v>0.0290741669211809</v>
+        <v>0.0294244101853956</v>
       </c>
       <c r="C31" t="n">
-        <v>0.0361340776985619</v>
+        <v>0.0337356683723237</v>
       </c>
     </row>
     <row r="32">
@@ -4076,10 +4076,10 @@
         <v>33</v>
       </c>
       <c r="B32" t="n">
-        <v>0.0290741669211809</v>
+        <v>0.0294244101853956</v>
       </c>
       <c r="C32" t="n">
-        <v>0.0361340776985619</v>
+        <v>0.0337356683723237</v>
       </c>
     </row>
     <row r="33">
@@ -4087,10 +4087,10 @@
         <v>34</v>
       </c>
       <c r="B33" t="n">
-        <v>0.0290741669211809</v>
+        <v>0.0294244101853956</v>
       </c>
       <c r="C33" t="n">
-        <v>0.0361340776985619</v>
+        <v>0.0337356683723237</v>
       </c>
     </row>
     <row r="34">
@@ -4098,10 +4098,10 @@
         <v>35</v>
       </c>
       <c r="B34" t="n">
-        <v>0.0290741669211809</v>
+        <v>0.0294244101853956</v>
       </c>
       <c r="C34" t="n">
-        <v>0.0361340776985619</v>
+        <v>0.0337356683723237</v>
       </c>
     </row>
     <row r="35">
@@ -4109,10 +4109,10 @@
         <v>36</v>
       </c>
       <c r="B35" t="n">
-        <v>0.0290741669211809</v>
+        <v>0.0294244101853956</v>
       </c>
       <c r="C35" t="n">
-        <v>0.0361340776985619</v>
+        <v>0.0337356683723237</v>
       </c>
     </row>
     <row r="36">
@@ -4120,10 +4120,10 @@
         <v>37</v>
       </c>
       <c r="B36" t="n">
-        <v>0.0290741669211809</v>
+        <v>0.0294244101853956</v>
       </c>
       <c r="C36" t="n">
-        <v>0.0361340776985619</v>
+        <v>0.0337356683723237</v>
       </c>
     </row>
     <row r="37">
@@ -4131,10 +4131,10 @@
         <v>38</v>
       </c>
       <c r="B37" t="n">
-        <v>0.0290741669211809</v>
+        <v>0.0294244101853956</v>
       </c>
       <c r="C37" t="n">
-        <v>0.0361340776985619</v>
+        <v>0.0337356683723237</v>
       </c>
     </row>
     <row r="38">
@@ -4142,10 +4142,10 @@
         <v>39</v>
       </c>
       <c r="B38" t="n">
-        <v>0.0290741669211809</v>
+        <v>0.0294244101853956</v>
       </c>
       <c r="C38" t="n">
-        <v>0.0361340776985619</v>
+        <v>0.0337356683723237</v>
       </c>
     </row>
     <row r="39">
@@ -4153,10 +4153,10 @@
         <v>40</v>
       </c>
       <c r="B39" t="n">
-        <v>0.0273405088799056</v>
+        <v>0.027663093234688</v>
       </c>
       <c r="C39" t="n">
-        <v>0.0324808822748395</v>
+        <v>0.0302068599136695</v>
       </c>
     </row>
     <row r="40">
@@ -4164,10 +4164,10 @@
         <v>41</v>
       </c>
       <c r="B40" t="n">
-        <v>0.0305531020853097</v>
+        <v>0.0308672881443419</v>
       </c>
       <c r="C40" t="n">
-        <v>0.0359140612014522</v>
+        <v>0.0336971042844264</v>
       </c>
     </row>
     <row r="41">
@@ -4175,10 +4175,10 @@
         <v>42</v>
       </c>
       <c r="B41" t="n">
-        <v>0.0286181394363038</v>
+        <v>0.0289409105917474</v>
       </c>
       <c r="C41" t="n">
-        <v>0.0354828242420157</v>
+        <v>0.0332054898574138</v>
       </c>
     </row>
     <row r="42">
@@ -4186,10 +4186,10 @@
         <v>43</v>
       </c>
       <c r="B42" t="n">
-        <v>0.0299377209517614</v>
+        <v>0.0302600904799901</v>
       </c>
       <c r="C42" t="n">
-        <v>0.0353095521370836</v>
+        <v>0.0330376470853896</v>
       </c>
     </row>
     <row r="43">
@@ -4197,10 +4197,10 @@
         <v>44</v>
       </c>
       <c r="B43" t="n">
-        <v>0.0286181394363038</v>
+        <v>0.0289409105917474</v>
       </c>
       <c r="C43" t="n">
-        <v>0.0354828242420157</v>
+        <v>0.0332054898574138</v>
       </c>
     </row>
     <row r="44">
@@ -4208,10 +4208,10 @@
         <v>45</v>
       </c>
       <c r="B44" t="n">
-        <v>0.0299597453425005</v>
+        <v>0.0302823296972829</v>
       </c>
       <c r="C44" t="n">
-        <v>0.0353358156428424</v>
+        <v>0.0330617932816724</v>
       </c>
     </row>
     <row r="45">
@@ -4219,10 +4219,10 @@
         <v>46</v>
       </c>
       <c r="B45" t="n">
-        <v>0.0280582337508546</v>
+        <v>0.0283806032790833</v>
       </c>
       <c r="C45" t="n">
-        <v>0.0332503135212235</v>
+        <v>0.0309784084695295</v>
       </c>
     </row>
     <row r="46">
@@ -4230,10 +4230,10 @@
         <v>47</v>
       </c>
       <c r="B46" t="n">
-        <v>0.0303082262360749</v>
+        <v>0.0306966713390421</v>
       </c>
       <c r="C46" t="n">
-        <v>0.0374576633734105</v>
+        <v>0.035177974125195</v>
       </c>
     </row>
     <row r="47">
@@ -4241,10 +4241,10 @@
         <v>48</v>
       </c>
       <c r="B47" t="n">
-        <v>0.0286181394363038</v>
+        <v>0.0289409105917474</v>
       </c>
       <c r="C47" t="n">
-        <v>0.0354828242420157</v>
+        <v>0.0332054898574138</v>
       </c>
     </row>
     <row r="48">
@@ -4252,10 +4252,10 @@
         <v>49</v>
       </c>
       <c r="B48" t="n">
-        <v>0.0286181394363038</v>
+        <v>0.0289409105917474</v>
       </c>
       <c r="C48" t="n">
-        <v>0.0354828242420157</v>
+        <v>0.0332054898574138</v>
       </c>
     </row>
     <row r="49">
@@ -4263,10 +4263,10 @@
         <v>50</v>
       </c>
       <c r="B49" t="n">
-        <v>0.0286181394363038</v>
+        <v>0.0289409105917474</v>
       </c>
       <c r="C49" t="n">
-        <v>0.0354828242420157</v>
+        <v>0.0332054898574138</v>
       </c>
     </row>
     <row r="50">
@@ -4274,10 +4274,10 @@
         <v>51</v>
       </c>
       <c r="B50" t="n">
-        <v>0.0286181394363038</v>
+        <v>0.0289409105917474</v>
       </c>
       <c r="C50" t="n">
-        <v>0.0354828242420157</v>
+        <v>0.0332054898574138</v>
       </c>
     </row>
     <row r="51">
@@ -4285,10 +4285,10 @@
         <v>52</v>
       </c>
       <c r="B51" t="n">
-        <v>0.0286181394363038</v>
+        <v>0.0289409105917474</v>
       </c>
       <c r="C51" t="n">
-        <v>0.0354828242420157</v>
+        <v>0.0332054898574138</v>
       </c>
     </row>
     <row r="52">
@@ -4296,10 +4296,10 @@
         <v>53</v>
       </c>
       <c r="B52" t="n">
-        <v>0.0286181394363038</v>
+        <v>0.0289409105917474</v>
       </c>
       <c r="C52" t="n">
-        <v>0.0354828242420157</v>
+        <v>0.0332054898574138</v>
       </c>
     </row>
     <row r="53">
@@ -4307,10 +4307,10 @@
         <v>54</v>
       </c>
       <c r="B53" t="n">
-        <v>0.0286181394363038</v>
+        <v>0.0289409105917474</v>
       </c>
       <c r="C53" t="n">
-        <v>0.0354828242420157</v>
+        <v>0.0332054898574138</v>
       </c>
     </row>
     <row r="54">
@@ -4318,10 +4318,10 @@
         <v>55</v>
       </c>
       <c r="B54" t="n">
-        <v>0.0286181394363038</v>
+        <v>0.0289409105917474</v>
       </c>
       <c r="C54" t="n">
-        <v>0.0354828242420157</v>
+        <v>0.0332054898574138</v>
       </c>
     </row>
     <row r="55">
@@ -4329,10 +4329,10 @@
         <v>56</v>
       </c>
       <c r="B55" t="n">
-        <v>0.0258835180877939</v>
+        <v>0.0261418504413375</v>
       </c>
       <c r="C55" t="n">
-        <v>0.0293349513801241</v>
+        <v>0.0282065625219223</v>
       </c>
     </row>
     <row r="56">
@@ -4340,10 +4340,10 @@
         <v>57</v>
       </c>
       <c r="B56" t="n">
-        <v>0.0328891681937744</v>
+        <v>0.0332554462768402</v>
       </c>
       <c r="C56" t="n">
-        <v>0.0362963842436793</v>
+        <v>0.0349337806887933</v>
       </c>
     </row>
     <row r="57">
@@ -4351,10 +4351,10 @@
         <v>58</v>
       </c>
       <c r="B57" t="n">
-        <v>0.0328891681937744</v>
+        <v>0.0332554462768402</v>
       </c>
       <c r="C57" t="n">
-        <v>0.0362963842436793</v>
+        <v>0.0349337806887933</v>
       </c>
     </row>
     <row r="58">
@@ -4362,10 +4362,10 @@
         <v>59</v>
       </c>
       <c r="B58" t="n">
-        <v>0.0328891681937744</v>
+        <v>0.0332554462768402</v>
       </c>
       <c r="C58" t="n">
-        <v>0.0362963842436793</v>
+        <v>0.0349337806887933</v>
       </c>
     </row>
     <row r="59">
@@ -4373,10 +4373,10 @@
         <v>60</v>
       </c>
       <c r="B59" t="n">
-        <v>0.025551875496777</v>
+        <v>0.0257722146213108</v>
       </c>
       <c r="C59" t="n">
-        <v>0.0285452877786666</v>
+        <v>0.0275166076011936</v>
       </c>
     </row>
     <row r="60">
@@ -4384,10 +4384,10 @@
         <v>61</v>
       </c>
       <c r="B60" t="n">
-        <v>0.027721935688864</v>
+        <v>0.0284785314127319</v>
       </c>
       <c r="C60" t="n">
-        <v>0.0357549409546139</v>
+        <v>0.0308451145791253</v>
       </c>
     </row>
     <row r="61">
@@ -4395,10 +4395,10 @@
         <v>62</v>
       </c>
       <c r="B61" t="n">
-        <v>0.0263048280102817</v>
+        <v>0.0269751778962121</v>
       </c>
       <c r="C61" t="n">
-        <v>0.0335408488930863</v>
+        <v>0.0291313175131199</v>
       </c>
     </row>
     <row r="62">
@@ -4406,10 +4406,10 @@
         <v>63</v>
       </c>
       <c r="B62" t="n">
-        <v>0.0259718017892545</v>
+        <v>0.026191895187551</v>
       </c>
       <c r="C62" t="n">
-        <v>0.0291096086784654</v>
+        <v>0.028053724165618</v>
       </c>
     </row>
     <row r="63">
@@ -4417,10 +4417,10 @@
         <v>64</v>
       </c>
       <c r="B63" t="n">
-        <v>0.0267247543027592</v>
+        <v>0.0273948584624523</v>
       </c>
       <c r="C63" t="n">
-        <v>0.0341051697928852</v>
+        <v>0.0296684340775442</v>
       </c>
     </row>
     <row r="64">
@@ -4428,10 +4428,10 @@
         <v>65</v>
       </c>
       <c r="B64" t="n">
-        <v>0.0269689831753593</v>
+        <v>0.0272755681378306</v>
       </c>
       <c r="C64" t="n">
-        <v>0.0307593798401942</v>
+        <v>0.029230404667199</v>
       </c>
     </row>
     <row r="65">
@@ -4439,10 +4439,10 @@
         <v>66</v>
       </c>
       <c r="B65" t="n">
-        <v>0.0321527965019797</v>
+        <v>0.0331832495705611</v>
       </c>
       <c r="C65" t="n">
-        <v>0.0422474812502961</v>
+        <v>0.0361201784143412</v>
       </c>
     </row>
     <row r="66">
@@ -4450,10 +4450,10 @@
         <v>67</v>
       </c>
       <c r="B66" t="n">
-        <v>0.022986095180372</v>
+        <v>0.0231443936944423</v>
       </c>
       <c r="C66" t="n">
-        <v>0.0257987531901014</v>
+        <v>0.0247789262363283</v>
       </c>
     </row>
     <row r="67">
@@ -4461,10 +4461,10 @@
         <v>68</v>
       </c>
       <c r="B67" t="n">
-        <v>0.0277596735756884</v>
+        <v>0.028520132645461</v>
       </c>
       <c r="C67" t="n">
-        <v>0.0361705225038571</v>
+        <v>0.0311495258676746</v>
       </c>
     </row>
     <row r="68">
@@ -4472,10 +4472,10 @@
         <v>69</v>
       </c>
       <c r="B68" t="n">
-        <v>0.0321905343888041</v>
+        <v>0.0332248508032901</v>
       </c>
       <c r="C68" t="n">
-        <v>0.0426630627995393</v>
+        <v>0.0364245897028905</v>
       </c>
     </row>
     <row r="69">
@@ -4483,10 +4483,10 @@
         <v>70</v>
       </c>
       <c r="B69" t="n">
-        <v>0.0267624921895836</v>
+        <v>0.0274364596951814</v>
       </c>
       <c r="C69" t="n">
-        <v>0.0345207513421283</v>
+        <v>0.0299728453660936</v>
       </c>
     </row>
     <row r="70">
@@ -4494,10 +4494,10 @@
         <v>71</v>
       </c>
       <c r="B70" t="n">
-        <v>0.0267854344780629</v>
+        <v>0.027450886056957</v>
       </c>
       <c r="C70" t="n">
-        <v>0.0345242273502812</v>
+        <v>0.0300363415496656</v>
       </c>
     </row>
     <row r="71">
@@ -4505,10 +4505,10 @@
         <v>72</v>
       </c>
       <c r="B71" t="n">
-        <v>0.0363095537490237</v>
+        <v>0.0369750053279177</v>
       </c>
       <c r="C71" t="n">
-        <v>0.0442183263724116</v>
+        <v>0.039730440571796</v>
       </c>
     </row>
     <row r="72">
@@ -4516,10 +4516,10 @@
         <v>73</v>
       </c>
       <c r="B72" t="n">
-        <v>0.0299989790812992</v>
+        <v>0.030171503752946</v>
       </c>
       <c r="C72" t="n">
-        <v>0.0350814905110707</v>
+        <v>0.0339509882579352</v>
       </c>
     </row>
     <row r="73">
@@ -4527,10 +4527,10 @@
         <v>74</v>
       </c>
       <c r="B73" t="n">
-        <v>0.0277596735756884</v>
+        <v>0.028520132645461</v>
       </c>
       <c r="C73" t="n">
-        <v>0.0361705225038571</v>
+        <v>0.0311495258676746</v>
       </c>
     </row>
     <row r="74">
@@ -4538,10 +4538,10 @@
         <v>75</v>
       </c>
       <c r="B74" t="n">
-        <v>0.0321905343888041</v>
+        <v>0.0332248508032901</v>
       </c>
       <c r="C74" t="n">
-        <v>0.0426630627995393</v>
+        <v>0.0364245897028905</v>
       </c>
     </row>
     <row r="75">
@@ -4549,10 +4549,10 @@
         <v>76</v>
       </c>
       <c r="B75" t="n">
-        <v>0.0297108238667316</v>
+        <v>0.0304712829365042</v>
       </c>
       <c r="C75" t="n">
-        <v>0.0377944513879427</v>
+        <v>0.0327734547517602</v>
       </c>
     </row>
     <row r="76">
@@ -4560,10 +4560,10 @@
         <v>77</v>
       </c>
       <c r="B76" t="n">
-        <v>0.0267624921895836</v>
+        <v>0.0274364596951814</v>
       </c>
       <c r="C76" t="n">
-        <v>0.0345207513421283</v>
+        <v>0.0299728453660936</v>
       </c>
     </row>
     <row r="77">
@@ -4571,10 +4571,10 @@
         <v>78</v>
       </c>
       <c r="B77" t="n">
-        <v>0.0277596735756884</v>
+        <v>0.028520132645461</v>
       </c>
       <c r="C77" t="n">
-        <v>0.0361705225038571</v>
+        <v>0.0311495258676746</v>
       </c>
     </row>
     <row r="78">
@@ -4582,10 +4582,10 @@
         <v>79</v>
       </c>
       <c r="B78" t="n">
-        <v>0.0267624921895836</v>
+        <v>0.0274364596951814</v>
       </c>
       <c r="C78" t="n">
-        <v>0.0345207513421283</v>
+        <v>0.0299728453660936</v>
       </c>
     </row>
     <row r="79">
@@ -4593,10 +4593,10 @@
         <v>80</v>
       </c>
       <c r="B79" t="n">
-        <v>0.0267854344780629</v>
+        <v>0.027450886056957</v>
       </c>
       <c r="C79" t="n">
-        <v>0.0345242273502812</v>
+        <v>0.0300363415496656</v>
       </c>
     </row>
     <row r="80">
@@ -4604,10 +4604,10 @@
         <v>81</v>
       </c>
       <c r="B80" t="n">
-        <v>0.0287365847691061</v>
+        <v>0.0294020363480002</v>
       </c>
       <c r="C80" t="n">
-        <v>0.0361481562343667</v>
+        <v>0.0316602704337511</v>
       </c>
     </row>
     <row r="81">
@@ -4615,10 +4615,10 @@
         <v>82</v>
       </c>
       <c r="B81" t="n">
-        <v>0.0372837928466491</v>
+        <v>0.0380442519164217</v>
       </c>
       <c r="C81" t="n">
-        <v>0.0458646215259875</v>
+        <v>0.0408436248898051</v>
       </c>
     </row>
     <row r="82">
@@ -4626,10 +4626,10 @@
         <v>83</v>
       </c>
       <c r="B82" t="n">
-        <v>0.0363095537490237</v>
+        <v>0.0369750053279177</v>
       </c>
       <c r="C82" t="n">
-        <v>0.0442183263724116</v>
+        <v>0.039730440571796</v>
       </c>
     </row>
     <row r="83">
@@ -4637,10 +4637,10 @@
         <v>84</v>
       </c>
       <c r="B83" t="n">
-        <v>0.0321905343888041</v>
+        <v>0.0332248508032901</v>
       </c>
       <c r="C83" t="n">
-        <v>0.0426630627995393</v>
+        <v>0.0364245897028905</v>
       </c>
     </row>
     <row r="84">
@@ -4648,10 +4648,10 @@
         <v>85</v>
       </c>
       <c r="B84" t="n">
-        <v>0.0321905343888041</v>
+        <v>0.0332248508032901</v>
       </c>
       <c r="C84" t="n">
-        <v>0.0426630627995393</v>
+        <v>0.0364245897028905</v>
       </c>
     </row>
     <row r="85">
@@ -4659,10 +4659,10 @@
         <v>86</v>
       </c>
       <c r="B85" t="n">
-        <v>0.0363095537490237</v>
+        <v>0.0369750053279177</v>
       </c>
       <c r="C85" t="n">
-        <v>0.0442183263724116</v>
+        <v>0.039730440571796</v>
       </c>
     </row>
     <row r="86">
@@ -4670,10 +4670,10 @@
         <v>87</v>
       </c>
       <c r="B86" t="n">
-        <v>0.0383703088961385</v>
+        <v>0.0391307970968791</v>
       </c>
       <c r="C86" t="n">
-        <v>0.0471145694883463</v>
+        <v>0.0420922054989461</v>
       </c>
     </row>
     <row r="87">
@@ -4681,10 +4681,10 @@
         <v>88</v>
       </c>
       <c r="B87" t="n">
-        <v>0.0321905343888041</v>
+        <v>0.0332248508032901</v>
       </c>
       <c r="C87" t="n">
-        <v>0.0426630627995393</v>
+        <v>0.0364245897028905</v>
       </c>
     </row>
     <row r="88">
@@ -4692,10 +4692,10 @@
         <v>89</v>
       </c>
       <c r="B88" t="n">
-        <v>0.0277596735756884</v>
+        <v>0.028520132645461</v>
       </c>
       <c r="C88" t="n">
-        <v>0.0361705225038571</v>
+        <v>0.0311495258676746</v>
       </c>
     </row>
     <row r="89">
@@ -4703,10 +4703,10 @@
         <v>90</v>
       </c>
       <c r="B89" t="n">
-        <v>0.0321905343888041</v>
+        <v>0.0332248508032901</v>
       </c>
       <c r="C89" t="n">
-        <v>0.0426630627995393</v>
+        <v>0.0364245897028905</v>
       </c>
     </row>
     <row r="90">
@@ -4714,10 +4714,10 @@
         <v>91</v>
       </c>
       <c r="B90" t="n">
-        <v>0.0321905343888041</v>
+        <v>0.0332248508032901</v>
       </c>
       <c r="C90" t="n">
-        <v>0.0426630627995393</v>
+        <v>0.0364245897028905</v>
       </c>
     </row>
     <row r="91">
@@ -4725,10 +4725,10 @@
         <v>92</v>
       </c>
       <c r="B91" t="n">
-        <v>0.0278719505275523</v>
+        <v>0.0285374312374143</v>
       </c>
       <c r="C91" t="n">
-        <v>0.03577417531264</v>
+        <v>0.0312849221588066</v>
       </c>
     </row>
     <row r="92">
@@ -4736,10 +4736,10 @@
         <v>93</v>
       </c>
       <c r="B92" t="n">
-        <v>0.0373960697985131</v>
+        <v>0.0380615505083751</v>
       </c>
       <c r="C92" t="n">
-        <v>0.0454682743347704</v>
+        <v>0.040979021180937</v>
       </c>
     </row>
     <row r="93">
@@ -4747,10 +4747,10 @@
         <v>94</v>
       </c>
       <c r="B93" t="n">
-        <v>0.0373960697985131</v>
+        <v>0.0380615505083751</v>
       </c>
       <c r="C93" t="n">
-        <v>0.0454682743347704</v>
+        <v>0.040979021180937</v>
       </c>
     </row>
     <row r="94">
@@ -4758,10 +4758,10 @@
         <v>95</v>
       </c>
       <c r="B94" t="n">
-        <v>0.0312086369681019</v>
+        <v>0.0316453214436196</v>
       </c>
       <c r="C94" t="n">
-        <v>0.0372848652393909</v>
+        <v>0.0348005881708817</v>
       </c>
     </row>
     <row r="95">
@@ -4769,10 +4769,10 @@
         <v>96</v>
       </c>
       <c r="B95" t="n">
-        <v>0.0331950326580459</v>
+        <v>0.0336827273888289</v>
       </c>
       <c r="C95" t="n">
-        <v>0.0397207256724301</v>
+        <v>0.0370693516860613</v>
       </c>
     </row>
     <row r="96">
@@ -4780,10 +4780,10 @@
         <v>97</v>
       </c>
       <c r="B96" t="n">
-        <v>0.0283575614092209</v>
+        <v>0.0285402365640473</v>
       </c>
       <c r="C96" t="n">
-        <v>0.0331586041512398</v>
+        <v>0.0320314474946304</v>
       </c>
     </row>
     <row r="97">
@@ -4791,10 +4791,10 @@
         <v>98</v>
       </c>
       <c r="B97" t="n">
-        <v>0.0251370568256476</v>
+        <v>0.0252345079324807</v>
       </c>
       <c r="C97" t="n">
-        <v>0.0283013300744526</v>
+        <v>0.0276095017404993</v>
       </c>
     </row>
     <row r="98">
@@ -4802,10 +4802,10 @@
         <v>99</v>
       </c>
       <c r="B98" t="n">
-        <v>0.026230532855474</v>
+        <v>0.0269061640485156</v>
       </c>
       <c r="C98" t="n">
-        <v>0.0338512889528091</v>
+        <v>0.0293653813955018</v>
       </c>
     </row>
     <row r="99">
@@ -4813,10 +4813,10 @@
         <v>100</v>
       </c>
       <c r="B99" t="n">
-        <v>0.0340410927375973</v>
+        <v>0.034477777213115</v>
       </c>
       <c r="C99" t="n">
-        <v>0.0406915441659584</v>
+        <v>0.0382072670974491</v>
       </c>
     </row>
     <row r="100">
@@ -4824,10 +4824,10 @@
         <v>101</v>
       </c>
       <c r="B100" t="n">
-        <v>0.0265034642260223</v>
+        <v>0.026602934759865</v>
       </c>
       <c r="C100" t="n">
-        <v>0.0297332755334449</v>
+        <v>0.0290234729452806</v>
       </c>
     </row>
     <row r="101">
@@ -4835,10 +4835,10 @@
         <v>102</v>
       </c>
       <c r="B101" t="n">
-        <v>0.0250154567862365</v>
+        <v>0.0250944968549048</v>
       </c>
       <c r="C101" t="n">
-        <v>0.0281130259862649</v>
+        <v>0.0275250063400676</v>
       </c>
     </row>
     <row r="102">
@@ -4846,10 +4846,10 @@
         <v>103</v>
       </c>
       <c r="B102" t="n">
-        <v>0.0310870369286908</v>
+        <v>0.0315053103660437</v>
       </c>
       <c r="C102" t="n">
-        <v>0.0370965611512032</v>
+        <v>0.03471609277045</v>
       </c>
     </row>
     <row r="103">
@@ -4857,10 +4857,10 @@
         <v>104</v>
       </c>
       <c r="B103" t="n">
-        <v>0.0311166681234365</v>
+        <v>0.0315399679564233</v>
       </c>
       <c r="C103" t="n">
-        <v>0.0371216011835512</v>
+        <v>0.0347097425789197</v>
       </c>
     </row>
     <row r="104">
@@ -4868,10 +4868,10 @@
         <v>105</v>
       </c>
       <c r="B104" t="n">
-        <v>0.0331597872591451</v>
+        <v>0.0335964717346628</v>
       </c>
       <c r="C104" t="n">
-        <v>0.0389087941234765</v>
+        <v>0.0364245170549672</v>
       </c>
     </row>
     <row r="105">
@@ -4879,10 +4879,10 @@
         <v>106</v>
       </c>
       <c r="B105" t="n">
-        <v>0.0279404103616815</v>
+        <v>0.0281097411204579</v>
       </c>
       <c r="C105" t="n">
-        <v>0.0326092836777083</v>
+        <v>0.0315539596468135</v>
       </c>
     </row>
     <row r="106">
@@ -4890,10 +4890,10 @@
         <v>107</v>
       </c>
       <c r="B106" t="n">
-        <v>0.0265034642260223</v>
+        <v>0.026602934759865</v>
       </c>
       <c r="C106" t="n">
-        <v>0.0297332755334449</v>
+        <v>0.0290234729452806</v>
       </c>
     </row>
     <row r="107">
@@ -4901,10 +4901,10 @@
         <v>108</v>
       </c>
       <c r="B107" t="n">
-        <v>0.025554207873187</v>
+        <v>0.0256650033760701</v>
       </c>
       <c r="C107" t="n">
-        <v>0.0288506505479841</v>
+        <v>0.0280869895883162</v>
       </c>
     </row>
     <row r="108">
@@ -4912,10 +4912,10 @@
         <v>109</v>
       </c>
       <c r="B108" t="n">
-        <v>0.0325750443684766</v>
+        <v>0.0330137482710039</v>
       </c>
       <c r="C108" t="n">
-        <v>0.0387168106983833</v>
+        <v>0.0362145593756631</v>
       </c>
     </row>
     <row r="109">
@@ -4923,10 +4923,10 @@
         <v>110</v>
       </c>
       <c r="B109" t="n">
-        <v>0.0258055555253687</v>
+        <v>0.025884595594037</v>
       </c>
       <c r="C109" t="n">
-        <v>0.0289750816382514</v>
+        <v>0.0283870619920541</v>
       </c>
     </row>
     <row r="110">
@@ -4934,10 +4934,10 @@
         <v>111</v>
       </c>
       <c r="B110" t="n">
-        <v>0.0259271555647799</v>
+        <v>0.0260246066716129</v>
       </c>
       <c r="C110" t="n">
-        <v>0.0291633857264391</v>
+        <v>0.0284715573924858</v>
       </c>
     </row>
     <row r="111">
@@ -4945,10 +4945,10 @@
         <v>112</v>
       </c>
       <c r="B111" t="n">
-        <v>0.0287305091008137</v>
+        <v>0.0288998398595902</v>
       </c>
       <c r="C111" t="n">
-        <v>0.0334713393296948</v>
+        <v>0.0324160152988</v>
       </c>
     </row>
     <row r="112">
@@ -4956,10 +4956,10 @@
         <v>113</v>
       </c>
       <c r="B112" t="n">
-        <v>0.0271234525155916</v>
+        <v>0.02727191387769</v>
       </c>
       <c r="C112" t="n">
-        <v>0.0307371905074918</v>
+        <v>0.0298782652556788</v>
       </c>
     </row>
     <row r="113">
@@ -4967,10 +4967,10 @@
         <v>114</v>
       </c>
       <c r="B113" t="n">
-        <v>0.0331030638133804</v>
+        <v>0.0335773739016326</v>
       </c>
       <c r="C113" t="n">
-        <v>0.0395574616165903</v>
+        <v>0.0369785060940993</v>
       </c>
     </row>
     <row r="114">
@@ -4978,10 +4978,10 @@
         <v>115</v>
       </c>
       <c r="B114" t="n">
-        <v>0.027969512595143</v>
+        <v>0.028066963701976</v>
       </c>
       <c r="C114" t="n">
-        <v>0.03170800900102</v>
+        <v>0.0310161806670667</v>
       </c>
     </row>
     <row r="115">
@@ -4989,10 +4989,10 @@
         <v>116</v>
       </c>
       <c r="B115" t="n">
-        <v>0.0291476601483531</v>
+        <v>0.0293303353031796</v>
       </c>
       <c r="C115" t="n">
-        <v>0.0340206598032263</v>
+        <v>0.0328935031466169</v>
       </c>
     </row>
     <row r="116">
@@ -5000,10 +5000,10 @@
         <v>117</v>
       </c>
       <c r="B116" t="n">
-        <v>0.0265034642260223</v>
+        <v>0.026602934759865</v>
       </c>
       <c r="C116" t="n">
-        <v>0.0297332755334449</v>
+        <v>0.0290234729452806</v>
       </c>
     </row>
     <row r="117">
@@ -5011,10 +5011,10 @@
         <v>118</v>
       </c>
       <c r="B117" t="n">
-        <v>0.0265034642260223</v>
+        <v>0.026602934759865</v>
       </c>
       <c r="C117" t="n">
-        <v>0.0297332755334449</v>
+        <v>0.0290234729452806</v>
       </c>
     </row>
     <row r="118">
@@ -5022,10 +5022,10 @@
         <v>119</v>
       </c>
       <c r="B118" t="n">
-        <v>0.0266576611177005</v>
+        <v>0.0267571316515432</v>
       </c>
       <c r="C118" t="n">
-        <v>0.0297332755334449</v>
+        <v>0.0290234729452806</v>
       </c>
     </row>
     <row r="119">
@@ -5033,10 +5033,10 @@
         <v>120</v>
       </c>
       <c r="B119" t="n">
-        <v>0.0266574074728754</v>
+        <v>0.0267568780067181</v>
       </c>
       <c r="C119" t="n">
-        <v>0.0297332755334449</v>
+        <v>0.0290234729452806</v>
       </c>
     </row>
     <row r="120">
@@ -5044,10 +5044,10 @@
         <v>121</v>
       </c>
       <c r="B120" t="n">
-        <v>0.0378816806801817</v>
+        <v>0.0380643558350081</v>
       </c>
       <c r="C120" t="n">
-        <v>0.0428527031733702</v>
+        <v>0.0417255465167609</v>
       </c>
     </row>
     <row r="121">
@@ -5055,10 +5055,10 @@
         <v>122</v>
       </c>
       <c r="B121" t="n">
-        <v>0.0406111561996516</v>
+        <v>0.0410294296370045</v>
       </c>
       <c r="C121" t="n">
-        <v>0.0467906601733336</v>
+        <v>0.0444101917925804</v>
       </c>
     </row>
     <row r="122">
@@ -5066,10 +5066,10 @@
         <v>123</v>
       </c>
       <c r="B122" t="n">
-        <v>0.0265034642260223</v>
+        <v>0.026602934759865</v>
       </c>
       <c r="C122" t="n">
-        <v>0.0297332755334449</v>
+        <v>0.0290234729452806</v>
       </c>
     </row>
     <row r="123">
@@ -5077,10 +5077,10 @@
         <v>124</v>
       </c>
       <c r="B123" t="n">
-        <v>0.0331950326580459</v>
+        <v>0.0336827273888289</v>
       </c>
       <c r="C123" t="n">
-        <v>0.0397207256724301</v>
+        <v>0.0370693516860613</v>
       </c>
     </row>
     <row r="124">
@@ -5088,10 +5088,10 @@
         <v>125</v>
       </c>
       <c r="B124" t="n">
-        <v>0.0331950326580459</v>
+        <v>0.0336827273888289</v>
       </c>
       <c r="C124" t="n">
-        <v>0.0397207256724301</v>
+        <v>0.0370693516860613</v>
       </c>
     </row>
     <row r="125">
@@ -5099,10 +5099,10 @@
         <v>126</v>
       </c>
       <c r="B125" t="n">
-        <v>0.027265023631616</v>
+        <v>0.0273644941654587</v>
       </c>
       <c r="C125" t="n">
-        <v>0.0297332755334449</v>
+        <v>0.0290234729452806</v>
       </c>
     </row>
     <row r="126">
@@ -5110,10 +5110,10 @@
         <v>127</v>
       </c>
       <c r="B126" t="n">
-        <v>0.0331950326580459</v>
+        <v>0.0336827273888289</v>
       </c>
       <c r="C126" t="n">
-        <v>0.0397207256724301</v>
+        <v>0.0370693516860613</v>
       </c>
     </row>
     <row r="127">
@@ -5121,10 +5121,10 @@
         <v>128</v>
       </c>
       <c r="B127" t="n">
-        <v>0.026230532855474</v>
+        <v>0.0269061640485156</v>
       </c>
       <c r="C127" t="n">
-        <v>0.0338512889528091</v>
+        <v>0.0293653813955018</v>
       </c>
     </row>
     <row r="128">
@@ -5132,10 +5132,10 @@
         <v>129</v>
       </c>
       <c r="B128" t="n">
-        <v>0.0331950326580459</v>
+        <v>0.0336827273888289</v>
       </c>
       <c r="C128" t="n">
-        <v>0.0397207256724301</v>
+        <v>0.0370693516860613</v>
       </c>
     </row>
     <row r="129">
@@ -5143,10 +5143,10 @@
         <v>130</v>
       </c>
       <c r="B129" t="n">
-        <v>0.0265034642260223</v>
+        <v>0.026602934759865</v>
       </c>
       <c r="C129" t="n">
-        <v>0.0297332755334449</v>
+        <v>0.0290234729452806</v>
       </c>
     </row>
     <row r="130">
@@ -5154,10 +5154,10 @@
         <v>131</v>
       </c>
       <c r="B130" t="n">
-        <v>0.0265034642260223</v>
+        <v>0.026602934759865</v>
       </c>
       <c r="C130" t="n">
-        <v>0.0297332755334449</v>
+        <v>0.0290234729452806</v>
       </c>
     </row>
     <row r="131">
@@ -5165,10 +5165,10 @@
         <v>132</v>
       </c>
       <c r="B131" t="n">
-        <v>0.0265034642260223</v>
+        <v>0.026602934759865</v>
       </c>
       <c r="C131" t="n">
-        <v>0.0297332755334449</v>
+        <v>0.0290234729452806</v>
       </c>
     </row>
     <row r="132">
@@ -5176,10 +5176,10 @@
         <v>133</v>
       </c>
       <c r="B132" t="n">
-        <v>0.0265034642260223</v>
+        <v>0.026602934759865</v>
       </c>
       <c r="C132" t="n">
-        <v>0.0297332755334449</v>
+        <v>0.0290234729452806</v>
       </c>
     </row>
     <row r="133">
@@ -5187,10 +5187,10 @@
         <v>134</v>
       </c>
       <c r="B133" t="n">
-        <v>0.0265034642260223</v>
+        <v>0.026602934759865</v>
       </c>
       <c r="C133" t="n">
-        <v>0.0297332755334449</v>
+        <v>0.0290234729452806</v>
       </c>
     </row>
     <row r="134">
@@ -5198,10 +5198,10 @@
         <v>135</v>
       </c>
       <c r="B134" t="n">
-        <v>0.0368411681759241</v>
+        <v>0.0375168284999338</v>
       </c>
       <c r="C134" t="n">
-        <v>0.0447953359372983</v>
+        <v>0.0403080610267732</v>
       </c>
     </row>
     <row r="135">
@@ -5209,10 +5209,10 @@
         <v>136</v>
       </c>
       <c r="B135" t="n">
-        <v>0.0389681967296711</v>
+        <v>0.0391509010154655</v>
       </c>
       <c r="C135" t="n">
-        <v>0.044102651135729</v>
+        <v>0.0429741271259019</v>
       </c>
     </row>
     <row r="136">
@@ -5220,10 +5220,10 @@
         <v>137</v>
       </c>
       <c r="B136" t="n">
-        <v>0.0389681967296711</v>
+        <v>0.0391509010154655</v>
       </c>
       <c r="C136" t="n">
-        <v>0.044102651135729</v>
+        <v>0.0429741271259019</v>
       </c>
     </row>
     <row r="137">
@@ -5231,10 +5231,10 @@
         <v>138</v>
       </c>
       <c r="B137" t="n">
-        <v>0.0389681967296711</v>
+        <v>0.0391509010154655</v>
       </c>
       <c r="C137" t="n">
-        <v>0.044102651135729</v>
+        <v>0.0429741271259019</v>
       </c>
     </row>
     <row r="138">
@@ -5242,10 +5242,10 @@
         <v>139</v>
       </c>
       <c r="B138" t="n">
-        <v>0.0265034642260223</v>
+        <v>0.026602934759865</v>
       </c>
       <c r="C138" t="n">
-        <v>0.0297332755334449</v>
+        <v>0.0290234729452806</v>
       </c>
     </row>
     <row r="139">
@@ -5253,10 +5253,10 @@
         <v>140</v>
       </c>
       <c r="B139" t="n">
-        <v>0.0346611760966084</v>
+        <v>0.0347586272034415</v>
       </c>
       <c r="C139" t="n">
-        <v>0.037995429096583</v>
+        <v>0.0373036007626297</v>
       </c>
     </row>
     <row r="140">
@@ -5264,10 +5264,10 @@
         <v>141</v>
       </c>
       <c r="B140" t="n">
-        <v>0.0374645296326423</v>
+        <v>0.0376338603914187</v>
       </c>
       <c r="C140" t="n">
-        <v>0.0423033826998387</v>
+        <v>0.0412480586689439</v>
       </c>
     </row>
     <row r="141">
@@ -5275,10 +5275,10 @@
         <v>142</v>
       </c>
       <c r="B141" t="n">
-        <v>0.030465557138576</v>
+        <v>0.0307176535868326</v>
       </c>
       <c r="C141" t="n">
-        <v>0.0357827686724667</v>
+        <v>0.0343847064102417</v>
       </c>
     </row>
     <row r="142">
@@ -5286,10 +5286,10 @@
         <v>143</v>
       </c>
       <c r="B142" t="n">
-        <v>0.0380032807195928</v>
+        <v>0.038204366912584</v>
       </c>
       <c r="C142" t="n">
-        <v>0.0430410072615579</v>
+        <v>0.0418100419171926</v>
       </c>
     </row>
     <row r="143">
@@ -5297,10 +5297,10 @@
         <v>144</v>
       </c>
       <c r="B143" t="n">
-        <v>0.0294440774587103</v>
+        <v>0.0296267817445047</v>
       </c>
       <c r="C143" t="n">
-        <v>0.0344085521135986</v>
+        <v>0.0332800281037715</v>
       </c>
     </row>
     <row r="144">
@@ -5308,10 +5308,10 @@
         <v>145</v>
       </c>
       <c r="B144" t="n">
-        <v>0.0273170489049634</v>
+        <v>0.027992709228973</v>
       </c>
       <c r="C144" t="n">
-        <v>0.0351012369151679</v>
+        <v>0.0306139620046428</v>
       </c>
     </row>
     <row r="145">
@@ -5319,10 +5319,10 @@
         <v>146</v>
       </c>
       <c r="B145" t="n">
-        <v>0.0321735529781802</v>
+        <v>0.0325918555465011</v>
       </c>
       <c r="C145" t="n">
-        <v>0.038346509113562</v>
+        <v>0.035964673379591</v>
       </c>
     </row>
     <row r="146">
@@ -5330,10 +5330,10 @@
         <v>147</v>
       </c>
       <c r="B146" t="n">
-        <v>0.0389681967296711</v>
+        <v>0.0391509010154655</v>
       </c>
       <c r="C146" t="n">
-        <v>0.044102651135729</v>
+        <v>0.0429741271259019</v>
       </c>
     </row>
     <row r="147">
@@ -5341,10 +5341,10 @@
         <v>148</v>
       </c>
       <c r="B147" t="n">
-        <v>0.041697672249141</v>
+        <v>0.0421159748174619</v>
       </c>
       <c r="C147" t="n">
-        <v>0.0480406081356924</v>
+        <v>0.0456587724017214</v>
       </c>
     </row>
     <row r="148">
@@ -5352,10 +5352,10 @@
         <v>149</v>
       </c>
       <c r="B148" t="n">
-        <v>0.0368411681759241</v>
+        <v>0.0375168284999338</v>
       </c>
       <c r="C148" t="n">
-        <v>0.0447953359372983</v>
+        <v>0.0403080610267732</v>
       </c>
     </row>
     <row r="149">
@@ -5363,10 +5363,10 @@
         <v>150</v>
       </c>
       <c r="B149" t="n">
-        <v>0.0265034642260223</v>
+        <v>0.026602934759865</v>
       </c>
       <c r="C149" t="n">
-        <v>0.0297332755334449</v>
+        <v>0.0290234729452806</v>
       </c>
     </row>
     <row r="150">
@@ -5374,10 +5374,10 @@
         <v>151</v>
       </c>
       <c r="B150" t="n">
-        <v>0.0265034642260223</v>
+        <v>0.026602934759865</v>
       </c>
       <c r="C150" t="n">
-        <v>0.0297332755334449</v>
+        <v>0.0290234729452806</v>
       </c>
     </row>
     <row r="151">
@@ -5385,10 +5385,10 @@
         <v>152</v>
       </c>
       <c r="B151" t="n">
-        <v>0.0345395760571972</v>
+        <v>0.0346186161258655</v>
       </c>
       <c r="C151" t="n">
-        <v>0.0378071250083953</v>
+        <v>0.037219105362198</v>
       </c>
     </row>
     <row r="152">
@@ -5396,10 +5396,10 @@
         <v>153</v>
       </c>
       <c r="B152" t="n">
-        <v>0.0265034642260223</v>
+        <v>0.026602934759865</v>
       </c>
       <c r="C152" t="n">
-        <v>0.0297332755334449</v>
+        <v>0.0290234729452806</v>
       </c>
     </row>
     <row r="153">
@@ -5407,10 +5407,10 @@
         <v>154</v>
       </c>
       <c r="B153" t="n">
-        <v>0.0265034642260223</v>
+        <v>0.026602934759865</v>
       </c>
       <c r="C153" t="n">
-        <v>0.0297332755334449</v>
+        <v>0.0290234729452806</v>
       </c>
     </row>
     <row r="154">
@@ -5418,10 +5418,10 @@
         <v>155</v>
       </c>
       <c r="B154" t="n">
-        <v>0.0265034642260223</v>
+        <v>0.026602934759865</v>
       </c>
       <c r="C154" t="n">
-        <v>0.0297332755334449</v>
+        <v>0.0290234729452806</v>
       </c>
     </row>
     <row r="155">
@@ -5429,10 +5429,10 @@
         <v>156</v>
       </c>
       <c r="B155" t="n">
-        <v>0.0331950326580459</v>
+        <v>0.0336827273888289</v>
       </c>
       <c r="C155" t="n">
-        <v>0.0397207256724301</v>
+        <v>0.0370693516860613</v>
       </c>
     </row>
     <row r="156">
@@ -5440,10 +5440,10 @@
         <v>157</v>
       </c>
       <c r="B156" t="n">
-        <v>0.0312086369681019</v>
+        <v>0.0316453214436196</v>
       </c>
       <c r="C156" t="n">
-        <v>0.0372848652393909</v>
+        <v>0.0348005881708817</v>
       </c>
     </row>
     <row r="157">
@@ -5451,10 +5451,10 @@
         <v>158</v>
       </c>
       <c r="B157" t="n">
-        <v>0.0265034642260223</v>
+        <v>0.026602934759865</v>
       </c>
       <c r="C157" t="n">
-        <v>0.0297332755334449</v>
+        <v>0.0290234729452806</v>
       </c>
     </row>
     <row r="158">
@@ -5462,10 +5462,10 @@
         <v>159</v>
       </c>
       <c r="B158" t="n">
-        <v>0.0251370568256476</v>
+        <v>0.0252345079324807</v>
       </c>
       <c r="C158" t="n">
-        <v>0.0283013300744526</v>
+        <v>0.0276095017404993</v>
       </c>
     </row>
     <row r="159">
@@ -5473,10 +5473,10 @@
         <v>160</v>
       </c>
       <c r="B159" t="n">
-        <v>0.0265034642260223</v>
+        <v>0.026602934759865</v>
       </c>
       <c r="C159" t="n">
-        <v>0.0297332755334449</v>
+        <v>0.0290234729452806</v>
       </c>
     </row>
     <row r="160">
@@ -5484,10 +5484,10 @@
         <v>161</v>
       </c>
       <c r="B160" t="n">
-        <v>0.0339412425075548</v>
+        <v>0.0343659256881943</v>
       </c>
       <c r="C160" t="n">
-        <v>0.0385315261924767</v>
+        <v>0.0361139592916281</v>
       </c>
     </row>
     <row r="161">
@@ -5495,10 +5495,10 @@
         <v>162</v>
       </c>
       <c r="B161" t="n">
-        <v>0.0311166681234365</v>
+        <v>0.0315399679564233</v>
       </c>
       <c r="C161" t="n">
-        <v>0.0371216011835512</v>
+        <v>0.0347097425789197</v>
       </c>
     </row>
     <row r="162">
@@ -5506,10 +5506,10 @@
         <v>163</v>
       </c>
       <c r="B162" t="n">
-        <v>0.0254052247298786</v>
+        <v>0.0254842330621995</v>
       </c>
       <c r="C162" t="n">
-        <v>0.0284640856777087</v>
+        <v>0.0278774042081057</v>
       </c>
     </row>
     <row r="163">
@@ -5517,10 +5517,10 @@
         <v>164</v>
       </c>
       <c r="B163" t="n">
-        <v>0.0307914859205625</v>
+        <v>0.0312148260000302</v>
       </c>
       <c r="C163" t="n">
-        <v>0.0367355447658594</v>
+        <v>0.0343231003230647</v>
       </c>
     </row>
     <row r="164">
@@ -5528,10 +5528,10 @@
         <v>165</v>
       </c>
       <c r="B164" t="n">
-        <v>0.0340332113522203</v>
+        <v>0.0344712791753907</v>
       </c>
       <c r="C164" t="n">
-        <v>0.0386947902483165</v>
+        <v>0.03620480488359</v>
       </c>
     </row>
     <row r="165">
@@ -5539,10 +5539,10 @@
         <v>166</v>
       </c>
       <c r="B165" t="n">
-        <v>0.0336160603046809</v>
+        <v>0.0340407837318012</v>
       </c>
       <c r="C165" t="n">
-        <v>0.038145469774785</v>
+        <v>0.0357273170357731</v>
       </c>
     </row>
     <row r="166">
@@ -5550,10 +5550,10 @@
         <v>167</v>
       </c>
       <c r="B166" t="n">
-        <v>0.027961631209766</v>
+        <v>0.0280604656642517</v>
       </c>
       <c r="C166" t="n">
-        <v>0.0297112550833781</v>
+        <v>0.0290137184532076</v>
       </c>
     </row>
     <row r="167">
@@ -5561,10 +5561,10 @@
         <v>168</v>
       </c>
       <c r="B167" t="n">
-        <v>0.0269206152735617</v>
+        <v>0.0270334302034544</v>
       </c>
       <c r="C167" t="n">
-        <v>0.0302825960069764</v>
+        <v>0.0295009607930976</v>
       </c>
     </row>
     <row r="168">
@@ -5572,10 +5572,10 @@
         <v>169</v>
       </c>
       <c r="B168" t="n">
-        <v>0.0266576611177005</v>
+        <v>0.0267571316515432</v>
       </c>
       <c r="C168" t="n">
-        <v>0.0297332755334449</v>
+        <v>0.0290234729452806</v>
       </c>
     </row>
     <row r="169">
@@ -5583,10 +5583,10 @@
         <v>170</v>
       </c>
       <c r="B169" t="n">
-        <v>0.0265034642260223</v>
+        <v>0.026602934759865</v>
       </c>
       <c r="C169" t="n">
-        <v>0.0297332755334449</v>
+        <v>0.0290234729452806</v>
       </c>
     </row>
     <row r="170">
@@ -5594,10 +5594,10 @@
         <v>171</v>
       </c>
       <c r="B170" t="n">
-        <v>0.0265034642260223</v>
+        <v>0.026602934759865</v>
       </c>
       <c r="C170" t="n">
-        <v>0.0297332755334449</v>
+        <v>0.0290234729452806</v>
       </c>
     </row>
     <row r="171">
@@ -5605,10 +5605,10 @@
         <v>172</v>
       </c>
       <c r="B171" t="n">
-        <v>0.0266651343544338</v>
+        <v>0.0267646048882765</v>
       </c>
       <c r="C171" t="n">
-        <v>0.0297332755334449</v>
+        <v>0.0290234729452806</v>
       </c>
     </row>
     <row r="172">
@@ -5616,10 +5616,10 @@
         <v>173</v>
       </c>
       <c r="B172" t="n">
-        <v>0.0265034642260223</v>
+        <v>0.026602934759865</v>
       </c>
       <c r="C172" t="n">
-        <v>0.0297332755334449</v>
+        <v>0.0290234729452806</v>
       </c>
     </row>
     <row r="173">
@@ -5627,10 +5627,10 @@
         <v>174</v>
       </c>
       <c r="B173" t="n">
-        <v>0.0340772729211162</v>
+        <v>0.03450197689467</v>
       </c>
       <c r="C173" t="n">
-        <v>0.0386845660507371</v>
+        <v>0.0362666740979398</v>
       </c>
     </row>
     <row r="174">
@@ -5638,10 +5638,10 @@
         <v>175</v>
       </c>
       <c r="B174" t="n">
-        <v>0.0340772729211162</v>
+        <v>0.03450197689467</v>
       </c>
       <c r="C174" t="n">
-        <v>0.0386845660507371</v>
+        <v>0.0362666740979398</v>
       </c>
     </row>
     <row r="175">
@@ -5649,10 +5649,10 @@
         <v>176</v>
       </c>
       <c r="B175" t="n">
-        <v>0.0312526985369978</v>
+        <v>0.031676019162899</v>
       </c>
       <c r="C175" t="n">
-        <v>0.0372746410418116</v>
+        <v>0.0348624573852315</v>
       </c>
     </row>
     <row r="176">
@@ -5660,10 +5660,10 @@
         <v>177</v>
       </c>
       <c r="B176" t="n">
-        <v>0.0265034642260223</v>
+        <v>0.026602934759865</v>
       </c>
       <c r="C176" t="n">
-        <v>0.0297332755334449</v>
+        <v>0.0290234729452806</v>
       </c>
     </row>
     <row r="177">
@@ -5671,10 +5671,10 @@
         <v>178</v>
       </c>
       <c r="B177" t="n">
-        <v>0.0265034642260223</v>
+        <v>0.026602934759865</v>
       </c>
       <c r="C177" t="n">
-        <v>0.0297332755334449</v>
+        <v>0.0290234729452806</v>
       </c>
     </row>
     <row r="178">
@@ -5682,10 +5682,10 @@
         <v>179</v>
       </c>
       <c r="B178" t="n">
-        <v>0.0267048796770159</v>
+        <v>0.0267842896365518</v>
       </c>
       <c r="C178" t="n">
-        <v>0.0314922911506436</v>
+        <v>0.0309001803481328</v>
       </c>
     </row>
     <row r="179">
@@ -5693,10 +5693,10 @@
         <v>180</v>
       </c>
       <c r="B179" t="n">
-        <v>0.0308214854714028</v>
+        <v>0.0314488025540288</v>
       </c>
       <c r="C179" t="n">
-        <v>0.0385323364954704</v>
+        <v>0.0346748470208018</v>
       </c>
     </row>
     <row r="180">
@@ -5704,10 +5704,10 @@
         <v>181</v>
       </c>
       <c r="B180" t="n">
-        <v>0.0261298570159313</v>
+        <v>0.0266068078992885</v>
       </c>
       <c r="C180" t="n">
-        <v>0.0322283528243731</v>
+        <v>0.0292638819824523</v>
       </c>
     </row>
     <row r="181">
@@ -5715,10 +5715,10 @@
         <v>182</v>
       </c>
       <c r="B181" t="n">
-        <v>0.0270048223598343</v>
+        <v>0.0271179500864859</v>
       </c>
       <c r="C181" t="n">
-        <v>0.00770420810940561</v>
+        <v>0.00694059729555411</v>
       </c>
     </row>
     <row r="182">
@@ -5726,10 +5726,10 @@
         <v>183</v>
       </c>
       <c r="B182" t="n">
-        <v>0.0272836207040672</v>
+        <v>0.0277975466023146</v>
       </c>
       <c r="C182" t="n">
-        <v>0.0337747371224559</v>
+        <v>0.0305950435028217</v>
       </c>
     </row>
     <row r="183">
@@ -5737,10 +5737,10 @@
         <v>184</v>
       </c>
       <c r="B183" t="n">
-        <v>0.0296677217832668</v>
+        <v>0.0302580638510027</v>
       </c>
       <c r="C183" t="n">
-        <v>0.0369859521973876</v>
+        <v>0.0333436855004323</v>
       </c>
     </row>
     <row r="184">
@@ -5748,10 +5748,10 @@
         <v>185</v>
       </c>
       <c r="B184" t="n">
-        <v>0.0308214854714028</v>
+        <v>0.0314488025540288</v>
       </c>
       <c r="C184" t="n">
-        <v>0.0385323364954704</v>
+        <v>0.0346748470208018</v>
       </c>
     </row>
     <row r="185">
@@ -5759,10 +5759,10 @@
         <v>186</v>
       </c>
       <c r="B185" t="n">
-        <v>0.0308214854714028</v>
+        <v>0.0314488025540288</v>
       </c>
       <c r="C185" t="n">
-        <v>0.0385323364954704</v>
+        <v>0.0346748470208018</v>
       </c>
     </row>
     <row r="186">
@@ -5770,10 +5770,10 @@
         <v>187</v>
       </c>
       <c r="B186" t="n">
-        <v>0.0308214854714028</v>
+        <v>0.0314488025540288</v>
       </c>
       <c r="C186" t="n">
-        <v>0.0385323364954704</v>
+        <v>0.0346748470208018</v>
       </c>
     </row>
     <row r="187">
@@ -5781,10 +5781,10 @@
         <v>188</v>
       </c>
       <c r="B187" t="n">
-        <v>0.0308214854714028</v>
+        <v>0.0314488025540288</v>
       </c>
       <c r="C187" t="n">
-        <v>0.0385323364954704</v>
+        <v>0.0346748470208018</v>
       </c>
     </row>
     <row r="188">
@@ -5792,10 +5792,10 @@
         <v>189</v>
       </c>
       <c r="B188" t="n">
-        <v>0.0308214854714028</v>
+        <v>0.0314488025540288</v>
       </c>
       <c r="C188" t="n">
-        <v>0.0385323364954704</v>
+        <v>0.0346748470208018</v>
       </c>
     </row>
     <row r="189">
@@ -5803,10 +5803,10 @@
         <v>190</v>
       </c>
       <c r="B189" t="n">
-        <v>0.0308214854714028</v>
+        <v>0.0314488025540288</v>
       </c>
       <c r="C189" t="n">
-        <v>0.0385323364954704</v>
+        <v>0.0346748470208018</v>
       </c>
     </row>
     <row r="190">
@@ -5814,10 +5814,10 @@
         <v>191</v>
       </c>
       <c r="B190" t="n">
-        <v>0.0275167582761075</v>
+        <v>0.0282772857130287</v>
       </c>
       <c r="C190" t="n">
-        <v>0.0358219205608805</v>
+        <v>0.0307958474364203</v>
       </c>
     </row>
     <row r="191">
@@ -5825,10 +5825,10 @@
         <v>192</v>
       </c>
       <c r="B191" t="n">
-        <v>0.0259215773487429</v>
+        <v>0.0263480942217563</v>
       </c>
       <c r="C191" t="n">
-        <v>0.0316973500743866</v>
+        <v>0.0289370075887419</v>
       </c>
     </row>
     <row r="192">
@@ -5836,10 +5836,10 @@
         <v>193</v>
       </c>
       <c r="B192" t="n">
-        <v>0.0265077007560506</v>
+        <v>0.0271955992963791</v>
       </c>
       <c r="C192" t="n">
-        <v>0.0342706698677205</v>
+        <v>0.0295885751937964</v>
       </c>
     </row>
     <row r="193">
@@ -5847,10 +5847,10 @@
         <v>194</v>
       </c>
       <c r="B193" t="n">
-        <v>0.0306132058042144</v>
+        <v>0.0311900888764965</v>
       </c>
       <c r="C193" t="n">
-        <v>0.0380013337454839</v>
+        <v>0.0343479726270913</v>
       </c>
     </row>
     <row r="194">
@@ -5858,10 +5858,10 @@
         <v>195</v>
       </c>
       <c r="B194" t="n">
-        <v>0.0269306348687998</v>
+        <v>0.0274297806384059</v>
       </c>
       <c r="C194" t="n">
-        <v>0.0332486007675467</v>
+        <v>0.0301442798313657</v>
       </c>
     </row>
     <row r="195">
@@ -5869,10 +5869,10 @@
         <v>196</v>
       </c>
       <c r="B195" t="n">
-        <v>0.0261639543951665</v>
+        <v>0.026575808161419</v>
       </c>
       <c r="C195" t="n">
-        <v>0.031858060810716</v>
+        <v>0.0292291720960218</v>
       </c>
     </row>
     <row r="196">
@@ -5880,10 +5880,10 @@
         <v>197</v>
       </c>
       <c r="B196" t="n">
-        <v>0.0267500778024742</v>
+        <v>0.0274233132360418</v>
       </c>
       <c r="C196" t="n">
-        <v>0.0344313806040498</v>
+        <v>0.0298807397010764</v>
       </c>
     </row>
     <row r="197">
@@ -5891,10 +5891,10 @@
         <v>198</v>
       </c>
       <c r="B197" t="n">
-        <v>0.0319476190892231</v>
+        <v>0.0329820038708579</v>
       </c>
       <c r="C197" t="n">
-        <v>0.0423144608565627</v>
+        <v>0.0360709112716361</v>
       </c>
     </row>
     <row r="198">
@@ -5902,10 +5902,10 @@
         <v>199</v>
       </c>
       <c r="B198" t="n">
-        <v>0.0294594421160784</v>
+        <v>0.0299993501734705</v>
       </c>
       <c r="C198" t="n">
-        <v>0.0364549494474011</v>
+        <v>0.0330168111067219</v>
       </c>
     </row>
     <row r="199">
@@ -5913,10 +5913,10 @@
         <v>200</v>
       </c>
       <c r="B199" t="n">
-        <v>0.0270753410368789</v>
+        <v>0.0275388329247823</v>
       </c>
       <c r="C199" t="n">
-        <v>0.0332437343724694</v>
+        <v>0.0302681691091113</v>
       </c>
     </row>
     <row r="200">
@@ -5924,10 +5924,10 @@
         <v>201</v>
       </c>
       <c r="B200" t="n">
-        <v>0.0319476190892231</v>
+        <v>0.0329820038708579</v>
       </c>
       <c r="C200" t="n">
-        <v>0.0423144608565627</v>
+        <v>0.0360709112716361</v>
       </c>
     </row>
     <row r="201">
@@ -5935,10 +5935,10 @@
         <v>202</v>
       </c>
       <c r="B201" t="n">
-        <v>0.0306132058042144</v>
+        <v>0.0311900888764965</v>
       </c>
       <c r="C201" t="n">
-        <v>0.0380013337454839</v>
+        <v>0.0343479726270913</v>
       </c>
     </row>
     <row r="202">
@@ -5946,10 +5946,10 @@
         <v>203</v>
       </c>
       <c r="B202" t="n">
-        <v>0.0315688307245297</v>
+        <v>0.0326588515926647</v>
       </c>
       <c r="C202" t="n">
-        <v>0.0421030257697707</v>
+        <v>0.0357260321650255</v>
       </c>
     </row>
     <row r="203">
@@ -5957,10 +5957,10 @@
         <v>204</v>
       </c>
       <c r="B203" t="n">
-        <v>0.027137969911414</v>
+        <v>0.0279541334348355</v>
       </c>
       <c r="C203" t="n">
-        <v>0.0356104854740885</v>
+        <v>0.0304509683298097</v>
       </c>
     </row>
     <row r="204">
@@ -5968,10 +5968,10 @@
         <v>205</v>
       </c>
       <c r="B204" t="n">
-        <v>0.0260761802197159</v>
+        <v>0.0267986927698946</v>
       </c>
       <c r="C204" t="n">
-        <v>0.0338015999359893</v>
+        <v>0.0291548907125838</v>
       </c>
     </row>
     <row r="205">
@@ -5979,10 +5979,10 @@
         <v>206</v>
       </c>
       <c r="B205" t="n">
-        <v>0.0274305820641576</v>
+        <v>0.0278840120179906</v>
       </c>
       <c r="C205" t="n">
-        <v>0.0327477782831469</v>
+        <v>0.0301484349011939</v>
       </c>
     </row>
     <row r="206">
@@ -5990,10 +5990,10 @@
         <v>207</v>
       </c>
       <c r="B206" t="n">
-        <v>0.0263687923724594</v>
+        <v>0.0267285713530497</v>
       </c>
       <c r="C206" t="n">
-        <v>0.0309388927450477</v>
+        <v>0.0288523572839681</v>
       </c>
     </row>
     <row r="207">
@@ -6001,10 +6001,10 @@
         <v>208</v>
       </c>
       <c r="B207" t="n">
-        <v>0.0310052877727463</v>
+        <v>0.0315018929584011</v>
       </c>
       <c r="C207" t="n">
-        <v>0.0364764955897222</v>
+        <v>0.033903680091854</v>
       </c>
     </row>
     <row r="208">
@@ -6012,10 +6012,10 @@
         <v>209</v>
       </c>
       <c r="B208" t="n">
-        <v>0.027858323716262</v>
+        <v>0.0282441692675712</v>
       </c>
       <c r="C208" t="n">
-        <v>0.0327152903561109</v>
+        <v>0.0305034456141344</v>
       </c>
     </row>
     <row r="209">
@@ -6023,10 +6023,10 @@
         <v>210</v>
       </c>
       <c r="B209" t="n">
-        <v>0.027137969911414</v>
+        <v>0.0279541334348355</v>
       </c>
       <c r="C209" t="n">
-        <v>0.0356104854740885</v>
+        <v>0.0304509683298097</v>
       </c>
     </row>
     <row r="210">
@@ -6034,10 +6034,10 @@
         <v>211</v>
       </c>
       <c r="B210" t="n">
-        <v>0.0290891202024572</v>
+        <v>0.0299052837258787</v>
       </c>
       <c r="C210" t="n">
-        <v>0.0372344143581741</v>
+        <v>0.0320748972138952</v>
       </c>
     </row>
     <row r="211">
@@ -6045,10 +6045,10 @@
         <v>212</v>
       </c>
       <c r="B211" t="n">
-        <v>0.0295157564289438</v>
+        <v>0.0299862950438796</v>
       </c>
       <c r="C211" t="n">
-        <v>0.0347000979786589</v>
+        <v>0.0322525917616877</v>
       </c>
     </row>
     <row r="212">
@@ -6056,10 +6056,10 @@
         <v>213</v>
       </c>
       <c r="B212" t="n">
-        <v>0.0293390480269695</v>
+        <v>0.0297235053242956</v>
       </c>
       <c r="C212" t="n">
-        <v>0.033043329128029</v>
+        <v>0.0308531254773403</v>
       </c>
     </row>
     <row r="213">
@@ -6067,10 +6067,10 @@
         <v>214</v>
       </c>
       <c r="B213" t="n">
-        <v>0.0290891202024572</v>
+        <v>0.0299052837258787</v>
       </c>
       <c r="C213" t="n">
-        <v>0.0372344143581741</v>
+        <v>0.0320748972138952</v>
       </c>
     </row>
     <row r="214">
@@ -6078,10 +6078,10 @@
         <v>215</v>
       </c>
       <c r="B214" t="n">
-        <v>0.0293817323552008</v>
+        <v>0.0298351623090338</v>
       </c>
       <c r="C214" t="n">
-        <v>0.0343717071672324</v>
+        <v>0.0317723637852795</v>
       </c>
     </row>
     <row r="215">
@@ -6089,10 +6089,10 @@
         <v>216</v>
       </c>
       <c r="B215" t="n">
-        <v>0.0303825159113033</v>
+        <v>0.0312418319824352</v>
       </c>
       <c r="C215" t="n">
-        <v>0.0390009376052317</v>
+        <v>0.0338683788366685</v>
       </c>
     </row>
     <row r="216">
@@ -6100,10 +6100,10 @@
         <v>217</v>
       </c>
       <c r="B216" t="n">
-        <v>0.0315688307245297</v>
+        <v>0.0326588515926647</v>
       </c>
       <c r="C216" t="n">
-        <v>0.0421030257697707</v>
+        <v>0.0357260321650255</v>
       </c>
     </row>
     <row r="217">
@@ -6111,10 +6111,10 @@
         <v>218</v>
       </c>
       <c r="B217" t="n">
-        <v>0.0303825159113033</v>
+        <v>0.0312418319824352</v>
       </c>
       <c r="C217" t="n">
-        <v>0.0390009376052317</v>
+        <v>0.0338683788366685</v>
       </c>
     </row>
     <row r="218">
@@ -6122,10 +6122,10 @@
         <v>219</v>
       </c>
       <c r="B218" t="n">
-        <v>0.0303825159113033</v>
+        <v>0.0312418319824352</v>
       </c>
       <c r="C218" t="n">
-        <v>0.0390009376052317</v>
+        <v>0.0338683788366685</v>
       </c>
     </row>
     <row r="219">
@@ -6133,10 +6133,10 @@
         <v>220</v>
       </c>
       <c r="B219" t="n">
-        <v>0.0315688307245297</v>
+        <v>0.0326588515926647</v>
       </c>
       <c r="C219" t="n">
-        <v>0.0421030257697707</v>
+        <v>0.0357260321650255</v>
       </c>
     </row>
     <row r="220">
@@ -6144,10 +6144,10 @@
         <v>221</v>
       </c>
       <c r="B220" t="n">
-        <v>0.0275371043097029</v>
+        <v>0.0282582286058985</v>
       </c>
       <c r="C220" t="n">
-        <v>0.0341296387079074</v>
+        <v>0.0295045705757897</v>
       </c>
     </row>
     <row r="221">
@@ -6155,10 +6155,10 @@
         <v>222</v>
       </c>
       <c r="B221" t="n">
-        <v>0.0315688307245297</v>
+        <v>0.0326588515926647</v>
       </c>
       <c r="C221" t="n">
-        <v>0.0421030257697707</v>
+        <v>0.0357260321650255</v>
       </c>
     </row>
     <row r="222">
@@ -6166,10 +6166,10 @@
         <v>223</v>
       </c>
       <c r="B222" t="n">
-        <v>0.0310566403981184</v>
+        <v>0.0315002194791958</v>
       </c>
       <c r="C222" t="n">
-        <v>0.0362575858588669</v>
+        <v>0.0338953727602947</v>
       </c>
     </row>
     <row r="223">
@@ -6177,10 +6177,10 @@
         <v>224</v>
       </c>
       <c r="B223" t="n">
-        <v>0.0311931875517886</v>
+        <v>0.0316223707622302</v>
       </c>
       <c r="C223" t="n">
-        <v>0.0371788568762391</v>
+        <v>0.0347646834556211</v>
       </c>
     </row>
     <row r="224">
@@ -6188,10 +6188,10 @@
         <v>225</v>
       </c>
       <c r="B224" t="n">
-        <v>0.0293784627490761</v>
+        <v>0.0295177656185253</v>
       </c>
       <c r="C224" t="n">
-        <v>0.0322995445146235</v>
+        <v>0.0313763795471989</v>
       </c>
     </row>
     <row r="225">
@@ -6199,10 +6199,10 @@
         <v>226</v>
       </c>
       <c r="B225" t="n">
-        <v>0.0264201449978315</v>
+        <v>0.0267268978738443</v>
       </c>
       <c r="C225" t="n">
-        <v>0.0307199830141923</v>
+        <v>0.0288440499524087</v>
       </c>
     </row>
     <row r="226">
@@ -6210,10 +6210,10 @@
         <v>227</v>
       </c>
       <c r="B226" t="n">
-        <v>0.0331795832417326</v>
+        <v>0.0336597767074395</v>
       </c>
       <c r="C226" t="n">
-        <v>0.0396147173092782</v>
+        <v>0.0370334469708007</v>
       </c>
     </row>
     <row r="227">
@@ -6221,10 +6221,10 @@
         <v>228</v>
       </c>
       <c r="B227" t="n">
-        <v>0.0279096763416341</v>
+        <v>0.0282424957883659</v>
       </c>
       <c r="C227" t="n">
-        <v>0.0324963806252556</v>
+        <v>0.030495138282575</v>
       </c>
     </row>
     <row r="228">
@@ -6232,10 +6232,10 @@
         <v>229</v>
       </c>
       <c r="B228" t="n">
-        <v>0.0312309830935123</v>
+        <v>0.0313792831395826</v>
       </c>
       <c r="C228" t="n">
-        <v>0.0339471867116321</v>
+        <v>0.0329367739067987</v>
       </c>
     </row>
     <row r="229">
@@ -6243,10 +6243,10 @@
         <v>230</v>
       </c>
       <c r="B229" t="n">
-        <v>0.0284949966515656</v>
+        <v>0.0286356877749979</v>
       </c>
       <c r="C229" t="n">
-        <v>0.0315759416173514</v>
+        <v>0.030631135558639</v>
       </c>
     </row>
     <row r="230">
@@ -6254,10 +6254,10 @@
         <v>231</v>
       </c>
       <c r="B230" t="n">
-        <v>0.027303611095342</v>
+        <v>0.0276089757173717</v>
       </c>
       <c r="C230" t="n">
-        <v>0.0314435859114645</v>
+        <v>0.0295892939409687</v>
       </c>
     </row>
     <row r="231">
@@ -6265,10 +6265,10 @@
         <v>232</v>
       </c>
       <c r="B231" t="n">
-        <v>0.0318675030158153</v>
+        <v>0.0322782434517447</v>
       </c>
       <c r="C231" t="n">
-        <v>0.0375515653008002</v>
+        <v>0.0352425387445326</v>
       </c>
     </row>
     <row r="232">
@@ -6276,10 +6276,10 @@
         <v>233</v>
       </c>
       <c r="B232" t="n">
-        <v>0.0307487235380716</v>
+        <v>0.0308880264075208</v>
       </c>
       <c r="C232" t="n">
-        <v>0.0337331108501037</v>
+        <v>0.0328099458826791</v>
       </c>
     </row>
     <row r="233">
@@ -6287,10 +6287,10 @@
         <v>234</v>
       </c>
       <c r="B233" t="n">
-        <v>0.0332377638048109</v>
+        <v>0.0336485042407403</v>
       </c>
       <c r="C233" t="n">
-        <v>0.0389851316362804</v>
+        <v>0.0366761050800128</v>
       </c>
     </row>
     <row r="234">
@@ -6298,10 +6298,10 @@
         <v>235</v>
       </c>
       <c r="B234" t="n">
-        <v>0.0299845279953681</v>
+        <v>0.0301512856895194</v>
       </c>
       <c r="C234" t="n">
-        <v>0.0333523392284146</v>
+        <v>0.0322822238888053</v>
       </c>
     </row>
     <row r="235">
@@ -6309,10 +6309,10 @@
         <v>236</v>
       </c>
       <c r="B235" t="n">
-        <v>0.0321524618139464</v>
+        <v>0.0325816450243879</v>
       </c>
       <c r="C235" t="n">
-        <v>0.0383051670632922</v>
+        <v>0.0358909936426742</v>
       </c>
     </row>
     <row r="236">
@@ -6320,10 +6320,10 @@
         <v>237</v>
       </c>
       <c r="B236" t="n">
-        <v>0.0286738718843376</v>
+        <v>0.0289792365063673</v>
       </c>
       <c r="C236" t="n">
-        <v>0.0328771522469446</v>
+        <v>0.0310228602764489</v>
       </c>
     </row>
     <row r="237">
@@ -6331,10 +6331,10 @@
         <v>238</v>
       </c>
       <c r="B237" t="n">
-        <v>0.0277904057868271</v>
+        <v>0.0280971586628399</v>
       </c>
       <c r="C237" t="n">
-        <v>0.0321535493496725</v>
+        <v>0.0302776162878889</v>
       </c>
     </row>
     <row r="238">
@@ -6342,10 +6342,10 @@
         <v>239</v>
       </c>
       <c r="B238" t="n">
-        <v>0.0331443378428318</v>
+        <v>0.0335735210532734</v>
       </c>
       <c r="C238" t="n">
-        <v>0.0388027857603246</v>
+        <v>0.0363886123397067</v>
       </c>
     </row>
     <row r="239">
@@ -6353,10 +6353,10 @@
         <v>240</v>
       </c>
       <c r="B239" t="n">
-        <v>0.0295822874647232</v>
+        <v>0.0297305875107936</v>
       </c>
       <c r="C239" t="n">
-        <v>0.0327881044766878</v>
+        <v>0.0317776916718544</v>
       </c>
     </row>
     <row r="240">
@@ -6364,10 +6364,10 @@
         <v>241</v>
       </c>
       <c r="B240" t="n">
-        <v>0.0263366834785718</v>
+        <v>0.0270232244447021</v>
       </c>
       <c r="C240" t="n">
-        <v>0.033933584677845</v>
+        <v>0.0294139720806729</v>
       </c>
     </row>
     <row r="241">
@@ -6375,10 +6375,10 @@
         <v>242</v>
       </c>
       <c r="B241" t="n">
-        <v>0.0316419607080499</v>
+        <v>0.0318934114658278</v>
       </c>
       <c r="C241" t="n">
-        <v>0.0353371468509627</v>
+        <v>0.0340313700363586</v>
       </c>
     </row>
     <row r="242">
@@ -6386,10 +6386,10 @@
         <v>243</v>
       </c>
       <c r="B242" t="n">
-        <v>0.0295671090543158</v>
+        <v>0.0299846215646742</v>
       </c>
       <c r="C242" t="n">
-        <v>0.0344811882478036</v>
+        <v>0.0322442844301283</v>
       </c>
     </row>
     <row r="243">
@@ -6397,10 +6397,10 @@
         <v>244</v>
       </c>
       <c r="B243" t="n">
-        <v>0.0331314920518524</v>
+        <v>0.0334090093803493</v>
       </c>
       <c r="C243" t="n">
-        <v>0.0371135444620259</v>
+        <v>0.0356824583665249</v>
       </c>
     </row>
     <row r="244">
@@ -6408,10 +6408,10 @@
         <v>245</v>
       </c>
       <c r="B244" t="n">
-        <v>0.0283712952888747</v>
+        <v>0.0286780481648875</v>
       </c>
       <c r="C244" t="n">
-        <v>0.0323439118982779</v>
+        <v>0.0304679788364943</v>
       </c>
     </row>
     <row r="245">
@@ -6419,10 +6419,10 @@
         <v>246</v>
       </c>
       <c r="B245" t="n">
-        <v>0.0295152015344506</v>
+        <v>0.0296572543238021</v>
       </c>
       <c r="C245" t="n">
-        <v>0.032042942745011</v>
+        <v>0.0310927145837368</v>
       </c>
     </row>
     <row r="246">
@@ -6430,10 +6430,10 @@
         <v>247</v>
       </c>
       <c r="B246" t="n">
-        <v>0.0275428376379127</v>
+        <v>0.0278804126713144</v>
       </c>
       <c r="C246" t="n">
-        <v>0.0321692172225907</v>
+        <v>0.0301342908595337</v>
       </c>
     </row>
     <row r="247">
@@ -6441,10 +6441,10 @@
         <v>248</v>
       </c>
       <c r="B247" t="n">
-        <v>0.0292686745688535</v>
+        <v>0.0294121156121881</v>
       </c>
       <c r="C247" t="n">
-        <v>0.0324294490499597</v>
+        <v>0.0314575797973976</v>
       </c>
     </row>
     <row r="248">
@@ -6452,10 +6452,10 @@
         <v>249</v>
       </c>
       <c r="B248" t="n">
-        <v>0.0331443378428318</v>
+        <v>0.0335735210532734</v>
       </c>
       <c r="C248" t="n">
-        <v>0.0388027857603246</v>
+        <v>0.0363886123397067</v>
       </c>
     </row>
     <row r="249">
@@ -6463,10 +6463,10 @@
         <v>250</v>
       </c>
       <c r="B249" t="n">
-        <v>0.0331795832417326</v>
+        <v>0.0336597767074395</v>
       </c>
       <c r="C249" t="n">
-        <v>0.0396147173092782</v>
+        <v>0.0370334469708007</v>
       </c>
     </row>
     <row r="250">
@@ -6474,10 +6474,10 @@
         <v>251</v>
       </c>
       <c r="B250" t="n">
-        <v>0.0298652574405611</v>
+        <v>0.0300059485639935</v>
       </c>
       <c r="C250" t="n">
-        <v>0.0330095079528316</v>
+        <v>0.0320647018941191</v>
       </c>
     </row>
     <row r="251">
@@ -6485,10 +6485,10 @@
         <v>252</v>
       </c>
       <c r="B251" t="n">
-        <v>0.0331795832417326</v>
+        <v>0.0336597767074395</v>
       </c>
       <c r="C251" t="n">
-        <v>0.0396147173092782</v>
+        <v>0.0370334469708007</v>
       </c>
     </row>
     <row r="252">
@@ -6496,10 +6496,10 @@
         <v>253</v>
       </c>
       <c r="B252" t="n">
-        <v>0.030152140666364</v>
+        <v>0.0302941934557155</v>
       </c>
       <c r="C252" t="n">
-        <v>0.0331530519472318</v>
+        <v>0.0322028237859575</v>
       </c>
     </row>
     <row r="253">
@@ -6507,10 +6507,10 @@
         <v>254</v>
       </c>
       <c r="B253" t="n">
-        <v>0.0315224014553596</v>
+        <v>0.031664454244711</v>
       </c>
       <c r="C253" t="n">
-        <v>0.034586618282712</v>
+        <v>0.0336363901214377</v>
       </c>
     </row>
     <row r="254">
@@ -6518,10 +6518,10 @@
         <v>255</v>
       </c>
       <c r="B254" t="n">
-        <v>0.0306389353578491</v>
+        <v>0.0307823764011837</v>
       </c>
       <c r="C254" t="n">
-        <v>0.0338630153854399</v>
+        <v>0.0328911461328778</v>
       </c>
     </row>
     <row r="255">
@@ -6529,10 +6529,10 @@
         <v>256</v>
       </c>
       <c r="B255" t="n">
-        <v>0.0331795832417326</v>
+        <v>0.0336597767074395</v>
       </c>
       <c r="C255" t="n">
-        <v>0.0396147173092782</v>
+        <v>0.0370334469708007</v>
       </c>
     </row>
     <row r="256">
@@ -6540,10 +6540,10 @@
         <v>257</v>
       </c>
       <c r="B256" t="n">
-        <v>0.0331795832417326</v>
+        <v>0.0336597767074395</v>
       </c>
       <c r="C256" t="n">
-        <v>0.0396147173092782</v>
+        <v>0.0370334469708007</v>
       </c>
     </row>
     <row r="257">
@@ -6551,10 +6551,10 @@
         <v>258</v>
       </c>
       <c r="B257" t="n">
-        <v>0.0310566403981184</v>
+        <v>0.0315002194791958</v>
       </c>
       <c r="C257" t="n">
-        <v>0.0362575858588669</v>
+        <v>0.0338953727602947</v>
       </c>
     </row>
     <row r="258">
@@ -6562,10 +6562,10 @@
         <v>259</v>
       </c>
       <c r="B258" t="n">
-        <v>0.0311931875517886</v>
+        <v>0.0316223707622302</v>
       </c>
       <c r="C258" t="n">
-        <v>0.0371788568762391</v>
+        <v>0.0347646834556211</v>
       </c>
     </row>
     <row r="259">
@@ -6573,10 +6573,10 @@
         <v>260</v>
       </c>
       <c r="B259" t="n">
-        <v>0.0293784627490761</v>
+        <v>0.0295177656185253</v>
       </c>
       <c r="C259" t="n">
-        <v>0.0322995445146235</v>
+        <v>0.0313763795471989</v>
       </c>
     </row>
     <row r="260">
@@ -6584,10 +6584,10 @@
         <v>261</v>
       </c>
       <c r="B260" t="n">
-        <v>0.031787427613933</v>
+        <v>0.0318432554067541</v>
       </c>
       <c r="C260" t="n">
-        <v>0.0349196201010676</v>
+        <v>0.0345350126931856</v>
       </c>
     </row>
     <row r="261">
@@ -6595,10 +6595,10 @@
         <v>262</v>
       </c>
       <c r="B261" t="n">
-        <v>0.0293867338431711</v>
+        <v>0.0294425824289066</v>
       </c>
       <c r="C261" t="n">
-        <v>0.0332133008993699</v>
+        <v>0.0328283684395393</v>
       </c>
     </row>
     <row r="262">
@@ -6606,10 +6606,10 @@
         <v>263</v>
       </c>
       <c r="B262" t="n">
-        <v>0.033822625779562</v>
+        <v>0.0342333870084058</v>
       </c>
       <c r="C262" t="n">
-        <v>0.0400438816762506</v>
+        <v>0.0377345300680343</v>
       </c>
     </row>
     <row r="263">
@@ -6617,10 +6617,10 @@
         <v>264</v>
       </c>
       <c r="B263" t="n">
-        <v>0.0339257930912415</v>
+        <v>0.0343429750068048</v>
       </c>
       <c r="C263" t="n">
-        <v>0.0384255178293249</v>
+        <v>0.0360780545763675</v>
       </c>
     </row>
     <row r="264">
@@ -6628,10 +6628,10 @@
         <v>265</v>
       </c>
       <c r="B264" t="n">
-        <v>0.0315475139476519</v>
+        <v>0.0316033625333873</v>
       </c>
       <c r="C264" t="n">
-        <v>0.0356589539156925</v>
+        <v>0.0352740214558619</v>
       </c>
     </row>
     <row r="265">
@@ -6639,10 +6639,10 @@
         <v>266</v>
       </c>
       <c r="B265" t="n">
-        <v>0.0292507034296098</v>
+        <v>0.0293065312224309</v>
       </c>
       <c r="C265" t="n">
-        <v>0.0330602610411095</v>
+        <v>0.0326756536332276</v>
       </c>
     </row>
     <row r="266">
@@ -6650,10 +6650,10 @@
         <v>267</v>
       </c>
       <c r="B266" t="n">
-        <v>0.03152581526152</v>
+        <v>0.0319365556974494</v>
       </c>
       <c r="C266" t="n">
-        <v>0.0374451888016676</v>
+        <v>0.0351361622454001</v>
       </c>
     </row>
     <row r="267">
@@ -6661,10 +6661,10 @@
         <v>268</v>
       </c>
       <c r="B267" t="n">
-        <v>0.0280474195413792</v>
+        <v>0.0282520467676276</v>
       </c>
       <c r="C267" t="n">
-        <v>0.0317187914127799</v>
+        <v>0.0301863539683084</v>
       </c>
     </row>
     <row r="268">
@@ -6672,10 +6672,10 @@
         <v>269</v>
       </c>
       <c r="B268" t="n">
-        <v>0.0289180757198785</v>
+        <v>0.0289923462872117</v>
       </c>
       <c r="C268" t="n">
-        <v>0.032793929115681</v>
+        <v>0.0323041748434486</v>
       </c>
     </row>
     <row r="269">
@@ -6683,10 +6683,10 @@
         <v>270</v>
       </c>
       <c r="B269" t="n">
-        <v>0.0316618456750813</v>
+        <v>0.0320726069039251</v>
       </c>
       <c r="C269" t="n">
-        <v>0.037598228659928</v>
+        <v>0.0352888770517118</v>
       </c>
     </row>
     <row r="270">
@@ -6694,10 +6694,10 @@
         <v>271</v>
       </c>
       <c r="B270" t="n">
-        <v>0.0311012187071232</v>
+        <v>0.0315170172750338</v>
       </c>
       <c r="C270" t="n">
-        <v>0.0370155928203993</v>
+        <v>0.0346738378636592</v>
       </c>
     </row>
     <row r="271">
@@ -6705,10 +6705,10 @@
         <v>272</v>
       </c>
       <c r="B271" t="n">
-        <v>0.0302363013076725</v>
+        <v>0.0303889089232839</v>
       </c>
       <c r="C271" t="n">
-        <v>0.0335047862855172</v>
+        <v>0.0324710264932842</v>
       </c>
     </row>
     <row r="272">
@@ -6716,10 +6716,10 @@
         <v>273</v>
       </c>
       <c r="B272" t="n">
-        <v>0.0297632011004409</v>
+        <v>0.0299740755834082</v>
       </c>
       <c r="C272" t="n">
-        <v>0.033623035379401</v>
+        <v>0.0320304132913704</v>
       </c>
     </row>
     <row r="273">
@@ -6727,10 +6727,10 @@
         <v>274</v>
       </c>
       <c r="B273" t="n">
-        <v>0.0319520828667342</v>
+        <v>0.0321109377390645</v>
       </c>
       <c r="C273" t="n">
-        <v>0.0354090302521383</v>
+        <v>0.0343150858163462</v>
       </c>
     </row>
     <row r="274">
@@ -6738,10 +6738,10 @@
         <v>275</v>
       </c>
       <c r="B274" t="n">
-        <v>0.0321524618139464</v>
+        <v>0.0325816450243879</v>
       </c>
       <c r="C274" t="n">
-        <v>0.0383051670632922</v>
+        <v>0.0358909936426742</v>
       </c>
     </row>
     <row r="275">
@@ -6749,10 +6749,10 @@
         <v>276</v>
       </c>
       <c r="B275" t="n">
-        <v>0.0314114835340905</v>
+        <v>0.0314673113269116</v>
       </c>
       <c r="C275" t="n">
-        <v>0.0355059140574321</v>
+        <v>0.0351213066495501</v>
       </c>
     </row>
     <row r="276">
@@ -6760,10 +6760,10 @@
         <v>277</v>
       </c>
       <c r="B276" t="n">
-        <v>0.03132921796535</v>
+        <v>0.0317584219687059</v>
       </c>
       <c r="C276" t="n">
-        <v>0.0373318967344995</v>
+        <v>0.0349173982619328</v>
       </c>
     </row>
     <row r="277">
@@ -6771,10 +6771,10 @@
         <v>278</v>
       </c>
       <c r="B277" t="n">
-        <v>0.0334899980698307</v>
+        <v>0.0339192020731866</v>
       </c>
       <c r="C277" t="n">
-        <v>0.039777549750822</v>
+        <v>0.0373630512782554</v>
       </c>
     </row>
     <row r="278">
@@ -6782,10 +6782,10 @@
         <v>279</v>
       </c>
       <c r="B278" t="n">
-        <v>0.0296961151701682</v>
+        <v>0.0299007423964167</v>
       </c>
       <c r="C278" t="n">
-        <v>0.0328778736477242</v>
+        <v>0.0313454362032527</v>
       </c>
     </row>
     <row r="279">
@@ -6793,10 +6793,10 @@
         <v>280</v>
       </c>
       <c r="B279" t="n">
-        <v>0.0314118967292299</v>
+        <v>0.0316227712121973</v>
       </c>
       <c r="C279" t="n">
-        <v>0.0347821176143453</v>
+        <v>0.0331894955263147</v>
       </c>
     </row>
     <row r="280">
@@ -6804,10 +6804,10 @@
         <v>281</v>
       </c>
       <c r="B280" t="n">
-        <v>0.0311418379218566</v>
+        <v>0.031211454144452</v>
       </c>
       <c r="C280" t="n">
-        <v>0.0352727223007713</v>
+        <v>0.0348123023127298</v>
       </c>
     </row>
     <row r="281">
@@ -6815,10 +6815,10 @@
         <v>282</v>
       </c>
       <c r="B281" t="n">
-        <v>0.033822625779562</v>
+        <v>0.0342333870084058</v>
       </c>
       <c r="C281" t="n">
-        <v>0.0400438816762506</v>
+        <v>0.0377345300680343</v>
       </c>
     </row>
     <row r="282">
@@ -6826,10 +6826,10 @@
         <v>283</v>
       </c>
       <c r="B282" t="n">
-        <v>0.0315475139476519</v>
+        <v>0.0316033625333873</v>
       </c>
       <c r="C282" t="n">
-        <v>0.0356589539156925</v>
+        <v>0.0352740214558619</v>
       </c>
     </row>
     <row r="283">
@@ -6837,10 +6837,10 @@
         <v>284</v>
       </c>
       <c r="B283" t="n">
-        <v>0.0319234580274943</v>
+        <v>0.0319793066132298</v>
       </c>
       <c r="C283" t="n">
-        <v>0.035072659959328</v>
+        <v>0.0346877274994974</v>
       </c>
     </row>
     <row r="284">
@@ -6848,10 +6848,10 @@
         <v>285</v>
       </c>
       <c r="B284" t="n">
-        <v>0.0336007784955232</v>
+        <v>0.0337596333678535</v>
       </c>
       <c r="C284" t="n">
-        <v>0.0365681124870826</v>
+        <v>0.0354741680512905</v>
       </c>
     </row>
     <row r="285">
@@ -6859,10 +6859,10 @@
         <v>286</v>
       </c>
       <c r="B285" t="n">
-        <v>0.034017761935907</v>
+        <v>0.0344483284940012</v>
       </c>
       <c r="C285" t="n">
-        <v>0.0385887818851646</v>
+        <v>0.0361689001683295</v>
       </c>
     </row>
     <row r="286">
@@ -6870,10 +6870,10 @@
         <v>287</v>
       </c>
       <c r="B286" t="n">
-        <v>0.0360347710525122</v>
+        <v>0.0360906196382477</v>
       </c>
       <c r="C286" t="n">
-        <v>0.035072659959328</v>
+        <v>0.0346877274994974</v>
       </c>
     </row>
     <row r="287">
@@ -6881,10 +6881,10 @@
         <v>288</v>
       </c>
       <c r="B287" t="n">
-        <v>0.0312372491206845</v>
+        <v>0.0316530684815095</v>
       </c>
       <c r="C287" t="n">
-        <v>0.0371686326786597</v>
+        <v>0.0348265526699709</v>
       </c>
     </row>
     <row r="288">
@@ -6892,10 +6892,10 @@
         <v>289</v>
       </c>
       <c r="B288" t="n">
-        <v>0.0340618235048029</v>
+        <v>0.0344790262132805</v>
       </c>
       <c r="C288" t="n">
-        <v>0.0385785576875853</v>
+        <v>0.0362307693826792</v>
       </c>
     </row>
     <row r="289">
@@ -6903,10 +6903,10 @@
         <v>290</v>
       </c>
       <c r="B289" t="n">
-        <v>0.030152140666364</v>
+        <v>0.0302941934557155</v>
       </c>
       <c r="C289" t="n">
-        <v>0.0331530519472318</v>
+        <v>0.0322028237859575</v>
       </c>
     </row>
     <row r="290">
@@ -6914,10 +6914,10 @@
         <v>291</v>
       </c>
       <c r="B290" t="n">
-        <v>0.0315224014553596</v>
+        <v>0.031664454244711</v>
       </c>
       <c r="C290" t="n">
-        <v>0.034586618282712</v>
+        <v>0.0336363901214377</v>
       </c>
     </row>
     <row r="291">
@@ -6925,10 +6925,10 @@
         <v>292</v>
       </c>
       <c r="B291" t="n">
-        <v>0.0325219360683749</v>
+        <v>0.0326745436839863</v>
       </c>
       <c r="C291" t="n">
-        <v>0.0357739777226823</v>
+        <v>0.0347402179304493</v>
       </c>
     </row>
     <row r="292">
@@ -6936,10 +6936,10 @@
         <v>293</v>
       </c>
       <c r="B292" t="n">
-        <v>0.0351238822906593</v>
+        <v>0.0351797308763948</v>
       </c>
       <c r="C292" t="n">
-        <v>0.0386389767855928</v>
+        <v>0.0382540443257622</v>
       </c>
     </row>
     <row r="293">
@@ -6947,10 +6947,10 @@
         <v>294</v>
       </c>
       <c r="B293" t="n">
-        <v>0.0281907920066639</v>
+        <v>0.0284136704414379</v>
       </c>
       <c r="C293" t="n">
-        <v>0.031815906970211</v>
+        <v>0.0301498587493312</v>
       </c>
     </row>
     <row r="294">
@@ -6958,10 +6958,10 @@
         <v>295</v>
       </c>
       <c r="B294" t="n">
-        <v>0.0328824204621354</v>
+        <v>0.0332556650961781</v>
       </c>
       <c r="C294" t="n">
-        <v>0.0381198906413083</v>
+        <v>0.0355608237876807</v>
       </c>
     </row>
     <row r="295">
@@ -6969,10 +6969,10 @@
         <v>296</v>
       </c>
       <c r="B295" t="n">
-        <v>0.030907214385633</v>
+        <v>0.031480462236555</v>
       </c>
       <c r="C295" t="n">
-        <v>0.0382717922611663</v>
+        <v>0.0347247321976169</v>
       </c>
     </row>
     <row r="296">
@@ -6980,10 +6980,10 @@
         <v>297</v>
       </c>
       <c r="B296" t="n">
-        <v>0.0328824204621354</v>
+        <v>0.0332556650961781</v>
       </c>
       <c r="C296" t="n">
-        <v>0.0381198906413083</v>
+        <v>0.0355608237876807</v>
       </c>
     </row>
     <row r="297">
@@ -6991,10 +6991,10 @@
         <v>298</v>
       </c>
       <c r="B297" t="n">
-        <v>0.0262155859301615</v>
+        <v>0.0266384675818147</v>
       </c>
       <c r="C297" t="n">
-        <v>0.031967808590069</v>
+        <v>0.0293137671592674</v>
       </c>
     </row>
     <row r="298">
@@ -7002,10 +7002,10 @@
         <v>299</v>
       </c>
       <c r="B298" t="n">
-        <v>0.0317286567739995</v>
+        <v>0.0320649263931521</v>
       </c>
       <c r="C298" t="n">
-        <v>0.0365735063432255</v>
+        <v>0.0342296622673113</v>
       </c>
     </row>
     <row r="299">
@@ -7013,10 +7013,10 @@
         <v>300</v>
       </c>
       <c r="B299" t="n">
-        <v>0.0317286567739995</v>
+        <v>0.0320649263931521</v>
       </c>
       <c r="C299" t="n">
-        <v>0.0365735063432255</v>
+        <v>0.0342296622673113</v>
       </c>
     </row>
     <row r="300">
@@ -7024,10 +7024,10 @@
         <v>301</v>
       </c>
       <c r="B300" t="n">
-        <v>0.029753450697497</v>
+        <v>0.0302897235335289</v>
       </c>
       <c r="C300" t="n">
-        <v>0.0367254079630835</v>
+        <v>0.0333935706772474</v>
       </c>
     </row>
     <row r="301">
@@ -7035,10 +7035,10 @@
         <v>302</v>
       </c>
       <c r="B301" t="n">
-        <v>0.0293445556947999</v>
+        <v>0.0296044091444639</v>
       </c>
       <c r="C301" t="n">
-        <v>0.0333622912682938</v>
+        <v>0.0314810202697007</v>
       </c>
     </row>
     <row r="302">
@@ -7046,10 +7046,10 @@
         <v>303</v>
       </c>
       <c r="B302" t="n">
-        <v>0.0273693496182975</v>
+        <v>0.0278292062848408</v>
       </c>
       <c r="C302" t="n">
-        <v>0.0335141928881518</v>
+        <v>0.0306449286796368</v>
       </c>
     </row>
     <row r="303">
@@ -7057,10 +7057,10 @@
         <v>304</v>
       </c>
       <c r="B303" t="n">
-        <v>0.0281907920066639</v>
+        <v>0.0284136704414379</v>
       </c>
       <c r="C303" t="n">
-        <v>0.031815906970211</v>
+        <v>0.0301498587493312</v>
       </c>
     </row>
     <row r="304">
@@ -7068,10 +7068,10 @@
         <v>305</v>
       </c>
       <c r="B304" t="n">
-        <v>0.0328824204621354</v>
+        <v>0.0332556650961781</v>
       </c>
       <c r="C304" t="n">
-        <v>0.0381198906413083</v>
+        <v>0.0355608237876807</v>
       </c>
     </row>
     <row r="305">
@@ -7079,10 +7079,10 @@
         <v>306</v>
       </c>
       <c r="B305" t="n">
-        <v>0.0256664997264987</v>
+        <v>0.0260747906480518</v>
       </c>
       <c r="C305" t="n">
-        <v>0.031176873654948</v>
+        <v>0.0286617478565381</v>
       </c>
     </row>
     <row r="306">
@@ -7090,10 +7090,10 @@
         <v>307</v>
       </c>
       <c r="B306" t="n">
-        <v>0.0291479843227317</v>
+        <v>0.0295562752442848</v>
       </c>
       <c r="C306" t="n">
-        <v>0.0327639397898549</v>
+        <v>0.030248813991445</v>
       </c>
     </row>
     <row r="307">
@@ -7101,10 +7101,10 @@
         <v>308</v>
       </c>
       <c r="B307" t="n">
-        <v>0.0273993287565776</v>
+        <v>0.0276222795680122</v>
       </c>
       <c r="C307" t="n">
-        <v>0.0308642612987607</v>
+        <v>0.029205674939322</v>
       </c>
     </row>
     <row r="308">
@@ -7112,10 +7112,10 @@
         <v>309</v>
       </c>
       <c r="B308" t="n">
-        <v>0.0240954952186994</v>
+        <v>0.0242247066374368</v>
       </c>
       <c r="C308" t="n">
-        <v>0.0272551651275397</v>
+        <v>0.0254998335514344</v>
       </c>
     </row>
     <row r="309">
@@ -7123,10 +7123,10 @@
         <v>310</v>
       </c>
       <c r="B309" t="n">
-        <v>0.0235921710277753</v>
+        <v>0.0237204980878152</v>
       </c>
       <c r="C309" t="n">
-        <v>0.0267545427722811</v>
+        <v>0.0250951447688095</v>
       </c>
     </row>
     <row r="310">
@@ -7134,10 +7134,10 @@
         <v>311</v>
       </c>
       <c r="B310" t="n">
-        <v>0.0281450299939253</v>
+        <v>0.0283542020572965</v>
       </c>
       <c r="C310" t="n">
-        <v>0.0315255943903486</v>
+        <v>0.0299025282292268</v>
       </c>
     </row>
     <row r="311">
@@ -7145,10 +7145,10 @@
         <v>312</v>
       </c>
       <c r="B311" t="n">
-        <v>0.0267647487919035</v>
+        <v>0.0271763044386104</v>
       </c>
       <c r="C311" t="n">
-        <v>0.03234372694811</v>
+        <v>0.029690050414382</v>
       </c>
     </row>
     <row r="312">
@@ -7156,10 +7156,10 @@
         <v>313</v>
       </c>
       <c r="B312" t="n">
-        <v>0.0254241226800751</v>
+        <v>0.0258470767083891</v>
       </c>
       <c r="C312" t="n">
-        <v>0.0310161629186186</v>
+        <v>0.0283695833492581</v>
       </c>
     </row>
     <row r="313">
@@ -7167,10 +7167,10 @@
         <v>314</v>
       </c>
       <c r="B313" t="n">
-        <v>0.0276417058030012</v>
+        <v>0.0278499935076749</v>
       </c>
       <c r="C313" t="n">
-        <v>0.03102497203509</v>
+        <v>0.0294978394466019</v>
       </c>
     </row>
     <row r="314">
@@ -7178,10 +7178,10 @@
         <v>315</v>
       </c>
       <c r="B314" t="n">
-        <v>0.0262614246009793</v>
+        <v>0.0266720958889887</v>
       </c>
       <c r="C314" t="n">
-        <v>0.0318431045928514</v>
+        <v>0.0292853616317572</v>
       </c>
     </row>
     <row r="315">
@@ -7189,10 +7189,10 @@
         <v>316</v>
       </c>
       <c r="B315" t="n">
-        <v>0.0246904200931801</v>
+        <v>0.0248220118783738</v>
       </c>
       <c r="C315" t="n">
-        <v>0.0279213960654432</v>
+        <v>0.0261234473266535</v>
       </c>
     </row>
     <row r="316">
@@ -7200,10 +7200,10 @@
         <v>317</v>
       </c>
       <c r="B316" t="n">
-        <v>0.0301157511355466</v>
+        <v>0.0306890713631293</v>
       </c>
       <c r="C316" t="n">
-        <v>0.0373201465897159</v>
+        <v>0.0337805483876076</v>
       </c>
     </row>
     <row r="317">
@@ -7211,10 +7211,10 @@
         <v>318</v>
       </c>
       <c r="B317" t="n">
-        <v>0.0476648796977728</v>
+        <v>0.0480731706193258</v>
       </c>
       <c r="C317" t="n">
-        <v>0.0327639397898549</v>
+        <v>0.030248813991445</v>
       </c>
     </row>
     <row r="318">
@@ -7222,10 +7222,10 @@
         <v>319</v>
       </c>
       <c r="B318" t="n">
-        <v>0.0301157511355466</v>
+        <v>0.0306890713631293</v>
       </c>
       <c r="C318" t="n">
-        <v>0.0373201465897159</v>
+        <v>0.0337805483876076</v>
       </c>
     </row>
     <row r="319">
@@ -7233,10 +7233,10 @@
         <v>320</v>
       </c>
       <c r="B319" t="n">
-        <v>0.02713745409813</v>
+        <v>0.0274650007783593</v>
       </c>
       <c r="C319" t="n">
-        <v>0.0316211035106698</v>
+        <v>0.0296300729475202</v>
       </c>
     </row>
     <row r="320">
@@ -7244,10 +7244,10 @@
         <v>321</v>
       </c>
       <c r="B320" t="n">
-        <v>0.0270313608475153</v>
+        <v>0.0271870633247303</v>
       </c>
       <c r="C320" t="n">
-        <v>0.0290640996067175</v>
+        <v>0.0270954896565918</v>
       </c>
     </row>
     <row r="321">
@@ -7255,10 +7255,10 @@
         <v>322</v>
       </c>
       <c r="B321" t="n">
-        <v>0.0249828232483443</v>
+        <v>0.0251390012979205</v>
       </c>
       <c r="C321" t="n">
-        <v>0.0284071279621379</v>
+        <v>0.0265000943478597</v>
       </c>
     </row>
     <row r="322">
@@ -7266,10 +7266,10 @@
         <v>323</v>
       </c>
       <c r="B322" t="n">
-        <v>0.0241843898393554</v>
+        <v>0.0243333245603448</v>
       </c>
       <c r="C322" t="n">
-        <v>0.0274881600256108</v>
+        <v>0.0257144356833528</v>
       </c>
     </row>
     <row r="323">
@@ -7277,10 +7277,10 @@
         <v>324</v>
       </c>
       <c r="B323" t="n">
-        <v>0.027041281037797</v>
+        <v>0.0273523848423503</v>
       </c>
       <c r="C323" t="n">
-        <v>0.0314299047740371</v>
+        <v>0.0293882570570799</v>
       </c>
     </row>
     <row r="324">
@@ -7288,10 +7288,10 @@
         <v>325</v>
       </c>
       <c r="B324" t="n">
-        <v>0.028598378188117</v>
+        <v>0.0289245366143632</v>
       </c>
       <c r="C324" t="n">
-        <v>0.0319491422825879</v>
+        <v>0.0299797528107262</v>
       </c>
     </row>
     <row r="325">
@@ -7299,10 +7299,10 @@
         <v>326</v>
       </c>
       <c r="B325" t="n">
-        <v>0.0244794990574202</v>
+        <v>0.0246347927482988</v>
       </c>
       <c r="C325" t="n">
-        <v>0.0279065056068793</v>
+        <v>0.0260954055652348</v>
       </c>
     </row>
     <row r="326">
@@ -7310,10 +7310,10 @@
         <v>327</v>
       </c>
       <c r="B326" t="n">
-        <v>0.0240882167790224</v>
+        <v>0.0242207086243359</v>
       </c>
       <c r="C326" t="n">
-        <v>0.0272969612889781</v>
+        <v>0.0254726197929125</v>
       </c>
     </row>
     <row r="327">
@@ -7321,10 +7321,10 @@
         <v>328</v>
       </c>
       <c r="B327" t="n">
-        <v>0.0262428476288081</v>
+        <v>0.0265467081047747</v>
       </c>
       <c r="C327" t="n">
-        <v>0.0305109368375101</v>
+        <v>0.028602598392573</v>
       </c>
     </row>
     <row r="328">
@@ -7332,10 +7332,10 @@
         <v>329</v>
       </c>
       <c r="B328" t="n">
-        <v>0.0302844181546143</v>
+        <v>0.0307227244691891</v>
       </c>
       <c r="C328" t="n">
-        <v>0.0353823087442811</v>
+        <v>0.0330303074252398</v>
       </c>
     </row>
     <row r="329">
@@ -7343,10 +7343,10 @@
         <v>330</v>
       </c>
       <c r="B329" t="n">
-        <v>0.0234932919045418</v>
+        <v>0.0236234033833989</v>
       </c>
       <c r="C329" t="n">
-        <v>0.0266307303510746</v>
+        <v>0.0248490060176934</v>
       </c>
     </row>
     <row r="330">
@@ -7354,10 +7354,10 @@
         <v>331</v>
       </c>
       <c r="B330" t="n">
-        <v>0.0256453139293424</v>
+        <v>0.0257928603963487</v>
       </c>
       <c r="C330" t="n">
-        <v>0.0278161987975289</v>
+        <v>0.0260641155465588</v>
       </c>
     </row>
     <row r="331">
@@ -7365,10 +7365,10 @@
         <v>332</v>
       </c>
       <c r="B331" t="n">
-        <v>0.0293898116852924</v>
+        <v>0.0298044317956046</v>
       </c>
       <c r="C331" t="n">
-        <v>0.0342721420711213</v>
+        <v>0.0320028328702926</v>
       </c>
     </row>
     <row r="332">
@@ -7376,10 +7376,10 @@
         <v>333</v>
       </c>
       <c r="B332" t="n">
-        <v>0.0266038901236934</v>
+        <v>0.0267560203316195</v>
       </c>
       <c r="C332" t="n">
-        <v>0.0300214737156952</v>
+        <v>0.028129200446726</v>
       </c>
     </row>
     <row r="333">
@@ -7387,10 +7387,10 @@
         <v>334</v>
       </c>
       <c r="B333" t="n">
-        <v>0.031355437220939</v>
+        <v>0.0316911716580067</v>
       </c>
       <c r="C333" t="n">
-        <v>0.0360685323711315</v>
+        <v>0.0338085543240272</v>
       </c>
     </row>
     <row r="334">
@@ -7398,10 +7398,10 @@
         <v>335</v>
       </c>
       <c r="B334" t="n">
-        <v>0.0276966236004069</v>
+        <v>0.0278504042014989</v>
       </c>
       <c r="C334" t="n">
-        <v>0.0311210553048717</v>
+        <v>0.0291350491872639</v>
       </c>
     </row>
     <row r="335">
@@ -7409,10 +7409,10 @@
         <v>336</v>
       </c>
       <c r="B335" t="n">
-        <v>0.0284853171993968</v>
+        <v>0.0288070696989001</v>
       </c>
       <c r="C335" t="n">
-        <v>0.0330285761718487</v>
+        <v>0.0309256224555687</v>
       </c>
     </row>
     <row r="336">
@@ -7420,10 +7420,10 @@
         <v>337</v>
       </c>
       <c r="B336" t="n">
-        <v>0.0248265035788648</v>
+        <v>0.0249663022423922</v>
       </c>
       <c r="C336" t="n">
-        <v>0.0280810991055889</v>
+        <v>0.0262521173188055</v>
       </c>
     </row>
     <row r="337">
@@ -7431,10 +7431,10 @@
         <v>338</v>
       </c>
       <c r="B337" t="n">
-        <v>0.0293041275498745</v>
+        <v>0.0296336278528566</v>
       </c>
       <c r="C337" t="n">
-        <v>0.0327636758637887</v>
+        <v>0.030737620683322</v>
       </c>
     </row>
     <row r="338">
@@ -7442,10 +7442,10 @@
         <v>339</v>
       </c>
       <c r="B338" t="n">
-        <v>0.0277470303995545</v>
+        <v>0.0280614760808437</v>
       </c>
       <c r="C338" t="n">
-        <v>0.0322444383552379</v>
+        <v>0.0301461249296757</v>
       </c>
     </row>
     <row r="339">
@@ -7453,10 +7453,10 @@
         <v>340</v>
       </c>
       <c r="B339" t="n">
-        <v>0.0267082339295264</v>
+        <v>0.026853564825306</v>
       </c>
       <c r="C339" t="n">
-        <v>0.030046366109946</v>
+        <v>0.0280886547935031</v>
       </c>
     </row>
     <row r="340">
@@ -7464,10 +7464,10 @@
         <v>341</v>
       </c>
       <c r="B340" t="n">
-        <v>0.0264463561633164</v>
+        <v>0.0267550796014133</v>
       </c>
       <c r="C340" t="n">
-        <v>0.0307636738361336</v>
+        <v>0.0287646432818608</v>
       </c>
     </row>
     <row r="341">
@@ -7475,10 +7475,10 @@
         <v>342</v>
       </c>
       <c r="B341" t="n">
-        <v>0.028598378188117</v>
+        <v>0.0289245366143632</v>
       </c>
       <c r="C341" t="n">
-        <v>0.0319491422825879</v>
+        <v>0.0299797528107262</v>
       </c>
     </row>
     <row r="342">
@@ -7486,10 +7486,10 @@
         <v>343</v>
       </c>
       <c r="B342" t="n">
-        <v>0.0277037717187951</v>
+        <v>0.0280062439407786</v>
       </c>
       <c r="C342" t="n">
-        <v>0.0308389756094281</v>
+        <v>0.0289522782557789</v>
       </c>
     </row>
     <row r="343">
@@ -7497,10 +7497,10 @@
         <v>344</v>
       </c>
       <c r="B343" t="n">
-        <v>0.0247507074600205</v>
+        <v>0.0248745677227642</v>
       </c>
       <c r="C343" t="n">
-        <v>0.0267060321243691</v>
+        <v>0.0250366409916115</v>
       </c>
     </row>
     <row r="344">
@@ -7508,10 +7508,10 @@
         <v>345</v>
       </c>
       <c r="B344" t="n">
-        <v>0.0269583368005646</v>
+        <v>0.0271048105834425</v>
       </c>
       <c r="C344" t="n">
-        <v>0.0303369174882609</v>
+        <v>0.0283555516613709</v>
       </c>
     </row>
     <row r="345">
@@ -7519,10 +7519,10 @@
         <v>346</v>
       </c>
       <c r="B345" t="n">
-        <v>0.0299348210091631</v>
+        <v>0.0302599067512809</v>
       </c>
       <c r="C345" t="n">
-        <v>0.0344958909103437</v>
+        <v>0.0322972188625621</v>
       </c>
     </row>
     <row r="346">
@@ -7530,10 +7530,10 @@
         <v>347</v>
       </c>
       <c r="B346" t="n">
-        <v>0.0313788571707629</v>
+        <v>0.0317145916078306</v>
       </c>
       <c r="C346" t="n">
-        <v>0.0360945623081554</v>
+        <v>0.033834584261051</v>
       </c>
     </row>
     <row r="347">
@@ -7541,10 +7541,10 @@
         <v>348</v>
       </c>
       <c r="B347" t="n">
-        <v>0.0311287542997247</v>
+        <v>0.0314633458496941</v>
       </c>
       <c r="C347" t="n">
-        <v>0.0358040109298405</v>
+        <v>0.0335676873931831</v>
       </c>
     </row>
     <row r="348">
@@ -7552,10 +7552,10 @@
         <v>349</v>
       </c>
       <c r="B348" t="n">
-        <v>0.0243383196500607</v>
+        <v>0.0244719543824724</v>
       </c>
       <c r="C348" t="n">
-        <v>0.027587512667293</v>
+        <v>0.0257395166607803</v>
       </c>
     </row>
     <row r="349">
@@ -7563,10 +7563,10 @@
         <v>350</v>
       </c>
       <c r="B349" t="n">
-        <v>0.0276047449764795</v>
+        <v>0.0277512187593574</v>
       </c>
       <c r="C349" t="n">
-        <v>0.0310479574922128</v>
+        <v>0.0290665916653228</v>
       </c>
     </row>
     <row r="350">
@@ -7574,10 +7574,10 @@
         <v>351</v>
       </c>
       <c r="B350" t="n">
-        <v>0.0272087389716564</v>
+        <v>0.0273552127545344</v>
       </c>
       <c r="C350" t="n">
-        <v>0.0306106341452215</v>
+        <v>0.0286292683183315</v>
       </c>
     </row>
     <row r="351">
@@ -7585,10 +7585,10 @@
         <v>352</v>
       </c>
       <c r="B351" t="n">
-        <v>0.0316058393920308</v>
+        <v>0.0319415738290985</v>
       </c>
       <c r="C351" t="n">
-        <v>0.0363422490280922</v>
+        <v>0.0340822709809878</v>
       </c>
     </row>
     <row r="352">
@@ -7596,10 +7596,10 @@
         <v>353</v>
       </c>
       <c r="B352" t="n">
-        <v>0.0319785571872524</v>
+        <v>0.0324286550838754</v>
       </c>
       <c r="C352" t="n">
-        <v>0.0372715315204077</v>
+        <v>0.0348345696915965</v>
       </c>
     </row>
     <row r="353">
@@ -7607,10 +7607,10 @@
         <v>354</v>
       </c>
       <c r="B353" t="n">
-        <v>0.0305345210256525</v>
+        <v>0.0309739702273257</v>
       </c>
       <c r="C353" t="n">
-        <v>0.035672860122596</v>
+        <v>0.0332972042931077</v>
       </c>
     </row>
     <row r="354">
@@ -7618,10 +7618,10 @@
         <v>355</v>
       </c>
       <c r="B354" t="n">
-        <v>0.029630026539757</v>
+        <v>0.0299766081306212</v>
       </c>
       <c r="C354" t="n">
-        <v>0.0344292942233234</v>
+        <v>0.0322199938783838</v>
       </c>
     </row>
     <row r="355">
@@ -7629,10 +7629,10 @@
         <v>356</v>
       </c>
       <c r="B355" t="n">
-        <v>0.0272572774652419</v>
+        <v>0.0274037512481198</v>
       </c>
       <c r="C355" t="n">
-        <v>0.0303369174882609</v>
+        <v>0.0283555516613709</v>
       </c>
     </row>
     <row r="356">
@@ -7640,10 +7640,10 @@
         <v>357</v>
       </c>
       <c r="B356" t="n">
-        <v>0.0232897833700335</v>
+        <v>0.0234150318867603</v>
       </c>
       <c r="C356" t="n">
-        <v>0.026377993352451</v>
+        <v>0.0246869611284056</v>
       </c>
     </row>
     <row r="357">
@@ -7651,10 +7651,10 @@
         <v>358</v>
       </c>
       <c r="B357" t="n">
-        <v>0.0286181784088375</v>
+        <v>0.0289443368350836</v>
       </c>
       <c r="C357" t="n">
-        <v>0.0319491422825879</v>
+        <v>0.0299797528107262</v>
       </c>
     </row>
     <row r="358">
@@ -7662,10 +7662,10 @@
         <v>359</v>
       </c>
       <c r="B358" t="n">
-        <v>0.0270028763572722</v>
+        <v>0.0271493501401501</v>
       </c>
       <c r="C358" t="n">
-        <v>0.0303369174882609</v>
+        <v>0.0283555516613709</v>
       </c>
     </row>
     <row r="359">
@@ -7673,10 +7673,10 @@
         <v>360</v>
       </c>
       <c r="B359" t="n">
-        <v>0.0274461402045149</v>
+        <v>0.0276029855688281</v>
       </c>
       <c r="C359" t="n">
-        <v>0.0293546509850324</v>
+        <v>0.0273623865244596</v>
       </c>
     </row>
     <row r="360">
@@ -7684,10 +7684,10 @@
         <v>361</v>
       </c>
       <c r="B360" t="n">
-        <v>0.0258656033238511</v>
+        <v>0.0260104267135632</v>
       </c>
       <c r="C360" t="n">
-        <v>0.0292373358990844</v>
+        <v>0.0273497029208331</v>
       </c>
     </row>
     <row r="361">
@@ -7695,10 +7695,10 @@
         <v>362</v>
       </c>
       <c r="B361" t="n">
-        <v>0.025076606449903</v>
+        <v>0.0252175480005288</v>
       </c>
       <c r="C361" t="n">
-        <v>0.0283716504839038</v>
+        <v>0.0265190141866733</v>
       </c>
     </row>
     <row r="362">
@@ -7706,10 +7706,10 @@
         <v>363</v>
       </c>
       <c r="B362" t="n">
-        <v>0.0270313608475153</v>
+        <v>0.0271870633247303</v>
       </c>
       <c r="C362" t="n">
-        <v>0.0290640996067175</v>
+        <v>0.0270954896565918</v>
       </c>
     </row>
     <row r="363">
@@ -7717,10 +7717,10 @@
         <v>364</v>
       </c>
       <c r="B363" t="n">
-        <v>0.0270313608475153</v>
+        <v>0.0271870633247303</v>
       </c>
       <c r="C363" t="n">
-        <v>0.0290640996067175</v>
+        <v>0.0270954896565918</v>
       </c>
     </row>
     <row r="364">
@@ -7728,10 +7728,10 @@
         <v>365</v>
       </c>
       <c r="B364" t="n">
-        <v>0.0325004458613528</v>
+        <v>0.0328598665026831</v>
       </c>
       <c r="C364" t="n">
-        <v>0.0374524157012519</v>
+        <v>0.035109745535935</v>
       </c>
     </row>
     <row r="365">
@@ -7739,10 +7739,10 @@
         <v>366</v>
       </c>
       <c r="B365" t="n">
-        <v>0.0272814637185536</v>
+        <v>0.0274383090828668</v>
       </c>
       <c r="C365" t="n">
-        <v>0.0293546509850324</v>
+        <v>0.0273623865244596</v>
       </c>
     </row>
     <row r="366">
@@ -7750,10 +7750,10 @@
         <v>367</v>
       </c>
       <c r="B366" t="n">
-        <v>0.0274461402045149</v>
+        <v>0.0276029855688281</v>
       </c>
       <c r="C366" t="n">
-        <v>0.0293546509850324</v>
+        <v>0.0273623865244596</v>
       </c>
     </row>
     <row r="367">
@@ -7761,10 +7761,10 @@
         <v>368</v>
       </c>
       <c r="B367" t="n">
-        <v>0.0291556802398771</v>
+        <v>0.0294818386661233</v>
       </c>
       <c r="C367" t="n">
-        <v>0.0319491422825879</v>
+        <v>0.0299797528107262</v>
       </c>
     </row>
     <row r="368">
@@ -7772,10 +7772,10 @@
         <v>369</v>
       </c>
       <c r="B368" t="n">
-        <v>0.0274461402045149</v>
+        <v>0.0276029855688281</v>
       </c>
       <c r="C368" t="n">
-        <v>0.0293546509850324</v>
+        <v>0.0273623865244596</v>
       </c>
     </row>
     <row r="369">
@@ -7783,10 +7783,10 @@
         <v>370</v>
       </c>
       <c r="B369" t="n">
-        <v>0.0274461402045149</v>
+        <v>0.0276029855688281</v>
       </c>
       <c r="C369" t="n">
-        <v>0.0293546509850324</v>
+        <v>0.0273623865244596</v>
       </c>
     </row>
     <row r="370">
@@ -7794,10 +7794,10 @@
         <v>371</v>
       </c>
       <c r="B370" t="n">
-        <v>0.0259726296997208</v>
+        <v>0.0261201761667271</v>
       </c>
       <c r="C370" t="n">
-        <v>0.0278161987975289</v>
+        <v>0.0260641155465588</v>
       </c>
     </row>
     <row r="371">
@@ -7805,10 +7805,10 @@
         <v>372</v>
       </c>
       <c r="B371" t="n">
-        <v>0.0296314433202528</v>
+        <v>0.0299609436232349</v>
       </c>
       <c r="C371" t="n">
-        <v>0.0327636758637887</v>
+        <v>0.030737620683322</v>
       </c>
     </row>
     <row r="372">
@@ -7816,10 +7816,10 @@
         <v>373</v>
       </c>
       <c r="B372" t="n">
-        <v>0.0270313608475153</v>
+        <v>0.0271870633247303</v>
       </c>
       <c r="C372" t="n">
-        <v>0.0290640996067175</v>
+        <v>0.0270954896565918</v>
       </c>
     </row>
     <row r="373">
@@ -7827,10 +7827,10 @@
         <v>374</v>
       </c>
       <c r="B373" t="n">
-        <v>0.0270313608475153</v>
+        <v>0.0271870633247303</v>
       </c>
       <c r="C373" t="n">
-        <v>0.0290640996067175</v>
+        <v>0.0270954896565918</v>
       </c>
     </row>
     <row r="374">
@@ -7838,10 +7838,10 @@
         <v>375</v>
       </c>
       <c r="B374" t="n">
-        <v>0.0270313608475153</v>
+        <v>0.0271870633247303</v>
       </c>
       <c r="C374" t="n">
-        <v>0.0290640996067175</v>
+        <v>0.0270954896565918</v>
       </c>
     </row>
     <row r="375">
@@ -7849,10 +7849,10 @@
         <v>376</v>
       </c>
       <c r="B375" t="n">
-        <v>0.0269583368005646</v>
+        <v>0.0271048105834425</v>
       </c>
       <c r="C375" t="n">
-        <v>0.0303369174882609</v>
+        <v>0.0283555516613709</v>
       </c>
     </row>
     <row r="376">
@@ -7860,10 +7860,10 @@
         <v>377</v>
       </c>
       <c r="B376" t="n">
-        <v>0.0311053343499008</v>
+        <v>0.0314399258998702</v>
       </c>
       <c r="C376" t="n">
-        <v>0.0357779809928166</v>
+        <v>0.0335416574561593</v>
       </c>
     </row>
     <row r="377">
@@ -7871,10 +7871,10 @@
         <v>378</v>
       </c>
       <c r="B377" t="n">
-        <v>0.0269583368005646</v>
+        <v>0.0271048105834425</v>
       </c>
       <c r="C377" t="n">
-        <v>0.0303369174882609</v>
+        <v>0.0283555516613709</v>
       </c>
     </row>
     <row r="378">
@@ -7882,10 +7882,10 @@
         <v>379</v>
       </c>
       <c r="B378" t="n">
-        <v>0.031355437220939</v>
+        <v>0.0316911716580067</v>
       </c>
       <c r="C378" t="n">
-        <v>0.0360685323711315</v>
+        <v>0.0338085543240272</v>
       </c>
     </row>
     <row r="379">
@@ -7893,10 +7893,10 @@
         <v>380</v>
       </c>
       <c r="B379" t="n">
-        <v>0.0287939559454375</v>
+        <v>0.0291201143716837</v>
       </c>
       <c r="C379" t="n">
-        <v>0.0319491422825879</v>
+        <v>0.0299797528107262</v>
       </c>
     </row>
     <row r="380">
@@ -7904,10 +7904,10 @@
         <v>381</v>
       </c>
       <c r="B380" t="n">
-        <v>0.0269583368005646</v>
+        <v>0.0271048105834425</v>
       </c>
       <c r="C380" t="n">
-        <v>0.0303369174882609</v>
+        <v>0.0283555516613709</v>
       </c>
     </row>
     <row r="381">
@@ -7915,10 +7915,10 @@
         <v>382</v>
       </c>
       <c r="B381" t="n">
-        <v>0.0276966236004069</v>
+        <v>0.0278504042014989</v>
       </c>
       <c r="C381" t="n">
-        <v>0.0311210553048717</v>
+        <v>0.0291350491872639</v>
       </c>
     </row>
     <row r="382">
@@ -7926,10 +7926,10 @@
         <v>383</v>
       </c>
       <c r="B382" t="n">
-        <v>0.0318362949258467</v>
+        <v>0.0321720293629144</v>
       </c>
       <c r="C382" t="n">
-        <v>0.0360685323711315</v>
+        <v>0.0338085543240272</v>
       </c>
     </row>
     <row r="383">
@@ -7937,10 +7937,10 @@
         <v>384</v>
       </c>
       <c r="B383" t="n">
-        <v>0.0270313608475153</v>
+        <v>0.0271870633247303</v>
       </c>
       <c r="C383" t="n">
-        <v>0.0290640996067175</v>
+        <v>0.0270954896565918</v>
       </c>
     </row>
     <row r="384">
@@ -7948,10 +7948,10 @@
         <v>385</v>
       </c>
       <c r="B384" t="n">
-        <v>0.0270313608475153</v>
+        <v>0.0271870633247303</v>
       </c>
       <c r="C384" t="n">
-        <v>0.0290640996067175</v>
+        <v>0.0270954896565918</v>
       </c>
     </row>
     <row r="385">
@@ -7959,10 +7959,10 @@
         <v>386</v>
       </c>
       <c r="B385" t="n">
-        <v>0.0270313608475153</v>
+        <v>0.0271870633247303</v>
       </c>
       <c r="C385" t="n">
-        <v>0.0290640996067175</v>
+        <v>0.0270954896565918</v>
       </c>
     </row>
     <row r="386">
@@ -7970,10 +7970,10 @@
         <v>387</v>
       </c>
       <c r="B386" t="n">
-        <v>0.0269583368005646</v>
+        <v>0.0271048105834425</v>
       </c>
       <c r="C386" t="n">
-        <v>0.0303369174882609</v>
+        <v>0.0283555516613709</v>
       </c>
     </row>
     <row r="387">
@@ -7981,10 +7981,10 @@
         <v>388</v>
       </c>
       <c r="B387" t="n">
-        <v>0.031355437220939</v>
+        <v>0.0316911716580067</v>
       </c>
       <c r="C387" t="n">
-        <v>0.0360685323711315</v>
+        <v>0.0338085543240272</v>
       </c>
     </row>
     <row r="388">
@@ -7992,10 +7992,10 @@
         <v>389</v>
       </c>
       <c r="B388" t="n">
-        <v>0.031355437220939</v>
+        <v>0.0316911716580067</v>
       </c>
       <c r="C388" t="n">
-        <v>0.0360685323711315</v>
+        <v>0.0338085543240272</v>
       </c>
     </row>
     <row r="389">
@@ -8003,10 +8003,10 @@
         <v>390</v>
       </c>
       <c r="B389" t="n">
-        <v>0.031355437220939</v>
+        <v>0.0316911716580067</v>
       </c>
       <c r="C389" t="n">
-        <v>0.0360685323711315</v>
+        <v>0.0338085543240272</v>
       </c>
     </row>
     <row r="390">
@@ -8014,10 +8014,10 @@
         <v>391</v>
       </c>
       <c r="B390" t="n">
-        <v>0.0286257138213144</v>
+        <v>0.0289518722475606</v>
       </c>
       <c r="C390" t="n">
-        <v>0.0319491422825879</v>
+        <v>0.0299797528107262</v>
       </c>
     </row>
     <row r="391">
@@ -8025,10 +8025,10 @@
         <v>392</v>
       </c>
       <c r="B391" t="n">
-        <v>0.0287187312945029</v>
+        <v>0.0290448897207491</v>
       </c>
       <c r="C391" t="n">
-        <v>0.0319491422825879</v>
+        <v>0.0299797528107262</v>
       </c>
     </row>
     <row r="392">
@@ -8036,10 +8036,10 @@
         <v>393</v>
       </c>
       <c r="B392" t="n">
-        <v>0.027824124825181</v>
+        <v>0.0281265970471645</v>
       </c>
       <c r="C392" t="n">
-        <v>0.0308389756094281</v>
+        <v>0.0289522782557789</v>
       </c>
     </row>
     <row r="393">
@@ -8047,10 +8047,10 @@
         <v>394</v>
       </c>
       <c r="B393" t="n">
-        <v>0.0269583368005646</v>
+        <v>0.0271048105834425</v>
       </c>
       <c r="C393" t="n">
-        <v>0.0303369174882609</v>
+        <v>0.0283555516613709</v>
       </c>
     </row>
     <row r="394">
@@ -8058,10 +8058,10 @@
         <v>395</v>
       </c>
       <c r="B394" t="n">
-        <v>0.0269583368005646</v>
+        <v>0.0271048105834425</v>
       </c>
       <c r="C394" t="n">
-        <v>0.0303369174882609</v>
+        <v>0.0283555516613709</v>
       </c>
     </row>
     <row r="395">
@@ -8069,10 +8069,10 @@
         <v>396</v>
       </c>
       <c r="B395" t="n">
-        <v>0.0266038901236934</v>
+        <v>0.0267560203316195</v>
       </c>
       <c r="C395" t="n">
-        <v>0.0300214737156952</v>
+        <v>0.028129200446726</v>
       </c>
     </row>
     <row r="396">
@@ -8080,10 +8080,10 @@
         <v>397</v>
       </c>
       <c r="B396" t="n">
-        <v>0.0288479887403722</v>
+        <v>0.0291741471666184</v>
       </c>
       <c r="C396" t="n">
-        <v>0.0320188668894294</v>
+        <v>0.0300494774175676</v>
       </c>
     </row>
     <row r="397">
@@ -8091,10 +8091,10 @@
         <v>398</v>
       </c>
       <c r="B397" t="n">
-        <v>0.0269583368005646</v>
+        <v>0.0271048105834425</v>
       </c>
       <c r="C397" t="n">
-        <v>0.0303369174882609</v>
+        <v>0.0283555516613709</v>
       </c>
     </row>
     <row r="398">
@@ -8102,10 +8102,10 @@
         <v>399</v>
       </c>
       <c r="B398" t="n">
-        <v>0.0270313608475153</v>
+        <v>0.0271870633247303</v>
       </c>
       <c r="C398" t="n">
-        <v>0.0290640996067175</v>
+        <v>0.0270954896565918</v>
       </c>
     </row>
     <row r="399">
@@ -8113,10 +8113,10 @@
         <v>400</v>
       </c>
       <c r="B399" t="n">
-        <v>0.0274218653439967</v>
+        <v>0.0277553463993643</v>
       </c>
       <c r="C399" t="n">
-        <v>0.0319510340211</v>
+        <v>0.0299531565227755</v>
       </c>
     </row>
     <row r="400">
@@ -8124,10 +8124,10 @@
         <v>401</v>
       </c>
       <c r="B400" t="n">
-        <v>0.030568829400481</v>
+        <v>0.0310130700901941</v>
       </c>
       <c r="C400" t="n">
-        <v>0.0357122392547113</v>
+        <v>0.0333533910004951</v>
       </c>
     </row>
     <row r="401">
@@ -8135,10 +8135,10 @@
         <v>402</v>
       </c>
       <c r="B401" t="n">
-        <v>0.0295479901049792</v>
+        <v>0.0298248051873864</v>
       </c>
       <c r="C401" t="n">
-        <v>0.0332485474349285</v>
+        <v>0.0317079950026151</v>
       </c>
     </row>
     <row r="402">
@@ -8146,10 +8146,10 @@
         <v>403</v>
       </c>
       <c r="B402" t="n">
-        <v>0.0252338339218372</v>
+        <v>0.02548601837173</v>
       </c>
       <c r="C402" t="n">
-        <v>0.0286099198378341</v>
+        <v>0.0272876977356678</v>
       </c>
     </row>
     <row r="403">
@@ -8157,10 +8157,10 @@
         <v>404</v>
       </c>
       <c r="B403" t="n">
-        <v>0.0284552566282657</v>
+        <v>0.0287304213175071</v>
       </c>
       <c r="C403" t="n">
-        <v>0.032148965845752</v>
+        <v>0.0307021462620772</v>
       </c>
     </row>
     <row r="404">
@@ -8168,10 +8168,10 @@
         <v>405</v>
       </c>
       <c r="B404" t="n">
-        <v>0.0269055947007925</v>
+        <v>0.0271065759661357</v>
       </c>
       <c r="C404" t="n">
-        <v>0.0304567629997949</v>
+        <v>0.0289510373870791</v>
       </c>
     </row>
     <row r="405">
@@ -8179,10 +8179,10 @@
         <v>406</v>
       </c>
       <c r="B405" t="n">
-        <v>0.0317252457298023</v>
+        <v>0.0319506495490306</v>
       </c>
       <c r="C405" t="n">
-        <v>0.0348265584958357</v>
+        <v>0.0331788425944933</v>
       </c>
     </row>
     <row r="406">
@@ -8190,10 +8190,10 @@
         <v>407</v>
       </c>
       <c r="B406" t="n">
-        <v>0.0354152934203321</v>
+        <v>0.0358595341100452</v>
       </c>
       <c r="C406" t="n">
-        <v>0.0357122392547113</v>
+        <v>0.0333533910004951</v>
       </c>
     </row>
     <row r="407">
@@ -8201,10 +8201,10 @@
         <v>408</v>
       </c>
       <c r="B407" t="n">
-        <v>0.0285542903295815</v>
+        <v>0.0287552715949248</v>
       </c>
       <c r="C407" t="n">
-        <v>0.0316158452347392</v>
+        <v>0.0301101196220234</v>
       </c>
     </row>
     <row r="408">
@@ -8212,10 +8212,10 @@
         <v>409</v>
       </c>
       <c r="B408" t="n">
-        <v>0.0259323340001941</v>
+        <v>0.0262397484848427</v>
       </c>
       <c r="C408" t="n">
-        <v>0.0301746364100367</v>
+        <v>0.0283020681926092</v>
       </c>
     </row>
     <row r="409">
@@ -8223,10 +8223,10 @@
         <v>410</v>
       </c>
       <c r="B409" t="n">
-        <v>0.0262459468960638</v>
+        <v>0.0265582203834482</v>
       </c>
       <c r="C409" t="n">
-        <v>0.0305332918367648</v>
+        <v>0.0286221800670661</v>
       </c>
     </row>
     <row r="410">
@@ -8234,10 +8234,10 @@
         <v>411</v>
       </c>
       <c r="B410" t="n">
-        <v>0.0250436217617382</v>
+        <v>0.0250871767379713</v>
       </c>
       <c r="C410" t="n">
-        <v>0.026128936323354</v>
+        <v>0.0258404476512371</v>
       </c>
     </row>
     <row r="411">
@@ -8245,10 +8245,10 @@
         <v>412</v>
       </c>
       <c r="B411" t="n">
-        <v>0.0278490360180208</v>
+        <v>0.0280733238718702</v>
       </c>
       <c r="C411" t="n">
-        <v>0.0310395450189532</v>
+        <v>0.0298595756050869</v>
       </c>
     </row>
     <row r="412">
@@ -8256,10 +8256,10 @@
         <v>413</v>
       </c>
       <c r="B412" t="n">
-        <v>0.0317829406120232</v>
+        <v>0.0321414940712465</v>
       </c>
       <c r="C412" t="n">
-        <v>0.0365935080170851</v>
+        <v>0.0343819978724982</v>
       </c>
     </row>
     <row r="413">
@@ -8267,10 +8267,10 @@
         <v>414</v>
       </c>
       <c r="B413" t="n">
-        <v>0.0288827894339837</v>
+        <v>0.0292148822353681</v>
       </c>
       <c r="C413" t="n">
-        <v>0.0322790727930181</v>
+        <v>0.0303028363859814</v>
       </c>
     </row>
     <row r="414">
@@ -8278,10 +8278,10 @@
         <v>415</v>
       </c>
       <c r="B414" t="n">
-        <v>0.0278770103334549</v>
+        <v>0.0281415263277463</v>
       </c>
       <c r="C414" t="n">
-        <v>0.0314585078991582</v>
+        <v>0.0300729943148061</v>
       </c>
     </row>
     <row r="415">
@@ -8289,10 +8289,10 @@
         <v>416</v>
       </c>
       <c r="B415" t="n">
-        <v>0.0285745040050259</v>
+        <v>0.028817882196472</v>
       </c>
       <c r="C415" t="n">
-        <v>0.0312927565326739</v>
+        <v>0.0299735022219722</v>
       </c>
     </row>
     <row r="416">
@@ -8300,10 +8300,10 @@
         <v>417</v>
       </c>
       <c r="B416" t="n">
-        <v>0.0293390759117941</v>
+        <v>0.0295912603616869</v>
       </c>
       <c r="C416" t="n">
-        <v>0.032870053764318</v>
+        <v>0.0315478316621517</v>
       </c>
     </row>
     <row r="417">
@@ -8311,10 +8311,10 @@
         <v>418</v>
       </c>
       <c r="B417" t="n">
-        <v>0.028912820590481</v>
+        <v>0.0292573921121398</v>
       </c>
       <c r="C417" t="n">
-        <v>0.0335535518178023</v>
+        <v>0.0314990660040398</v>
       </c>
     </row>
     <row r="418">
@@ -8322,10 +8322,10 @@
         <v>419</v>
       </c>
       <c r="B418" t="n">
-        <v>0.024469262015069</v>
+        <v>0.0247126402065151</v>
       </c>
       <c r="C418" t="n">
-        <v>0.02703262260619</v>
+        <v>0.0257133682954882</v>
       </c>
     </row>
     <row r="419">
@@ -8333,10 +8333,10 @@
         <v>420</v>
       </c>
       <c r="B419" t="n">
-        <v>0.026677870083437</v>
+        <v>0.0269407032282797</v>
       </c>
       <c r="C419" t="n">
-        <v>0.0302085912356457</v>
+        <v>0.0288250631341566</v>
       </c>
     </row>
     <row r="420">
@@ -8344,10 +8344,10 @@
         <v>421</v>
       </c>
       <c r="B420" t="n">
-        <v>0.0254550325506197</v>
+        <v>0.0256962163561379</v>
       </c>
       <c r="C420" t="n">
-        <v>0.0287870026524199</v>
+        <v>0.0274855425956718</v>
       </c>
     </row>
     <row r="421">
@@ -8355,10 +8355,10 @@
         <v>422</v>
       </c>
       <c r="B421" t="n">
-        <v>0.0259132981766688</v>
+        <v>0.0261673250630649</v>
       </c>
       <c r="C421" t="n">
-        <v>0.0286312940040016</v>
+        <v>0.0272507336939771</v>
       </c>
     </row>
     <row r="422">
@@ -8366,10 +8366,10 @@
         <v>423</v>
       </c>
       <c r="B422" t="n">
-        <v>0.0277354782398664</v>
+        <v>0.0280738182979698</v>
       </c>
       <c r="C422" t="n">
-        <v>0.0323096894478281</v>
+        <v>0.0302732683972324</v>
       </c>
     </row>
     <row r="423">
@@ -8377,10 +8377,10 @@
         <v>424</v>
       </c>
       <c r="B423" t="n">
-        <v>0.0260996237886262</v>
+        <v>0.026351808238519</v>
       </c>
       <c r="C423" t="n">
-        <v>0.0295181332890519</v>
+        <v>0.0281959111868856</v>
       </c>
     </row>
     <row r="424">
@@ -8388,10 +8388,10 @@
         <v>425</v>
       </c>
       <c r="B424" t="n">
-        <v>0.0292753901028034</v>
+        <v>0.0294869261944066</v>
       </c>
       <c r="C424" t="n">
-        <v>0.0330776887752454</v>
+        <v>0.0314884315315709</v>
       </c>
     </row>
     <row r="425">
@@ -8399,10 +8399,10 @@
         <v>426</v>
       </c>
       <c r="B425" t="n">
-        <v>0.0286157422980748</v>
+        <v>0.0289385706117191</v>
       </c>
       <c r="C425" t="n">
-        <v>0.0331542176122153</v>
+        <v>0.0311595742115579</v>
       </c>
     </row>
     <row r="426">
@@ -8410,10 +8410,10 @@
         <v>427</v>
       </c>
       <c r="B426" t="n">
-        <v>0.0273763701617939</v>
+        <v>0.0276944333413925</v>
       </c>
       <c r="C426" t="n">
-        <v>0.0317733078078484</v>
+        <v>0.0298394335910981</v>
       </c>
     </row>
     <row r="427">
@@ -8421,10 +8421,10 @@
         <v>428</v>
       </c>
       <c r="B427" t="n">
-        <v>0.0314859186561004</v>
+        <v>0.0318428874568841</v>
       </c>
       <c r="C427" t="n">
-        <v>0.0362991102398795</v>
+        <v>0.034106556921855</v>
       </c>
     </row>
     <row r="428">
@@ -8432,10 +8432,10 @@
         <v>429</v>
       </c>
       <c r="B428" t="n">
-        <v>0.0308189322715192</v>
+        <v>0.0312643158483307</v>
       </c>
       <c r="C428" t="n">
-        <v>0.0360027906330262</v>
+        <v>0.033620287868363</v>
       </c>
     </row>
     <row r="429">
@@ -8443,10 +8443,10 @@
         <v>430</v>
       </c>
       <c r="B429" t="n">
-        <v>0.0330223690847875</v>
+        <v>0.0334058462276315</v>
       </c>
       <c r="C429" t="n">
-        <v>0.0380793542498335</v>
+        <v>0.0357661893347967</v>
       </c>
     </row>
     <row r="430">
@@ -8454,10 +8454,10 @@
         <v>431</v>
       </c>
       <c r="B430" t="n">
-        <v>0.0290792980566784</v>
+        <v>0.0294974721756726</v>
       </c>
       <c r="C430" t="n">
-        <v>0.033935841643648</v>
+        <v>0.0317023026703288</v>
       </c>
     </row>
     <row r="431">
@@ -8465,10 +8465,10 @@
         <v>432</v>
       </c>
       <c r="B431" t="n">
-        <v>0.0299173222066049</v>
+        <v>0.0301801553514476</v>
       </c>
       <c r="C431" t="n">
-        <v>0.0335605117109119</v>
+        <v>0.0321769836094228</v>
       </c>
     </row>
     <row r="432">
@@ -8476,10 +8476,10 @@
         <v>433</v>
       </c>
       <c r="B432" t="n">
-        <v>0.0296043253353176</v>
+        <v>0.0298620329196732</v>
       </c>
       <c r="C432" t="n">
-        <v>0.0324116341832573</v>
+        <v>0.0310024266433558</v>
       </c>
     </row>
     <row r="433">
@@ -8487,10 +8487,10 @@
         <v>434</v>
       </c>
       <c r="B433" t="n">
-        <v>0.029297887233941</v>
+        <v>0.0295735594292498</v>
       </c>
       <c r="C433" t="n">
-        <v>0.0329579960566136</v>
+        <v>0.0314410981347473</v>
       </c>
     </row>
     <row r="434">
@@ -8498,10 +8498,10 @@
         <v>435</v>
       </c>
       <c r="B434" t="n">
-        <v>0.028552351150698</v>
+        <v>0.0288726046858128</v>
       </c>
       <c r="C434" t="n">
-        <v>0.0329240412310046</v>
+        <v>0.0309181031931998</v>
       </c>
     </row>
     <row r="435">
@@ -8509,10 +8509,10 @@
         <v>436</v>
       </c>
       <c r="B435" t="n">
-        <v>0.0302464901833361</v>
+        <v>0.0305785353004991</v>
       </c>
       <c r="C435" t="n">
-        <v>0.0348132640071312</v>
+        <v>0.0327223654595565</v>
       </c>
     </row>
     <row r="436">
@@ -8520,10 +8520,10 @@
         <v>437</v>
       </c>
       <c r="B436" t="n">
-        <v>0.0307874185777435</v>
+        <v>0.0310891573437714</v>
       </c>
       <c r="C436" t="n">
-        <v>0.0347343936676769</v>
+        <v>0.0330921864649136</v>
       </c>
     </row>
     <row r="437">
@@ -8531,10 +8531,10 @@
         <v>438</v>
       </c>
       <c r="B437" t="n">
-        <v>0.0277614368052539</v>
+        <v>0.0280106006585025</v>
       </c>
       <c r="C437" t="n">
-        <v>0.0311777520466597</v>
+        <v>0.0297814657218055</v>
       </c>
     </row>
     <row r="438">
@@ -8542,10 +8542,10 @@
         <v>439</v>
       </c>
       <c r="B438" t="n">
-        <v>0.0299963873122979</v>
+        <v>0.0303272895423625</v>
       </c>
       <c r="C438" t="n">
-        <v>0.0345227126288163</v>
+        <v>0.0324554685916887</v>
       </c>
     </row>
     <row r="439">
@@ -8553,10 +8553,10 @@
         <v>440</v>
       </c>
       <c r="B439" t="n">
-        <v>0.0318392758423616</v>
+        <v>0.0321787218035333</v>
       </c>
       <c r="C439" t="n">
-        <v>0.0357565947654139</v>
+        <v>0.0336764295132389</v>
       </c>
     </row>
     <row r="440">
@@ -8564,10 +8564,10 @@
         <v>441</v>
       </c>
       <c r="B440" t="n">
-        <v>0.0288024540217363</v>
+        <v>0.0291238504439493</v>
       </c>
       <c r="C440" t="n">
-        <v>0.0332145926093195</v>
+        <v>0.0311850000610677</v>
       </c>
     </row>
     <row r="441">
@@ -8575,10 +8575,10 @@
         <v>442</v>
       </c>
       <c r="B441" t="n">
-        <v>0.0290792980566784</v>
+        <v>0.0294974721756726</v>
       </c>
       <c r="C441" t="n">
-        <v>0.033935841643648</v>
+        <v>0.0317023026703288</v>
       </c>
     </row>
     <row r="442">
@@ -8586,10 +8586,10 @@
         <v>443</v>
       </c>
       <c r="B442" t="n">
-        <v>0.0314490934586894</v>
+        <v>0.0318778224039434</v>
       </c>
       <c r="C442" t="n">
-        <v>0.0365567674190985</v>
+        <v>0.0342396968148206</v>
       </c>
     </row>
     <row r="443">
@@ -8597,10 +8597,10 @@
         <v>444</v>
       </c>
       <c r="B443" t="n">
-        <v>0.0272324190954483</v>
+        <v>0.0274859344453652</v>
       </c>
       <c r="C443" t="n">
-        <v>0.0307273772625262</v>
+        <v>0.0293626257235924</v>
       </c>
     </row>
     <row r="444">
@@ -8608,10 +8608,10 @@
         <v>445</v>
       </c>
       <c r="B444" t="n">
-        <v>0.0294392463946248</v>
+        <v>0.029772283624261</v>
       </c>
       <c r="C444" t="n">
-        <v>0.0339339064051417</v>
+        <v>0.0318220317861705</v>
       </c>
     </row>
     <row r="445">
@@ -8619,10 +8619,10 @@
         <v>446</v>
       </c>
       <c r="B445" t="n">
-        <v>0.0323778654865038</v>
+        <v>0.0327387993121834</v>
       </c>
       <c r="C445" t="n">
-        <v>0.0372597389549886</v>
+        <v>0.0350056116477173</v>
       </c>
     </row>
     <row r="446">
@@ -8630,10 +8630,10 @@
         <v>447</v>
       </c>
       <c r="B446" t="n">
-        <v>0.0301429149794598</v>
+        <v>0.0304221104283233</v>
       </c>
       <c r="C446" t="n">
-        <v>0.033914778372832</v>
+        <v>0.0323316087778342</v>
       </c>
     </row>
     <row r="447">
@@ -8641,10 +8641,10 @@
         <v>448</v>
       </c>
       <c r="B447" t="n">
-        <v>0.0322820113380548</v>
+        <v>0.0326405647972781</v>
       </c>
       <c r="C447" t="n">
-        <v>0.0365935080170851</v>
+        <v>0.0343819978724982</v>
       </c>
     </row>
     <row r="448">
@@ -8652,10 +8652,10 @@
         <v>449</v>
       </c>
       <c r="B448" t="n">
-        <v>0.0300470608310108</v>
+        <v>0.030323875913418</v>
       </c>
       <c r="C448" t="n">
-        <v>0.0332485474349285</v>
+        <v>0.0317079950026151</v>
       </c>
     </row>
     <row r="449">
@@ -8663,10 +8663,10 @@
         <v>450</v>
       </c>
       <c r="B449" t="n">
-        <v>0.0300004649586827</v>
+        <v>0.0302772800646662</v>
       </c>
       <c r="C449" t="n">
-        <v>0.0337481707873308</v>
+        <v>0.0322076145835208</v>
       </c>
     </row>
     <row r="450">
@@ -8674,10 +8674,10 @@
         <v>451</v>
       </c>
       <c r="B450" t="n">
-        <v>0.0296581871877343</v>
+        <v>0.0299350022701415</v>
       </c>
       <c r="C450" t="n">
-        <v>0.0332485474349285</v>
+        <v>0.0317079950026151</v>
       </c>
     </row>
     <row r="451">
@@ -8685,10 +8685,10 @@
         <v>452</v>
       </c>
       <c r="B451" t="n">
-        <v>0.0293894202153627</v>
+        <v>0.0297149984489093</v>
       </c>
       <c r="C451" t="n">
-        <v>0.0340077250448236</v>
+        <v>0.0319860184503165</v>
       </c>
     </row>
     <row r="452">
@@ -8696,10 +8696,10 @@
         <v>453</v>
       </c>
       <c r="B452" t="n">
-        <v>0.0316398484668057</v>
+        <v>0.0319815172790117</v>
       </c>
       <c r="C452" t="n">
-        <v>0.0363984628815617</v>
+        <v>0.0341316378992825</v>
       </c>
     </row>
     <row r="453">
@@ -8707,10 +8707,10 @@
         <v>454</v>
       </c>
       <c r="B453" t="n">
-        <v>0.0328769362125355</v>
+        <v>0.0332378700382151</v>
       </c>
       <c r="C453" t="n">
-        <v>0.0372597389549886</v>
+        <v>0.0350056116477173</v>
       </c>
     </row>
     <row r="454">
@@ -8718,10 +8718,10 @@
         <v>455</v>
       </c>
       <c r="B454" t="n">
-        <v>0.0295650906562074</v>
+        <v>0.0298419057386146</v>
       </c>
       <c r="C454" t="n">
-        <v>0.0332677272730058</v>
+        <v>0.0317271748406924</v>
       </c>
     </row>
     <row r="455">
@@ -8729,10 +8729,10 @@
         <v>456</v>
       </c>
       <c r="B455" t="n">
-        <v>0.0300924420042122</v>
+        <v>0.0303692570866194</v>
       </c>
       <c r="C455" t="n">
-        <v>0.0332485474349285</v>
+        <v>0.0317079950026151</v>
       </c>
     </row>
     <row r="456">
@@ -8740,10 +8740,10 @@
         <v>457</v>
       </c>
       <c r="B456" t="n">
-        <v>0.0292753901028034</v>
+        <v>0.0294869261944066</v>
       </c>
       <c r="C456" t="n">
-        <v>0.0330776887752454</v>
+        <v>0.0314884315315709</v>
       </c>
     </row>
     <row r="457">
@@ -8751,10 +8751,10 @@
         <v>458</v>
       </c>
       <c r="B457" t="n">
-        <v>0.0269055947007925</v>
+        <v>0.0271065759661357</v>
       </c>
       <c r="C457" t="n">
-        <v>0.0304567629997949</v>
+        <v>0.0289510373870791</v>
       </c>
     </row>
     <row r="458">
@@ -8762,10 +8762,10 @@
         <v>459</v>
       </c>
       <c r="B458" t="n">
-        <v>0.0315328377409849</v>
+        <v>0.0318902483131099</v>
       </c>
       <c r="C458" t="n">
-        <v>0.0363029566387702</v>
+        <v>0.0341151010046304</v>
       </c>
     </row>
     <row r="459">
@@ -8773,10 +8773,10 @@
         <v>460</v>
       </c>
       <c r="B459" t="n">
-        <v>0.0326797956101785</v>
+        <v>0.0330261116692389</v>
       </c>
       <c r="C459" t="n">
-        <v>0.0375022938309948</v>
+        <v>0.0353129746106373</v>
       </c>
     </row>
     <row r="460">
@@ -8784,10 +8784,10 @@
         <v>461</v>
       </c>
       <c r="B460" t="n">
-        <v>0.0306172570542385</v>
+        <v>0.0309200244974253</v>
       </c>
       <c r="C460" t="n">
-        <v>0.0337338585672993</v>
+        <v>0.0321665625272454</v>
       </c>
     </row>
     <row r="461">
@@ -8795,10 +8795,10 @@
         <v>462</v>
       </c>
       <c r="B461" t="n">
-        <v>0.0304448451031345</v>
+        <v>0.0307094227853789</v>
       </c>
       <c r="C461" t="n">
-        <v>0.0341573332488383</v>
+        <v>0.0326389717407542</v>
       </c>
     </row>
     <row r="462">
@@ -8806,10 +8806,10 @@
         <v>463</v>
       </c>
       <c r="B462" t="n">
-        <v>0.0323956039741142</v>
+        <v>0.0326289065683902</v>
       </c>
       <c r="C462" t="n">
-        <v>0.035571722461039</v>
+        <v>0.0338897637542235</v>
       </c>
     </row>
     <row r="463">
@@ -8817,10 +8817,10 @@
         <v>464</v>
       </c>
       <c r="B463" t="n">
-        <v>0.0325096340866735</v>
+        <v>0.0328569788228928</v>
       </c>
       <c r="C463" t="n">
-        <v>0.0365017587306172</v>
+        <v>0.0343873506729691</v>
       </c>
     </row>
     <row r="464">
@@ -8828,10 +8828,10 @@
         <v>465</v>
       </c>
       <c r="B464" t="n">
-        <v>0.0302746835796295</v>
+        <v>0.0305402899390328</v>
       </c>
       <c r="C464" t="n">
-        <v>0.0331567981484607</v>
+        <v>0.031713347803086</v>
       </c>
     </row>
     <row r="465">
@@ -8839,10 +8839,10 @@
         <v>466</v>
       </c>
       <c r="B465" t="n">
-        <v>0.0323956039741142</v>
+        <v>0.0326289065683902</v>
       </c>
       <c r="C465" t="n">
-        <v>0.035571722461039</v>
+        <v>0.0338897637542235</v>
       </c>
     </row>
     <row r="466">
@@ -8850,10 +8850,10 @@
         <v>467</v>
       </c>
       <c r="B466" t="n">
-        <v>0.0325096340866735</v>
+        <v>0.0328569788228928</v>
       </c>
       <c r="C466" t="n">
-        <v>0.0365017587306172</v>
+        <v>0.0343873506729691</v>
       </c>
     </row>
     <row r="467">
@@ -8861,10 +8861,10 @@
         <v>468</v>
       </c>
       <c r="B467" t="n">
-        <v>0.0288659015055965</v>
+        <v>0.029210031255914</v>
       </c>
       <c r="C467" t="n">
-        <v>0.0335497054189116</v>
+        <v>0.0314905219212644</v>
       </c>
     </row>
     <row r="468">
@@ -8872,10 +8872,10 @@
         <v>469</v>
       </c>
       <c r="B468" t="n">
-        <v>0.028333878893437</v>
+        <v>0.028696381206334</v>
       </c>
       <c r="C468" t="n">
-        <v>0.0323672786725547</v>
+        <v>0.030679388130612</v>
       </c>
     </row>
     <row r="469">
@@ -8883,10 +8883,10 @@
         <v>470</v>
       </c>
       <c r="B469" t="n">
-        <v>0.0295479901049792</v>
+        <v>0.0298248051873864</v>
       </c>
       <c r="C469" t="n">
-        <v>0.0332485474349285</v>
+        <v>0.0317079950026151</v>
       </c>
     </row>
     <row r="470">
@@ -8894,10 +8894,10 @@
         <v>471</v>
       </c>
       <c r="B470" t="n">
-        <v>0.0484469470399679</v>
+        <v>0.0488911877296811</v>
       </c>
       <c r="C470" t="n">
-        <v>0.0357122392547113</v>
+        <v>0.0333533910004951</v>
       </c>
     </row>
     <row r="471">
@@ -8905,10 +8905,10 @@
         <v>472</v>
       </c>
       <c r="B471" t="n">
-        <v>0.024609583894853</v>
+        <v>0.0248338717487024</v>
       </c>
       <c r="C471" t="n">
-        <v>0.027687624543687</v>
+        <v>0.0265076551298208</v>
       </c>
     </row>
     <row r="472">
@@ -8916,10 +8916,10 @@
         <v>473</v>
       </c>
       <c r="B472" t="n">
-        <v>0.029297887233941</v>
+        <v>0.0295735594292498</v>
       </c>
       <c r="C472" t="n">
-        <v>0.0329579960566136</v>
+        <v>0.0314410981347473</v>
       </c>
     </row>
     <row r="473">
@@ -8927,10 +8927,10 @@
         <v>474</v>
       </c>
       <c r="B473" t="n">
-        <v>0.0295479901049792</v>
+        <v>0.0298248051873864</v>
       </c>
       <c r="C473" t="n">
-        <v>0.0332485474349285</v>
+        <v>0.0317079950026151</v>
       </c>
     </row>
     <row r="474">
@@ -8938,10 +8938,10 @@
         <v>475</v>
       </c>
       <c r="B474" t="n">
-        <v>0.030568829400481</v>
+        <v>0.0310130700901941</v>
       </c>
       <c r="C474" t="n">
-        <v>0.0357122392547113</v>
+        <v>0.0333533910004951</v>
       </c>
     </row>
     <row r="475">
@@ -8949,10 +8949,10 @@
         <v>476</v>
       </c>
       <c r="B475" t="n">
-        <v>0.0218041696385703</v>
+        <v>0.0218477246148034</v>
       </c>
       <c r="C475" t="n">
-        <v>0.0227770158480879</v>
+        <v>0.0224885271759709</v>
       </c>
     </row>
     <row r="476">
@@ -8960,10 +8960,10 @@
         <v>477</v>
       </c>
       <c r="B476" t="n">
-        <v>0.0310655979250736</v>
+        <v>0.0314022939663431</v>
       </c>
       <c r="C476" t="n">
-        <v>0.0349030873328056</v>
+        <v>0.0328499852744803</v>
       </c>
     </row>
     <row r="477">
@@ -8971,10 +8971,10 @@
         <v>478</v>
       </c>
       <c r="B477" t="n">
-        <v>0.0291527502998367</v>
+        <v>0.0294067771862327</v>
       </c>
       <c r="C477" t="n">
-        <v>0.0319832144792678</v>
+        <v>0.0306026541692432</v>
       </c>
     </row>
     <row r="478">
@@ -8982,10 +8982,10 @@
         <v>479</v>
       </c>
       <c r="B478" t="n">
-        <v>0.0295479901049792</v>
+        <v>0.0298248051873864</v>
       </c>
       <c r="C478" t="n">
-        <v>0.0332485474349285</v>
+        <v>0.0317079950026151</v>
       </c>
     </row>
     <row r="479">
@@ -8993,10 +8993,10 @@
         <v>480</v>
       </c>
       <c r="B479" t="n">
-        <v>0.0279048881776185</v>
+        <v>0.0281599397107619</v>
       </c>
       <c r="C479" t="n">
-        <v>0.0305358723730102</v>
+        <v>0.0291759536585942</v>
       </c>
     </row>
     <row r="480">
@@ -9004,10 +9004,10 @@
         <v>481</v>
       </c>
       <c r="B480" t="n">
-        <v>0.0295479901049792</v>
+        <v>0.0298248051873864</v>
       </c>
       <c r="C480" t="n">
-        <v>0.0332485474349285</v>
+        <v>0.0317079950026151</v>
       </c>
     </row>
     <row r="481">
@@ -9015,10 +9015,10 @@
         <v>482</v>
       </c>
       <c r="B481" t="n">
-        <v>0.030568829400481</v>
+        <v>0.0310130700901941</v>
       </c>
       <c r="C481" t="n">
-        <v>0.0357122392547113</v>
+        <v>0.0333533910004951</v>
       </c>
     </row>
     <row r="482">
@@ -9026,10 +9026,10 @@
         <v>483</v>
       </c>
       <c r="B482" t="n">
-        <v>0.030568829400481</v>
+        <v>0.0310130700901941</v>
       </c>
       <c r="C482" t="n">
-        <v>0.0357122392547113</v>
+        <v>0.0333533910004951</v>
       </c>
     </row>
     <row r="483">
@@ -9037,10 +9037,10 @@
         <v>484</v>
       </c>
       <c r="B483" t="n">
-        <v>0.030568829400481</v>
+        <v>0.0310130700901941</v>
       </c>
       <c r="C483" t="n">
-        <v>0.0357122392547113</v>
+        <v>0.0333533910004951</v>
       </c>
     </row>
     <row r="484">
@@ -9048,10 +9048,10 @@
         <v>485</v>
       </c>
       <c r="B484" t="n">
-        <v>0.0284552566282657</v>
+        <v>0.0287304213175071</v>
       </c>
       <c r="C484" t="n">
-        <v>0.032148965845752</v>
+        <v>0.0307021462620772</v>
       </c>
     </row>
     <row r="485">
@@ -9059,10 +9059,10 @@
         <v>486</v>
       </c>
       <c r="B485" t="n">
-        <v>0.0317252457298023</v>
+        <v>0.0319506495490306</v>
       </c>
       <c r="C485" t="n">
-        <v>0.0348265584958357</v>
+        <v>0.0331788425944933</v>
       </c>
     </row>
     <row r="486">
@@ -9070,10 +9070,10 @@
         <v>487</v>
       </c>
       <c r="B486" t="n">
-        <v>0.0284552566282657</v>
+        <v>0.0287304213175071</v>
       </c>
       <c r="C486" t="n">
-        <v>0.032148965845752</v>
+        <v>0.0307021462620772</v>
       </c>
     </row>
     <row r="487">
@@ -9081,10 +9081,10 @@
         <v>488</v>
       </c>
       <c r="B487" t="n">
-        <v>0.026677870083437</v>
+        <v>0.0269407032282797</v>
       </c>
       <c r="C487" t="n">
-        <v>0.0302085912356457</v>
+        <v>0.0288250631341566</v>
       </c>
     </row>
     <row r="488">
@@ -9092,10 +9092,10 @@
         <v>489</v>
       </c>
       <c r="B488" t="n">
-        <v>0.0269055947007925</v>
+        <v>0.0271065759661357</v>
       </c>
       <c r="C488" t="n">
-        <v>0.0304567629997949</v>
+        <v>0.0289510373870791</v>
       </c>
     </row>
     <row r="489">
@@ -9103,10 +9103,10 @@
         <v>490</v>
       </c>
       <c r="B489" t="n">
-        <v>0.0317252457298023</v>
+        <v>0.0319506495490306</v>
       </c>
       <c r="C489" t="n">
-        <v>0.0348265584958357</v>
+        <v>0.0331788425944933</v>
       </c>
     </row>
     <row r="490">
@@ -9114,10 +9114,10 @@
         <v>491</v>
       </c>
       <c r="B490" t="n">
-        <v>0.0342255389128413</v>
+        <v>0.0346728409274537</v>
       </c>
       <c r="C490" t="n">
-        <v>0.0321786109916061</v>
+        <v>0.0296232339561265</v>
       </c>
     </row>
     <row r="491">
@@ -9125,10 +9125,10 @@
         <v>492</v>
       </c>
       <c r="B491" t="n">
-        <v>0.0250436217617382</v>
+        <v>0.0250871767379713</v>
       </c>
       <c r="C491" t="n">
-        <v>0.026128936323354</v>
+        <v>0.0258404476512371</v>
       </c>
     </row>
     <row r="492">
@@ -9136,10 +9136,10 @@
         <v>493</v>
       </c>
       <c r="B492" t="n">
-        <v>0.0317384163598404</v>
+        <v>0.0321222917157639</v>
       </c>
       <c r="C492" t="n">
-        <v>0.0299669702360375</v>
+        <v>0.0277645444015218</v>
       </c>
     </row>
     <row r="493">
@@ -9147,10 +9147,10 @@
         <v>494</v>
       </c>
       <c r="B493" t="n">
-        <v>0.0223894793472545</v>
+        <v>0.0224521246610844</v>
       </c>
       <c r="C493" t="n">
-        <v>0.0228836976540485</v>
+        <v>0.022455924085096</v>
       </c>
     </row>
     <row r="494">
@@ -9158,10 +9158,10 @@
         <v>495</v>
       </c>
       <c r="B494" t="n">
-        <v>0.0257690897487432</v>
+        <v>0.0258317350625731</v>
       </c>
       <c r="C494" t="n">
-        <v>0.0263821478370747</v>
+        <v>0.0259543742681223</v>
       </c>
     </row>
     <row r="495">
@@ -9169,10 +9169,10 @@
         <v>496</v>
       </c>
       <c r="B495" t="n">
-        <v>0.0285745040050259</v>
+        <v>0.028817882196472</v>
       </c>
       <c r="C495" t="n">
-        <v>0.0312927565326739</v>
+        <v>0.0299735022219722</v>
       </c>
     </row>
     <row r="496">
@@ -9180,10 +9180,10 @@
         <v>497</v>
       </c>
       <c r="B496" t="n">
-        <v>0.0245351666802782</v>
+        <v>0.0246268247036658</v>
       </c>
       <c r="C496" t="n">
-        <v>0.0247035749997641</v>
+        <v>0.0241312463055134</v>
       </c>
     </row>
     <row r="497">
@@ -9191,10 +9191,10 @@
         <v>498</v>
       </c>
       <c r="B497" t="n">
-        <v>0.0216640113602495</v>
+        <v>0.0217075663364826</v>
       </c>
       <c r="C497" t="n">
-        <v>0.0226304861403278</v>
+        <v>0.0223419974682108</v>
       </c>
     </row>
     <row r="498">
@@ -9202,10 +9202,10 @@
         <v>499</v>
       </c>
       <c r="B498" t="n">
-        <v>0.0243950084019574</v>
+        <v>0.0244866664253449</v>
       </c>
       <c r="C498" t="n">
-        <v>0.024557045292004</v>
+        <v>0.0239847165977533</v>
       </c>
     </row>
     <row r="499">
@@ -9213,10 +9213,10 @@
         <v>500</v>
       </c>
       <c r="B499" t="n">
-        <v>0.0292753901028034</v>
+        <v>0.0294869261944066</v>
       </c>
       <c r="C499" t="n">
-        <v>0.0330776887752454</v>
+        <v>0.0314884315315709</v>
       </c>
     </row>
     <row r="500">
@@ -9224,10 +9224,10 @@
         <v>501</v>
       </c>
       <c r="B500" t="n">
-        <v>0.034384261178609</v>
+        <v>0.0348186287679976</v>
       </c>
       <c r="C500" t="n">
-        <v>0.0319019374314047</v>
+        <v>0.029439314287334</v>
       </c>
     </row>
     <row r="501">
@@ -9235,10 +9235,10 @@
         <v>502</v>
       </c>
       <c r="B501" t="n">
-        <v>0.0287628924319724</v>
+        <v>0.0288193818334293</v>
       </c>
       <c r="C501" t="n">
-        <v>0.032514914436954</v>
+        <v>0.0321336718734281</v>
       </c>
     </row>
     <row r="502">
@@ -9246,10 +9246,10 @@
         <v>503</v>
       </c>
       <c r="B502" t="n">
-        <v>0.0318785746381612</v>
+        <v>0.0322624499940847</v>
       </c>
       <c r="C502" t="n">
-        <v>0.0301134999437976</v>
+        <v>0.0279110741092818</v>
       </c>
     </row>
     <row r="503">
@@ -9257,10 +9257,10 @@
         <v>504</v>
       </c>
       <c r="B503" t="n">
-        <v>0.0256289314704224</v>
+        <v>0.0256915767842522</v>
       </c>
       <c r="C503" t="n">
-        <v>0.0262356181293147</v>
+        <v>0.0258078445603622</v>
       </c>
     </row>
     <row r="504">
@@ -9268,10 +9268,10 @@
         <v>505</v>
       </c>
       <c r="B504" t="n">
-        <v>0.0253583765595836</v>
+        <v>0.0254169292764885</v>
       </c>
       <c r="C504" t="n">
-        <v>0.0268839182378762</v>
+        <v>0.0265206357612595</v>
       </c>
     </row>
     <row r="505">
@@ -9279,10 +9279,10 @@
         <v>506</v>
       </c>
       <c r="B505" t="n">
-        <v>0.0260838445465886</v>
+        <v>0.0261614876010903</v>
       </c>
       <c r="C505" t="n">
-        <v>0.0271371297515969</v>
+        <v>0.0266345623781448</v>
       </c>
     </row>
     <row r="506">
@@ -9290,10 +9290,10 @@
         <v>507</v>
       </c>
       <c r="B506" t="n">
-        <v>0.0225296376255753</v>
+        <v>0.0225922829394052</v>
       </c>
       <c r="C506" t="n">
-        <v>0.0230302273618086</v>
+        <v>0.0226024537928561</v>
       </c>
     </row>
     <row r="507">
@@ -9301,10 +9301,10 @@
         <v>508</v>
       </c>
       <c r="B507" t="n">
-        <v>0.0249034634834173</v>
+        <v>0.0249470184596505</v>
       </c>
       <c r="C507" t="n">
-        <v>0.025982406615594</v>
+        <v>0.025693917943477</v>
       </c>
     </row>
     <row r="508">
@@ -9312,10 +9312,10 @@
         <v>509</v>
       </c>
       <c r="B508" t="n">
-        <v>0.0337439454145433</v>
+        <v>0.0341568334800245</v>
       </c>
       <c r="C508" t="n">
-        <v>0.0316403178739931</v>
+        <v>0.029293336914179</v>
       </c>
     </row>
     <row r="509">
@@ -9323,10 +9323,10 @@
         <v>510</v>
       </c>
       <c r="B509" t="n">
-        <v>0.0245046322703726</v>
+        <v>0.0245962902937602</v>
       </c>
       <c r="C509" t="n">
-        <v>0.024557045292004</v>
+        <v>0.0239847165977533</v>
       </c>
     </row>
     <row r="510">
@@ -9334,10 +9334,10 @@
         <v>511</v>
       </c>
       <c r="B510" t="n">
-        <v>0.0343143471759372</v>
+        <v>0.0347616491905495</v>
       </c>
       <c r="C510" t="n">
-        <v>0.0321786109916061</v>
+        <v>0.0296232339561265</v>
       </c>
     </row>
     <row r="511">
@@ -9345,10 +9345,10 @@
         <v>512</v>
       </c>
       <c r="B511" t="n">
-        <v>0.0317252457298023</v>
+        <v>0.0319506495490306</v>
       </c>
       <c r="C511" t="n">
-        <v>0.0348265584958357</v>
+        <v>0.0331788425944933</v>
       </c>
     </row>
     <row r="512">
@@ -9356,10 +9356,10 @@
         <v>513</v>
       </c>
       <c r="B512" t="n">
-        <v>0.025335051881858</v>
+        <v>0.0255784300733042</v>
       </c>
       <c r="C512" t="n">
-        <v>0.0279408360574077</v>
+        <v>0.026621581746706</v>
       </c>
     </row>
     <row r="513">
@@ -9367,10 +9367,10 @@
         <v>514</v>
       </c>
       <c r="B513" t="n">
-        <v>0.0355469600548748</v>
+        <v>0.0356034702492461</v>
       </c>
       <c r="C513" t="n">
-        <v>0.0345273133551724</v>
+        <v>0.0341457457396978</v>
       </c>
     </row>
     <row r="514">
@@ -9378,10 +9378,10 @@
         <v>515</v>
       </c>
       <c r="B514" t="n">
-        <v>0.0346360712930219</v>
+        <v>0.0346925814873931</v>
       </c>
       <c r="C514" t="n">
-        <v>0.0380936301814372</v>
+        <v>0.0377120625659627</v>
       </c>
     </row>
     <row r="515">
@@ -9389,10 +9389,10 @@
         <v>516</v>
       </c>
       <c r="B515" t="n">
-        <v>0.0317252457298023</v>
+        <v>0.0319506495490306</v>
       </c>
       <c r="C515" t="n">
-        <v>0.0348265584958357</v>
+        <v>0.0331788425944933</v>
       </c>
     </row>
     <row r="516">
@@ -9400,10 +9400,10 @@
         <v>517</v>
       </c>
       <c r="B516" t="n">
-        <v>0.0342255389128413</v>
+        <v>0.0346728409274537</v>
       </c>
       <c r="C516" t="n">
-        <v>0.0321786109916061</v>
+        <v>0.0296232339561265</v>
       </c>
     </row>
     <row r="517">
@@ -9411,10 +9411,10 @@
         <v>518</v>
       </c>
       <c r="B517" t="n">
-        <v>0.0342255389128413</v>
+        <v>0.0346728409274537</v>
       </c>
       <c r="C517" t="n">
-        <v>0.0321786109916061</v>
+        <v>0.0296232339561265</v>
       </c>
     </row>
     <row r="518">
@@ -9422,10 +9422,10 @@
         <v>519</v>
       </c>
       <c r="B518" t="n">
-        <v>0.034384261178609</v>
+        <v>0.0348186287679976</v>
       </c>
       <c r="C518" t="n">
-        <v>0.0319019374314047</v>
+        <v>0.029439314287334</v>
       </c>
     </row>
   </sheetData>
@@ -9494,7 +9494,7 @@
         <v>534</v>
       </c>
       <c r="C2" t="n">
-        <v>2143398600</v>
+        <v>2381885847</v>
       </c>
       <c r="D2" t="n">
         <v>896132706</v>
@@ -9503,7 +9503,7 @@
         <v>894603984</v>
       </c>
       <c r="F2" t="n">
-        <v>20185223034</v>
+        <v>19946735787</v>
       </c>
       <c r="G2" t="n">
         <v>20171940</v>
@@ -9527,10 +9527,10 @@
         <v>535</v>
       </c>
       <c r="N2" t="n">
-        <v>0.00108181701848021</v>
+        <v>0.00109475144370398</v>
       </c>
       <c r="O2" t="n">
-        <v>0.00127431208926187</v>
+        <v>0.00118155819785299</v>
       </c>
     </row>
     <row r="3">
@@ -9541,7 +9541,7 @@
         <v>537</v>
       </c>
       <c r="C3" t="n">
-        <v>2618447178</v>
+        <v>2879895939</v>
       </c>
       <c r="D3" t="n">
         <v>913710633</v>
@@ -9550,7 +9550,7 @@
         <v>952969923</v>
       </c>
       <c r="F3" t="n">
-        <v>23087398290</v>
+        <v>22825949529</v>
       </c>
       <c r="G3" t="n">
         <v>33430464</v>
@@ -9574,10 +9574,10 @@
         <v>538</v>
       </c>
       <c r="N3" t="n">
-        <v>0.00246766148244069</v>
+        <v>0.0024959261132869</v>
       </c>
       <c r="O3" t="n">
-        <v>0.00288119824960204</v>
+        <v>0.00268466496623774</v>
       </c>
     </row>
     <row r="4">
@@ -9588,7 +9588,7 @@
         <v>540</v>
       </c>
       <c r="C4" t="n">
-        <v>108623412</v>
+        <v>112971621</v>
       </c>
       <c r="D4" t="n">
         <v>194286888</v>
@@ -9597,7 +9597,7 @@
         <v>32212455</v>
       </c>
       <c r="F4" t="n">
-        <v>522001344</v>
+        <v>517653135</v>
       </c>
       <c r="G4" t="n">
         <v>1614681</v>
@@ -9621,10 +9621,10 @@
         <v>541</v>
       </c>
       <c r="N4" t="n">
-        <v>0.00104685067630784</v>
+        <v>0.00105564406559616</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0011403820164646</v>
+        <v>0.00110622799982555</v>
       </c>
     </row>
     <row r="5">
@@ -9635,7 +9635,7 @@
         <v>543</v>
       </c>
       <c r="C5" t="n">
-        <v>2618447178</v>
+        <v>2879895939</v>
       </c>
       <c r="D5" t="n">
         <v>913710633</v>
@@ -9644,7 +9644,7 @@
         <v>952969923</v>
       </c>
       <c r="F5" t="n">
-        <v>23087398290</v>
+        <v>22825949529</v>
       </c>
       <c r="G5" t="n">
         <v>33430464</v>
@@ -9668,10 +9668,10 @@
         <v>544</v>
       </c>
       <c r="N5" t="n">
-        <v>0.000706044299805771</v>
+        <v>0.000714131341580783</v>
       </c>
       <c r="O5" t="n">
-        <v>0.000824364933229343</v>
+        <v>0.000768133069614843</v>
       </c>
     </row>
     <row r="6">
@@ -9682,7 +9682,7 @@
         <v>546</v>
       </c>
       <c r="C6" t="n">
-        <v>88474188</v>
+        <v>92665158</v>
       </c>
       <c r="D6" t="n">
         <v>12139770</v>
@@ -9691,7 +9691,7 @@
         <v>31900707</v>
       </c>
       <c r="F6" t="n">
-        <v>276183846</v>
+        <v>271992876</v>
       </c>
       <c r="G6" t="n">
         <v>1462284</v>
@@ -9715,10 +9715,10 @@
         <v>547</v>
       </c>
       <c r="N6" t="n">
-        <v>0.00700565010598049</v>
+        <v>0.00711359583550269</v>
       </c>
       <c r="O6" t="n">
-        <v>0.00696143286355515</v>
+        <v>0.006727218166871</v>
       </c>
     </row>
     <row r="7">
@@ -9729,7 +9729,7 @@
         <v>549</v>
       </c>
       <c r="C7" t="n">
-        <v>58833771</v>
+        <v>60848052</v>
       </c>
       <c r="D7" t="n">
         <v>44204886</v>
@@ -9738,7 +9738,7 @@
         <v>20962152</v>
       </c>
       <c r="F7" t="n">
-        <v>286236336</v>
+        <v>284222055</v>
       </c>
       <c r="G7" t="n">
         <v>152397</v>
@@ -9762,10 +9762,10 @@
         <v>550</v>
       </c>
       <c r="N7" t="n">
-        <v>0.00178968595377772</v>
+        <v>0.00180236945370056</v>
       </c>
       <c r="O7" t="n">
-        <v>0.00193517042217809</v>
+        <v>0.0018875238350463</v>
       </c>
     </row>
     <row r="8">
@@ -9776,7 +9776,7 @@
         <v>552</v>
       </c>
       <c r="C8" t="n">
-        <v>102979746</v>
+        <v>107327955</v>
       </c>
       <c r="D8" t="n">
         <v>179511789</v>
@@ -9785,7 +9785,7 @@
         <v>32212455</v>
       </c>
       <c r="F8" t="n">
-        <v>503465517</v>
+        <v>499117308</v>
       </c>
       <c r="G8" t="n">
         <v>1614681</v>
@@ -9809,10 +9809,10 @@
         <v>553</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0186252761576916</v>
+        <v>0.0187875357950921</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0208275913046197</v>
+        <v>0.0201785841821735</v>
       </c>
     </row>
     <row r="9">
@@ -9917,7 +9917,7 @@
         <v>559</v>
       </c>
       <c r="C11" t="n">
-        <v>15087936</v>
+        <v>16044396</v>
       </c>
       <c r="D11" t="n">
         <v>98628702</v>
@@ -9926,7 +9926,7 @@
         <v>10528680</v>
       </c>
       <c r="F11" t="n">
-        <v>165084771</v>
+        <v>164128311</v>
       </c>
       <c r="G11" t="n">
         <v>59340</v>
@@ -9950,10 +9950,10 @@
         <v>560</v>
       </c>
       <c r="N11" t="n">
-        <v>0.00146677696878533</v>
+        <v>0.00147532463183637</v>
       </c>
       <c r="O11" t="n">
-        <v>0.00170470291626341</v>
+        <v>0.00164334456424992</v>
       </c>
     </row>
     <row r="12">
@@ -10011,7 +10011,7 @@
         <v>563</v>
       </c>
       <c r="C13" t="n">
-        <v>15529938</v>
+        <v>16486398</v>
       </c>
       <c r="D13" t="n">
         <v>88884939</v>
@@ -10020,7 +10020,7 @@
         <v>10528680</v>
       </c>
       <c r="F13" t="n">
-        <v>154223418</v>
+        <v>153266958</v>
       </c>
       <c r="G13" t="n">
         <v>59340</v>
@@ -10044,10 +10044,10 @@
         <v>564</v>
       </c>
       <c r="N13" t="n">
-        <v>0.0160594958412866</v>
+        <v>0.0161597148682236</v>
       </c>
       <c r="O13" t="n">
-        <v>0.0180810567160546</v>
+        <v>0.0174409028173082</v>
       </c>
     </row>
     <row r="14">
@@ -10058,7 +10058,7 @@
         <v>565</v>
       </c>
       <c r="C14" t="n">
-        <v>11793570</v>
+        <v>12750030</v>
       </c>
       <c r="D14" t="n">
         <v>49749294</v>
@@ -10067,7 +10067,7 @@
         <v>10528680</v>
       </c>
       <c r="F14" t="n">
-        <v>117055692</v>
+        <v>116099232</v>
       </c>
       <c r="G14" t="n">
         <v>59340</v>
@@ -10091,10 +10091,10 @@
         <v>566</v>
       </c>
       <c r="N14" t="n">
-        <v>0.00189766867552242</v>
+        <v>0.0019133022344196</v>
       </c>
       <c r="O14" t="n">
-        <v>0.00228395076661179</v>
+        <v>0.0021901093316597</v>
       </c>
     </row>
     <row r="15">
@@ -10105,7 +10105,7 @@
         <v>567</v>
       </c>
       <c r="C15" t="n">
-        <v>11624943</v>
+        <v>12581403</v>
       </c>
       <c r="D15" t="n">
         <v>911409</v>
@@ -10114,7 +10114,7 @@
         <v>8219898</v>
       </c>
       <c r="F15" t="n">
-        <v>58179831</v>
+        <v>57223371</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -10138,10 +10138,10 @@
         <v>568</v>
       </c>
       <c r="N15" t="n">
-        <v>0.00228137977918843</v>
+        <v>0.00231951190012906</v>
       </c>
       <c r="O15" t="n">
-        <v>0.00285445522088083</v>
+        <v>0.00272320514952406</v>
       </c>
     </row>
     <row r="16">
@@ -10387,7 +10387,7 @@
         <v>580</v>
       </c>
       <c r="C21" t="n">
-        <v>61692027</v>
+        <v>74489733</v>
       </c>
       <c r="D21" t="n">
         <v>46193346</v>
@@ -10396,7 +10396,7 @@
         <v>71413065</v>
       </c>
       <c r="F21" t="n">
-        <v>540198945</v>
+        <v>527401239</v>
       </c>
       <c r="G21" t="n">
         <v>124200</v>
@@ -10420,10 +10420,10 @@
         <v>581</v>
       </c>
       <c r="N21" t="n">
-        <v>0.0000362402410837733</v>
+        <v>0.0000371196321743946</v>
       </c>
       <c r="O21" t="n">
-        <v>0.0000446361586226919</v>
+        <v>0.0000407209462837032</v>
       </c>
     </row>
     <row r="22">
@@ -10434,7 +10434,7 @@
         <v>583</v>
       </c>
       <c r="C22" t="n">
-        <v>74909841</v>
+        <v>87744795</v>
       </c>
       <c r="D22" t="n">
         <v>55943019</v>
@@ -10443,7 +10443,7 @@
         <v>76775922</v>
       </c>
       <c r="F22" t="n">
-        <v>978412803</v>
+        <v>965577849</v>
       </c>
       <c r="G22" t="n">
         <v>2926770</v>
@@ -10467,10 +10467,10 @@
         <v>584</v>
       </c>
       <c r="N22" t="n">
-        <v>0.0102298123443505</v>
+        <v>0.0103657922355673</v>
       </c>
       <c r="O22" t="n">
-        <v>0.0123067255824134</v>
+        <v>0.0113466260908649</v>
       </c>
     </row>
     <row r="23">
@@ -10481,7 +10481,7 @@
         <v>585</v>
       </c>
       <c r="C23" t="n">
-        <v>41341968</v>
+        <v>54098109</v>
       </c>
       <c r="D23" t="n">
         <v>33341547</v>
@@ -10490,7 +10490,7 @@
         <v>30946479</v>
       </c>
       <c r="F23" t="n">
-        <v>225681099</v>
+        <v>212924958</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -10514,10 +10514,10 @@
         <v>586</v>
       </c>
       <c r="N23" t="n">
-        <v>0.00200588986851752</v>
+        <v>0.00212606091015408</v>
       </c>
       <c r="O23" t="n">
-        <v>0.00278409467006533</v>
+        <v>0.00236649838317754</v>
       </c>
     </row>
     <row r="24">
@@ -10528,7 +10528,7 @@
         <v>588</v>
       </c>
       <c r="C24" t="n">
-        <v>74909841</v>
+        <v>87744795</v>
       </c>
       <c r="D24" t="n">
         <v>55943019</v>
@@ -10537,7 +10537,7 @@
         <v>76775922</v>
       </c>
       <c r="F24" t="n">
-        <v>978412803</v>
+        <v>965577849</v>
       </c>
       <c r="G24" t="n">
         <v>2926770</v>
@@ -10561,10 +10561,10 @@
         <v>589</v>
       </c>
       <c r="N24" t="n">
-        <v>0.00969436063276862</v>
+        <v>0.00982322302631862</v>
       </c>
       <c r="O24" t="n">
-        <v>0.0116625634800017</v>
+        <v>0.0107527177869034</v>
       </c>
     </row>
     <row r="25">
@@ -10575,7 +10575,7 @@
         <v>591</v>
       </c>
       <c r="C25" t="n">
-        <v>73923555</v>
+        <v>86758509</v>
       </c>
       <c r="D25" t="n">
         <v>55827123</v>
@@ -10584,7 +10584,7 @@
         <v>76775922</v>
       </c>
       <c r="F25" t="n">
-        <v>923777145</v>
+        <v>910942191</v>
       </c>
       <c r="G25" t="n">
         <v>2926770</v>
@@ -10608,10 +10608,10 @@
         <v>592</v>
       </c>
       <c r="N25" t="n">
-        <v>0.000580809822914595</v>
+        <v>0.000588993292111113</v>
       </c>
       <c r="O25" t="n">
-        <v>0.000700112515984379</v>
+        <v>0.000645164381316128</v>
       </c>
     </row>
     <row r="26">
@@ -10622,7 +10622,7 @@
         <v>593</v>
       </c>
       <c r="C26" t="n">
-        <v>34944333</v>
+        <v>47636997</v>
       </c>
       <c r="D26" t="n">
         <v>1937004</v>
@@ -10631,7 +10631,7 @@
         <v>24503130</v>
       </c>
       <c r="F26" t="n">
-        <v>112574769</v>
+        <v>99882105</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -10655,10 +10655,10 @@
         <v>594</v>
       </c>
       <c r="N26" t="n">
-        <v>0.00232993211827066</v>
+        <v>0.00262601163641876</v>
       </c>
       <c r="O26" t="n">
-        <v>0.00362657091018333</v>
+        <v>0.00298849543195287</v>
       </c>
     </row>
     <row r="27">
@@ -10669,7 +10669,7 @@
         <v>595</v>
       </c>
       <c r="C27" t="n">
-        <v>61692027</v>
+        <v>74489733</v>
       </c>
       <c r="D27" t="n">
         <v>46193346</v>
@@ -10678,7 +10678,7 @@
         <v>71413065</v>
       </c>
       <c r="F27" t="n">
-        <v>540198945</v>
+        <v>527401239</v>
       </c>
       <c r="G27" t="n">
         <v>124200</v>
@@ -10702,10 +10702,10 @@
         <v>596</v>
       </c>
       <c r="N27" t="n">
-        <v>0.00109827893129262</v>
+        <v>0.00112492932539356</v>
       </c>
       <c r="O27" t="n">
-        <v>0.0013527206006514</v>
+        <v>0.00123406817736285</v>
       </c>
     </row>
     <row r="28">
@@ -10763,7 +10763,7 @@
         <v>599</v>
       </c>
       <c r="C29" t="n">
-        <v>26595075</v>
+        <v>26673888</v>
       </c>
       <c r="D29" t="n">
         <v>7070796</v>
@@ -10772,7 +10772,7 @@
         <v>44760405</v>
       </c>
       <c r="F29" t="n">
-        <v>539123463</v>
+        <v>539044650</v>
       </c>
       <c r="G29" t="n">
         <v>440100</v>
@@ -10796,10 +10796,10 @@
         <v>600</v>
       </c>
       <c r="N29" t="n">
-        <v>0.00127763055639817</v>
+        <v>0.00127781735705938</v>
       </c>
       <c r="O29" t="n">
-        <v>0.00300194196717617</v>
+        <v>0.00299862994374425</v>
       </c>
     </row>
     <row r="30">
@@ -10810,7 +10810,7 @@
         <v>601</v>
       </c>
       <c r="C30" t="n">
-        <v>31720773</v>
+        <v>31799586</v>
       </c>
       <c r="D30" t="n">
         <v>22504584</v>
@@ -10819,7 +10819,7 @@
         <v>45829443</v>
       </c>
       <c r="F30" t="n">
-        <v>697682673</v>
+        <v>697603860</v>
       </c>
       <c r="G30" t="n">
         <v>2614047</v>
@@ -10843,10 +10843,10 @@
         <v>602</v>
       </c>
       <c r="N30" t="n">
-        <v>0.00190151159164591</v>
+        <v>0.00190172641819958</v>
       </c>
       <c r="O30" t="n">
-        <v>0.00208550212161885</v>
+        <v>0.00208338481214289</v>
       </c>
     </row>
     <row r="31">
@@ -10857,7 +10857,7 @@
         <v>603</v>
       </c>
       <c r="C31" t="n">
-        <v>22906536</v>
+        <v>22982742</v>
       </c>
       <c r="D31" t="n">
         <v>15396</v>
@@ -10866,7 +10866,7 @@
         <v>40925244</v>
       </c>
       <c r="F31" t="n">
-        <v>2037330</v>
+        <v>1961124</v>
       </c>
       <c r="G31" t="n">
         <v>124200</v>
@@ -10890,10 +10890,10 @@
         <v>604</v>
       </c>
       <c r="N31" t="n">
-        <v>0.0016900867997711</v>
+        <v>0.00175576074729474</v>
       </c>
       <c r="O31" t="n">
-        <v>0.00197483913139477</v>
+        <v>0.00197248426778122</v>
       </c>
     </row>
     <row r="32">
@@ -10951,7 +10951,7 @@
         <v>607</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>11813625</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
@@ -10960,7 +10960,7 @@
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>20756328</v>
+        <v>8942703</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -11609,7 +11609,7 @@
         <v>635</v>
       </c>
       <c r="C47" t="n">
-        <v>13217814</v>
+        <v>13255062</v>
       </c>
       <c r="D47" t="n">
         <v>9749673</v>
@@ -11618,7 +11618,7 @@
         <v>5362857</v>
       </c>
       <c r="F47" t="n">
-        <v>438213858</v>
+        <v>438176610</v>
       </c>
       <c r="G47" t="n">
         <v>2802570</v>
@@ -11642,10 +11642,10 @@
         <v>636</v>
       </c>
       <c r="N47" t="n">
-        <v>0.000678491687499303</v>
+        <v>0.000678549363919722</v>
       </c>
       <c r="O47" t="n">
-        <v>0.000746103302727872</v>
+        <v>0.000744610608736669</v>
       </c>
     </row>
     <row r="48">
@@ -12361,7 +12361,7 @@
         <v>667</v>
       </c>
       <c r="C63" t="n">
-        <v>42291807</v>
+        <v>44625735</v>
       </c>
       <c r="D63" t="n">
         <v>48361749</v>
@@ -12370,7 +12370,7 @@
         <v>11250303</v>
       </c>
       <c r="F63" t="n">
-        <v>122483130</v>
+        <v>120149202</v>
       </c>
       <c r="G63" t="n">
         <v>1462284</v>
@@ -12394,10 +12394,10 @@
         <v>668</v>
       </c>
       <c r="N63" t="n">
-        <v>0.00195586845306778</v>
+        <v>0.00199386168207759</v>
       </c>
       <c r="O63" t="n">
-        <v>0.00238710278694657</v>
+        <v>0.00228739410621777</v>
       </c>
     </row>
     <row r="64">
@@ -12549,7 +12549,7 @@
         <v>675</v>
       </c>
       <c r="C67" t="n">
-        <v>253698060</v>
+        <v>324410631</v>
       </c>
       <c r="D67" t="n">
         <v>134617371</v>
@@ -12558,7 +12558,7 @@
         <v>119417463</v>
       </c>
       <c r="F67" t="n">
-        <v>1903985370</v>
+        <v>1833272799</v>
       </c>
       <c r="G67" t="n">
         <v>1687149</v>
@@ -12582,10 +12582,10 @@
         <v>676</v>
       </c>
       <c r="N67" t="n">
-        <v>0.00246395835489009</v>
+        <v>0.00255899758211598</v>
       </c>
       <c r="O67" t="n">
-        <v>0.00335447407799219</v>
+        <v>0.00282002506583101</v>
       </c>
     </row>
     <row r="68">
@@ -12596,7 +12596,7 @@
         <v>677</v>
       </c>
       <c r="C68" t="n">
-        <v>23984211</v>
+        <v>24049125</v>
       </c>
       <c r="D68" t="n">
         <v>171003891</v>
@@ -12605,7 +12605,7 @@
         <v>26958012</v>
       </c>
       <c r="F68" t="n">
-        <v>944866626</v>
+        <v>944801712</v>
       </c>
       <c r="G68" t="n">
         <v>554229</v>
@@ -12629,10 +12629,10 @@
         <v>678</v>
       </c>
       <c r="N68" t="n">
-        <v>0.000330159708699458</v>
+        <v>0.000330182392810905</v>
       </c>
       <c r="O68" t="n">
-        <v>0.000338265175432175</v>
+        <v>0.00033783468380121</v>
       </c>
     </row>
     <row r="69">
@@ -12643,7 +12643,7 @@
         <v>679</v>
       </c>
       <c r="C69" t="n">
-        <v>260391738</v>
+        <v>331117506</v>
       </c>
       <c r="D69" t="n">
         <v>175382124</v>
@@ -12652,7 +12652,7 @@
         <v>116201145</v>
       </c>
       <c r="F69" t="n">
-        <v>2271124845</v>
+        <v>2200399077</v>
       </c>
       <c r="G69" t="n">
         <v>1687149</v>
@@ -12676,10 +12676,10 @@
         <v>680</v>
       </c>
       <c r="N69" t="n">
-        <v>0.0190480689624969</v>
+        <v>0.0196603166771825</v>
       </c>
       <c r="O69" t="n">
-        <v>0.0254848872436073</v>
+        <v>0.0214554594102985</v>
       </c>
     </row>
     <row r="70">
@@ -12690,7 +12690,7 @@
         <v>681</v>
       </c>
       <c r="C70" t="n">
-        <v>236407527</v>
+        <v>307068381</v>
       </c>
       <c r="D70" t="n">
         <v>3247110</v>
@@ -12699,7 +12699,7 @@
         <v>89243133</v>
       </c>
       <c r="F70" t="n">
-        <v>1299000786</v>
+        <v>1228339932</v>
       </c>
       <c r="G70" t="n">
         <v>1132920</v>
@@ -12723,10 +12723,10 @@
         <v>682</v>
       </c>
       <c r="N70" t="n">
-        <v>0.00476102052181514</v>
+        <v>0.00503490055064008</v>
       </c>
       <c r="O70" t="n">
-        <v>0.00683080547111435</v>
+        <v>0.00561289851901704</v>
       </c>
     </row>
     <row r="71">
@@ -12737,7 +12737,7 @@
         <v>683</v>
       </c>
       <c r="C71" t="n">
-        <v>27351594</v>
+        <v>29241240</v>
       </c>
       <c r="D71" t="n">
         <v>48739473</v>
@@ -12746,7 +12746,7 @@
         <v>4975614</v>
       </c>
       <c r="F71" t="n">
-        <v>814792044</v>
+        <v>812902398</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -12770,10 +12770,10 @@
         <v>684</v>
       </c>
       <c r="N71" t="n">
-        <v>0.00166196374887529</v>
+        <v>0.00166582709477996</v>
       </c>
       <c r="O71" t="n">
-        <v>0.00201302073473218</v>
+        <v>0.00190185047403832</v>
       </c>
     </row>
     <row r="72">
@@ -12784,7 +12784,7 @@
         <v>685</v>
       </c>
       <c r="C72" t="n">
-        <v>16475829</v>
+        <v>16489026</v>
       </c>
       <c r="D72" t="n">
         <v>7849782</v>
@@ -12793,7 +12793,7 @@
         <v>356910</v>
       </c>
       <c r="F72" t="n">
-        <v>619486662</v>
+        <v>619473465</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -12817,10 +12817,10 @@
         <v>686</v>
       </c>
       <c r="N72" t="n">
-        <v>0.00148971925726465</v>
+        <v>0.00148975099361197</v>
       </c>
       <c r="O72" t="n">
-        <v>0.00170817892441628</v>
+        <v>0.00170684074782191</v>
       </c>
     </row>
     <row r="73">
@@ -12925,7 +12925,7 @@
         <v>691</v>
       </c>
       <c r="C75" t="n">
-        <v>432703575</v>
+        <v>473903745</v>
       </c>
       <c r="D75" t="n">
         <v>39166989</v>
@@ -12934,7 +12934,7 @@
         <v>158952795</v>
       </c>
       <c r="F75" t="n">
-        <v>3021401280</v>
+        <v>2980201110</v>
       </c>
       <c r="G75" t="n">
         <v>5383659</v>
@@ -12958,10 +12958,10 @@
         <v>692</v>
       </c>
       <c r="N75" t="n">
-        <v>0.00763468847805612</v>
+        <v>0.00774023520177804</v>
       </c>
       <c r="O75" t="n">
-        <v>0.00914903862186086</v>
+        <v>0.00855341872583003</v>
       </c>
     </row>
     <row r="76">
@@ -12972,7 +12972,7 @@
         <v>693</v>
       </c>
       <c r="C76" t="n">
-        <v>411011907</v>
+        <v>452090412</v>
       </c>
       <c r="D76" t="n">
         <v>34459731</v>
@@ -12981,7 +12981,7 @@
         <v>145599768</v>
       </c>
       <c r="F76" t="n">
-        <v>2766814248</v>
+        <v>2725735743</v>
       </c>
       <c r="G76" t="n">
         <v>5383659</v>
@@ -13005,10 +13005,10 @@
         <v>694</v>
       </c>
       <c r="N76" t="n">
-        <v>0.000913542006597329</v>
+        <v>0.000927309643457245</v>
       </c>
       <c r="O76" t="n">
-        <v>0.00109833973568736</v>
+        <v>0.00102285220747646</v>
       </c>
     </row>
     <row r="77">
@@ -13019,7 +13019,7 @@
         <v>695</v>
       </c>
       <c r="C77" t="n">
-        <v>11901765</v>
+        <v>11914962</v>
       </c>
       <c r="D77" t="n">
         <v>1295724</v>
@@ -13028,7 +13028,7 @@
         <v>148902</v>
       </c>
       <c r="F77" t="n">
-        <v>492230013</v>
+        <v>492216816</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -13052,10 +13052,10 @@
         <v>696</v>
       </c>
       <c r="N77" t="n">
-        <v>0.0010865160494894</v>
+        <v>0.00108654518045737</v>
       </c>
       <c r="O77" t="n">
-        <v>0.00124994796235879</v>
+        <v>0.00124858060914101</v>
       </c>
     </row>
     <row r="78">
@@ -13489,7 +13489,7 @@
         <v>715</v>
       </c>
       <c r="C87" t="n">
-        <v>418552095</v>
+        <v>459752265</v>
       </c>
       <c r="D87" t="n">
         <v>36592155</v>
@@ -13498,7 +13498,7 @@
         <v>158952795</v>
       </c>
       <c r="F87" t="n">
-        <v>2784371949</v>
+        <v>2743171779</v>
       </c>
       <c r="G87" t="n">
         <v>5383659</v>
@@ -13522,10 +13522,10 @@
         <v>716</v>
       </c>
       <c r="N87" t="n">
-        <v>0.0156865022597597</v>
+        <v>0.0159221005422862</v>
       </c>
       <c r="O87" t="n">
-        <v>0.0188210462598854</v>
+        <v>0.0175677345357415</v>
       </c>
     </row>
     <row r="88">
@@ -13536,7 +13536,7 @@
         <v>717</v>
       </c>
       <c r="C88" t="n">
-        <v>550595538</v>
+        <v>592730835</v>
       </c>
       <c r="D88" t="n">
         <v>53940291</v>
@@ -13545,7 +13545,7 @@
         <v>167243088</v>
       </c>
       <c r="F88" t="n">
-        <v>3723436995</v>
+        <v>3681301698</v>
       </c>
       <c r="G88" t="n">
         <v>5383659</v>
@@ -13569,10 +13569,10 @@
         <v>718</v>
       </c>
       <c r="N88" t="n">
-        <v>0.00161131929667579</v>
+        <v>0.0016297620711879</v>
       </c>
       <c r="O88" t="n">
-        <v>0.00189648301260401</v>
+        <v>0.0017913361482536</v>
       </c>
     </row>
     <row r="89">
@@ -13583,7 +13583,7 @@
         <v>719</v>
       </c>
       <c r="C89" t="n">
-        <v>447267045</v>
+        <v>489402342</v>
       </c>
       <c r="D89" t="n">
         <v>40017258</v>
@@ -13592,7 +13592,7 @@
         <v>27712083</v>
       </c>
       <c r="F89" t="n">
-        <v>3363827541</v>
+        <v>3321692244</v>
       </c>
       <c r="G89" t="n">
         <v>5237427</v>
@@ -13616,10 +13616,10 @@
         <v>720</v>
       </c>
       <c r="N89" t="n">
-        <v>0.00110706212628634</v>
+        <v>0.00112110508633864</v>
       </c>
       <c r="O89" t="n">
-        <v>0.00134008233726009</v>
+        <v>0.00123089031987456</v>
       </c>
     </row>
     <row r="90">
@@ -13630,7 +13630,7 @@
         <v>721</v>
       </c>
       <c r="C90" t="n">
-        <v>417208929</v>
+        <v>458229114</v>
       </c>
       <c r="D90" t="n">
         <v>4666035</v>
@@ -13639,7 +13639,7 @@
         <v>139743888</v>
       </c>
       <c r="F90" t="n">
-        <v>1638391503</v>
+        <v>1597371318</v>
       </c>
       <c r="G90" t="n">
         <v>4969842</v>
@@ -13663,10 +13663,10 @@
         <v>722</v>
       </c>
       <c r="N90" t="n">
-        <v>0.00198639568994396</v>
+        <v>0.00203740594520929</v>
       </c>
       <c r="O90" t="n">
-        <v>0.00243586043303916</v>
+        <v>0.00226876351517957</v>
       </c>
     </row>
     <row r="91">
@@ -13677,7 +13677,7 @@
         <v>723</v>
       </c>
       <c r="C91" t="n">
-        <v>131095290</v>
+        <v>132030417</v>
       </c>
       <c r="D91" t="n">
         <v>21921873</v>
@@ -13686,7 +13686,7 @@
         <v>8439195</v>
       </c>
       <c r="F91" t="n">
-        <v>1097683308</v>
+        <v>1096748181</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -13710,10 +13710,10 @@
         <v>724</v>
       </c>
       <c r="N91" t="n">
-        <v>0.000496390959057929</v>
+        <v>0.000496814199867818</v>
       </c>
       <c r="O91" t="n">
-        <v>0.000549019262155875</v>
+        <v>0.000545364359659511</v>
       </c>
     </row>
     <row r="92">
@@ -13724,7 +13724,7 @@
         <v>725</v>
       </c>
       <c r="C92" t="n">
-        <v>132997551</v>
+        <v>133932678</v>
       </c>
       <c r="D92" t="n">
         <v>20501601</v>
@@ -13733,7 +13733,7 @@
         <v>8439195</v>
       </c>
       <c r="F92" t="n">
-        <v>1083829032</v>
+        <v>1082893905</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -13757,10 +13757,10 @@
         <v>726</v>
       </c>
       <c r="N92" t="n">
-        <v>0.0176667616429009</v>
+        <v>0.0176820176765147</v>
       </c>
       <c r="O92" t="n">
-        <v>0.0195358701903394</v>
+        <v>0.019407554679006</v>
       </c>
     </row>
     <row r="93">
@@ -13818,7 +13818,7 @@
         <v>729</v>
       </c>
       <c r="C94" t="n">
-        <v>73153185</v>
+        <v>74088312</v>
       </c>
       <c r="D94" t="n">
         <v>3876846</v>
@@ -13827,7 +13827,7 @@
         <v>409959</v>
       </c>
       <c r="F94" t="n">
-        <v>633671268</v>
+        <v>632736141</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -13851,10 +13851,10 @@
         <v>730</v>
       </c>
       <c r="N94" t="n">
-        <v>0.00136640740037467</v>
+        <v>0.00136842682738428</v>
       </c>
       <c r="O94" t="n">
-        <v>0.00143194545899235</v>
+        <v>0.00141397120478138</v>
       </c>
     </row>
     <row r="95">
@@ -13865,7 +13865,7 @@
         <v>731</v>
       </c>
       <c r="C95" t="n">
-        <v>23593929</v>
+        <v>23715594</v>
       </c>
       <c r="D95" t="n">
         <v>3286986</v>
@@ -13874,7 +13874,7 @@
         <v>13353027</v>
       </c>
       <c r="F95" t="n">
-        <v>261109077</v>
+        <v>260987412</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -13898,10 +13898,10 @@
         <v>732</v>
       </c>
       <c r="N95" t="n">
-        <v>0.000821573161931862</v>
+        <v>0.0008219561562609</v>
       </c>
       <c r="O95" t="n">
-        <v>0.000935075679847617</v>
+        <v>0.000932006615514508</v>
       </c>
     </row>
     <row r="96">
@@ -15181,7 +15181,7 @@
         <v>787</v>
       </c>
       <c r="C123" t="n">
-        <v>7399176</v>
+        <v>7483536</v>
       </c>
       <c r="D123" t="n">
         <v>846189</v>
@@ -15190,7 +15190,7 @@
         <v>13353027</v>
       </c>
       <c r="F123" t="n">
-        <v>172333971</v>
+        <v>172249611</v>
       </c>
       <c r="G123" t="n">
         <v>264975</v>
@@ -15214,10 +15214,10 @@
         <v>788</v>
       </c>
       <c r="N123" t="n">
-        <v>0.00282457438411838</v>
+        <v>0.00282595773177102</v>
       </c>
       <c r="O123" t="n">
-        <v>0.00140992500892556</v>
+        <v>0.00140421671270833</v>
       </c>
     </row>
     <row r="124">
@@ -15416,7 +15416,7 @@
         <v>798</v>
       </c>
       <c r="C128" t="n">
-        <v>23037444</v>
+        <v>23115264</v>
       </c>
       <c r="D128" t="n">
         <v>309150</v>
@@ -15425,7 +15425,7 @@
         <v>13523685</v>
       </c>
       <c r="F128" t="n">
-        <v>509188116</v>
+        <v>509110296</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -15449,10 +15449,10 @@
         <v>799</v>
       </c>
       <c r="N128" t="n">
-        <v>0.000136030413561341</v>
+        <v>0.000136051206475699</v>
       </c>
       <c r="O128" t="n">
-        <v>0.000153039858260395</v>
+        <v>0.00015271480631172</v>
       </c>
     </row>
     <row r="129">
@@ -15604,7 +15604,7 @@
         <v>806</v>
       </c>
       <c r="C132" t="n">
-        <v>63403122</v>
+        <v>74776167</v>
       </c>
       <c r="D132" t="n">
         <v>137378748</v>
@@ -15613,7 +15613,7 @@
         <v>43852821</v>
       </c>
       <c r="F132" t="n">
-        <v>512533119</v>
+        <v>501160074</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -15637,10 +15637,10 @@
         <v>807</v>
       </c>
       <c r="N132" t="n">
-        <v>0.00909170119404518</v>
+        <v>0.00929802315018415</v>
       </c>
       <c r="O132" t="n">
-        <v>0.0114504767348882</v>
+        <v>0.0103527114300259</v>
       </c>
     </row>
     <row r="133">
@@ -15651,7 +15651,7 @@
         <v>808</v>
       </c>
       <c r="C133" t="n">
-        <v>66015096</v>
+        <v>77543673</v>
       </c>
       <c r="D133" t="n">
         <v>197624094</v>
@@ -15660,7 +15660,7 @@
         <v>22199520</v>
       </c>
       <c r="F133" t="n">
-        <v>726552153</v>
+        <v>715023576</v>
       </c>
       <c r="G133" t="n">
         <v>583056</v>
@@ -15684,10 +15684,10 @@
         <v>809</v>
       </c>
       <c r="N133" t="n">
-        <v>0.000909432884166266</v>
+        <v>0.000924095990927158</v>
       </c>
       <c r="O133" t="n">
-        <v>0.00113731459194925</v>
+        <v>0.00100586082099858</v>
       </c>
     </row>
     <row r="134">
@@ -15698,7 +15698,7 @@
         <v>810</v>
       </c>
       <c r="C134" t="n">
-        <v>76206309</v>
+        <v>87734886</v>
       </c>
       <c r="D134" t="n">
         <v>220168464</v>
@@ -15707,7 +15707,7 @@
         <v>46902633</v>
       </c>
       <c r="F134" t="n">
-        <v>785093976</v>
+        <v>773565399</v>
       </c>
       <c r="G134" t="n">
         <v>583056</v>
@@ -15731,10 +15731,10 @@
         <v>811</v>
       </c>
       <c r="N134" t="n">
-        <v>0.00916306675367994</v>
+        <v>0.00929962549940784</v>
       </c>
       <c r="O134" t="n">
-        <v>0.0111457507286514</v>
+        <v>0.010191376001217</v>
       </c>
     </row>
     <row r="135">
@@ -15745,7 +15745,7 @@
         <v>812</v>
       </c>
       <c r="C135" t="n">
-        <v>76206309</v>
+        <v>87734886</v>
       </c>
       <c r="D135" t="n">
         <v>220168464</v>
@@ -15754,7 +15754,7 @@
         <v>46902633</v>
       </c>
       <c r="F135" t="n">
-        <v>785093976</v>
+        <v>773565399</v>
       </c>
       <c r="G135" t="n">
         <v>583056</v>
@@ -15778,10 +15778,10 @@
         <v>813</v>
       </c>
       <c r="N135" t="n">
-        <v>0.000537337316163537</v>
+        <v>0.00054534534577858</v>
       </c>
       <c r="O135" t="n">
-        <v>0.000653605162166043</v>
+        <v>0.000597639057802305</v>
       </c>
     </row>
     <row r="136">
@@ -15792,7 +15792,7 @@
         <v>814</v>
       </c>
       <c r="C136" t="n">
-        <v>49889739</v>
+        <v>60708918</v>
       </c>
       <c r="D136" t="n">
         <v>9848337</v>
@@ -15801,7 +15801,7 @@
         <v>15233298</v>
       </c>
       <c r="F136" t="n">
-        <v>348383271</v>
+        <v>337564092</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -15825,10 +15825,10 @@
         <v>815</v>
       </c>
       <c r="N136" t="n">
-        <v>0.00353786476733551</v>
+        <v>0.0036512559517142</v>
       </c>
       <c r="O136" t="n">
-        <v>0.0047575993730145</v>
+        <v>0.00407980351798004</v>
       </c>
     </row>
     <row r="137">
@@ -15839,7 +15839,7 @@
         <v>817</v>
       </c>
       <c r="C137" t="n">
-        <v>49330656</v>
+        <v>60146082</v>
       </c>
       <c r="D137" t="n">
         <v>9213306</v>
@@ -15848,7 +15848,7 @@
         <v>17563188</v>
       </c>
       <c r="F137" t="n">
-        <v>348298611</v>
+        <v>337483185</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -15872,10 +15872,10 @@
         <v>818</v>
       </c>
       <c r="N137" t="n">
-        <v>0.00115376368813598</v>
+        <v>0.00119073870302605</v>
       </c>
       <c r="O137" t="n">
-        <v>0.0015463842980828</v>
+        <v>0.00133116152036945</v>
       </c>
     </row>
     <row r="138">
@@ -15886,7 +15886,7 @@
         <v>820</v>
       </c>
       <c r="C138" t="n">
-        <v>72377406</v>
+        <v>83905983</v>
       </c>
       <c r="D138" t="n">
         <v>236336244</v>
@@ -15895,7 +15895,7 @@
         <v>46175316</v>
       </c>
       <c r="F138" t="n">
-        <v>823234728</v>
+        <v>811706151</v>
       </c>
       <c r="G138" t="n">
         <v>583056</v>
@@ -15919,10 +15919,10 @@
         <v>821</v>
       </c>
       <c r="N138" t="n">
-        <v>0.000545467950666921</v>
+        <v>0.000553215174539191</v>
       </c>
       <c r="O138" t="n">
-        <v>0.000665908792882883</v>
+        <v>0.000606892002208557</v>
       </c>
     </row>
     <row r="139">
@@ -15933,7 +15933,7 @@
         <v>822</v>
       </c>
       <c r="C139" t="n">
-        <v>45176826</v>
+        <v>55953789</v>
       </c>
       <c r="D139" t="n">
         <v>55424466</v>
@@ -15942,7 +15942,7 @@
         <v>17897070</v>
       </c>
       <c r="F139" t="n">
-        <v>333363582</v>
+        <v>322586619</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -15966,10 +15966,10 @@
         <v>823</v>
       </c>
       <c r="N139" t="n">
-        <v>0.00162732811648274</v>
+        <v>0.00168169383987995</v>
       </c>
       <c r="O139" t="n">
-        <v>0.00219542154174209</v>
+        <v>0.00187504643649439</v>
       </c>
     </row>
     <row r="140">
@@ -16262,7 +16262,7 @@
         <v>836</v>
       </c>
       <c r="C146" t="n">
-        <v>5058720</v>
+        <v>5654802</v>
       </c>
       <c r="D146" t="n">
         <v>83037546</v>
@@ -16271,7 +16271,7 @@
         <v>2879889</v>
       </c>
       <c r="F146" t="n">
-        <v>215736207</v>
+        <v>215140125</v>
       </c>
       <c r="G146" t="n">
         <v>438456</v>
@@ -16295,10 +16295,10 @@
         <v>837</v>
       </c>
       <c r="N146" t="n">
-        <v>0.00141904844929437</v>
+        <v>0.00142298016234768</v>
       </c>
       <c r="O146" t="n">
-        <v>0.00166441879175558</v>
+        <v>0.00154817204278397</v>
       </c>
     </row>
     <row r="147">
@@ -16403,7 +16403,7 @@
         <v>842</v>
       </c>
       <c r="C149" t="n">
-        <v>238361454</v>
+        <v>307197576</v>
       </c>
       <c r="D149" t="n">
         <v>58900764</v>
@@ -16412,7 +16412,7 @@
         <v>93368949</v>
       </c>
       <c r="F149" t="n">
-        <v>1270953216</v>
+        <v>1202117094</v>
       </c>
       <c r="G149" t="n">
         <v>1248693</v>
@@ -16436,10 +16436,10 @@
         <v>843</v>
       </c>
       <c r="N149" t="n">
-        <v>0.00104026008460094</v>
+        <v>0.00109982788415452</v>
       </c>
       <c r="O149" t="n">
-        <v>0.00145298370496358</v>
+        <v>0.00120329293617334</v>
       </c>
     </row>
     <row r="150">
@@ -16450,7 +16450,7 @@
         <v>844</v>
       </c>
       <c r="C150" t="n">
-        <v>40139049</v>
+        <v>41184249</v>
       </c>
       <c r="D150" t="n">
         <v>30412599</v>
@@ -16459,7 +16459,7 @@
         <v>33463056</v>
       </c>
       <c r="F150" t="n">
-        <v>1056721398</v>
+        <v>1055676198</v>
       </c>
       <c r="G150" t="n">
         <v>4564041</v>
@@ -16483,10 +16483,10 @@
         <v>845</v>
       </c>
       <c r="N150" t="n">
-        <v>0.00140216866319196</v>
+        <v>0.00140355691717509</v>
       </c>
       <c r="O150" t="n">
-        <v>0.00154558853989298</v>
+        <v>0.00152394744860514</v>
       </c>
     </row>
     <row r="151">
@@ -16497,7 +16497,7 @@
         <v>846</v>
       </c>
       <c r="C151" t="n">
-        <v>686767995</v>
+        <v>755809671</v>
       </c>
       <c r="D151" t="n">
         <v>38701596</v>
@@ -16506,7 +16506,7 @@
         <v>278194860</v>
       </c>
       <c r="F151" t="n">
-        <v>4982585013</v>
+        <v>4913543337</v>
       </c>
       <c r="G151" t="n">
         <v>7917285</v>
@@ -16530,10 +16530,10 @@
         <v>847</v>
       </c>
       <c r="N151" t="n">
-        <v>0.0118182475454734</v>
+        <v>0.0119843092980539</v>
       </c>
       <c r="O151" t="n">
-        <v>0.0139450487863598</v>
+        <v>0.0130139217832886</v>
       </c>
     </row>
     <row r="152">
@@ -16544,7 +16544,7 @@
         <v>848</v>
       </c>
       <c r="C152" t="n">
-        <v>907714146</v>
+        <v>989419275</v>
       </c>
       <c r="D152" t="n">
         <v>55717377</v>
@@ -16553,7 +16553,7 @@
         <v>378315921</v>
       </c>
       <c r="F152" t="n">
-        <v>7767797466</v>
+        <v>7686092337</v>
       </c>
       <c r="G152" t="n">
         <v>7917285</v>
@@ -16577,10 +16577,10 @@
         <v>849</v>
       </c>
       <c r="N152" t="n">
-        <v>0.00785259327846641</v>
+        <v>0.0079360683550945</v>
       </c>
       <c r="O152" t="n">
-        <v>0.00901539644173809</v>
+        <v>0.00847683888219544</v>
       </c>
     </row>
     <row r="153">
@@ -16591,7 +16591,7 @@
         <v>850</v>
       </c>
       <c r="C153" t="n">
-        <v>675829833</v>
+        <v>743826309</v>
       </c>
       <c r="D153" t="n">
         <v>5285781</v>
@@ -16600,7 +16600,7 @@
         <v>199279029</v>
       </c>
       <c r="F153" t="n">
-        <v>2826184779</v>
+        <v>2758188303</v>
       </c>
       <c r="G153" t="n">
         <v>4396620</v>
@@ -16624,10 +16624,10 @@
         <v>851</v>
       </c>
       <c r="N153" t="n">
-        <v>0.00454913271967629</v>
+        <v>0.00466128060800496</v>
       </c>
       <c r="O153" t="n">
-        <v>0.00530679377350426</v>
+        <v>0.00492418192632476</v>
       </c>
     </row>
     <row r="154">
@@ -16638,7 +16638,7 @@
         <v>852</v>
       </c>
       <c r="C154" t="n">
-        <v>687503646</v>
+        <v>755981481</v>
       </c>
       <c r="D154" t="n">
         <v>14585055</v>
@@ -16647,7 +16647,7 @@
         <v>214767546</v>
       </c>
       <c r="F154" t="n">
-        <v>3981531174</v>
+        <v>3913053339</v>
       </c>
       <c r="G154" t="n">
         <v>6095355</v>
@@ -16671,10 +16671,10 @@
         <v>853</v>
       </c>
       <c r="N154" t="n">
-        <v>0.00148953134380256</v>
+        <v>0.00151559791452155</v>
       </c>
       <c r="O154" t="n">
-        <v>0.00177639761106326</v>
+        <v>0.00165108833016631</v>
       </c>
     </row>
     <row r="155">
@@ -16967,7 +16967,7 @@
         <v>866</v>
       </c>
       <c r="C161" t="n">
-        <v>353572533</v>
+        <v>371876217</v>
       </c>
       <c r="D161" t="n">
         <v>57548244</v>
@@ -16976,7 +16976,7 @@
         <v>205996443</v>
       </c>
       <c r="F161" t="n">
-        <v>3072639627</v>
+        <v>3054335943</v>
       </c>
       <c r="G161" t="n">
         <v>146232</v>
@@ -17000,10 +17000,10 @@
         <v>867</v>
       </c>
       <c r="N161" t="n">
-        <v>0.00000530389566573145</v>
+        <v>0.00000533568026049975</v>
       </c>
       <c r="O161" t="n">
-        <v>0.00000599607938235661</v>
+        <v>0.00000580615805565192</v>
       </c>
     </row>
     <row r="162">
@@ -17014,7 +17014,7 @@
         <v>868</v>
       </c>
       <c r="C162" t="n">
-        <v>353572533</v>
+        <v>371876217</v>
       </c>
       <c r="D162" t="n">
         <v>57548244</v>
@@ -17023,7 +17023,7 @@
         <v>205996443</v>
       </c>
       <c r="F162" t="n">
-        <v>3072639627</v>
+        <v>3054335943</v>
       </c>
       <c r="G162" t="n">
         <v>146232</v>
@@ -17047,10 +17047,10 @@
         <v>869</v>
       </c>
       <c r="N162" t="n">
-        <v>0.0010863088143073</v>
+        <v>0.00109281872468866</v>
       </c>
       <c r="O162" t="n">
-        <v>0.00122807789472589</v>
+        <v>0.00118917944655835</v>
       </c>
     </row>
     <row r="163">
@@ -17155,7 +17155,7 @@
         <v>874</v>
       </c>
       <c r="C165" t="n">
-        <v>109601664</v>
+        <v>117417396</v>
       </c>
       <c r="D165" t="n">
         <v>5419950</v>
@@ -17164,7 +17164,7 @@
         <v>129872604</v>
       </c>
       <c r="F165" t="n">
-        <v>2154372123</v>
+        <v>2146556391</v>
       </c>
       <c r="G165" t="n">
         <v>2246874</v>
@@ -17188,10 +17188,10 @@
         <v>875</v>
       </c>
       <c r="N165" t="n">
-        <v>0.0017157815590617</v>
+        <v>0.0017220288157806</v>
       </c>
       <c r="O165" t="n">
-        <v>0.00190424396662108</v>
+        <v>0.00184405932306199</v>
       </c>
     </row>
     <row r="166">
@@ -17202,7 +17202,7 @@
         <v>876</v>
       </c>
       <c r="C166" t="n">
-        <v>122485710</v>
+        <v>130301442</v>
       </c>
       <c r="D166" t="n">
         <v>11193294</v>
@@ -17211,7 +17211,7 @@
         <v>116187771</v>
       </c>
       <c r="F166" t="n">
-        <v>2206737690</v>
+        <v>2198921958</v>
       </c>
       <c r="G166" t="n">
         <v>731640</v>
@@ -17235,10 +17235,10 @@
         <v>877</v>
       </c>
       <c r="N166" t="n">
-        <v>0.00077367791728794</v>
+        <v>0.000776427837190209</v>
       </c>
       <c r="O166" t="n">
-        <v>0.000853507432608317</v>
+        <v>0.000826444238758635</v>
       </c>
     </row>
     <row r="167">
@@ -17813,7 +17813,7 @@
         <v>902</v>
       </c>
       <c r="C179" t="n">
-        <v>105858480</v>
+        <v>113674212</v>
       </c>
       <c r="D179" t="n">
         <v>4144233</v>
@@ -17822,7 +17822,7 @@
         <v>90308961</v>
       </c>
       <c r="F179" t="n">
-        <v>1766326140</v>
+        <v>1758510408</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -17846,10 +17846,10 @@
         <v>903</v>
       </c>
       <c r="N179" t="n">
-        <v>0.0117042174329142</v>
+        <v>0.0117562370435512</v>
       </c>
       <c r="O179" t="n">
-        <v>0.0130150125167815</v>
+        <v>0.012516334864543</v>
       </c>
     </row>
     <row r="180">
@@ -17860,7 +17860,7 @@
         <v>904</v>
       </c>
       <c r="C180" t="n">
-        <v>107318355</v>
+        <v>115097988</v>
       </c>
       <c r="D180" t="n">
         <v>4370907</v>
@@ -17869,7 +17869,7 @@
         <v>128999253</v>
       </c>
       <c r="F180" t="n">
-        <v>1754481858</v>
+        <v>1746702225</v>
       </c>
       <c r="G180" t="n">
         <v>731640</v>
@@ -17893,10 +17893,10 @@
         <v>905</v>
       </c>
       <c r="N180" t="n">
-        <v>0.00236979540201093</v>
+        <v>0.00238035022827088</v>
       </c>
       <c r="O180" t="n">
-        <v>0.00262092577545047</v>
+        <v>0.00253739414449178</v>
       </c>
     </row>
     <row r="181">
@@ -18048,7 +18048,7 @@
         <v>912</v>
       </c>
       <c r="C184" t="n">
-        <v>12803187</v>
+        <v>12958719</v>
       </c>
       <c r="D184" t="n">
         <v>82789716</v>
@@ -18057,7 +18057,7 @@
         <v>3049812</v>
       </c>
       <c r="F184" t="n">
-        <v>272560857</v>
+        <v>272405325</v>
       </c>
       <c r="G184" t="n">
         <v>583056</v>
@@ -18081,10 +18081,10 @@
         <v>913</v>
       </c>
       <c r="N184" t="n">
-        <v>0.0110669072705477</v>
+        <v>0.0110732260098073</v>
       </c>
       <c r="O184" t="n">
-        <v>0.0112985751150303</v>
+        <v>0.0111888030200897</v>
       </c>
     </row>
     <row r="185">
@@ -18095,7 +18095,7 @@
         <v>914</v>
       </c>
       <c r="C185" t="n">
-        <v>4262460</v>
+        <v>4296483</v>
       </c>
       <c r="D185" t="n">
         <v>58992399</v>
@@ -18104,7 +18104,7 @@
         <v>2322495</v>
       </c>
       <c r="F185" t="n">
-        <v>196610658</v>
+        <v>196576635</v>
       </c>
       <c r="G185" t="n">
         <v>583056</v>
@@ -18128,10 +18128,10 @@
         <v>915</v>
       </c>
       <c r="N185" t="n">
-        <v>0.00171305703071295</v>
+        <v>0.00171335352240616</v>
       </c>
       <c r="O185" t="n">
-        <v>0.00193487730743794</v>
+        <v>0.00192493161330949</v>
       </c>
     </row>
     <row r="186">
@@ -18236,7 +18236,7 @@
         <v>920</v>
       </c>
       <c r="C188" t="n">
-        <v>23175408</v>
+        <v>23296917</v>
       </c>
       <c r="D188" t="n">
         <v>88689276</v>
@@ -18245,7 +18245,7 @@
         <v>24802737</v>
       </c>
       <c r="F188" t="n">
-        <v>303703905</v>
+        <v>303582396</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -18269,10 +18269,10 @@
         <v>921</v>
       </c>
       <c r="N188" t="n">
-        <v>0.000921593780626561</v>
+        <v>0.000921962648980476</v>
       </c>
       <c r="O188" t="n">
-        <v>0.000983231635987594</v>
+        <v>0.000980747803300207</v>
       </c>
     </row>
     <row r="189">
@@ -18330,7 +18330,7 @@
         <v>924</v>
       </c>
       <c r="C190" t="n">
-        <v>146548185</v>
+        <v>160801038</v>
       </c>
       <c r="D190" t="n">
         <v>58685358</v>
@@ -18339,7 +18339,7 @@
         <v>65897115</v>
       </c>
       <c r="F190" t="n">
-        <v>3647984859</v>
+        <v>3633732006</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -18363,10 +18363,10 @@
         <v>925</v>
       </c>
       <c r="N190" t="n">
-        <v>0.00220060207218091</v>
+        <v>0.00220923365475071</v>
       </c>
       <c r="O190" t="n">
-        <v>0.00246455647642005</v>
+        <v>0.002309606113112</v>
       </c>
     </row>
     <row r="191">
@@ -18377,7 +18377,7 @@
         <v>926</v>
       </c>
       <c r="C191" t="n">
-        <v>124966554</v>
+        <v>139219407</v>
       </c>
       <c r="D191" t="n">
         <v>59773428</v>
@@ -18386,7 +18386,7 @@
         <v>65656305</v>
       </c>
       <c r="F191" t="n">
-        <v>3024220815</v>
+        <v>3009967962</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -18410,10 +18410,10 @@
         <v>927</v>
       </c>
       <c r="N191" t="n">
-        <v>0.000705749361757501</v>
+        <v>0.000709091238493388</v>
       </c>
       <c r="O191" t="n">
-        <v>0.000814533581200773</v>
+        <v>0.00075786787259585</v>
       </c>
     </row>
     <row r="192">
@@ -18424,7 +18424,7 @@
         <v>928</v>
       </c>
       <c r="C192" t="n">
-        <v>134744769</v>
+        <v>148997622</v>
       </c>
       <c r="D192" t="n">
         <v>59811249</v>
@@ -18433,7 +18433,7 @@
         <v>65716332</v>
       </c>
       <c r="F192" t="n">
-        <v>3391094556</v>
+        <v>3376841703</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -18457,10 +18457,10 @@
         <v>929</v>
       </c>
       <c r="N192" t="n">
-        <v>0.0160120272034078</v>
+        <v>0.0160796101966406</v>
       </c>
       <c r="O192" t="n">
-        <v>0.018012968161838</v>
+        <v>0.0168172555287208</v>
       </c>
     </row>
     <row r="193">
@@ -18471,7 +18471,7 @@
         <v>930</v>
       </c>
       <c r="C193" t="n">
-        <v>143391141</v>
+        <v>157643994</v>
       </c>
       <c r="D193" t="n">
         <v>53333157</v>
@@ -18480,7 +18480,7 @@
         <v>65169798</v>
       </c>
       <c r="F193" t="n">
-        <v>3576467721</v>
+        <v>3562214868</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -18504,10 +18504,10 @@
         <v>931</v>
       </c>
       <c r="N193" t="n">
-        <v>0.000594924874480644</v>
+        <v>0.000597305240936971</v>
       </c>
       <c r="O193" t="n">
-        <v>0.000666230937903478</v>
+        <v>0.000623613775219085</v>
       </c>
     </row>
     <row r="194">
@@ -18565,7 +18565,7 @@
         <v>934</v>
       </c>
       <c r="C195" t="n">
-        <v>155479584</v>
+        <v>174839970</v>
       </c>
       <c r="D195" t="n">
         <v>41326434</v>
@@ -18574,7 +18574,7 @@
         <v>65716332</v>
       </c>
       <c r="F195" t="n">
-        <v>4892387388</v>
+        <v>4873027002</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -18598,10 +18598,10 @@
         <v>935</v>
       </c>
       <c r="N195" t="n">
-        <v>0.000319390466468924</v>
+        <v>0.000320659394942544</v>
       </c>
       <c r="O195" t="n">
-        <v>0.000358796859522488</v>
+        <v>0.000329920269559182</v>
       </c>
     </row>
     <row r="196">
@@ -18612,7 +18612,7 @@
         <v>936</v>
       </c>
       <c r="C196" t="n">
-        <v>96269268</v>
+        <v>110522121</v>
       </c>
       <c r="D196" t="n">
         <v>3451395</v>
@@ -18621,7 +18621,7 @@
         <v>64060485</v>
       </c>
       <c r="F196" t="n">
-        <v>1821536685</v>
+        <v>1807283832</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -18645,10 +18645,10 @@
         <v>937</v>
       </c>
       <c r="N196" t="n">
-        <v>0.00294314406849292</v>
+        <v>0.0029663547003944</v>
       </c>
       <c r="O196" t="n">
-        <v>0.00176713831773944</v>
+        <v>0.00162286986367932</v>
       </c>
     </row>
     <row r="197">
@@ -18659,7 +18659,7 @@
         <v>938</v>
       </c>
       <c r="C197" t="n">
-        <v>479252670</v>
+        <v>502214184</v>
       </c>
       <c r="D197" t="n">
         <v>1725546</v>
@@ -18668,7 +18668,7 @@
         <v>96551289</v>
       </c>
       <c r="F197" t="n">
-        <v>3136700493</v>
+        <v>3113738979</v>
       </c>
       <c r="G197" t="n">
         <v>16019748</v>
@@ -18692,10 +18692,10 @@
         <v>939</v>
       </c>
       <c r="N197" t="n">
-        <v>0.00144403616159983</v>
+        <v>0.00145468485654976</v>
       </c>
       <c r="O197" t="n">
-        <v>0.00159867139781163</v>
+        <v>0.00153736539848883</v>
       </c>
     </row>
     <row r="198">
@@ -18706,7 +18706,7 @@
         <v>940</v>
       </c>
       <c r="C198" t="n">
-        <v>361774863</v>
+        <v>374672853</v>
       </c>
       <c r="D198" t="n">
         <v>527217</v>
@@ -18715,7 +18715,7 @@
         <v>20750535</v>
       </c>
       <c r="F198" t="n">
-        <v>1871928225</v>
+        <v>1859030235</v>
       </c>
       <c r="G198" t="n">
         <v>5117544</v>
@@ -18739,10 +18739,10 @@
         <v>941</v>
       </c>
       <c r="N198" t="n">
-        <v>0.00177738654482866</v>
+        <v>0.00178971808922731</v>
       </c>
       <c r="O198" t="n">
-        <v>0.00194037461010628</v>
+        <v>0.0018770831279206</v>
       </c>
     </row>
     <row r="199">
@@ -18753,7 +18753,7 @@
         <v>942</v>
       </c>
       <c r="C199" t="n">
-        <v>138742953</v>
+        <v>148732632</v>
       </c>
       <c r="D199" t="n">
         <v>822336</v>
@@ -18762,7 +18762,7 @@
         <v>57203550</v>
       </c>
       <c r="F199" t="n">
-        <v>2048546220</v>
+        <v>2038556541</v>
       </c>
       <c r="G199" t="n">
         <v>10884105</v>
@@ -18786,10 +18786,10 @@
         <v>943</v>
       </c>
       <c r="N199" t="n">
-        <v>0.00262001715050393</v>
+        <v>0.0026328562009701</v>
       </c>
       <c r="O199" t="n">
-        <v>0.00274940482096789</v>
+        <v>0.00261603500059062</v>
       </c>
     </row>
     <row r="200">
@@ -18800,7 +18800,7 @@
         <v>945</v>
       </c>
       <c r="C200" t="n">
-        <v>101785689</v>
+        <v>112654164</v>
       </c>
       <c r="D200" t="n">
         <v>245523</v>
@@ -18809,7 +18809,7 @@
         <v>20844705</v>
       </c>
       <c r="F200" t="n">
-        <v>2389263336</v>
+        <v>2378394861</v>
       </c>
       <c r="G200" t="n">
         <v>1576818</v>
@@ -18833,10 +18833,10 @@
         <v>946</v>
       </c>
       <c r="N200" t="n">
-        <v>0.000250102871038239</v>
+        <v>0.000251245758136542</v>
       </c>
       <c r="O200" t="n">
-        <v>0.000290551378314906</v>
+        <v>0.000266896867867847</v>
       </c>
     </row>
     <row r="201">
@@ -20586,7 +20586,7 @@
         <v>1021</v>
       </c>
       <c r="C238" t="n">
-        <v>1118846157</v>
+        <v>1200101583</v>
       </c>
       <c r="D238" t="n">
         <v>22979289</v>
@@ -20595,7 +20595,7 @@
         <v>366452547</v>
       </c>
       <c r="F238" t="n">
-        <v>6892319904</v>
+        <v>6811064478</v>
       </c>
       <c r="G238" t="n">
         <v>21175809</v>
@@ -20619,10 +20619,10 @@
         <v>1022</v>
       </c>
       <c r="N238" t="n">
-        <v>0.000603801712335609</v>
+        <v>0.000611005015947523</v>
       </c>
       <c r="O238" t="n">
-        <v>0.00068872736995265</v>
+        <v>0.000653003844814478</v>
       </c>
     </row>
     <row r="239">
@@ -20633,7 +20633,7 @@
         <v>1023</v>
       </c>
       <c r="C239" t="n">
-        <v>456759885</v>
+        <v>479721399</v>
       </c>
       <c r="D239" t="n">
         <v>5666682</v>
@@ -20642,7 +20642,7 @@
         <v>58328766</v>
       </c>
       <c r="F239" t="n">
-        <v>2404113957</v>
+        <v>2381152443</v>
       </c>
       <c r="G239" t="n">
         <v>13258524</v>
@@ -20666,10 +20666,10 @@
         <v>1024</v>
       </c>
       <c r="N239" t="n">
-        <v>0.0015552940820933</v>
+        <v>0.00157029182276508</v>
       </c>
       <c r="O239" t="n">
-        <v>0.00175262044358263</v>
+        <v>0.00167782663908299</v>
       </c>
     </row>
     <row r="240">
@@ -20680,7 +20680,7 @@
         <v>1025</v>
       </c>
       <c r="C240" t="n">
-        <v>453118437</v>
+        <v>476079951</v>
       </c>
       <c r="D240" t="n">
         <v>2007942</v>
@@ -20689,7 +20689,7 @@
         <v>60754548</v>
       </c>
       <c r="F240" t="n">
-        <v>2441720538</v>
+        <v>2418759024</v>
       </c>
       <c r="G240" t="n">
         <v>9968274</v>
@@ -20713,10 +20713,10 @@
         <v>1026</v>
       </c>
       <c r="N240" t="n">
-        <v>0.00293861909187906</v>
+        <v>0.00296651568792245</v>
       </c>
       <c r="O240" t="n">
-        <v>0.00332583254984692</v>
+        <v>0.00318357986154686</v>
       </c>
     </row>
     <row r="241">
@@ -20727,7 +20727,7 @@
         <v>1027</v>
       </c>
       <c r="C241" t="n">
-        <v>456759885</v>
+        <v>479721399</v>
       </c>
       <c r="D241" t="n">
         <v>4066242</v>
@@ -20736,7 +20736,7 @@
         <v>58328766</v>
       </c>
       <c r="F241" t="n">
-        <v>2372992392</v>
+        <v>2350030878</v>
       </c>
       <c r="G241" t="n">
         <v>13258524</v>
@@ -20760,10 +20760,10 @@
         <v>1028</v>
       </c>
       <c r="N241" t="n">
-        <v>0.0169624132532828</v>
+        <v>0.0171281483902272</v>
       </c>
       <c r="O241" t="n">
-        <v>0.0191371762916205</v>
+        <v>0.0183204893543709</v>
       </c>
     </row>
     <row r="242">
@@ -20774,7 +20774,7 @@
         <v>1029</v>
       </c>
       <c r="C242" t="n">
-        <v>100383531</v>
+        <v>108096867</v>
       </c>
       <c r="D242" t="n">
         <v>1989486</v>
@@ -20783,7 +20783,7 @@
         <v>122658000</v>
       </c>
       <c r="F242" t="n">
-        <v>1370341743</v>
+        <v>1362628407</v>
       </c>
       <c r="G242" t="n">
         <v>731640</v>
@@ -20807,10 +20807,10 @@
         <v>1030</v>
       </c>
       <c r="N242" t="n">
-        <v>0.00244985562699888</v>
+        <v>0.002463723354624</v>
       </c>
       <c r="O242" t="n">
-        <v>0.00174886972059029</v>
+        <v>0.00169041106292246</v>
       </c>
     </row>
     <row r="243">
@@ -21150,7 +21150,7 @@
         <v>1045</v>
       </c>
       <c r="C250" t="n">
-        <v>54507231</v>
+        <v>59354952</v>
       </c>
       <c r="D250" t="n">
         <v>2217663</v>
@@ -21159,7 +21159,7 @@
         <v>1501692</v>
       </c>
       <c r="F250" t="n">
-        <v>556916229</v>
+        <v>552068508</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -21183,10 +21183,10 @@
         <v>1046</v>
       </c>
       <c r="N250" t="n">
-        <v>0.00217404718511085</v>
+        <v>0.0021931375227076</v>
       </c>
       <c r="O250" t="n">
-        <v>0.00174853531820278</v>
+        <v>0.0016092504213673</v>
       </c>
     </row>
     <row r="251">
@@ -21244,7 +21244,7 @@
         <v>1049</v>
       </c>
       <c r="C252" t="n">
-        <v>794835</v>
+        <v>794841</v>
       </c>
       <c r="D252" t="n">
         <v>0</v>
@@ -21253,7 +21253,7 @@
         <v>0</v>
       </c>
       <c r="F252" t="n">
-        <v>115151442</v>
+        <v>115151436</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -21277,10 +21277,10 @@
         <v>1050</v>
       </c>
       <c r="N252" t="n">
-        <v>0.000452474853703468</v>
+        <v>0.000452474877279805</v>
       </c>
       <c r="O252" t="n">
-        <v>0.000499623352402296</v>
+        <v>0.000499619580905714</v>
       </c>
     </row>
     <row r="253">
@@ -21432,7 +21432,7 @@
         <v>1057</v>
       </c>
       <c r="C256" t="n">
-        <v>184563</v>
+        <v>184566</v>
       </c>
       <c r="D256" t="n">
         <v>0</v>
@@ -21441,7 +21441,7 @@
         <v>0</v>
       </c>
       <c r="F256" t="n">
-        <v>71705583</v>
+        <v>71705580</v>
       </c>
       <c r="G256" t="n">
         <v>0</v>
@@ -21761,7 +21761,7 @@
         <v>1071</v>
       </c>
       <c r="C263" t="n">
-        <v>2763216</v>
+        <v>8484231</v>
       </c>
       <c r="D263" t="n">
         <v>0</v>
@@ -21770,7 +21770,7 @@
         <v>0</v>
       </c>
       <c r="F263" t="n">
-        <v>5721057</v>
+        <v>42</v>
       </c>
       <c r="G263" t="n">
         <v>0</v>
@@ -21808,7 +21808,7 @@
         <v>1073</v>
       </c>
       <c r="C264" t="n">
-        <v>0</v>
+        <v>2587926</v>
       </c>
       <c r="D264" t="n">
         <v>0</v>
@@ -21817,7 +21817,7 @@
         <v>0</v>
       </c>
       <c r="F264" t="n">
-        <v>2587965</v>
+        <v>39</v>
       </c>
       <c r="G264" t="n">
         <v>0</v>
@@ -21902,7 +21902,7 @@
         <v>1077</v>
       </c>
       <c r="C266" t="n">
-        <v>44865048</v>
+        <v>49712769</v>
       </c>
       <c r="D266" t="n">
         <v>0</v>
@@ -21911,7 +21911,7 @@
         <v>1464519</v>
       </c>
       <c r="F266" t="n">
-        <v>330430329</v>
+        <v>325582608</v>
       </c>
       <c r="G266" t="n">
         <v>0</v>
@@ -21935,10 +21935,10 @@
         <v>1078</v>
       </c>
       <c r="N266" t="n">
-        <v>0.015968097528965</v>
+        <v>0.0162058524944305</v>
       </c>
       <c r="O266" t="n">
-        <v>0.0130494256507944</v>
+        <v>0.0118133309447738</v>
       </c>
     </row>
     <row r="267">
@@ -21949,7 +21949,7 @@
         <v>1079</v>
       </c>
       <c r="C267" t="n">
-        <v>36584640</v>
+        <v>41432361</v>
       </c>
       <c r="D267" t="n">
         <v>0</v>
@@ -21958,7 +21958,7 @@
         <v>1464519</v>
       </c>
       <c r="F267" t="n">
-        <v>313128840</v>
+        <v>308281119</v>
       </c>
       <c r="G267" t="n">
         <v>0</v>
@@ -21982,10 +21982,10 @@
         <v>1080</v>
       </c>
       <c r="N267" t="n">
-        <v>0.00136594735253386</v>
+        <v>0.0013874268764413</v>
       </c>
       <c r="O267" t="n">
-        <v>0.00102330330086928</v>
+        <v>0.000907661116612677</v>
       </c>
     </row>
     <row r="268">
@@ -21996,7 +21996,7 @@
         <v>1081</v>
       </c>
       <c r="C268" t="n">
-        <v>49767051</v>
+        <v>54614772</v>
       </c>
       <c r="D268" t="n">
         <v>0</v>
@@ -22005,7 +22005,7 @@
         <v>1501692</v>
       </c>
       <c r="F268" t="n">
-        <v>339950697</v>
+        <v>335102976</v>
       </c>
       <c r="G268" t="n">
         <v>0</v>
@@ -22029,10 +22029,10 @@
         <v>1082</v>
       </c>
       <c r="N268" t="n">
-        <v>0.00200552905470289</v>
+        <v>0.00203454176426055</v>
       </c>
       <c r="O268" t="n">
-        <v>0.00167334763795555</v>
+        <v>0.00152879251265725</v>
       </c>
     </row>
     <row r="269">
@@ -22218,7 +22218,7 @@
         <v>1090</v>
       </c>
       <c r="C2" t="n">
-        <v>675829833</v>
+        <v>743826309</v>
       </c>
       <c r="D2" t="n">
         <v>5285781</v>
@@ -22227,7 +22227,7 @@
         <v>199279029</v>
       </c>
       <c r="F2" t="n">
-        <v>2826184779</v>
+        <v>2758188303</v>
       </c>
       <c r="G2" t="n">
         <v>4396620</v>
@@ -22241,7 +22241,7 @@
         <v>1092</v>
       </c>
       <c r="C3" t="n">
-        <v>675829833</v>
+        <v>743826309</v>
       </c>
       <c r="D3" t="n">
         <v>5285781</v>
@@ -22250,7 +22250,7 @@
         <v>199279029</v>
       </c>
       <c r="F3" t="n">
-        <v>2826182382</v>
+        <v>2758185906</v>
       </c>
       <c r="G3" t="n">
         <v>4396620</v>
@@ -22264,14 +22264,14 @@
         <v>1094</v>
       </c>
       <c r="C4" t="n">
-        <v>36986802</v>
+        <v>39501549</v>
       </c>
       <c r="D4"/>
       <c r="E4" t="n">
         <v>12394479</v>
       </c>
       <c r="F4" t="n">
-        <v>28446414</v>
+        <v>25931667</v>
       </c>
       <c r="G4"/>
     </row>
@@ -22317,14 +22317,14 @@
         <v>1097</v>
       </c>
       <c r="C7" t="n">
-        <v>2446293</v>
+        <v>2569050</v>
       </c>
       <c r="D7"/>
       <c r="E7" t="n">
         <v>3095193</v>
       </c>
       <c r="F7" t="n">
-        <v>581178</v>
+        <v>458421</v>
       </c>
       <c r="G7"/>
     </row>
@@ -22336,14 +22336,14 @@
         <v>1098</v>
       </c>
       <c r="C8" t="n">
-        <v>26730351</v>
+        <v>27115929</v>
       </c>
       <c r="D8"/>
       <c r="E8" t="n">
         <v>251481</v>
       </c>
       <c r="F8" t="n">
-        <v>491151</v>
+        <v>105573</v>
       </c>
       <c r="G8"/>
     </row>
@@ -22374,13 +22374,11 @@
         <v>1100</v>
       </c>
       <c r="C10" t="n">
-        <v>20270535</v>
+        <v>21215058</v>
       </c>
       <c r="D10"/>
       <c r="E10"/>
-      <c r="F10" t="n">
-        <v>944523</v>
-      </c>
+      <c r="F10"/>
       <c r="G10"/>
     </row>
     <row r="11">
@@ -22391,14 +22389,14 @@
         <v>1101</v>
       </c>
       <c r="C11" t="n">
-        <v>11828343</v>
+        <v>14009706</v>
       </c>
       <c r="D11"/>
       <c r="E11" t="n">
         <v>1464519</v>
       </c>
       <c r="F11" t="n">
-        <v>6846075</v>
+        <v>4664712</v>
       </c>
       <c r="G11"/>
     </row>
@@ -22410,14 +22408,14 @@
         <v>1102</v>
       </c>
       <c r="C12" t="n">
-        <v>11495229</v>
+        <v>11621139</v>
       </c>
       <c r="D12"/>
       <c r="E12" t="n">
         <v>904218</v>
       </c>
       <c r="F12" t="n">
-        <v>6325815</v>
+        <v>6199905</v>
       </c>
       <c r="G12"/>
     </row>
@@ -22469,14 +22467,14 @@
         <v>1105</v>
       </c>
       <c r="C15" t="n">
-        <v>13577211</v>
+        <v>13801452</v>
       </c>
       <c r="D15"/>
       <c r="E15" t="n">
         <v>680640</v>
       </c>
       <c r="F15" t="n">
-        <v>3186828</v>
+        <v>2962587</v>
       </c>
       <c r="G15"/>
     </row>
@@ -22488,14 +22486,14 @@
         <v>1106</v>
       </c>
       <c r="C16" t="n">
-        <v>3238581</v>
+        <v>3302985</v>
       </c>
       <c r="D16" t="n">
         <v>20340</v>
       </c>
       <c r="E16"/>
       <c r="F16" t="n">
-        <v>417456</v>
+        <v>353052</v>
       </c>
       <c r="G16"/>
     </row>
@@ -22507,12 +22505,12 @@
         <v>1107</v>
       </c>
       <c r="C17" t="n">
-        <v>34835121</v>
+        <v>38265633</v>
       </c>
       <c r="D17"/>
       <c r="E17"/>
       <c r="F17" t="n">
-        <v>17742222</v>
+        <v>14311710</v>
       </c>
       <c r="G17"/>
     </row>
@@ -22524,14 +22522,14 @@
         <v>1108</v>
       </c>
       <c r="C18" t="n">
-        <v>38074791</v>
+        <v>40244088</v>
       </c>
       <c r="D18"/>
       <c r="E18" t="n">
         <v>662949</v>
       </c>
       <c r="F18" t="n">
-        <v>18196650</v>
+        <v>16027353</v>
       </c>
       <c r="G18"/>
     </row>
@@ -22562,7 +22560,7 @@
         <v>1111</v>
       </c>
       <c r="C20" t="n">
-        <v>1118846157</v>
+        <v>1200101583</v>
       </c>
       <c r="D20" t="n">
         <v>22979289</v>
@@ -22571,7 +22569,7 @@
         <v>366452547</v>
       </c>
       <c r="F20" t="n">
-        <v>6892319904</v>
+        <v>6811064478</v>
       </c>
       <c r="G20" t="n">
         <v>21175809</v>
@@ -22585,7 +22583,7 @@
         <v>1112</v>
       </c>
       <c r="C21" t="n">
-        <v>13217814</v>
+        <v>13255062</v>
       </c>
       <c r="D21" t="n">
         <v>9749673</v>
@@ -22594,7 +22592,7 @@
         <v>5362857</v>
       </c>
       <c r="F21" t="n">
-        <v>438213858</v>
+        <v>438176610</v>
       </c>
       <c r="G21" t="n">
         <v>2802570</v>
@@ -22608,7 +22606,7 @@
         <v>1113</v>
       </c>
       <c r="C22" t="n">
-        <v>58833771</v>
+        <v>60848052</v>
       </c>
       <c r="D22" t="n">
         <v>44204886</v>
@@ -22617,7 +22615,7 @@
         <v>20962152</v>
       </c>
       <c r="F22" t="n">
-        <v>286236336</v>
+        <v>284222055</v>
       </c>
       <c r="G22" t="n">
         <v>152397</v>
@@ -22631,7 +22629,7 @@
         <v>1114</v>
       </c>
       <c r="C23" t="n">
-        <v>23175408</v>
+        <v>23296917</v>
       </c>
       <c r="D23" t="n">
         <v>88689276</v>
@@ -22640,7 +22638,7 @@
         <v>24802737</v>
       </c>
       <c r="F23" t="n">
-        <v>303703905</v>
+        <v>303582396</v>
       </c>
       <c r="G23"/>
     </row>
@@ -22652,7 +22650,7 @@
         <v>1115</v>
       </c>
       <c r="C24" t="n">
-        <v>238361454</v>
+        <v>307197576</v>
       </c>
       <c r="D24" t="n">
         <v>58900764</v>
@@ -22661,7 +22659,7 @@
         <v>93368949</v>
       </c>
       <c r="F24" t="n">
-        <v>1270953216</v>
+        <v>1202117094</v>
       </c>
       <c r="G24" t="n">
         <v>1248693</v>
@@ -22675,7 +22673,7 @@
         <v>1116</v>
       </c>
       <c r="C25" t="n">
-        <v>155479584</v>
+        <v>174839970</v>
       </c>
       <c r="D25" t="n">
         <v>41326434</v>
@@ -22684,7 +22682,7 @@
         <v>65716332</v>
       </c>
       <c r="F25" t="n">
-        <v>4892387388</v>
+        <v>4873027002</v>
       </c>
       <c r="G25"/>
     </row>
@@ -22696,7 +22694,7 @@
         <v>1117</v>
       </c>
       <c r="C26" t="n">
-        <v>27351594</v>
+        <v>29241240</v>
       </c>
       <c r="D26" t="n">
         <v>48739473</v>
@@ -22705,7 +22703,7 @@
         <v>4975614</v>
       </c>
       <c r="F26" t="n">
-        <v>814792044</v>
+        <v>812902398</v>
       </c>
       <c r="G26"/>
     </row>
@@ -22738,7 +22736,7 @@
         <v>1119</v>
       </c>
       <c r="C28" t="n">
-        <v>11793570</v>
+        <v>12750030</v>
       </c>
       <c r="D28" t="n">
         <v>49749294</v>
@@ -22747,7 +22745,7 @@
         <v>10528680</v>
       </c>
       <c r="F28" t="n">
-        <v>117055692</v>
+        <v>116099232</v>
       </c>
       <c r="G28" t="n">
         <v>59340</v>
@@ -22761,7 +22759,7 @@
         <v>1120</v>
       </c>
       <c r="C29" t="n">
-        <v>45176826</v>
+        <v>55953789</v>
       </c>
       <c r="D29" t="n">
         <v>55424466</v>
@@ -22770,7 +22768,7 @@
         <v>17897070</v>
       </c>
       <c r="F29" t="n">
-        <v>333363582</v>
+        <v>322586619</v>
       </c>
       <c r="G29"/>
     </row>
@@ -22782,7 +22780,7 @@
         <v>1121</v>
       </c>
       <c r="C30" t="n">
-        <v>447267045</v>
+        <v>489402342</v>
       </c>
       <c r="D30" t="n">
         <v>40017258</v>
@@ -22791,7 +22789,7 @@
         <v>27712083</v>
       </c>
       <c r="F30" t="n">
-        <v>3363827541</v>
+        <v>3321692244</v>
       </c>
       <c r="G30" t="n">
         <v>5237427</v>
@@ -22805,7 +22803,7 @@
         <v>1122</v>
       </c>
       <c r="C31" t="n">
-        <v>353572533</v>
+        <v>371876217</v>
       </c>
       <c r="D31" t="n">
         <v>57548244</v>
@@ -22814,7 +22812,7 @@
         <v>205996443</v>
       </c>
       <c r="F31" t="n">
-        <v>3072639627</v>
+        <v>3054335943</v>
       </c>
       <c r="G31" t="n">
         <v>146232</v>
@@ -22828,7 +22826,7 @@
         <v>1123</v>
       </c>
       <c r="C32" t="n">
-        <v>61692027</v>
+        <v>74489733</v>
       </c>
       <c r="D32" t="n">
         <v>46193346</v>
@@ -22837,7 +22835,7 @@
         <v>71413065</v>
       </c>
       <c r="F32" t="n">
-        <v>540198945</v>
+        <v>527401239</v>
       </c>
       <c r="G32" t="n">
         <v>124200</v>
@@ -22851,7 +22849,7 @@
         <v>1124</v>
       </c>
       <c r="C33" t="n">
-        <v>4262460</v>
+        <v>4296483</v>
       </c>
       <c r="D33" t="n">
         <v>58992399</v>
@@ -22860,7 +22858,7 @@
         <v>2322495</v>
       </c>
       <c r="F33" t="n">
-        <v>196610658</v>
+        <v>196576635</v>
       </c>
       <c r="G33" t="n">
         <v>583056</v>
@@ -22874,7 +22872,7 @@
         <v>1125</v>
       </c>
       <c r="C34" t="n">
-        <v>5058720</v>
+        <v>5654802</v>
       </c>
       <c r="D34" t="n">
         <v>83037546</v>
@@ -22883,7 +22881,7 @@
         <v>2879889</v>
       </c>
       <c r="F34" t="n">
-        <v>215736207</v>
+        <v>215140125</v>
       </c>
       <c r="G34" t="n">
         <v>438456</v>
@@ -22897,7 +22895,7 @@
         <v>1126</v>
       </c>
       <c r="C35" t="n">
-        <v>42291807</v>
+        <v>44625735</v>
       </c>
       <c r="D35" t="n">
         <v>48361749</v>
@@ -22906,7 +22904,7 @@
         <v>11250303</v>
       </c>
       <c r="F35" t="n">
-        <v>122483130</v>
+        <v>120149202</v>
       </c>
       <c r="G35" t="n">
         <v>1462284</v>
